--- a/Data Analysis/1_Data/economic_MF.xlsx
+++ b/Data Analysis/1_Data/economic_MF.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W83"/>
+  <dimension ref="A1:V81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -417,7 +417,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>TNleaching_av</t>
+          <t>av_leaching</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -437,35 +437,30 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>leaching_standardized</t>
+          <t>meanSR</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>meanSR</t>
+          <t>mean_org_diff</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_org_diff</t>
+          <t>SOC_costs_mid</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>SOC_costs_mid</t>
+          <t>SOC_costs_lo</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>SOC_costs_lo</t>
+          <t>SOC_costs_hi</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>SOC_costs_hi</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>costs_total_mid</t>
         </is>
@@ -478,22 +473,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>435.4745416666667</v>
+        <v>382.2721153846154</v>
       </c>
       <c r="C2">
-        <v>123.0564943</v>
+        <v>76.00643430769233</v>
       </c>
       <c r="D2">
         <v>16</v>
       </c>
       <c r="E2">
-        <v>15.94866666666667</v>
+        <v>16.6</v>
       </c>
       <c r="F2">
-        <v>6.759</v>
+        <v>6.383333333333334</v>
       </c>
       <c r="G2">
-        <v>22.70766666666667</v>
+        <v>22.98333333333333</v>
       </c>
       <c r="H2">
         <v>18.76454505833333</v>
@@ -513,37 +508,34 @@
         </is>
       </c>
       <c r="M2">
-        <v>2.095065631874623</v>
+        <v>2.813264729287163</v>
       </c>
       <c r="N2">
-        <v>-13.19891348081012</v>
+        <v>-17.72356779450913</v>
       </c>
       <c r="O2">
-        <v>-23.52758704595201</v>
+        <v>-31.59296290989484</v>
       </c>
       <c r="P2">
-        <v>-41.90131263749245</v>
+        <v>-56.26529458574326</v>
       </c>
       <c r="Q2">
-        <v>0.1923070961317632</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="R2">
-        <v>11.83333333333333</v>
+        <v>2.164545058333331</v>
       </c>
       <c r="S2">
-        <v>2.815878391666667</v>
+        <v>290.7276213575302</v>
       </c>
       <c r="T2">
-        <v>378.2104806225052</v>
+        <v>104.3637615129596</v>
       </c>
       <c r="U2">
-        <v>135.767864838848</v>
+        <v>400.5182984691637</v>
       </c>
       <c r="V2">
-        <v>521.0382744329734</v>
-      </c>
-      <c r="W2">
-        <v>477.7393878765532</v>
+        <v>335.1410927553277</v>
       </c>
     </row>
     <row r="3">
@@ -553,22 +545,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>329.558375</v>
+        <v>350.5780769230769</v>
       </c>
       <c r="C3">
-        <v>64.93847587500001</v>
+        <v>61.40733846153847</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3">
-        <v>16.14375</v>
+        <v>17.03833333333333</v>
       </c>
       <c r="F3">
-        <v>6.362083333333334</v>
+        <v>6.225</v>
       </c>
       <c r="G3">
-        <v>22.50583333333334</v>
+        <v>23.26333333333334</v>
       </c>
       <c r="H3">
         <v>16.83361475166667</v>
@@ -588,37 +580,34 @@
         </is>
       </c>
       <c r="M3">
-        <v>2.614593071827771</v>
+        <v>5.003784345866223</v>
       </c>
       <c r="N3">
-        <v>-16.47193635251496</v>
+        <v>-31.5238413789572</v>
       </c>
       <c r="O3">
-        <v>-29.36188019662587</v>
+        <v>-56.19249820407769</v>
       </c>
       <c r="P3">
-        <v>-52.29186143655542</v>
+        <v>-100.0756869173245</v>
       </c>
       <c r="Q3">
-        <v>0.2399947732231784</v>
+        <v>5.728813559322034</v>
       </c>
       <c r="R3">
-        <v>5.728813559322034</v>
+        <v>-0.2047185816666683</v>
       </c>
       <c r="S3">
-        <v>0.6898647516666649</v>
+        <v>-28.21970380582596</v>
       </c>
       <c r="T3">
-        <v>95.09531963156741</v>
+        <v>-10.13015008414265</v>
       </c>
       <c r="U3">
-        <v>34.13678140620369</v>
+        <v>-38.87662169434402</v>
       </c>
       <c r="V3">
-        <v>131.0072136708937</v>
-      </c>
-      <c r="W3">
-        <v>130.6719153099415</v>
+        <v>-23.00486354836517</v>
       </c>
     </row>
     <row r="4">
@@ -628,22 +617,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>307.92475</v>
+        <v>171.8553846153846</v>
       </c>
       <c r="C4">
-        <v>47.57967425</v>
+        <v>-55.9362173076923</v>
       </c>
       <c r="D4">
         <v>8</v>
       </c>
       <c r="E4">
-        <v>14.31</v>
+        <v>15.42</v>
       </c>
       <c r="F4">
-        <v>6.942083333333334</v>
+        <v>6.928333333333333</v>
       </c>
       <c r="G4">
-        <v>21.25208333333333</v>
+        <v>22.34833333333333</v>
       </c>
       <c r="H4">
         <v>13.88983349316667</v>
@@ -663,37 +652,34 @@
         </is>
       </c>
       <c r="M4">
-        <v>7.874606776195011</v>
+        <v>10.62294565431209</v>
       </c>
       <c r="N4">
-        <v>-49.61002269002857</v>
+        <v>-66.92455762216619</v>
       </c>
       <c r="O4">
-        <v>-88.43183409666999</v>
+        <v>-119.2956796979248</v>
       </c>
       <c r="P4">
-        <v>-157.4921355239002</v>
+        <v>-212.4589130862419</v>
       </c>
       <c r="Q4">
-        <v>0.7228139965021354</v>
+        <v>6.186440677966102</v>
       </c>
       <c r="R4">
-        <v>6.186440677966102</v>
+        <v>-1.530166506833334</v>
       </c>
       <c r="S4">
-        <v>-0.4201665068333345</v>
+        <v>-230.153281394325</v>
       </c>
       <c r="T4">
-        <v>-63.19750161033677</v>
+        <v>-82.61912665437308</v>
       </c>
       <c r="U4">
-        <v>-22.68628262935166</v>
+        <v>-317.0686026347255</v>
       </c>
       <c r="V4">
-        <v>-87.06347093641472</v>
-      </c>
-      <c r="W4">
-        <v>-104.0496614570067</v>
+        <v>-405.3851783999421</v>
       </c>
     </row>
     <row r="5">
@@ -703,22 +689,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>425.0958333333334</v>
+        <v>281.1561538461539</v>
       </c>
       <c r="C5">
-        <v>124.6636935</v>
+        <v>20.2405803846154</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5">
-        <v>17.15666666666667</v>
+        <v>17.11666666666667</v>
       </c>
       <c r="F5">
-        <v>6.6225</v>
+        <v>6.623333333333333</v>
       </c>
       <c r="G5">
-        <v>23.77916666666667</v>
+        <v>23.74</v>
       </c>
       <c r="H5">
         <v>16.13080275</v>
@@ -738,37 +724,34 @@
         </is>
       </c>
       <c r="M5">
-        <v>6.762593017775271</v>
+        <v>10.03208662826186</v>
       </c>
       <c r="N5">
-        <v>-42.6043360119842</v>
+        <v>-63.20214575804974</v>
       </c>
       <c r="O5">
-        <v>-75.9439195896163</v>
+        <v>-112.6603328353807</v>
       </c>
       <c r="P5">
-        <v>-135.2518603555054</v>
+        <v>-200.6417325652373</v>
       </c>
       <c r="Q5">
-        <v>0.6207417112778671</v>
+        <v>3.35</v>
       </c>
       <c r="R5">
-        <v>3.35</v>
+        <v>-0.9858639166666663</v>
       </c>
       <c r="S5">
-        <v>-1.025863916666665</v>
+        <v>-142.2482160701825</v>
       </c>
       <c r="T5">
-        <v>-148.0197313337146</v>
+        <v>-51.06346217903989</v>
       </c>
       <c r="U5">
-        <v>-53.13528817107704</v>
+        <v>-195.9669782825325</v>
       </c>
       <c r="V5">
-        <v>-203.9180544896876</v>
-      </c>
-      <c r="W5">
-        <v>-99.29995742333085</v>
+        <v>-234.6679685209479</v>
       </c>
     </row>
     <row r="6">
@@ -778,22 +761,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>409.3909166666667</v>
+        <v>170.7674358974359</v>
       </c>
       <c r="C6">
-        <v>110.8697125</v>
+        <v>-57.2744023076923</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6">
-        <v>16.8925</v>
+        <v>18.13666666666667</v>
       </c>
       <c r="F6">
-        <v>6.172083333333333</v>
+        <v>6.268333333333334</v>
       </c>
       <c r="G6">
-        <v>23.06458333333333</v>
+        <v>24.405</v>
       </c>
       <c r="H6">
         <v>14.88611025333333</v>
@@ -813,37 +796,34 @@
         </is>
       </c>
       <c r="M6">
-        <v>5.452538173207431</v>
+        <v>7.607418619499584</v>
       </c>
       <c r="N6">
-        <v>-34.35099049120682</v>
+        <v>-47.92673730284738</v>
       </c>
       <c r="O6">
-        <v>-61.23200368511945</v>
+        <v>-85.43131109698034</v>
       </c>
       <c r="P6">
-        <v>-109.0507634641486</v>
+        <v>-152.1483723899917</v>
       </c>
       <c r="Q6">
-        <v>0.50049113816968</v>
+        <v>1.864406779661017</v>
       </c>
       <c r="R6">
-        <v>1.864406779661017</v>
+        <v>-3.250556413333333</v>
       </c>
       <c r="S6">
-        <v>-2.006389746666668</v>
+        <v>-468.6008132950027</v>
       </c>
       <c r="T6">
-        <v>-289.2415166887126</v>
+        <v>-168.2156765674369</v>
       </c>
       <c r="U6">
-        <v>-103.830288042102</v>
+        <v>-645.5637050439462</v>
       </c>
       <c r="V6">
-        <v>-398.4709797090039</v>
-      </c>
-      <c r="W6">
-        <v>-239.6038078738321</v>
+        <v>-611.3065266996754</v>
       </c>
     </row>
     <row r="7">
@@ -853,22 +833,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>285.4118083333333</v>
+        <v>242.4952179487179</v>
       </c>
       <c r="C7">
-        <v>37.418234875</v>
+        <v>-9.735079423076913</v>
       </c>
       <c r="D7">
         <v>16</v>
       </c>
       <c r="E7">
-        <v>15.53666666666667</v>
+        <v>15.41</v>
       </c>
       <c r="F7">
-        <v>5.979583333333333</v>
+        <v>6.038333333333333</v>
       </c>
       <c r="G7">
-        <v>21.51625</v>
+        <v>21.44833333333333</v>
       </c>
       <c r="H7">
         <v>16.76970075833334</v>
@@ -888,37 +868,34 @@
         </is>
       </c>
       <c r="M7">
-        <v>1.266329559472203</v>
+        <v>1.175780674075467</v>
       </c>
       <c r="N7">
-        <v>-7.977876224674879</v>
+        <v>-7.407418246675445</v>
       </c>
       <c r="O7">
-        <v>-14.22088095287284</v>
+        <v>-13.2040169698675</v>
       </c>
       <c r="P7">
-        <v>-25.32659118944406</v>
+        <v>-23.51561348150935</v>
       </c>
       <c r="Q7">
-        <v>0.1162370078640514</v>
+        <v>12.89830508474576</v>
       </c>
       <c r="R7">
-        <v>12.89830508474576</v>
+        <v>1.359700758333336</v>
       </c>
       <c r="S7">
-        <v>1.233034091666669</v>
+        <v>194.7869053707685</v>
       </c>
       <c r="T7">
-        <v>176.6409950574773</v>
+        <v>69.92350449207073</v>
       </c>
       <c r="U7">
-        <v>63.40958796935083</v>
+        <v>268.3464320964268</v>
       </c>
       <c r="V7">
-        <v>243.3478816012344</v>
-      </c>
-      <c r="W7">
-        <v>199.8383489796045</v>
+        <v>171.8478089778241</v>
       </c>
     </row>
     <row r="8">
@@ -928,22 +905,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>195.5060666666667</v>
+        <v>117.4245256410256</v>
       </c>
       <c r="C8">
-        <v>-25.66698999999999</v>
+        <v>-90.71716211538461</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8">
-        <v>17.26520833333333</v>
+        <v>16.13166666666667</v>
       </c>
       <c r="F8">
-        <v>5.810833333333333</v>
+        <v>5.843333333333334</v>
       </c>
       <c r="G8">
-        <v>23.07604166666667</v>
+        <v>21.975</v>
       </c>
       <c r="H8">
         <v>16.93685348</v>
@@ -963,37 +940,34 @@
         </is>
       </c>
       <c r="M8">
-        <v>5.834182375549821</v>
+        <v>8.587698582789461</v>
       </c>
       <c r="N8">
-        <v>-36.75534896596387</v>
+        <v>-54.1025010715736</v>
       </c>
       <c r="O8">
-        <v>-65.5178680774245</v>
+        <v>-96.43985508472565</v>
       </c>
       <c r="P8">
-        <v>-116.6836475109964</v>
+        <v>-171.7539716557892</v>
       </c>
       <c r="Q8">
-        <v>0.5355224456339324</v>
+        <v>2</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>0.8051868133333322</v>
       </c>
       <c r="S8">
-        <v>-0.3283548533333338</v>
+        <v>111.0688404456992</v>
       </c>
       <c r="T8">
-        <v>-45.2938277310723</v>
+        <v>39.87086580102022</v>
       </c>
       <c r="U8">
-        <v>-16.25932277525672</v>
+        <v>153.0129912683724</v>
       </c>
       <c r="V8">
-        <v>-62.39863529064237</v>
-      </c>
-      <c r="W8">
-        <v>-136.4786858084968</v>
+        <v>-76.08817675441108</v>
       </c>
     </row>
     <row r="9">
@@ -1003,22 +977,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>332.1990833333333</v>
+        <v>319.7814102564103</v>
       </c>
       <c r="C9">
-        <v>69.24102800000001</v>
+        <v>44.22396923076924</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>16.34416666666667</v>
+        <v>16.26333333333333</v>
       </c>
       <c r="F9">
-        <v>5.929166666666667</v>
+        <v>5.896666666666667</v>
       </c>
       <c r="G9">
-        <v>22.27333333333333</v>
+        <v>22.16</v>
       </c>
       <c r="H9">
         <v>15.82495804166667</v>
@@ -1038,74 +1012,71 @@
         </is>
       </c>
       <c r="M9">
-        <v>9.555711420707254</v>
+        <v>11.79392739577335</v>
       </c>
       <c r="N9">
-        <v>-60.2009819504557</v>
+        <v>-74.3017425933721</v>
       </c>
       <c r="O9">
-        <v>-107.3106392545425</v>
+        <v>-132.4458046545347</v>
       </c>
       <c r="P9">
-        <v>-191.1142284141451</v>
+        <v>-235.878547915467</v>
       </c>
       <c r="Q9">
-        <v>0.8771234117114802</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>1</v>
+        <v>-0.4383752916666666</v>
       </c>
       <c r="S9">
-        <v>-0.519208625000001</v>
+        <v>-60.51076386339979</v>
       </c>
       <c r="T9">
-        <v>-71.66852489283329</v>
+        <v>-21.72181266891274</v>
       </c>
       <c r="U9">
-        <v>-25.72716278204272</v>
+        <v>-83.36211079109599</v>
       </c>
       <c r="V9">
-        <v>-98.73350013954223</v>
-      </c>
-      <c r="W9">
-        <v>-109.7381361473757</v>
+        <v>-148.7325992871653</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B1A09</t>
+          <t>B1A11</t>
         </is>
       </c>
       <c r="B10">
-        <v>95.10555555555555</v>
+        <v>277.5409487179487</v>
       </c>
       <c r="C10">
-        <v>-48.10225833333333</v>
+        <v>12.76036961538462</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E10">
-        <v>17.04191666666667</v>
+        <v>20.57</v>
       </c>
       <c r="F10">
-        <v>6.105958333333334</v>
+        <v>7.835</v>
       </c>
       <c r="G10">
-        <v>23.147875</v>
+        <v>28.405</v>
       </c>
       <c r="H10">
-        <v>17.754681005</v>
+        <v>20.74362609</v>
       </c>
       <c r="I10">
-        <v>5.934877986166667</v>
+        <v>8.007693386333333</v>
       </c>
       <c r="J10">
-        <v>1.236999865833333</v>
+        <v>1.312353860333333</v>
       </c>
       <c r="K10">
-        <v>23.68955899116667</v>
+        <v>28.75131947633333</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1113,74 +1084,71 @@
         </is>
       </c>
       <c r="M10">
-        <v>4.444804068467144</v>
+        <v>2.710670323817271</v>
       </c>
       <c r="N10">
-        <v>-28.00226563134301</v>
+        <v>-17.07722304004881</v>
       </c>
       <c r="O10">
-        <v>-49.91514968888603</v>
+        <v>-30.44082773646796</v>
       </c>
       <c r="P10">
-        <v>-88.89608136934288</v>
+        <v>-54.21340647634543</v>
       </c>
       <c r="Q10">
-        <v>0.4079907332147559</v>
+        <v>11.03333333333333</v>
       </c>
       <c r="R10">
-        <v>0.9523809523809523</v>
+        <v>0.1736260899999991</v>
       </c>
       <c r="S10">
-        <v>0.7127643383333364</v>
+        <v>24.39343127069136</v>
       </c>
       <c r="T10">
-        <v>94.38925774163492</v>
+        <v>8.756616353581514</v>
       </c>
       <c r="U10">
-        <v>33.88332329186895</v>
+        <v>33.60539167465911</v>
       </c>
       <c r="V10">
-        <v>130.034513844681</v>
-      </c>
-      <c r="W10">
-        <v>-3.628150280584443</v>
+        <v>6.71297314960802</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B1A11</t>
+          <t>B1A12</t>
         </is>
       </c>
       <c r="B11">
-        <v>297.311575</v>
+        <v>404.5358461538461</v>
       </c>
       <c r="C11">
-        <v>43.06043187500001</v>
+        <v>98.45986653846157</v>
       </c>
       <c r="D11">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E11">
-        <v>19.29833333333333</v>
+        <v>18.10333333333333</v>
       </c>
       <c r="F11">
-        <v>8.320416666666667</v>
+        <v>7.890000000000001</v>
       </c>
       <c r="G11">
-        <v>27.61875</v>
+        <v>25.99333333333333</v>
       </c>
       <c r="H11">
-        <v>20.74362609</v>
+        <v>15.448378665</v>
       </c>
       <c r="I11">
-        <v>8.007693386333333</v>
+        <v>8.4151640775</v>
       </c>
       <c r="J11">
-        <v>1.312353860333333</v>
+        <v>1.245958471666667</v>
       </c>
       <c r="K11">
-        <v>28.75131947633333</v>
+        <v>23.8635427425</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1188,74 +1156,71 @@
         </is>
       </c>
       <c r="M11">
-        <v>2.325544502250153</v>
+        <v>7.824389819187211</v>
       </c>
       <c r="N11">
-        <v>-14.65093036417596</v>
+        <v>-49.29365586087943</v>
       </c>
       <c r="O11">
-        <v>-26.11586476026922</v>
+        <v>-87.86789766947238</v>
       </c>
       <c r="P11">
-        <v>-46.51089004500306</v>
+        <v>-156.4877963837442</v>
       </c>
       <c r="Q11">
-        <v>0.2134628640501115</v>
+        <v>5.3</v>
       </c>
       <c r="R11">
-        <v>11.03333333333333</v>
+        <v>-2.654954668333332</v>
       </c>
       <c r="S11">
-        <v>1.445292756666667</v>
+        <v>-354.1340068957437</v>
       </c>
       <c r="T11">
-        <v>203.0550220060625</v>
+        <v>-127.1250281164208</v>
       </c>
       <c r="U11">
-        <v>72.89154636115065</v>
+        <v>-487.8695364742183</v>
       </c>
       <c r="V11">
-        <v>279.736928777993</v>
-      </c>
-      <c r="W11">
-        <v>219.9995891207933</v>
+        <v>-343.5420380267544</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B1A12</t>
+          <t>B1A13</t>
         </is>
       </c>
       <c r="B12">
-        <v>453.8560083333334</v>
+        <v>308.8033333333333</v>
       </c>
       <c r="C12">
-        <v>142.988681625</v>
+        <v>35.80333192307694</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>16.93</v>
+        <v>15.54166666666667</v>
       </c>
       <c r="F12">
-        <v>8.091666666666667</v>
+        <v>6.416666666666667</v>
       </c>
       <c r="G12">
-        <v>25.02166666666667</v>
+        <v>21.95833333333333</v>
       </c>
       <c r="H12">
-        <v>15.448378665</v>
+        <v>16.183862175</v>
       </c>
       <c r="I12">
-        <v>8.4151640775</v>
+        <v>6.791461165499999</v>
       </c>
       <c r="J12">
-        <v>1.245958471666667</v>
+        <v>1.289940989333333</v>
       </c>
       <c r="K12">
-        <v>23.8635427425</v>
+        <v>22.9753233405</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1263,74 +1228,71 @@
         </is>
       </c>
       <c r="M12">
-        <v>6.7695929031412</v>
+        <v>6.603782064222194</v>
       </c>
       <c r="N12">
-        <v>-42.64843528978956</v>
+        <v>-41.60382700459982</v>
       </c>
       <c r="O12">
-        <v>-76.02252830227569</v>
+        <v>-74.16047258121525</v>
       </c>
       <c r="P12">
-        <v>-135.391858062824</v>
+        <v>-132.0756412844439</v>
       </c>
       <c r="Q12">
-        <v>0.6213842341695117</v>
+        <v>3.2</v>
       </c>
       <c r="R12">
-        <v>5.3</v>
+        <v>0.6421955083333355</v>
       </c>
       <c r="S12">
-        <v>-1.481621335</v>
+        <v>88.68375278906213</v>
       </c>
       <c r="T12">
-        <v>-197.6276681195279</v>
+        <v>31.83519330889409</v>
       </c>
       <c r="U12">
-        <v>-70.94326547880488</v>
+        <v>122.1743761500187</v>
       </c>
       <c r="V12">
-        <v>-272.2599834032306</v>
-      </c>
-      <c r="W12">
-        <v>-130.6615147968035</v>
+        <v>50.32661213092382</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B1A13</t>
+          <t>B1A14</t>
         </is>
       </c>
       <c r="B13">
-        <v>442.4480833333333</v>
+        <v>173.5197435897436</v>
       </c>
       <c r="C13">
-        <v>138.1340535</v>
+        <v>-53.60853769230769</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E13">
-        <v>16.44041666666667</v>
+        <v>14.40166666666667</v>
       </c>
       <c r="F13">
-        <v>6.741666666666666</v>
+        <v>6.755</v>
       </c>
       <c r="G13">
-        <v>23.18208333333333</v>
+        <v>21.15666666666667</v>
       </c>
       <c r="H13">
-        <v>16.183862175</v>
+        <v>16.193342365</v>
       </c>
       <c r="I13">
-        <v>6.791461165499999</v>
+        <v>7.529579546166667</v>
       </c>
       <c r="J13">
-        <v>1.289940989333333</v>
+        <v>1.357109041833333</v>
       </c>
       <c r="K13">
-        <v>22.9753233405</v>
+        <v>23.72292191116667</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1338,74 +1300,71 @@
         </is>
       </c>
       <c r="M13">
-        <v>6.202177180698082</v>
+        <v>1.39202396258024</v>
       </c>
       <c r="N13">
-        <v>-39.07371623839791</v>
+        <v>-8.769750964255509</v>
       </c>
       <c r="O13">
-        <v>-69.65044973923946</v>
+        <v>-15.63242909977609</v>
       </c>
       <c r="P13">
-        <v>-124.0435436139616</v>
+        <v>-27.84047925160479</v>
       </c>
       <c r="Q13">
-        <v>0.5693008682728042</v>
+        <v>6.559322033898305</v>
       </c>
       <c r="R13">
-        <v>3.2</v>
+        <v>1.791675698333332</v>
       </c>
       <c r="S13">
-        <v>-0.256554491666666</v>
+        <v>260.3041565167735</v>
       </c>
       <c r="T13">
-        <v>-35.42879827194373</v>
+        <v>93.44251772396997</v>
       </c>
       <c r="U13">
-        <v>-12.71803014890288</v>
+        <v>358.6056851623899</v>
       </c>
       <c r="V13">
-        <v>-48.80816598858956</v>
-      </c>
-      <c r="W13">
-        <v>33.0548054888168</v>
+        <v>191.0631897246897</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B1A14</t>
+          <t>B1A15</t>
         </is>
       </c>
       <c r="B14">
-        <v>226.6676666666667</v>
+        <v>9.844230769230769</v>
       </c>
       <c r="C14">
-        <v>-3.254158499999996</v>
+        <v>-156.8178538461538</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>14.30708333333333</v>
+        <v>18.25833333333333</v>
       </c>
       <c r="F14">
-        <v>6.802291666666667</v>
+        <v>7.81</v>
       </c>
       <c r="G14">
-        <v>21.109375</v>
+        <v>26.06833333333333</v>
       </c>
       <c r="H14">
-        <v>16.193342365</v>
+        <v>16.58950539833333</v>
       </c>
       <c r="I14">
-        <v>7.529579546166667</v>
+        <v>8.428237891833334</v>
       </c>
       <c r="J14">
-        <v>1.357109041833333</v>
+        <v>1.336857178666667</v>
       </c>
       <c r="K14">
-        <v>23.72292191116667</v>
+        <v>25.01774329016667</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1413,74 +1372,71 @@
         </is>
       </c>
       <c r="M14">
-        <v>1.699209011408265</v>
+        <v>4.23496647898634</v>
       </c>
       <c r="N14">
-        <v>-10.70501677187207</v>
+        <v>-26.68028881761394</v>
       </c>
       <c r="O14">
-        <v>-19.08211719811482</v>
+        <v>-47.5586735590166</v>
       </c>
       <c r="P14">
-        <v>-33.9841802281653</v>
+        <v>-84.69932957972681</v>
       </c>
       <c r="Q14">
-        <v>0.1559712238763901</v>
+        <v>0.95</v>
       </c>
       <c r="R14">
-        <v>6.559322033898305</v>
+        <v>-1.668827934999999</v>
       </c>
       <c r="S14">
-        <v>1.886259031666667</v>
+        <v>-238.838056873739</v>
       </c>
       <c r="T14">
-        <v>274.0457252765558</v>
+        <v>-85.73673836493194</v>
       </c>
       <c r="U14">
-        <v>98.37538856081491</v>
+        <v>-329.0331056336473</v>
       </c>
       <c r="V14">
-        <v>377.5366340425331</v>
-      </c>
-      <c r="W14">
-        <v>251.709449578441</v>
+        <v>-443.2145842789095</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B1A15</t>
+          <t>B1A16</t>
         </is>
       </c>
       <c r="B15">
-        <v>77.20100000000001</v>
+        <v>119.2246153846154</v>
       </c>
       <c r="C15">
-        <v>-91.68593625</v>
+        <v>-86.55015807692307</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15">
-        <v>18.75</v>
+        <v>18.37</v>
       </c>
       <c r="F15">
-        <v>8.1525</v>
+        <v>8.023333333333333</v>
       </c>
       <c r="G15">
-        <v>26.9025</v>
+        <v>26.39333333333333</v>
       </c>
       <c r="H15">
-        <v>16.58950539833333</v>
+        <v>16.12405039333333</v>
       </c>
       <c r="I15">
-        <v>8.428237891833334</v>
+        <v>8.497587742333334</v>
       </c>
       <c r="J15">
-        <v>1.336857178666667</v>
+        <v>1.317444145666667</v>
       </c>
       <c r="K15">
-        <v>25.01774329016667</v>
+        <v>24.62163813566667</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1488,74 +1444,71 @@
         </is>
       </c>
       <c r="M15">
-        <v>3.853968818605062</v>
+        <v>1.071580227281821</v>
       </c>
       <c r="N15">
-        <v>-24.28000355721189</v>
+        <v>-6.750955431875472</v>
       </c>
       <c r="O15">
-        <v>-43.28006983293485</v>
+        <v>-12.03384595237485</v>
       </c>
       <c r="P15">
-        <v>-77.07937637210124</v>
+        <v>-21.43160454563642</v>
       </c>
       <c r="Q15">
-        <v>0.3537576774743516</v>
+        <v>1.983050847457627</v>
       </c>
       <c r="R15">
-        <v>0.95</v>
+        <v>-2.245949606666667</v>
       </c>
       <c r="S15">
-        <v>-2.160494601666667</v>
+        <v>-316.7664484257349</v>
       </c>
       <c r="T15">
-        <v>-309.2040357943011</v>
+        <v>-113.7110327682125</v>
       </c>
       <c r="U15">
-        <v>-110.996320541544</v>
+        <v>-436.3904548978945</v>
       </c>
       <c r="V15">
-        <v>-425.9721650040053</v>
-      </c>
-      <c r="W15">
-        <v>-444.1700418772359</v>
+        <v>-415.3504524550328</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B1A16</t>
+          <t>B1A17</t>
         </is>
       </c>
       <c r="B16">
-        <v>155.476625</v>
+        <v>134.5203846153846</v>
       </c>
       <c r="C16">
-        <v>-47.09960087499999</v>
+        <v>-78.23088269230769</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16">
-        <v>18.36195833333333</v>
+        <v>18.88</v>
       </c>
       <c r="F16">
-        <v>8.019708333333334</v>
+        <v>8.141666666666667</v>
       </c>
       <c r="G16">
-        <v>26.38166666666667</v>
+        <v>27.02166666666667</v>
       </c>
       <c r="H16">
-        <v>16.12405039333333</v>
+        <v>16.225695985</v>
       </c>
       <c r="I16">
-        <v>8.497587742333334</v>
+        <v>9.332896422999999</v>
       </c>
       <c r="J16">
-        <v>1.317444145666667</v>
+        <v>1.2739333915</v>
       </c>
       <c r="K16">
-        <v>24.62163813566667</v>
+        <v>25.558592408</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1563,74 +1516,71 @@
         </is>
       </c>
       <c r="M16">
-        <v>1.136531189147966</v>
+        <v>4.497018075011564</v>
       </c>
       <c r="N16">
-        <v>-7.160146491632185</v>
+        <v>-28.33121387257285</v>
       </c>
       <c r="O16">
-        <v>-12.76324525413166</v>
+        <v>-50.50151298237986</v>
       </c>
       <c r="P16">
-        <v>-22.73062378295932</v>
+        <v>-89.94036150023128</v>
       </c>
       <c r="Q16">
-        <v>0.1043227521481793</v>
+        <v>2</v>
       </c>
       <c r="R16">
-        <v>1.983050847457627</v>
+        <v>-2.654304015000001</v>
       </c>
       <c r="S16">
-        <v>-2.237907939999999</v>
+        <v>-361.9964745597835</v>
       </c>
       <c r="T16">
-        <v>-315.6322599373277</v>
+        <v>-129.9474524060761</v>
       </c>
       <c r="U16">
-        <v>-113.3038881826305</v>
+        <v>-498.7011944909756</v>
       </c>
       <c r="V16">
-        <v>-434.8279503054549</v>
-      </c>
-      <c r="W16">
-        <v>-375.4951060664594</v>
+        <v>-490.7288702344709</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B1A17</t>
+          <t>B1A18</t>
         </is>
       </c>
       <c r="B17">
-        <v>185.8095416666667</v>
+        <v>53.65576923076923</v>
       </c>
       <c r="C17">
-        <v>-27.516846125</v>
+        <v>-129.6682176923077</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>18.91</v>
+        <v>18.19666666666667</v>
       </c>
       <c r="F17">
-        <v>8.28375</v>
+        <v>7.733333333333333</v>
       </c>
       <c r="G17">
-        <v>27.19375</v>
+        <v>25.93</v>
       </c>
       <c r="H17">
-        <v>16.225695985</v>
+        <v>17.84053773833333</v>
       </c>
       <c r="I17">
-        <v>9.332896422999999</v>
+        <v>8.176969806833334</v>
       </c>
       <c r="J17">
-        <v>1.2739333915</v>
+        <v>1.254831114166667</v>
       </c>
       <c r="K17">
-        <v>25.558592408</v>
+        <v>26.01750754516667</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1638,74 +1588,71 @@
         </is>
       </c>
       <c r="M17">
-        <v>2.892220428878251</v>
+        <v>2.39641692676325</v>
       </c>
       <c r="N17">
-        <v>-18.22098870193298</v>
+        <v>-15.09742663860848</v>
       </c>
       <c r="O17">
-        <v>-32.47963541630276</v>
+        <v>-26.9117620875513</v>
       </c>
       <c r="P17">
-        <v>-57.84440857756502</v>
+        <v>-47.928338535265</v>
       </c>
       <c r="Q17">
-        <v>0.2654783237281533</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>-0.3561289283333338</v>
       </c>
       <c r="S17">
-        <v>-2.684304015000002</v>
+        <v>-47.84091610353833</v>
       </c>
       <c r="T17">
-        <v>-366.0879027365946</v>
+        <v>-17.17366219101376</v>
       </c>
       <c r="U17">
-        <v>-131.4161702131365</v>
+        <v>-65.9076087284848</v>
       </c>
       <c r="V17">
-        <v>-504.3377138008142</v>
-      </c>
-      <c r="W17">
-        <v>-426.0843842778974</v>
+        <v>-204.4208958833973</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B1A18</t>
+          <t>B1A19</t>
         </is>
       </c>
       <c r="B18">
-        <v>56.48408333333333</v>
+        <v>183.2476923076923</v>
       </c>
       <c r="C18">
-        <v>-108.9703285</v>
+        <v>-47.38314423076922</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18">
-        <v>19.03166666666667</v>
+        <v>18.44</v>
       </c>
       <c r="F18">
-        <v>7.8775</v>
+        <v>7.836666666666667</v>
       </c>
       <c r="G18">
-        <v>26.90916666666666</v>
+        <v>26.27666666666666</v>
       </c>
       <c r="H18">
-        <v>17.84053773833333</v>
+        <v>17.29026594833334</v>
       </c>
       <c r="I18">
-        <v>8.176969806833334</v>
+        <v>8.751537780333333</v>
       </c>
       <c r="J18">
-        <v>1.254831114166667</v>
+        <v>1.301592840833333</v>
       </c>
       <c r="K18">
-        <v>26.01750754516667</v>
+        <v>26.04180372866667</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1713,74 +1660,71 @@
         </is>
       </c>
       <c r="M18">
-        <v>2.173775254829633</v>
+        <v>3.063092334736524</v>
       </c>
       <c r="N18">
-        <v>-13.69478410542669</v>
+        <v>-19.2974817088401</v>
       </c>
       <c r="O18">
-        <v>-24.41149611173678</v>
+        <v>-34.39852691909116</v>
       </c>
       <c r="P18">
-        <v>-43.47550509659266</v>
+        <v>-61.26184669473047</v>
       </c>
       <c r="Q18">
-        <v>0.1995318908101811</v>
+        <v>3.559322033898305</v>
       </c>
       <c r="R18">
-        <v>1</v>
+        <v>-1.149734051666663</v>
       </c>
       <c r="S18">
-        <v>-1.191128928333335</v>
+        <v>-160.2062670333225</v>
       </c>
       <c r="T18">
-        <v>-160.0114301176773</v>
+        <v>-57.50994201196193</v>
       </c>
       <c r="U18">
-        <v>-57.44000055506367</v>
+        <v>-220.7067260299064</v>
       </c>
       <c r="V18">
-        <v>-220.4383107016043</v>
-      </c>
-      <c r="W18">
-        <v>-293.3932547294141</v>
+        <v>-241.9879381831829</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B1A19</t>
+          <t>B1A20</t>
         </is>
       </c>
       <c r="B19">
-        <v>238.2480416666667</v>
+        <v>501.1975641025641</v>
       </c>
       <c r="C19">
-        <v>6.679780875000003</v>
+        <v>157.5468319230769</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E19">
-        <v>18.97583333333333</v>
+        <v>20.27166666666667</v>
       </c>
       <c r="F19">
-        <v>8.157500000000001</v>
+        <v>7.295</v>
       </c>
       <c r="G19">
-        <v>27.13333333333333</v>
+        <v>27.56666666666667</v>
       </c>
       <c r="H19">
-        <v>17.29026594833334</v>
+        <v>19.76502023666666</v>
       </c>
       <c r="I19">
-        <v>8.751537780333333</v>
+        <v>7.915039723833333</v>
       </c>
       <c r="J19">
-        <v>1.301592840833333</v>
+        <v>1.243342730833333</v>
       </c>
       <c r="K19">
-        <v>26.04180372866667</v>
+        <v>27.6800599605</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1788,74 +1732,71 @@
         </is>
       </c>
       <c r="M19">
-        <v>2.185989068317086</v>
+        <v>2.598609080226484</v>
       </c>
       <c r="N19">
-        <v>-13.77173113039764</v>
+        <v>-16.37123720542685</v>
       </c>
       <c r="O19">
-        <v>-24.54865723720087</v>
+        <v>-29.18237997094342</v>
       </c>
       <c r="P19">
-        <v>-43.71978136634172</v>
+        <v>-51.97218160452968</v>
       </c>
       <c r="Q19">
-        <v>0.2006530027069789</v>
+        <v>12.15254237288136</v>
       </c>
       <c r="R19">
-        <v>3.559322033898305</v>
+        <v>-0.5066464300000035</v>
       </c>
       <c r="S19">
-        <v>-1.685567384999999</v>
+        <v>-67.43770810878988</v>
       </c>
       <c r="T19">
-        <v>-234.8703669274814</v>
+        <v>-24.20840803905278</v>
       </c>
       <c r="U19">
-        <v>-84.31243940986512</v>
+        <v>-92.9049533658734</v>
       </c>
       <c r="V19">
-        <v>-323.5670531866596</v>
-      </c>
-      <c r="W19">
-        <v>-252.7392432896823</v>
+        <v>60.92674384334363</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B1A20</t>
+          <t>B1A21</t>
         </is>
       </c>
       <c r="B20">
-        <v>581.4750416666667</v>
+        <v>101.4121794871795</v>
       </c>
       <c r="C20">
-        <v>221.979044875</v>
+        <v>-99.973775</v>
       </c>
       <c r="D20">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E20">
-        <v>19.55875</v>
+        <v>19.17833333333333</v>
       </c>
       <c r="F20">
-        <v>7.629583333333334</v>
+        <v>8.326666666666666</v>
       </c>
       <c r="G20">
-        <v>27.18833333333333</v>
+        <v>27.505</v>
       </c>
       <c r="H20">
-        <v>19.76502023666666</v>
+        <v>17.63945969833333</v>
       </c>
       <c r="I20">
-        <v>7.915039723833333</v>
+        <v>8.806338972999999</v>
       </c>
       <c r="J20">
-        <v>1.243342730833333</v>
+        <v>1.410547525</v>
       </c>
       <c r="K20">
-        <v>27.6800599605</v>
+        <v>26.44579867133333</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1863,74 +1804,71 @@
         </is>
       </c>
       <c r="M20">
-        <v>3.356827381619648</v>
+        <v>0.8470214289750483</v>
       </c>
       <c r="N20">
-        <v>-21.14801250420378</v>
+        <v>-5.336235002542804</v>
       </c>
       <c r="O20">
-        <v>-37.69717149558865</v>
+        <v>-9.512050647389792</v>
       </c>
       <c r="P20">
-        <v>-67.13654763239296</v>
+        <v>-16.94042857950097</v>
       </c>
       <c r="Q20">
-        <v>0.3081248225131958</v>
+        <v>3.694915254237288</v>
       </c>
       <c r="R20">
-        <v>12.15254237288136</v>
+        <v>-1.538873635000002</v>
       </c>
       <c r="S20">
-        <v>0.2062702366666649</v>
+        <v>-232.3794064855021</v>
       </c>
       <c r="T20">
-        <v>27.45581768306836</v>
+        <v>-83.4182484819751</v>
       </c>
       <c r="U20">
-        <v>9.855934552896336</v>
+        <v>-320.1354038885398</v>
       </c>
       <c r="V20">
-        <v>37.8242608327153</v>
-      </c>
-      <c r="W20">
-        <v>211.7376910624797</v>
+        <v>-341.8652321328919</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B1A21</t>
+          <t>B1A22</t>
         </is>
       </c>
       <c r="B21">
-        <v>128.7385</v>
+        <v>580.2130641025641</v>
       </c>
       <c r="C21">
-        <v>-62.13411575</v>
+        <v>205.6821628846154</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="E21">
-        <v>18.67708333333333</v>
+        <v>17.25333333333333</v>
       </c>
       <c r="F21">
-        <v>8.781666666666666</v>
+        <v>17.76666666666667</v>
       </c>
       <c r="G21">
-        <v>27.45875</v>
+        <v>35.02</v>
       </c>
       <c r="H21">
-        <v>17.63945969833333</v>
+        <v>21.81097294</v>
       </c>
       <c r="I21">
-        <v>8.806338972999999</v>
+        <v>9.169695069499999</v>
       </c>
       <c r="J21">
-        <v>1.410547525</v>
+        <v>1.2817225465</v>
       </c>
       <c r="K21">
-        <v>26.44579867133333</v>
+        <v>30.9806680095</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1938,149 +1876,143 @@
         </is>
       </c>
       <c r="M21">
-        <v>0.9990682892502492</v>
+        <v>0.9806401652694139</v>
       </c>
       <c r="N21">
-        <v>-6.29413022227657</v>
+        <v>-6.178033041197307</v>
       </c>
       <c r="O21">
-        <v>-11.2195368882803</v>
+        <v>-11.01258905597552</v>
       </c>
       <c r="P21">
-        <v>-19.98136578500498</v>
+        <v>-19.61280330538828</v>
       </c>
       <c r="Q21">
-        <v>0.09170496552469892</v>
+        <v>33.2280701754386</v>
       </c>
       <c r="R21">
-        <v>3.694915254237288</v>
+        <v>4.557639606666665</v>
       </c>
       <c r="S21">
-        <v>-1.037623634999999</v>
+        <v>625.3756399867557</v>
       </c>
       <c r="T21">
-        <v>-156.6875661344532</v>
+        <v>224.4938194824251</v>
       </c>
       <c r="U21">
-        <v>-56.2468186123678</v>
+        <v>861.5431380822669</v>
       </c>
       <c r="V21">
-        <v>-215.8592193146641</v>
-      </c>
-      <c r="W21">
-        <v>-230.0412187727335</v>
+        <v>820.0452138153956</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B1A22</t>
+          <t>B2A01</t>
         </is>
       </c>
       <c r="B22">
-        <v>659.353575</v>
+        <v>379.4884615384615</v>
       </c>
       <c r="C22">
-        <v>266.963392625</v>
+        <v>78.69687000000002</v>
       </c>
       <c r="D22">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="E22">
-        <v>19.48395833333333</v>
+        <v>19.13833333333333</v>
       </c>
       <c r="F22">
-        <v>11.54416666666667</v>
+        <v>8.976666666666667</v>
       </c>
       <c r="G22">
-        <v>31.028125</v>
+        <v>28.115</v>
       </c>
       <c r="H22">
-        <v>21.81097294</v>
+        <v>19.59409039666667</v>
       </c>
       <c r="I22">
-        <v>9.169695069499999</v>
+        <v>7.509411629000001</v>
       </c>
       <c r="J22">
-        <v>1.2817225465</v>
+        <v>1.295684132333333</v>
       </c>
       <c r="K22">
-        <v>30.9806680095</v>
+        <v>27.10350202566666</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="M22">
-        <v>1.370103848357541</v>
+        <v>2.359231208098899</v>
       </c>
       <c r="N22">
-        <v>-8.631654244652507</v>
+        <v>-14.86315661102306</v>
       </c>
       <c r="O22">
-        <v>-15.38626621705519</v>
+        <v>-26.49416646695063</v>
       </c>
       <c r="P22">
-        <v>-27.40207696715082</v>
+        <v>-47.18462416197798</v>
       </c>
       <c r="Q22">
-        <v>0.1257625004524727</v>
+        <v>3.6</v>
       </c>
       <c r="R22">
-        <v>33.2280701754386</v>
+        <v>0.4557570633333334</v>
       </c>
       <c r="S22">
-        <v>2.327014606666665</v>
+        <v>63.21781832783648</v>
       </c>
       <c r="T22">
-        <v>319.3008606415528</v>
+        <v>22.69357580999258</v>
       </c>
       <c r="U22">
-        <v>114.6208217687626</v>
+        <v>87.09146007994869</v>
       </c>
       <c r="V22">
-        <v>439.8819651422911</v>
-      </c>
-      <c r="W22">
-        <v>570.8779870494976</v>
+        <v>115.4205218608859</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B2A01</t>
+          <t>B2A02</t>
         </is>
       </c>
       <c r="B23">
-        <v>442.4108333333334</v>
+        <v>111.9438461538462</v>
       </c>
       <c r="C23">
-        <v>134.661824</v>
+        <v>-93.66125115384615</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>17.76895833333333</v>
+        <v>16.91833333333333</v>
       </c>
       <c r="F23">
-        <v>7.829583333333334</v>
+        <v>8.901666666666667</v>
       </c>
       <c r="G23">
-        <v>25.59854166666667</v>
+        <v>25.82</v>
       </c>
       <c r="H23">
-        <v>19.59409039666667</v>
+        <v>16.15549779666667</v>
       </c>
       <c r="I23">
-        <v>7.509411629000001</v>
+        <v>9.634761951333333</v>
       </c>
       <c r="J23">
-        <v>1.295684132333333</v>
+        <v>1.422238535666667</v>
       </c>
       <c r="K23">
-        <v>27.10350202566666</v>
+        <v>25.790259748</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2088,74 +2020,71 @@
         </is>
       </c>
       <c r="M23">
-        <v>1.87831184917383</v>
+        <v>0.6724456699305441</v>
       </c>
       <c r="N23">
-        <v>-11.83336464979513</v>
+        <v>-4.236407720562428</v>
       </c>
       <c r="O23">
-        <v>-21.09344206622211</v>
+        <v>-7.551564873320011</v>
       </c>
       <c r="P23">
-        <v>-37.5662369834766</v>
+        <v>-13.44891339861088</v>
       </c>
       <c r="Q23">
-        <v>0.1724111607049253</v>
+        <v>1.983050847457627</v>
       </c>
       <c r="R23">
-        <v>3.6</v>
+        <v>-0.7628355366666675</v>
       </c>
       <c r="S23">
-        <v>1.825132063333331</v>
+        <v>-116.147619714007</v>
       </c>
       <c r="T23">
-        <v>253.163091670459</v>
+        <v>-41.6940173332333</v>
       </c>
       <c r="U23">
-        <v>90.8790585483699</v>
+        <v>-160.0097259485685</v>
       </c>
       <c r="V23">
-        <v>348.7678612633441</v>
-      </c>
-      <c r="W23">
-        <v>366.731473604237</v>
+        <v>-217.3604357411732</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B2A02</t>
+          <t>B2A03</t>
         </is>
       </c>
       <c r="B24">
-        <v>192.1180833333333</v>
+        <v>616.7175512820513</v>
       </c>
       <c r="C24">
-        <v>-24.00183575</v>
+        <v>227.9293871153847</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="E24">
-        <v>16.64125</v>
+        <v>20.02</v>
       </c>
       <c r="F24">
-        <v>8.686249999999999</v>
+        <v>7.49</v>
       </c>
       <c r="G24">
-        <v>25.3275</v>
+        <v>27.51</v>
       </c>
       <c r="H24">
-        <v>16.15549779666667</v>
+        <v>18.00963822</v>
       </c>
       <c r="I24">
-        <v>9.634761951333333</v>
+        <v>8.657248975</v>
       </c>
       <c r="J24">
-        <v>1.422238535666667</v>
+        <v>1.379606870166667</v>
       </c>
       <c r="K24">
-        <v>25.790259748</v>
+        <v>26.666887195</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2163,74 +2092,71 @@
         </is>
       </c>
       <c r="M24">
-        <v>0.7408975943918668</v>
+        <v>1.637969963880097</v>
       </c>
       <c r="N24">
-        <v>-4.66765484466876</v>
+        <v>-10.31921077244461</v>
       </c>
       <c r="O24">
-        <v>-8.320279985020663</v>
+        <v>-18.39440269437349</v>
       </c>
       <c r="P24">
-        <v>-14.81795188783734</v>
+        <v>-32.75939927760194</v>
       </c>
       <c r="Q24">
-        <v>0.06800735153152251</v>
+        <v>33.47457627118644</v>
       </c>
       <c r="R24">
-        <v>1.983050847457627</v>
+        <v>-2.01036178</v>
       </c>
       <c r="S24">
-        <v>-0.4857522033333339</v>
+        <v>-296.9179977740847</v>
       </c>
       <c r="T24">
-        <v>-73.95953580575548</v>
+        <v>-106.5859479189022</v>
       </c>
       <c r="U24">
-        <v>-26.54957695591223</v>
+        <v>-409.0464149847698</v>
       </c>
       <c r="V24">
-        <v>-101.8896907633751</v>
-      </c>
-      <c r="W24">
-        <v>-106.2816515407761</v>
+        <v>-87.38301335307352</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B2A03</t>
+          <t>B2A04</t>
         </is>
       </c>
       <c r="B25">
-        <v>713.231575</v>
+        <v>118.075</v>
       </c>
       <c r="C25">
-        <v>302.090400625</v>
+        <v>-90.13130423076923</v>
       </c>
       <c r="D25">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>19.125</v>
+        <v>16.915</v>
       </c>
       <c r="F25">
-        <v>7.810833333333333</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G25">
-        <v>26.93583333333333</v>
+        <v>25.885</v>
       </c>
       <c r="H25">
-        <v>18.00963822</v>
+        <v>14.5059828</v>
       </c>
       <c r="I25">
-        <v>8.657248975</v>
+        <v>9.411386414333334</v>
       </c>
       <c r="J25">
-        <v>1.379606870166667</v>
+        <v>1.447401226833333</v>
       </c>
       <c r="K25">
-        <v>26.666887195</v>
+        <v>23.91736921433333</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2238,74 +2164,71 @@
         </is>
       </c>
       <c r="M25">
-        <v>1.389876030177799</v>
+        <v>6.174000995376301</v>
       </c>
       <c r="N25">
-        <v>-8.756218990120134</v>
+        <v>-38.89620627087069</v>
       </c>
       <c r="O25">
-        <v>-15.60830781889668</v>
+        <v>-69.33403117807586</v>
       </c>
       <c r="P25">
-        <v>-27.79752060355598</v>
+        <v>-123.480019907526</v>
       </c>
       <c r="Q25">
-        <v>0.1275773986648217</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>33.47457627118644</v>
+        <v>-2.409017199999999</v>
       </c>
       <c r="S25">
-        <v>-1.115361780000001</v>
+        <v>-373.2809210242492</v>
       </c>
       <c r="T25">
-        <v>-164.7320347043901</v>
+        <v>-133.9982793420382</v>
       </c>
       <c r="U25">
-        <v>-59.13457656055029</v>
+        <v>-514.2471108920734</v>
       </c>
       <c r="V25">
-        <v>-226.9416092460889</v>
-      </c>
-      <c r="W25">
-        <v>121.7500581017133</v>
+        <v>-532.7462564330942</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B2A04</t>
+          <t>B2A05</t>
         </is>
       </c>
       <c r="B26">
-        <v>142.4275</v>
+        <v>62.20987179487179</v>
       </c>
       <c r="C26">
-        <v>-57.19269775</v>
+        <v>-124.8120323076923</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>16.69375</v>
+        <v>19.155</v>
       </c>
       <c r="F26">
-        <v>8.734166666666667</v>
+        <v>10.21</v>
       </c>
       <c r="G26">
-        <v>25.42791666666667</v>
+        <v>29.365</v>
       </c>
       <c r="H26">
-        <v>14.5059828</v>
+        <v>17.06013133166667</v>
       </c>
       <c r="I26">
-        <v>9.411386414333334</v>
+        <v>11.02718368683333</v>
       </c>
       <c r="J26">
-        <v>1.447401226833333</v>
+        <v>1.4471556175</v>
       </c>
       <c r="K26">
-        <v>23.91736921433333</v>
+        <v>28.0873150185</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2313,74 +2236,71 @@
         </is>
       </c>
       <c r="M26">
-        <v>5.03432563844431</v>
+        <v>2.075840817204807</v>
       </c>
       <c r="N26">
-        <v>-31.71625152219915</v>
+        <v>-13.07779714839029</v>
       </c>
       <c r="O26">
-        <v>-56.5354769197296</v>
+        <v>-23.31169237720999</v>
       </c>
       <c r="P26">
-        <v>-100.6865127688862</v>
+        <v>-41.51681634409614</v>
       </c>
       <c r="Q26">
-        <v>0.4621032056378304</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="R26">
-        <v>1</v>
+        <v>-2.094868668333334</v>
       </c>
       <c r="S26">
-        <v>-2.187767200000001</v>
+        <v>-324.5480409123278</v>
       </c>
       <c r="T26">
-        <v>-338.9978931668248</v>
+        <v>-116.5044249428869</v>
       </c>
       <c r="U26">
-        <v>-121.6915513932192</v>
+        <v>-447.1106959522448</v>
       </c>
       <c r="V26">
-        <v>-467.0174052324913</v>
-      </c>
-      <c r="W26">
-        <v>-452.7260678365544</v>
+        <v>-472.6717655972301</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B2A05</t>
+          <t>B2A06</t>
         </is>
       </c>
       <c r="B27">
-        <v>153.53375</v>
+        <v>229.5128205128205</v>
       </c>
       <c r="C27">
-        <v>-43.88250625</v>
+        <v>-17.83788538461537</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E27">
-        <v>19.26958333333333</v>
+        <v>20.59166666666667</v>
       </c>
       <c r="F27">
-        <v>9.976666666666667</v>
+        <v>12.02833333333333</v>
       </c>
       <c r="G27">
-        <v>29.24625</v>
+        <v>32.62</v>
       </c>
       <c r="H27">
-        <v>17.06013133166667</v>
+        <v>19.40672484</v>
       </c>
       <c r="I27">
-        <v>11.02718368683333</v>
+        <v>13.72259501166667</v>
       </c>
       <c r="J27">
-        <v>1.4471556175</v>
+        <v>1.368905493</v>
       </c>
       <c r="K27">
-        <v>28.0873150185</v>
+        <v>33.12931985166666</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2388,74 +2308,71 @@
         </is>
       </c>
       <c r="M27">
-        <v>1.903937605799871</v>
+        <v>2.268599779202153</v>
       </c>
       <c r="N27">
-        <v>-11.99480691653919</v>
+        <v>-14.29217860897357</v>
       </c>
       <c r="O27">
-        <v>-21.38121931313255</v>
+        <v>-25.47637552044019</v>
       </c>
       <c r="P27">
-        <v>-38.07875211599742</v>
+        <v>-45.37199558404307</v>
       </c>
       <c r="Q27">
-        <v>0.1747633614035372</v>
+        <v>3.677966101694915</v>
       </c>
       <c r="R27">
-        <v>0.9833333333333333</v>
+        <v>-1.18494182666667</v>
       </c>
       <c r="S27">
-        <v>-2.209452001666666</v>
+        <v>-173.6510652044595</v>
       </c>
       <c r="T27">
-        <v>-342.2998918596826</v>
+        <v>-62.33627981698547</v>
       </c>
       <c r="U27">
-        <v>-122.876884257322</v>
+        <v>-239.2288315719282</v>
       </c>
       <c r="V27">
-        <v>-471.5663740983853</v>
-      </c>
-      <c r="W27">
-        <v>-407.5636174228152</v>
+        <v>-216.9653261095151</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B2A06</t>
+          <t>B2A08</t>
         </is>
       </c>
       <c r="B28">
-        <v>321.4800416666667</v>
+        <v>130.1305</v>
       </c>
       <c r="C28">
-        <v>53.11916737500001</v>
+        <v>-82.71224711538461</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>20.56541666666667</v>
+        <v>21.44833333333333</v>
       </c>
       <c r="F28">
-        <v>12.00541666666667</v>
+        <v>10.89</v>
       </c>
       <c r="G28">
-        <v>32.57083333333333</v>
+        <v>32.33833333333333</v>
       </c>
       <c r="H28">
-        <v>19.40672484</v>
+        <v>20.44729365833333</v>
       </c>
       <c r="I28">
-        <v>13.72259501166667</v>
+        <v>12.14286722666667</v>
       </c>
       <c r="J28">
-        <v>1.368905493</v>
+        <v>1.247915171166667</v>
       </c>
       <c r="K28">
-        <v>33.12931985166666</v>
+        <v>32.590160885</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2463,74 +2380,71 @@
         </is>
       </c>
       <c r="M28">
-        <v>2.494660573312057</v>
+        <v>0.7360342021259476</v>
       </c>
       <c r="N28">
-        <v>-15.71636161186596</v>
+        <v>-4.63701547339347</v>
       </c>
       <c r="O28">
-        <v>-28.0150382382944</v>
+        <v>-8.265664089874392</v>
       </c>
       <c r="P28">
-        <v>-49.89321146624114</v>
+        <v>-14.72068404251895</v>
       </c>
       <c r="Q28">
-        <v>0.2289861106922835</v>
+        <v>1.627118644067797</v>
       </c>
       <c r="R28">
-        <v>3.677966101694915</v>
+        <v>-1.001039674999998</v>
       </c>
       <c r="S28">
-        <v>-1.158691826666669</v>
+        <v>-133.7344546116859</v>
       </c>
       <c r="T28">
-        <v>-169.8041755436901</v>
+        <v>-48.00724011701544</v>
       </c>
       <c r="U28">
-        <v>-60.95534506696568</v>
+        <v>-184.2380712147861</v>
       </c>
       <c r="V28">
-        <v>-233.929198554138</v>
-      </c>
-      <c r="W28">
-        <v>-144.7000464069845</v>
+        <v>-224.7123658169449</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B2A08</t>
+          <t>B2A09</t>
         </is>
       </c>
       <c r="B29">
-        <v>150.5134916666667</v>
+        <v>146.1408974358974</v>
       </c>
       <c r="C29">
-        <v>-53.119888375</v>
+        <v>-71.83924653846152</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>21.74958333333333</v>
+        <v>21.98666666666666</v>
       </c>
       <c r="F29">
-        <v>10.90166666666667</v>
+        <v>11.99</v>
       </c>
       <c r="G29">
-        <v>32.65125</v>
+        <v>33.97666666666667</v>
       </c>
       <c r="H29">
-        <v>20.44729365833333</v>
+        <v>20.36209860166667</v>
       </c>
       <c r="I29">
-        <v>12.14286722666667</v>
+        <v>13.86795943166667</v>
       </c>
       <c r="J29">
-        <v>1.247915171166667</v>
+        <v>1.302890749166667</v>
       </c>
       <c r="K29">
-        <v>32.590160885</v>
+        <v>34.23005803333334</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2538,74 +2452,71 @@
         </is>
       </c>
       <c r="M29">
-        <v>2.013311318365398</v>
+        <v>0.6936343066418474</v>
       </c>
       <c r="N29">
-        <v>-12.68386130570201</v>
+        <v>-4.369896131843639</v>
       </c>
       <c r="O29">
-        <v>-22.60948610524342</v>
+        <v>-7.789513263587947</v>
       </c>
       <c r="P29">
-        <v>-40.26622636730796</v>
+        <v>-13.87268613283695</v>
       </c>
       <c r="Q29">
-        <v>0.1848028278224515</v>
+        <v>3.933333333333333</v>
       </c>
       <c r="R29">
-        <v>1.627118644067797</v>
+        <v>-1.624568064999998</v>
       </c>
       <c r="S29">
-        <v>-1.302289675000001</v>
+        <v>-226.59632815965</v>
       </c>
       <c r="T29">
-        <v>-173.980116654772</v>
+        <v>-81.34227164705385</v>
       </c>
       <c r="U29">
-        <v>-62.45440085043099</v>
+        <v>-312.1683979323506</v>
       </c>
       <c r="V29">
-        <v>-239.6821463494254</v>
-      </c>
-      <c r="W29">
-        <v>-249.7094911350154</v>
+        <v>-306.2250879616994</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B2A09</t>
+          <t>B2A10</t>
         </is>
       </c>
       <c r="B30">
-        <v>184.4895</v>
+        <v>337.4911538461538</v>
       </c>
       <c r="C30">
-        <v>-29.02871074999999</v>
+        <v>52.38197307692309</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E30">
-        <v>21.85333333333333</v>
+        <v>22.705</v>
       </c>
       <c r="F30">
-        <v>12.00583333333333</v>
+        <v>11.96666666666667</v>
       </c>
       <c r="G30">
-        <v>33.85916666666667</v>
+        <v>34.67166666666667</v>
       </c>
       <c r="H30">
-        <v>20.36209860166667</v>
+        <v>23.50365367666667</v>
       </c>
       <c r="I30">
-        <v>13.86795943166667</v>
+        <v>13.197827925</v>
       </c>
       <c r="J30">
-        <v>1.302890749166667</v>
+        <v>1.2313447075</v>
       </c>
       <c r="K30">
-        <v>34.23005803333334</v>
+        <v>36.70148160166666</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2613,74 +2524,71 @@
         </is>
       </c>
       <c r="M30">
-        <v>0.9993273242222674</v>
+        <v>0.7101404810624976</v>
       </c>
       <c r="N30">
-        <v>-6.295762142600284</v>
+        <v>-4.473885030693735</v>
       </c>
       <c r="O30">
-        <v>-11.22244585101606</v>
+        <v>-7.974877602331849</v>
       </c>
       <c r="P30">
-        <v>-19.98654648444535</v>
+        <v>-14.20280962124995</v>
       </c>
       <c r="Q30">
-        <v>0.09172874247111412</v>
+        <v>12.86440677966102</v>
       </c>
       <c r="R30">
-        <v>3.933333333333333</v>
+        <v>0.7986536766666674</v>
       </c>
       <c r="S30">
-        <v>-1.491234731666665</v>
+        <v>105.279811622898</v>
       </c>
       <c r="T30">
-        <v>-207.9988656060451</v>
+        <v>37.79275289027108</v>
       </c>
       <c r="U30">
-        <v>-74.66625944832387</v>
+        <v>145.0377876634632</v>
       </c>
       <c r="V30">
-        <v>-286.5477705456818</v>
-      </c>
-      <c r="W30">
-        <v>-248.2500222070611</v>
+        <v>149.6869070974893</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B2A10</t>
+          <t>B2A12</t>
         </is>
       </c>
       <c r="B31">
-        <v>344.1929166666667</v>
+        <v>334.3515</v>
       </c>
       <c r="C31">
-        <v>74.82817325000001</v>
+        <v>49.16695634615385</v>
       </c>
       <c r="D31">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E31">
-        <v>22.67833333333333</v>
+        <v>17.7</v>
       </c>
       <c r="F31">
-        <v>11.503125</v>
+        <v>8.788333333333334</v>
       </c>
       <c r="G31">
-        <v>34.18145833333334</v>
+        <v>26.48833333333333</v>
       </c>
       <c r="H31">
-        <v>23.50365367666667</v>
+        <v>18.23542061666667</v>
       </c>
       <c r="I31">
-        <v>13.197827925</v>
+        <v>9.010506192166666</v>
       </c>
       <c r="J31">
-        <v>1.2313447075</v>
+        <v>1.383368769</v>
       </c>
       <c r="K31">
-        <v>36.70148160166666</v>
+        <v>27.24592680883333</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2688,74 +2596,71 @@
         </is>
       </c>
       <c r="M31">
-        <v>1.08660229088038</v>
+        <v>0.9077257805083475</v>
       </c>
       <c r="N31">
-        <v>-6.845594432546394</v>
+        <v>-5.71867241720259</v>
       </c>
       <c r="O31">
-        <v>-12.20254372658667</v>
+        <v>-10.19376051510874</v>
       </c>
       <c r="P31">
-        <v>-21.7320458176076</v>
+        <v>-18.15451561016695</v>
       </c>
       <c r="Q31">
-        <v>0.09973975422543346</v>
+        <v>6.135593220338983</v>
       </c>
       <c r="R31">
-        <v>12.86440677966102</v>
+        <v>0.5354206166666664</v>
       </c>
       <c r="S31">
-        <v>0.8253203433333312</v>
+        <v>79.29394268193208</v>
       </c>
       <c r="T31">
-        <v>108.7950544938686</v>
+        <v>28.46449224479613</v>
       </c>
       <c r="U31">
-        <v>39.05463494651695</v>
+        <v>109.2385885234576</v>
       </c>
       <c r="V31">
-        <v>149.8805304576045</v>
-      </c>
-      <c r="W31">
-        <v>171.420684017282</v>
+        <v>118.2671385129772</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B2A12</t>
+          <t>B2A13</t>
         </is>
       </c>
       <c r="B32">
-        <v>340.3929333333333</v>
+        <v>84.00628205128206</v>
       </c>
       <c r="C32">
-        <v>73.25939950000001</v>
+        <v>-109.7441807692308</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>17.9225</v>
+        <v>15.83</v>
       </c>
       <c r="F32">
-        <v>8.876250000000001</v>
+        <v>13.04333333333333</v>
       </c>
       <c r="G32">
-        <v>26.79875</v>
+        <v>28.87333333333333</v>
       </c>
       <c r="H32">
-        <v>18.23542061666667</v>
+        <v>13.97646859166667</v>
       </c>
       <c r="I32">
-        <v>9.010506192166666</v>
+        <v>16.79281487833333</v>
       </c>
       <c r="J32">
-        <v>1.383368769</v>
+        <v>1.482308474333333</v>
       </c>
       <c r="K32">
-        <v>27.24592680883333</v>
+        <v>30.76928347</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2763,74 +2668,71 @@
         </is>
       </c>
       <c r="M32">
-        <v>0.9556834864386684</v>
+        <v>7.358028853615001</v>
       </c>
       <c r="N32">
-        <v>-6.020805964563611</v>
+        <v>-46.3555817777745</v>
       </c>
       <c r="O32">
-        <v>-10.73232555270625</v>
+        <v>-82.63066402609647</v>
       </c>
       <c r="P32">
-        <v>-19.11366972877337</v>
+        <v>-147.1605770723</v>
       </c>
       <c r="Q32">
-        <v>0.08772265331547284</v>
+        <v>1</v>
       </c>
       <c r="R32">
-        <v>6.135593220338983</v>
+        <v>-1.853531408333334</v>
       </c>
       <c r="S32">
-        <v>0.3129206166666663</v>
+        <v>-294.1341813919292</v>
       </c>
       <c r="T32">
-        <v>46.34246173865392</v>
+        <v>-105.5866292176156</v>
       </c>
       <c r="U32">
-        <v>16.63575549592705</v>
+        <v>-405.2113153288608</v>
       </c>
       <c r="V32">
-        <v>63.84327652036917</v>
-      </c>
-      <c r="W32">
-        <v>108.8695356859477</v>
+        <v>-486.5090261872564</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B2A13</t>
+          <t>B2A14</t>
         </is>
       </c>
       <c r="B33">
-        <v>95.69158333333333</v>
+        <v>266.2105897435898</v>
       </c>
       <c r="C33">
-        <v>-85.06298</v>
+        <v>6.197641153846162</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E33">
-        <v>16.18583333333333</v>
+        <v>18.02666666666667</v>
       </c>
       <c r="F33">
-        <v>12.83333333333333</v>
+        <v>10.27333333333333</v>
       </c>
       <c r="G33">
-        <v>29.01916666666667</v>
+        <v>28.3</v>
       </c>
       <c r="H33">
-        <v>13.97646859166667</v>
+        <v>18.806023575</v>
       </c>
       <c r="I33">
-        <v>16.79281487833333</v>
+        <v>10.669294244</v>
       </c>
       <c r="J33">
-        <v>1.482308474333333</v>
+        <v>1.342777728666667</v>
       </c>
       <c r="K33">
-        <v>30.76928347</v>
+        <v>29.475317819</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2838,74 +2740,71 @@
         </is>
       </c>
       <c r="M33">
-        <v>5.517142053953108</v>
+        <v>1.844119286466969</v>
       </c>
       <c r="N33">
-        <v>-34.75799493990458</v>
+        <v>-11.61795150474191</v>
       </c>
       <c r="O33">
-        <v>-61.95750526589341</v>
+        <v>-20.70945958702407</v>
       </c>
       <c r="P33">
-        <v>-110.3428410790622</v>
+        <v>-36.88238572933939</v>
       </c>
       <c r="Q33">
-        <v>0.5064211598912083</v>
+        <v>6</v>
       </c>
       <c r="R33">
-        <v>1</v>
+        <v>0.7793569083333338</v>
       </c>
       <c r="S33">
-        <v>-2.209364741666668</v>
+        <v>112.0333892840541</v>
       </c>
       <c r="T33">
-        <v>-350.6008513072089</v>
+        <v>40.21711410196814</v>
       </c>
       <c r="U33">
-        <v>-125.8567158538698</v>
+        <v>154.3417933193246</v>
       </c>
       <c r="V33">
-        <v>-483.0021163854799</v>
-      </c>
-      <c r="W33">
-        <v>-497.6213365731023</v>
+        <v>97.52157085087619</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B2A14</t>
+          <t>B2A15</t>
         </is>
       </c>
       <c r="B34">
-        <v>330.4918833333333</v>
+        <v>204.8405128205128</v>
       </c>
       <c r="C34">
-        <v>65.70050675</v>
+        <v>-33.63691384615384</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>18.049375</v>
+        <v>19.39833333333333</v>
       </c>
       <c r="F34">
-        <v>10.525625</v>
+        <v>10.76666666666667</v>
       </c>
       <c r="G34">
-        <v>28.575</v>
+        <v>30.165</v>
       </c>
       <c r="H34">
-        <v>18.806023575</v>
+        <v>17.420768235</v>
       </c>
       <c r="I34">
-        <v>10.669294244</v>
+        <v>11.58500638166667</v>
       </c>
       <c r="J34">
-        <v>1.342777728666667</v>
+        <v>1.4339126615</v>
       </c>
       <c r="K34">
-        <v>29.475317819</v>
+        <v>29.00577461666667</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2913,74 +2812,71 @@
         </is>
       </c>
       <c r="M34">
-        <v>1.365713000697533</v>
+        <v>4.45829362716574</v>
       </c>
       <c r="N34">
-        <v>-8.603991904394459</v>
+        <v>-28.08724985114416</v>
       </c>
       <c r="O34">
-        <v>-15.3369569978333</v>
+        <v>-50.06663743307126</v>
       </c>
       <c r="P34">
-        <v>-27.31426001395066</v>
+        <v>-89.1658725433148</v>
       </c>
       <c r="Q34">
-        <v>0.1253594624043055</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="R34">
-        <v>6</v>
+        <v>-1.977565098333333</v>
       </c>
       <c r="S34">
-        <v>0.7566485749999998</v>
+        <v>-303.5711138379897</v>
       </c>
       <c r="T34">
-        <v>108.7690420753201</v>
+        <v>-108.9742459931245</v>
       </c>
       <c r="U34">
-        <v>39.04529715524312</v>
+        <v>-418.2120206227567</v>
       </c>
       <c r="V34">
-        <v>149.8446946826359</v>
-      </c>
-      <c r="W34">
-        <v>159.1325918274868</v>
+        <v>-387.2746651172149</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B2A15</t>
+          <t>B2A16</t>
         </is>
       </c>
       <c r="B35">
-        <v>449.8763333333333</v>
+        <v>509.6371538461539</v>
       </c>
       <c r="C35">
-        <v>129.402371</v>
+        <v>162.6234432692308</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>20.262125</v>
+        <v>21.27166666666667</v>
       </c>
       <c r="F35">
-        <v>10.754125</v>
+        <v>12.33</v>
       </c>
       <c r="G35">
-        <v>31.01625</v>
+        <v>33.60166666666667</v>
       </c>
       <c r="H35">
-        <v>17.420768235</v>
+        <v>20.34924550333333</v>
       </c>
       <c r="I35">
-        <v>11.58500638166667</v>
+        <v>13.3018109</v>
       </c>
       <c r="J35">
-        <v>1.4339126615</v>
+        <v>1.363697516166667</v>
       </c>
       <c r="K35">
-        <v>29.00577461666667</v>
+        <v>33.65105640333333</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2988,74 +2884,71 @@
         </is>
       </c>
       <c r="M35">
-        <v>4.138422420662683</v>
+        <v>1.331719516371994</v>
       </c>
       <c r="N35">
-        <v>-26.0720612501749</v>
+        <v>-8.389832953143562</v>
       </c>
       <c r="O35">
-        <v>-46.47448378404193</v>
+        <v>-14.95521016885749</v>
       </c>
       <c r="P35">
-        <v>-82.76844841325365</v>
+        <v>-26.63439032743988</v>
       </c>
       <c r="Q35">
-        <v>0.3798678123377518</v>
+        <v>3.610169491525424</v>
       </c>
       <c r="R35">
-        <v>0.7333333333333333</v>
+        <v>-0.9224211633333361</v>
       </c>
       <c r="S35">
-        <v>-2.841356765</v>
+        <v>-134.6648537645158</v>
       </c>
       <c r="T35">
-        <v>-436.1696303646878</v>
+        <v>-48.34122955649285</v>
       </c>
       <c r="U35">
-        <v>-156.5737134642469</v>
+        <v>-185.5198272579462</v>
       </c>
       <c r="V35">
-        <v>-600.8851769290756</v>
-      </c>
-      <c r="W35">
-        <v>-353.2417431487297</v>
+        <v>13.00337933585752</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B2A16</t>
+          <t>B2A17</t>
         </is>
       </c>
       <c r="B36">
-        <v>478.5481916666667</v>
+        <v>259.0865384615385</v>
       </c>
       <c r="C36">
-        <v>158.515088</v>
+        <v>-0.3553538461538302</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E36">
-        <v>21.45375</v>
+        <v>20.25666666666667</v>
       </c>
       <c r="F36">
-        <v>12.25416666666667</v>
+        <v>13.38</v>
       </c>
       <c r="G36">
-        <v>33.70791666666666</v>
+        <v>33.63666666666667</v>
       </c>
       <c r="H36">
-        <v>20.34924550333333</v>
+        <v>19.53381813333333</v>
       </c>
       <c r="I36">
-        <v>13.3018109</v>
+        <v>14.71755182666667</v>
       </c>
       <c r="J36">
-        <v>1.363697516166667</v>
+        <v>1.358907214</v>
       </c>
       <c r="K36">
-        <v>33.65105640333333</v>
+        <v>34.25136996</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -3063,74 +2956,71 @@
         </is>
       </c>
       <c r="M36">
-        <v>1.406406261621896</v>
+        <v>2.991736858382932</v>
       </c>
       <c r="N36">
-        <v>-8.860359448217944</v>
+        <v>-18.84794220781247</v>
       </c>
       <c r="O36">
-        <v>-15.79394231801389</v>
+        <v>-33.59720491964033</v>
       </c>
       <c r="P36">
-        <v>-28.12812523243792</v>
+        <v>-59.83473716765864</v>
       </c>
       <c r="Q36">
-        <v>0.1290947166710151</v>
+        <v>6.220338983050848</v>
       </c>
       <c r="R36">
-        <v>3.610169491525424</v>
+        <v>-0.7228485333333339</v>
       </c>
       <c r="S36">
-        <v>-1.104504496666667</v>
+        <v>-105.1584228883923</v>
       </c>
       <c r="T36">
-        <v>-161.247315692948</v>
+        <v>-37.74917744711517</v>
       </c>
       <c r="U36">
-        <v>-57.88365178721212</v>
+        <v>-144.8705575627574</v>
       </c>
       <c r="V36">
-        <v>-222.1409173730952</v>
-      </c>
-      <c r="W36">
-        <v>-18.52617001096192</v>
+        <v>-139.1109816541864</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B2A17</t>
+          <t>B2A18</t>
         </is>
       </c>
       <c r="B37">
-        <v>330.23375</v>
+        <v>324.4254487179487</v>
       </c>
       <c r="C37">
-        <v>59.16419275000002</v>
+        <v>41.64623942307693</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E37">
-        <v>20.14854166666667</v>
+        <v>21.50666666666667</v>
       </c>
       <c r="F37">
-        <v>13.441875</v>
+        <v>12.89166666666667</v>
       </c>
       <c r="G37">
-        <v>33.59041666666667</v>
+        <v>34.39833333333333</v>
       </c>
       <c r="H37">
-        <v>19.53381813333333</v>
+        <v>21.70943054333333</v>
       </c>
       <c r="I37">
-        <v>14.71755182666667</v>
+        <v>14.36475716833333</v>
       </c>
       <c r="J37">
-        <v>1.358907214</v>
+        <v>1.326444698333333</v>
       </c>
       <c r="K37">
-        <v>34.25136996</v>
+        <v>36.07418771166667</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -3138,74 +3028,71 @@
         </is>
       </c>
       <c r="M37">
-        <v>2.906916865566272</v>
+        <v>0.9167533653688136</v>
       </c>
       <c r="N37">
-        <v>-18.31357625306751</v>
+        <v>-5.775546201823525</v>
       </c>
       <c r="O37">
-        <v>-32.64467640030924</v>
+        <v>-10.29514029309178</v>
       </c>
       <c r="P37">
-        <v>-58.13833731132544</v>
+        <v>-18.33506730737627</v>
       </c>
       <c r="Q37">
-        <v>0.2668273168193285</v>
+        <v>11.2</v>
       </c>
       <c r="R37">
-        <v>6.220338983050848</v>
+        <v>0.2027638766666655</v>
       </c>
       <c r="S37">
-        <v>-0.6147235333333327</v>
+        <v>28.79298493513431</v>
       </c>
       <c r="T37">
-        <v>-89.42863448808259</v>
+        <v>10.33594331004821</v>
       </c>
       <c r="U37">
-        <v>-32.1025867393117</v>
+        <v>39.66639729730503</v>
       </c>
       <c r="V37">
-        <v>-123.2005557378385</v>
-      </c>
-      <c r="W37">
-        <v>-62.90911813839181</v>
+        <v>60.14408406511946</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B2A18</t>
+          <t>B2A19</t>
         </is>
       </c>
       <c r="B38">
-        <v>370.9917916666666</v>
+        <v>142.2470512820513</v>
       </c>
       <c r="C38">
-        <v>89.22180687500001</v>
+        <v>-73.8621246153846</v>
       </c>
       <c r="D38">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>21.13083333333333</v>
+        <v>22.74666666666667</v>
       </c>
       <c r="F38">
-        <v>13.22041666666667</v>
+        <v>12.90666666666667</v>
       </c>
       <c r="G38">
-        <v>34.35125</v>
+        <v>35.65333333333334</v>
       </c>
       <c r="H38">
-        <v>21.70943054333333</v>
+        <v>21.53524523833333</v>
       </c>
       <c r="I38">
-        <v>14.36475716833333</v>
+        <v>14.45000332833333</v>
       </c>
       <c r="J38">
-        <v>1.326444698333333</v>
+        <v>1.288804584666667</v>
       </c>
       <c r="K38">
-        <v>36.07418771166667</v>
+        <v>35.98524856666667</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -3213,74 +3100,71 @@
         </is>
       </c>
       <c r="M38">
-        <v>1.13456411529597</v>
+        <v>0.6187439129779645</v>
       </c>
       <c r="N38">
-        <v>-7.147753926364611</v>
+        <v>-3.898086651761176</v>
       </c>
       <c r="O38">
-        <v>-12.74115501477374</v>
+        <v>-6.948494142742542</v>
       </c>
       <c r="P38">
-        <v>-22.6912823059194</v>
+        <v>-12.37487825955929</v>
       </c>
       <c r="Q38">
-        <v>0.1041421934799454</v>
+        <v>2</v>
       </c>
       <c r="R38">
-        <v>11.2</v>
+        <v>-1.211421428333335</v>
       </c>
       <c r="S38">
-        <v>0.5785972100000016</v>
+        <v>-167.1434182175345</v>
       </c>
       <c r="T38">
-        <v>82.1622718253129</v>
+        <v>-60.00020141142262</v>
       </c>
       <c r="U38">
-        <v>29.49414886036873</v>
+        <v>-230.263630102351</v>
       </c>
       <c r="V38">
-        <v>113.1901164264208</v>
-      </c>
-      <c r="W38">
-        <v>158.6429236855392</v>
+        <v>-247.9540369756616</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B2A19</t>
+          <t>B2A20</t>
         </is>
       </c>
       <c r="B39">
-        <v>169.8209166666667</v>
+        <v>126.2232051282051</v>
       </c>
       <c r="C39">
-        <v>-39.96764974999999</v>
+        <v>-83.73494846153845</v>
       </c>
       <c r="D39">
         <v>2</v>
       </c>
       <c r="E39">
-        <v>22.37333333333333</v>
+        <v>22.77666666666667</v>
       </c>
       <c r="F39">
-        <v>12.92916666666667</v>
+        <v>12.88833333333333</v>
       </c>
       <c r="G39">
-        <v>35.3025</v>
+        <v>35.665</v>
       </c>
       <c r="H39">
-        <v>21.53524523833333</v>
+        <v>20.42762157666667</v>
       </c>
       <c r="I39">
-        <v>14.45000332833333</v>
+        <v>14.15560386</v>
       </c>
       <c r="J39">
-        <v>1.288804584666667</v>
+        <v>1.286318249666667</v>
       </c>
       <c r="K39">
-        <v>35.98524856666667</v>
+        <v>34.58322543666667</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -3288,74 +3172,71 @@
         </is>
       </c>
       <c r="M39">
-        <v>0.7742258026830298</v>
+        <v>1.395749491872198</v>
       </c>
       <c r="N39">
-        <v>-4.877622556903088</v>
+        <v>-8.793221798794846</v>
       </c>
       <c r="O39">
-        <v>-8.694555764130424</v>
+        <v>-15.67426679372478</v>
       </c>
       <c r="P39">
-        <v>-15.4845160536606</v>
+        <v>-27.91498983744396</v>
       </c>
       <c r="Q39">
-        <v>0.07106656402502957</v>
+        <v>1.88135593220339</v>
       </c>
       <c r="R39">
-        <v>2</v>
+        <v>-2.349045090000001</v>
       </c>
       <c r="S39">
-        <v>-0.8380880950000034</v>
+        <v>-323.4794829118566</v>
       </c>
       <c r="T39">
-        <v>-115.6335076212451</v>
+        <v>-116.1208400196408</v>
       </c>
       <c r="U39">
-        <v>-41.50946427429311</v>
+        <v>-445.6386066125186</v>
       </c>
       <c r="V39">
-        <v>-159.3014640378015</v>
-      </c>
-      <c r="W39">
-        <v>-164.2957131353755</v>
+        <v>-422.8886981671198</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B2A20</t>
+          <t>B2A21</t>
         </is>
       </c>
       <c r="B40">
-        <v>155.9118333333333</v>
+        <v>372.6879487179487</v>
       </c>
       <c r="C40">
-        <v>-48.933466125</v>
+        <v>72.4979007692308</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E40">
-        <v>22.52895833333333</v>
+        <v>22.43166666666667</v>
       </c>
       <c r="F40">
-        <v>12.88520833333333</v>
+        <v>13.03166666666667</v>
       </c>
       <c r="G40">
-        <v>35.41416666666667</v>
+        <v>35.46333333333334</v>
       </c>
       <c r="H40">
-        <v>20.42762157666667</v>
+        <v>20.91067990666667</v>
       </c>
       <c r="I40">
-        <v>14.15560386</v>
+        <v>14.24542969666667</v>
       </c>
       <c r="J40">
-        <v>1.286318249666667</v>
+        <v>1.177016317833333</v>
       </c>
       <c r="K40">
-        <v>34.58322543666667</v>
+        <v>35.15610960333333</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -3363,74 +3244,71 @@
         </is>
       </c>
       <c r="M40">
-        <v>2.404323882427713</v>
+        <v>1.143627946389912</v>
       </c>
       <c r="N40">
-        <v>-15.14724045929459</v>
+        <v>-7.204856062256444</v>
       </c>
       <c r="O40">
-        <v>-27.00055719966322</v>
+        <v>-12.84294183795871</v>
       </c>
       <c r="P40">
-        <v>-48.08647764855426</v>
+        <v>-22.87255892779823</v>
       </c>
       <c r="Q40">
-        <v>0.2206940617780084</v>
+        <v>6.915254237288136</v>
       </c>
       <c r="R40">
-        <v>1.88135593220339</v>
+        <v>-1.520986760000003</v>
       </c>
       <c r="S40">
-        <v>-2.101336756666665</v>
+        <v>-191.6526696659098</v>
       </c>
       <c r="T40">
-        <v>-289.3683609411731</v>
+        <v>-68.79839423904454</v>
       </c>
       <c r="U40">
-        <v>-103.8758218763186</v>
+        <v>-264.0285804053847</v>
       </c>
       <c r="V40">
-        <v>-398.6457255550603</v>
-      </c>
-      <c r="W40">
-        <v>-365.3023842658363</v>
+        <v>-131.9977107346377</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B2A21</t>
+          <t>B2A22</t>
         </is>
       </c>
       <c r="B41">
-        <v>557.3905416666666</v>
+        <v>386.626282051282</v>
       </c>
       <c r="C41">
-        <v>203.469684875</v>
+        <v>77.57301846153848</v>
       </c>
       <c r="D41">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E41">
-        <v>22.07958333333333</v>
+        <v>22.64166666666667</v>
       </c>
       <c r="F41">
-        <v>13.01458333333333</v>
+        <v>12.98166666666667</v>
       </c>
       <c r="G41">
-        <v>35.09416666666667</v>
+        <v>35.62333333333333</v>
       </c>
       <c r="H41">
-        <v>20.91067990666667</v>
+        <v>23.87834243333333</v>
       </c>
       <c r="I41">
-        <v>14.24542969666667</v>
+        <v>12.781894505</v>
       </c>
       <c r="J41">
-        <v>1.177016317833333</v>
+        <v>1.134298261833333</v>
       </c>
       <c r="K41">
-        <v>35.15610960333333</v>
+        <v>36.66023693833333</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -3438,149 +3316,143 @@
         </is>
       </c>
       <c r="M41">
-        <v>1.57617971818797</v>
+        <v>5.855716016589727</v>
       </c>
       <c r="N41">
-        <v>-9.92993222458421</v>
+        <v>-36.89101090451528</v>
       </c>
       <c r="O41">
-        <v>-17.7004982352509</v>
+        <v>-65.75969086630263</v>
       </c>
       <c r="P41">
-        <v>-31.5235943637594</v>
+        <v>-117.1143203317945</v>
       </c>
       <c r="Q41">
-        <v>0.1446783050492275</v>
+        <v>11.22033898305085</v>
       </c>
       <c r="R41">
-        <v>6.915254237288136</v>
+        <v>1.236675766666668</v>
       </c>
       <c r="S41">
-        <v>-1.168903426666667</v>
+        <v>150.1723832207024</v>
       </c>
       <c r="T41">
-        <v>-147.2882395782961</v>
+        <v>53.90803500230344</v>
       </c>
       <c r="U41">
-        <v>-52.87270138708063</v>
+        <v>206.8836360431256</v>
       </c>
       <c r="V41">
-        <v>-202.9103214375049</v>
-      </c>
-      <c r="W41">
-        <v>38.48094706145304</v>
+        <v>161.9857108159383</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B2A22</t>
+          <t>B3A01</t>
         </is>
       </c>
       <c r="B42">
-        <v>562.0825416666667</v>
+        <v>221.565641025641</v>
       </c>
       <c r="C42">
-        <v>205.459719375</v>
+        <v>-23.22944307692307</v>
       </c>
       <c r="D42">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>22.85291666666667</v>
+        <v>19.05333333333333</v>
       </c>
       <c r="F42">
-        <v>12.58791666666667</v>
+        <v>13.72</v>
       </c>
       <c r="G42">
-        <v>35.44083333333333</v>
+        <v>32.77333333333333</v>
       </c>
       <c r="H42">
-        <v>23.87834243333333</v>
+        <v>18.11070592666667</v>
       </c>
       <c r="I42">
-        <v>12.781894505</v>
+        <v>13.97844794</v>
       </c>
       <c r="J42">
-        <v>1.134298261833333</v>
+        <v>1.2480027205</v>
       </c>
       <c r="K42">
-        <v>36.66023693833333</v>
+        <v>32.08915386666667</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="M42">
-        <v>3.67911496942543</v>
+        <v>1.809020597434316</v>
       </c>
       <c r="N42">
-        <v>-23.17842430738021</v>
+        <v>-11.39682976383619</v>
       </c>
       <c r="O42">
-        <v>-41.31646110664758</v>
+        <v>-20.31530130918737</v>
       </c>
       <c r="P42">
-        <v>-73.5822993885086</v>
+        <v>-36.18041194868632</v>
       </c>
       <c r="Q42">
-        <v>0.3377077573803883</v>
+        <v>1</v>
       </c>
       <c r="R42">
-        <v>11.22033898305085</v>
+        <v>-0.9426274066666664</v>
       </c>
       <c r="S42">
-        <v>1.025425766666668</v>
+        <v>-125.9396698555875</v>
       </c>
       <c r="T42">
-        <v>124.5198097568576</v>
+        <v>-45.20911225585194</v>
       </c>
       <c r="U42">
-        <v>44.69941888707709</v>
+        <v>-173.4996559487438</v>
       </c>
       <c r="V42">
-        <v>171.5435984260627</v>
-      </c>
-      <c r="W42">
-        <v>288.66306802521</v>
+        <v>-169.484414241698</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B3A01</t>
+          <t>B3A02</t>
         </is>
       </c>
       <c r="B43">
-        <v>234.8489166666667</v>
+        <v>117.894358974359</v>
       </c>
       <c r="C43">
-        <v>3.932893250000005</v>
+        <v>-90.68202692307692</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43">
-        <v>19.62166666666667</v>
+        <v>19.465</v>
       </c>
       <c r="F43">
-        <v>15.00916666666667</v>
+        <v>13.27833333333333</v>
       </c>
       <c r="G43">
-        <v>34.63083333333334</v>
+        <v>32.74333333333333</v>
       </c>
       <c r="H43">
-        <v>18.11070592666667</v>
+        <v>15.78657563583333</v>
       </c>
       <c r="I43">
-        <v>13.97844794</v>
+        <v>14.74983727833333</v>
       </c>
       <c r="J43">
-        <v>1.2480027205</v>
+        <v>1.273350069</v>
       </c>
       <c r="K43">
-        <v>32.08915386666667</v>
+        <v>30.53641291416667</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3588,74 +3460,71 @@
         </is>
       </c>
       <c r="M43">
-        <v>1.333235766632308</v>
+        <v>3.786722414738152</v>
       </c>
       <c r="N43">
-        <v>-8.39938532978354</v>
+        <v>-23.85635121285036</v>
       </c>
       <c r="O43">
-        <v>-14.97223765928082</v>
+        <v>-42.52489271750945</v>
       </c>
       <c r="P43">
-        <v>-26.66471533264616</v>
+        <v>-75.73444829476304</v>
       </c>
       <c r="Q43">
-        <v>0.1223783612500249</v>
+        <v>1.932203389830508</v>
       </c>
       <c r="R43">
-        <v>1</v>
+        <v>-3.678424364166666</v>
       </c>
       <c r="S43">
-        <v>-1.510960739999998</v>
+        <v>-501.4372609232367</v>
       </c>
       <c r="T43">
-        <v>-201.8718057787648</v>
+        <v>-180.0031193057773</v>
       </c>
       <c r="U43">
-        <v>-72.46680207442839</v>
+        <v>-690.8005424329145</v>
       </c>
       <c r="V43">
-        <v>-278.1068815610635</v>
-      </c>
-      <c r="W43">
-        <v>-212.9111501880456</v>
+        <v>-634.6441805638232</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B3A02</t>
+          <t>B3A03</t>
         </is>
       </c>
       <c r="B44">
-        <v>144.7225</v>
+        <v>181.2729487179487</v>
       </c>
       <c r="C44">
-        <v>-54.61284625</v>
+        <v>-50.87757269230769</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E44">
-        <v>19.21375</v>
+        <v>16.74666666666667</v>
       </c>
       <c r="F44">
-        <v>14.38708333333333</v>
+        <v>14.75</v>
       </c>
       <c r="G44">
-        <v>33.60083333333333</v>
+        <v>31.49666666666667</v>
       </c>
       <c r="H44">
-        <v>15.78657563583333</v>
+        <v>16.34161234133333</v>
       </c>
       <c r="I44">
-        <v>14.74983727833333</v>
+        <v>15.09101679166667</v>
       </c>
       <c r="J44">
-        <v>1.273350069</v>
+        <v>1.209331958</v>
       </c>
       <c r="K44">
-        <v>30.53641291416667</v>
+        <v>31.432629133</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3663,74 +3532,71 @@
         </is>
       </c>
       <c r="M44">
-        <v>2.775396414933245</v>
+        <v>2.420979241851507</v>
       </c>
       <c r="N44">
-        <v>-17.48499741407944</v>
+        <v>-15.25216922366449</v>
       </c>
       <c r="O44">
-        <v>-31.16770173970034</v>
+        <v>-27.18759688599242</v>
       </c>
       <c r="P44">
-        <v>-55.50792829866489</v>
+        <v>-48.41958483703014</v>
       </c>
       <c r="Q44">
-        <v>0.2547549905120389</v>
+        <v>3.491525423728814</v>
       </c>
       <c r="R44">
-        <v>1.932203389830508</v>
+        <v>-0.4050543253333316</v>
       </c>
       <c r="S44">
-        <v>-3.427174364166667</v>
+        <v>-52.44037150035414</v>
       </c>
       <c r="T44">
-        <v>-467.1872398994921</v>
+        <v>-18.82474874371687</v>
       </c>
       <c r="U44">
-        <v>-167.7082399639202</v>
+        <v>-72.24400717874428</v>
       </c>
       <c r="V44">
-        <v>-643.6163083415361</v>
-      </c>
-      <c r="W44">
-        <v>-552.9677878891924</v>
+        <v>-130.5055410786543</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B3A03</t>
+          <t>B3A04</t>
         </is>
       </c>
       <c r="B45">
-        <v>280.7613333333333</v>
+        <v>309.4958974358975</v>
       </c>
       <c r="C45">
-        <v>32.07340675000001</v>
+        <v>31.6079503846154</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E45">
-        <v>17.22083333333333</v>
+        <v>17.50333333333333</v>
       </c>
       <c r="F45">
-        <v>16.3125</v>
+        <v>17.73166666666667</v>
       </c>
       <c r="G45">
-        <v>33.53333333333333</v>
+        <v>35.235</v>
       </c>
       <c r="H45">
-        <v>16.34161234133333</v>
+        <v>17.679803865</v>
       </c>
       <c r="I45">
-        <v>15.09101679166667</v>
+        <v>18.16225364</v>
       </c>
       <c r="J45">
-        <v>1.209331958</v>
+        <v>1.211471480333333</v>
       </c>
       <c r="K45">
-        <v>31.432629133</v>
+        <v>35.842057505</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3738,74 +3604,71 @@
         </is>
       </c>
       <c r="M45">
-        <v>1.815511680039976</v>
+        <v>0.8786257682716357</v>
       </c>
       <c r="N45">
-        <v>-11.43772358425185</v>
+        <v>-5.535342340111305</v>
       </c>
       <c r="O45">
-        <v>-20.38819616684893</v>
+        <v>-9.86696737769047</v>
       </c>
       <c r="P45">
-        <v>-36.31023360079952</v>
+        <v>-17.57251536543271</v>
       </c>
       <c r="Q45">
-        <v>0.1666467025519324</v>
+        <v>6.35593220338983</v>
       </c>
       <c r="R45">
-        <v>3.491525423728814</v>
+        <v>0.1764705316666664</v>
       </c>
       <c r="S45">
-        <v>-0.8792209920000005</v>
+        <v>22.8871831328695</v>
       </c>
       <c r="T45">
-        <v>-113.8283745358041</v>
+        <v>8.215911893850588</v>
       </c>
       <c r="U45">
-        <v>-40.86146778208352</v>
+        <v>31.53032244520031</v>
       </c>
       <c r="V45">
-        <v>-156.8146386425559</v>
-      </c>
-      <c r="W45">
-        <v>-102.143163952653</v>
+        <v>44.62816613979442</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B3A04</t>
+          <t>B3A05</t>
         </is>
       </c>
       <c r="B46">
-        <v>363.53175</v>
+        <v>400.8861538461538</v>
       </c>
       <c r="C46">
-        <v>83.94919325000001</v>
+        <v>93.36799769230771</v>
       </c>
       <c r="D46">
         <v>8</v>
       </c>
       <c r="E46">
-        <v>17.60666666666667</v>
+        <v>20.60166666666667</v>
       </c>
       <c r="F46">
-        <v>18.43125</v>
+        <v>14.57333333333333</v>
       </c>
       <c r="G46">
-        <v>36.03791666666666</v>
+        <v>35.175</v>
       </c>
       <c r="H46">
-        <v>17.679803865</v>
+        <v>20.82464430333333</v>
       </c>
       <c r="I46">
-        <v>18.16225364</v>
+        <v>15.52260234</v>
       </c>
       <c r="J46">
-        <v>1.211471480333333</v>
+        <v>1.2708509925</v>
       </c>
       <c r="K46">
-        <v>35.842057505</v>
+        <v>36.34724664333334</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3813,74 +3676,71 @@
         </is>
       </c>
       <c r="M46">
-        <v>0.983265948598725</v>
+        <v>1.002883629259998</v>
       </c>
       <c r="N46">
-        <v>-6.194575476171967</v>
+        <v>-6.318166864337985</v>
       </c>
       <c r="O46">
-        <v>-11.04207660276368</v>
+        <v>-11.26238315658977</v>
       </c>
       <c r="P46">
-        <v>-19.6653189719745</v>
+        <v>-20.05767258519995</v>
       </c>
       <c r="Q46">
-        <v>0.09025446096935456</v>
+        <v>5.491525423728813</v>
       </c>
       <c r="R46">
-        <v>6.35593220338983</v>
+        <v>0.2229776366666663</v>
       </c>
       <c r="S46">
-        <v>0.07313719833333465</v>
+        <v>30.33631996665316</v>
       </c>
       <c r="T46">
-        <v>9.485461602404254</v>
+        <v>10.88996101367036</v>
       </c>
       <c r="U46">
-        <v>3.405037498298963</v>
+        <v>41.79255895303437</v>
       </c>
       <c r="V46">
-        <v>13.06756105061476</v>
-      </c>
-      <c r="W46">
-        <v>82.39257824964058</v>
+        <v>112.4419345023711</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B3A05</t>
+          <t>B3A06</t>
         </is>
       </c>
       <c r="B47">
-        <v>559.8954583333333</v>
+        <v>153.6873076923077</v>
       </c>
       <c r="C47">
-        <v>205.867610625</v>
+        <v>-66.60177923076922</v>
       </c>
       <c r="D47">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>20.18708333333333</v>
+        <v>21.58333333333333</v>
       </c>
       <c r="F47">
-        <v>15.62416666666667</v>
+        <v>15.355</v>
       </c>
       <c r="G47">
-        <v>35.81125</v>
+        <v>36.93833333333333</v>
       </c>
       <c r="H47">
-        <v>20.82464430333333</v>
+        <v>19.75802325166667</v>
       </c>
       <c r="I47">
-        <v>15.52260234</v>
+        <v>16.70883446166667</v>
       </c>
       <c r="J47">
-        <v>1.2708509925</v>
+        <v>1.273792166333333</v>
       </c>
       <c r="K47">
-        <v>36.34724664333334</v>
+        <v>36.46685771333334</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3888,74 +3748,71 @@
         </is>
       </c>
       <c r="M47">
-        <v>1.469352354643475</v>
+        <v>0.675106066584323</v>
       </c>
       <c r="N47">
-        <v>-9.256919834253893</v>
+        <v>-4.253168219481235</v>
       </c>
       <c r="O47">
-        <v>-16.50082694264622</v>
+        <v>-7.581441127741948</v>
       </c>
       <c r="P47">
-        <v>-29.3870470928695</v>
+        <v>-13.50212133168646</v>
       </c>
       <c r="Q47">
-        <v>0.1348725692488307</v>
+        <v>1</v>
       </c>
       <c r="R47">
-        <v>5.491525423728813</v>
+        <v>-1.825310081666665</v>
       </c>
       <c r="S47">
-        <v>0.6375609699999991</v>
+        <v>-248.9099067102928</v>
       </c>
       <c r="T47">
-        <v>86.7407775654352</v>
+        <v>-89.35227420369485</v>
       </c>
       <c r="U47">
-        <v>31.13771502348956</v>
+        <v>-342.9084991725798</v>
       </c>
       <c r="V47">
-        <v>119.4976537701462</v>
-      </c>
-      <c r="W47">
-        <v>276.107561247789</v>
+        <v>-323.0931270688039</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B3A06</t>
+          <t>B3A07</t>
         </is>
       </c>
       <c r="B48">
-        <v>260.8305</v>
+        <v>417.6919230769231</v>
       </c>
       <c r="C48">
-        <v>21.04615475000001</v>
+        <v>103.2146934615385</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E48">
-        <v>21.06666666666667</v>
+        <v>20.42333333333333</v>
       </c>
       <c r="F48">
-        <v>15.81270833333333</v>
+        <v>15.33</v>
       </c>
       <c r="G48">
-        <v>36.879375</v>
+        <v>35.75333333333333</v>
       </c>
       <c r="H48">
-        <v>19.75802325166667</v>
+        <v>20.94664231166667</v>
       </c>
       <c r="I48">
-        <v>16.70883446166667</v>
+        <v>15.58443038</v>
       </c>
       <c r="J48">
-        <v>1.273792166333333</v>
+        <v>1.272812508666667</v>
       </c>
       <c r="K48">
-        <v>36.46685771333334</v>
+        <v>36.53107269166667</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -3963,74 +3820,71 @@
         </is>
       </c>
       <c r="M48">
-        <v>0.7231897938302607</v>
+        <v>1.042897672376869</v>
       </c>
       <c r="N48">
-        <v>-4.556095701130642</v>
+        <v>-6.570255335974272</v>
       </c>
       <c r="O48">
-        <v>-8.121421384713829</v>
+        <v>-11.71174086079223</v>
       </c>
       <c r="P48">
-        <v>-14.46379587660521</v>
+        <v>-20.85795344753737</v>
       </c>
       <c r="Q48">
-        <v>0.06638194388172214</v>
+        <v>6.203389830508475</v>
       </c>
       <c r="R48">
-        <v>1</v>
+        <v>0.5233089783333362</v>
       </c>
       <c r="S48">
-        <v>-1.308643414999999</v>
+        <v>71.30657492840973</v>
       </c>
       <c r="T48">
-        <v>-178.4542328541052</v>
+        <v>25.59723202558298</v>
       </c>
       <c r="U48">
-        <v>-64.06049384506339</v>
+        <v>98.23486301932302</v>
       </c>
       <c r="V48">
-        <v>-245.8458723791118</v>
-      </c>
-      <c r="W48">
-        <v>-165.529499488819</v>
+        <v>162.809527529156</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B3A07</t>
+          <t>B3A08</t>
         </is>
       </c>
       <c r="B49">
-        <v>574.8780416666667</v>
+        <v>182.8228205128205</v>
       </c>
       <c r="C49">
-        <v>218.572691625</v>
+        <v>-49.14041346153846</v>
       </c>
       <c r="D49">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>19.70083333333333</v>
+        <v>21.07666666666667</v>
       </c>
       <c r="F49">
-        <v>15.2175</v>
+        <v>13.84</v>
       </c>
       <c r="G49">
-        <v>34.91833333333333</v>
+        <v>34.91666666666667</v>
       </c>
       <c r="H49">
-        <v>20.94664231166667</v>
+        <v>18.28368143833333</v>
       </c>
       <c r="I49">
-        <v>15.58443038</v>
+        <v>15.45937701166667</v>
       </c>
       <c r="J49">
-        <v>1.272812508666667</v>
+        <v>1.303480212</v>
       </c>
       <c r="K49">
-        <v>36.53107269166667</v>
+        <v>33.74305845</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -4038,74 +3892,71 @@
         </is>
       </c>
       <c r="M49">
-        <v>1.235925826614334</v>
+        <v>0.9046072052730504</v>
       </c>
       <c r="N49">
-        <v>-7.786332707670304</v>
+        <v>-5.699025393220217</v>
       </c>
       <c r="O49">
-        <v>-13.87944703287897</v>
+        <v>-10.15873891521636</v>
       </c>
       <c r="P49">
-        <v>-24.71851653228668</v>
+        <v>-18.09214410546101</v>
       </c>
       <c r="Q49">
-        <v>0.1134462343968588</v>
+        <v>1.864406779661017</v>
       </c>
       <c r="R49">
-        <v>6.203389830508475</v>
+        <v>-2.792985228333336</v>
       </c>
       <c r="S49">
-        <v>1.245808978333336</v>
+        <v>-389.7445376506309</v>
       </c>
       <c r="T49">
-        <v>169.7551063292213</v>
+        <v>-139.9082955668931</v>
       </c>
       <c r="U49">
-        <v>60.93773047715634</v>
+        <v>-536.9280645870024</v>
       </c>
       <c r="V49">
-        <v>233.8615987911897</v>
-      </c>
-      <c r="W49">
-        <v>374.4483509213423</v>
+        <v>-449.0436900273857</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B3A08</t>
+          <t>B3A09</t>
         </is>
       </c>
       <c r="B50">
-        <v>240.8029166666667</v>
+        <v>395.8517948717949</v>
       </c>
       <c r="C50">
-        <v>5.585642500000002</v>
+        <v>88.41334000000002</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E50">
-        <v>20.74166666666667</v>
+        <v>24.175</v>
       </c>
       <c r="F50">
-        <v>13.93916666666667</v>
+        <v>12.51833333333333</v>
       </c>
       <c r="G50">
-        <v>34.68083333333333</v>
+        <v>36.69333333333334</v>
       </c>
       <c r="H50">
-        <v>18.28368143833333</v>
+        <v>22.554342445</v>
       </c>
       <c r="I50">
-        <v>15.45937701166667</v>
+        <v>14.18910566833333</v>
       </c>
       <c r="J50">
-        <v>1.303480212</v>
+        <v>1.2398925705</v>
       </c>
       <c r="K50">
-        <v>33.74305845</v>
+        <v>36.74344811333333</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -4113,74 +3964,71 @@
         </is>
       </c>
       <c r="M50">
-        <v>1.079519997394771</v>
+        <v>0.8637637605319486</v>
       </c>
       <c r="N50">
-        <v>-6.800975983587056</v>
+        <v>-5.441711691351276</v>
       </c>
       <c r="O50">
-        <v>-12.12300957074328</v>
+        <v>-9.700067030773782</v>
       </c>
       <c r="P50">
-        <v>-21.59039994789542</v>
+        <v>-17.27527521063897</v>
       </c>
       <c r="Q50">
-        <v>0.09908966705229239</v>
+        <v>11.5</v>
       </c>
       <c r="R50">
-        <v>1.864406779661017</v>
+        <v>-1.620657555000001</v>
       </c>
       <c r="S50">
-        <v>-2.457985228333335</v>
+        <v>-215.1207342787013</v>
       </c>
       <c r="T50">
-        <v>-342.9972728285847</v>
+        <v>-77.22282768979022</v>
       </c>
       <c r="U50">
-        <v>-123.1272261435945</v>
+        <v>-296.3591490083606</v>
       </c>
       <c r="V50">
-        <v>-472.5271147316461</v>
-      </c>
-      <c r="W50">
-        <v>-349.5346398993279</v>
+        <v>-136.4074613094751</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B3A09</t>
+          <t>B3A11</t>
         </is>
       </c>
       <c r="B51">
-        <v>433.2290416666667</v>
+        <v>308.5635897435898</v>
       </c>
       <c r="C51">
-        <v>129.777326125</v>
+        <v>33.71135653846155</v>
       </c>
       <c r="D51">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E51">
-        <v>22.64479166666667</v>
+        <v>22.30166666666667</v>
       </c>
       <c r="F51">
-        <v>13.0525</v>
+        <v>13.18333333333333</v>
       </c>
       <c r="G51">
-        <v>35.69729166666666</v>
+        <v>35.485</v>
       </c>
       <c r="H51">
-        <v>22.554342445</v>
+        <v>21.7940397</v>
       </c>
       <c r="I51">
-        <v>14.18910566833333</v>
+        <v>13.728815925</v>
       </c>
       <c r="J51">
-        <v>1.2398925705</v>
+        <v>1.233803417166667</v>
       </c>
       <c r="K51">
-        <v>36.74344811333333</v>
+        <v>35.522855625</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -4188,74 +4036,71 @@
         </is>
       </c>
       <c r="M51">
-        <v>0.8097760221559134</v>
+        <v>1.268561254316011</v>
       </c>
       <c r="N51">
-        <v>-5.101588939582254</v>
+        <v>-7.991935902190866</v>
       </c>
       <c r="O51">
-        <v>-9.093784728810908</v>
+        <v>-14.2459428859688</v>
       </c>
       <c r="P51">
-        <v>-16.19552044311827</v>
+        <v>-25.37122508632021</v>
       </c>
       <c r="Q51">
-        <v>0.07432973600860122</v>
+        <v>3.254237288135593</v>
       </c>
       <c r="R51">
-        <v>11.5</v>
+        <v>-0.5076269666666668</v>
       </c>
       <c r="S51">
-        <v>-0.0904492216666668</v>
+        <v>-67.04981896849986</v>
       </c>
       <c r="T51">
-        <v>-12.00593112335219</v>
+        <v>-24.06916578356405</v>
       </c>
       <c r="U51">
-        <v>-4.30982142889566</v>
+        <v>-92.37058137280924</v>
       </c>
       <c r="V51">
-        <v>-16.53986326655043</v>
-      </c>
-      <c r="W51">
-        <v>108.6776102728369</v>
+        <v>-47.58440531600711</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B3A11</t>
+          <t>B3A12</t>
         </is>
       </c>
       <c r="B52">
-        <v>315.6002083333333</v>
+        <v>72.74282051282051</v>
       </c>
       <c r="C52">
-        <v>54.19418262500001</v>
+        <v>-117.7863165384615</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>22.11875</v>
+        <v>24.76</v>
       </c>
       <c r="F52">
-        <v>13.1175</v>
+        <v>14.07666666666667</v>
       </c>
       <c r="G52">
-        <v>35.23625</v>
+        <v>38.83666666666667</v>
       </c>
       <c r="H52">
-        <v>21.7940397</v>
+        <v>21.62069094333333</v>
       </c>
       <c r="I52">
-        <v>13.728815925</v>
+        <v>14.54494359833333</v>
       </c>
       <c r="J52">
-        <v>1.233803417166667</v>
+        <v>1.244754985333333</v>
       </c>
       <c r="K52">
-        <v>35.522855625</v>
+        <v>36.16563454166666</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -4263,74 +4108,71 @@
         </is>
       </c>
       <c r="M52">
-        <v>1.167208942651994</v>
+        <v>12.71122695655753</v>
       </c>
       <c r="N52">
-        <v>-7.353416338707563</v>
+        <v>-80.08072982631244</v>
       </c>
       <c r="O52">
-        <v>-13.10775642598189</v>
+        <v>-142.7470787221411</v>
       </c>
       <c r="P52">
-        <v>-23.34417885303988</v>
+        <v>-254.2245391311506</v>
       </c>
       <c r="Q52">
-        <v>0.1071386781041251</v>
+        <v>1</v>
       </c>
       <c r="R52">
-        <v>3.254237288135593</v>
+        <v>-3.139309056666665</v>
       </c>
       <c r="S52">
-        <v>-0.3247102999999996</v>
+        <v>-418.3356759532402</v>
       </c>
       <c r="T52">
-        <v>-42.8893030943009</v>
+        <v>-150.1717811114196</v>
       </c>
       <c r="U52">
-        <v>-15.39616008513365</v>
+        <v>-576.3163896824536</v>
       </c>
       <c r="V52">
-        <v>-59.0860635038615</v>
-      </c>
-      <c r="W52">
-        <v>-1.802876895282779</v>
+        <v>-678.8690712138427</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B3A12</t>
+          <t>B3A13</t>
         </is>
       </c>
       <c r="B53">
-        <v>137.2265833333333</v>
+        <v>323.8462820512821</v>
       </c>
       <c r="C53">
-        <v>-58.6701845</v>
+        <v>42.50846615384616</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E53">
-        <v>24.41</v>
+        <v>20.80333333333333</v>
       </c>
       <c r="F53">
-        <v>13.79666666666667</v>
+        <v>19.93166666666666</v>
       </c>
       <c r="G53">
-        <v>38.20666666666666</v>
+        <v>40.735</v>
       </c>
       <c r="H53">
-        <v>21.62069094333333</v>
+        <v>21.31049074166667</v>
       </c>
       <c r="I53">
-        <v>14.54494359833333</v>
+        <v>21.137494145</v>
       </c>
       <c r="J53">
-        <v>1.244754985333333</v>
+        <v>1.129676881</v>
       </c>
       <c r="K53">
-        <v>36.16563454166666</v>
+        <v>42.44798488666666</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -4338,74 +4180,71 @@
         </is>
       </c>
       <c r="M53">
-        <v>8.03801840660449</v>
+        <v>0.6924872803624826</v>
       </c>
       <c r="N53">
-        <v>-50.63951596160828</v>
+        <v>-4.362669866283641</v>
       </c>
       <c r="O53">
-        <v>-90.26694670616843</v>
+        <v>-7.77663215847068</v>
       </c>
       <c r="P53">
-        <v>-160.7603681320898</v>
+        <v>-13.84974560724965</v>
       </c>
       <c r="Q53">
-        <v>0.7378136297547152</v>
+        <v>3.033898305084746</v>
       </c>
       <c r="R53">
-        <v>1</v>
+        <v>0.507157408333331</v>
       </c>
       <c r="S53">
-        <v>-2.789309056666667</v>
+        <v>61.33437873671558</v>
       </c>
       <c r="T53">
-        <v>-371.6956402190395</v>
+        <v>22.01746929010303</v>
       </c>
       <c r="U53">
-        <v>-133.4292041811937</v>
+        <v>84.49675642990395</v>
       </c>
       <c r="V53">
-        <v>-512.0631630176551</v>
-      </c>
-      <c r="W53">
-        <v>-520.6327714252079</v>
+        <v>96.06621273209106</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B3A13</t>
+          <t>B3A14</t>
         </is>
       </c>
       <c r="B54">
-        <v>359.9379166666667</v>
+        <v>650.37</v>
       </c>
       <c r="C54">
-        <v>82.74101350000001</v>
+        <v>248.2846788461539</v>
       </c>
       <c r="D54">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="E54">
-        <v>20.43333333333333</v>
+        <v>20.26333333333333</v>
       </c>
       <c r="F54">
-        <v>18.50208333333333</v>
+        <v>18.00833333333333</v>
       </c>
       <c r="G54">
-        <v>38.93541666666667</v>
+        <v>38.27166666666666</v>
       </c>
       <c r="H54">
-        <v>21.31049074166667</v>
+        <v>20.86098047666666</v>
       </c>
       <c r="I54">
-        <v>21.137494145</v>
+        <v>19.11635910666667</v>
       </c>
       <c r="J54">
-        <v>1.129676881</v>
+        <v>1.151697198166667</v>
       </c>
       <c r="K54">
-        <v>42.44798488666666</v>
+        <v>39.97733958333333</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -4413,74 +4252,71 @@
         </is>
       </c>
       <c r="M54">
-        <v>1.145410111775375</v>
+        <v>0.8316001654117181</v>
       </c>
       <c r="N54">
-        <v>-7.216083704184863</v>
+        <v>-5.239081042093824</v>
       </c>
       <c r="O54">
-        <v>-12.86295555523746</v>
+        <v>-9.338869857573595</v>
       </c>
       <c r="P54">
-        <v>-22.9082022355075</v>
+        <v>-16.63200330823436</v>
       </c>
       <c r="Q54">
-        <v>0.1051377527864781</v>
+        <v>33.78947368421053</v>
       </c>
       <c r="R54">
-        <v>3.033898305084746</v>
+        <v>0.597647143333333</v>
       </c>
       <c r="S54">
-        <v>0.877157408333332</v>
+        <v>73.68687079994217</v>
       </c>
       <c r="T54">
-        <v>106.081275380034</v>
+        <v>26.45169721023565</v>
       </c>
       <c r="U54">
-        <v>38.08045782873017</v>
+        <v>101.5140562651101</v>
       </c>
       <c r="V54">
-        <v>146.1419170158582</v>
-      </c>
-      <c r="W54">
-        <v>175.9593333247966</v>
+        <v>312.6326797885224</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B3A14</t>
+          <t>B3A16</t>
         </is>
       </c>
       <c r="B55">
-        <v>697.1215833333333</v>
+        <v>455.2126923076923</v>
       </c>
       <c r="C55">
-        <v>288.03922475</v>
+        <v>129.6424426923077</v>
       </c>
       <c r="D55">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E55">
-        <v>19.25916666666667</v>
+        <v>18.29</v>
       </c>
       <c r="F55">
-        <v>17.47791666666667</v>
+        <v>20.22333333333333</v>
       </c>
       <c r="G55">
-        <v>36.73708333333333</v>
+        <v>38.51333333333334</v>
       </c>
       <c r="H55">
-        <v>20.86098047666666</v>
+        <v>20.22225977666667</v>
       </c>
       <c r="I55">
-        <v>19.11635910666667</v>
+        <v>20.56386172833333</v>
       </c>
       <c r="J55">
-        <v>1.151697198166667</v>
+        <v>1.129646918166667</v>
       </c>
       <c r="K55">
-        <v>39.97733958333333</v>
+        <v>40.786121505</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -4488,74 +4324,71 @@
         </is>
       </c>
       <c r="M55">
-        <v>1.825901354378047</v>
+        <v>1.781220700091808</v>
       </c>
       <c r="N55">
-        <v>-11.50317853258169</v>
+        <v>-11.22169041057839</v>
       </c>
       <c r="O55">
-        <v>-20.50487220966547</v>
+        <v>-20.003108462031</v>
       </c>
       <c r="P55">
-        <v>-36.51802708756094</v>
+        <v>-35.62441400183615</v>
       </c>
       <c r="Q55">
-        <v>0.1676003758265597</v>
+        <v>10.33898305084746</v>
       </c>
       <c r="R55">
-        <v>33.78947368421053</v>
+        <v>1.932259776666669</v>
       </c>
       <c r="S55">
-        <v>1.601813809999999</v>
+        <v>233.6765817151533</v>
       </c>
       <c r="T55">
-        <v>197.4955432811319</v>
+        <v>83.88390112851657</v>
       </c>
       <c r="U55">
-        <v>70.89583604963708</v>
+        <v>321.9224457023527</v>
       </c>
       <c r="V55">
-        <v>272.0779628053501</v>
-      </c>
-      <c r="W55">
-        <v>465.0298958214664</v>
+        <v>343.31591594543</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B3A16</t>
+          <t>B3A17</t>
         </is>
       </c>
       <c r="B56">
-        <v>548.5222083333333</v>
+        <v>29.9974358974359</v>
       </c>
       <c r="C56">
-        <v>198.782336125</v>
+        <v>-144.1901461538461</v>
       </c>
       <c r="D56">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>17.798875</v>
+        <v>20.10833333333333</v>
       </c>
       <c r="F56">
-        <v>19.7475</v>
+        <v>19.19833333333333</v>
       </c>
       <c r="G56">
-        <v>37.546375</v>
+        <v>39.30666666666667</v>
       </c>
       <c r="H56">
-        <v>20.22225977666667</v>
+        <v>17.13503540333333</v>
       </c>
       <c r="I56">
-        <v>20.56386172833333</v>
+        <v>20.508566085</v>
       </c>
       <c r="J56">
-        <v>1.129646918166667</v>
+        <v>1.366434788833333</v>
       </c>
       <c r="K56">
-        <v>40.786121505</v>
+        <v>37.64360148833333</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -4563,74 +4396,71 @@
         </is>
       </c>
       <c r="M56">
-        <v>1.626887657587317</v>
+        <v>2.244100031449752</v>
       </c>
       <c r="N56">
-        <v>-10.2493922428001</v>
+        <v>-14.13783019813344</v>
       </c>
       <c r="O56">
-        <v>-18.26994839470557</v>
+        <v>-25.20124335318072</v>
       </c>
       <c r="P56">
-        <v>-32.53775315174634</v>
+        <v>-44.88200062899504</v>
       </c>
       <c r="Q56">
-        <v>0.149332811537403</v>
+        <v>1</v>
       </c>
       <c r="R56">
-        <v>10.33898305084746</v>
+        <v>-2.973297930000001</v>
       </c>
       <c r="S56">
-        <v>2.423384776666669</v>
+        <v>-434.9449519907423</v>
       </c>
       <c r="T56">
-        <v>293.0704647637536</v>
+        <v>-156.13408533001</v>
       </c>
       <c r="U56">
-        <v>105.2047822228859</v>
+        <v>-599.1980097579128</v>
       </c>
       <c r="V56">
-        <v>403.7458956622296</v>
-      </c>
-      <c r="W56">
-        <v>473.5828524940481</v>
+        <v>-604.3363414977691</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B3A17</t>
+          <t>B3A19</t>
         </is>
       </c>
       <c r="B57">
-        <v>65.56358333333333</v>
+        <v>93.61538461538461</v>
       </c>
       <c r="C57">
-        <v>-101.43094625</v>
+        <v>-103.574325</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>19.804875</v>
+        <v>20.47166666666667</v>
       </c>
       <c r="F57">
-        <v>17.93291666666667</v>
+        <v>16.93</v>
       </c>
       <c r="G57">
-        <v>37.73779166666667</v>
+        <v>37.40166666666667</v>
       </c>
       <c r="H57">
-        <v>17.13503540333333</v>
+        <v>19.28397925833333</v>
       </c>
       <c r="I57">
-        <v>20.508566085</v>
+        <v>18.13899774833333</v>
       </c>
       <c r="J57">
-        <v>1.366434788833333</v>
+        <v>1.2727740835</v>
       </c>
       <c r="K57">
-        <v>37.64360148833333</v>
+        <v>37.42297700666667</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -4638,74 +4468,71 @@
         </is>
       </c>
       <c r="M57">
-        <v>3.404752088070881</v>
+        <v>2.35487853771158</v>
       </c>
       <c r="N57">
-        <v>-21.44993815484655</v>
+        <v>-14.83573478758296</v>
       </c>
       <c r="O57">
-        <v>-38.23536594903599</v>
+        <v>-26.44528597850105</v>
       </c>
       <c r="P57">
-        <v>-68.09504176141762</v>
+        <v>-47.09757075423161</v>
       </c>
       <c r="Q57">
-        <v>0.3125238546916566</v>
+        <v>1.983050847457627</v>
       </c>
       <c r="R57">
-        <v>1</v>
+        <v>-1.187687408333336</v>
       </c>
       <c r="S57">
-        <v>-2.669839596666666</v>
+        <v>-161.8305207073712</v>
       </c>
       <c r="T57">
-        <v>-390.5539513812413</v>
+        <v>-58.09300743341532</v>
       </c>
       <c r="U57">
-        <v>-140.198854341984</v>
+        <v>-222.9443645273242</v>
       </c>
       <c r="V57">
-        <v>-538.0431461490085</v>
-      </c>
-      <c r="W57">
-        <v>-530.2202635802773</v>
+        <v>-291.8501316858723</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B3A19</t>
+          <t>B3A20</t>
         </is>
       </c>
       <c r="B58">
-        <v>144.3691666666667</v>
+        <v>391.1703846153846</v>
       </c>
       <c r="C58">
-        <v>-54.22052875</v>
+        <v>85.34052692307694</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E58">
-        <v>20.23708333333333</v>
+        <v>21.13833333333333</v>
       </c>
       <c r="F58">
-        <v>17.31333333333333</v>
+        <v>15.39666666666667</v>
       </c>
       <c r="G58">
-        <v>37.55041666666666</v>
+        <v>36.535</v>
       </c>
       <c r="H58">
-        <v>19.28397925833333</v>
+        <v>18.90949340833333</v>
       </c>
       <c r="I58">
-        <v>18.13899774833333</v>
+        <v>16.265840325</v>
       </c>
       <c r="J58">
-        <v>1.2727740835</v>
+        <v>1.302041297333333</v>
       </c>
       <c r="K58">
-        <v>37.42297700666667</v>
+        <v>35.17533373333333</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -4713,74 +4540,71 @@
         </is>
       </c>
       <c r="M58">
-        <v>1.702722532239643</v>
+        <v>5.768294627152565</v>
       </c>
       <c r="N58">
-        <v>-10.72715195310975</v>
+        <v>-36.34025615106115</v>
       </c>
       <c r="O58">
-        <v>-19.12157403705119</v>
+        <v>-64.77794866292331</v>
       </c>
       <c r="P58">
-        <v>-34.05445064479287</v>
+        <v>-115.3658925430513</v>
       </c>
       <c r="Q58">
-        <v>0.1562937316670774</v>
+        <v>5.186440677966102</v>
       </c>
       <c r="R58">
-        <v>1.983050847457627</v>
+        <v>-2.228839924999999</v>
       </c>
       <c r="S58">
-        <v>-0.9531040750000024</v>
+        <v>-310.6780664315124</v>
       </c>
       <c r="T58">
-        <v>-129.8669394516966</v>
+        <v>-111.5254597446455</v>
       </c>
       <c r="U58">
-        <v>-46.6189013416347</v>
+        <v>-428.0028500828794</v>
       </c>
       <c r="V58">
-        <v>-178.9100236630963</v>
-      </c>
-      <c r="W58">
-        <v>-203.2090422387478</v>
+        <v>-290.1154881713587</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B3A20</t>
+          <t>B3A21</t>
         </is>
       </c>
       <c r="B59">
-        <v>485.0668333333334</v>
+        <v>186.5998717948718</v>
       </c>
       <c r="C59">
-        <v>162.921749</v>
+        <v>-46.6601523076923</v>
       </c>
       <c r="D59">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E59">
-        <v>20.38291666666667</v>
+        <v>21.78166666666667</v>
       </c>
       <c r="F59">
-        <v>15.71083333333333</v>
+        <v>15.13833333333333</v>
       </c>
       <c r="G59">
-        <v>36.09375</v>
+        <v>36.92</v>
       </c>
       <c r="H59">
-        <v>18.90949340833333</v>
+        <v>20.00068769833333</v>
       </c>
       <c r="I59">
-        <v>16.265840325</v>
+        <v>15.62423430166667</v>
       </c>
       <c r="J59">
-        <v>1.302041297333333</v>
+        <v>1.2796586495</v>
       </c>
       <c r="K59">
-        <v>35.17533373333333</v>
+        <v>35.624922</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -4788,74 +4612,71 @@
         </is>
       </c>
       <c r="M59">
-        <v>3.520144908087444</v>
+        <v>4.634270652459132</v>
       </c>
       <c r="N59">
-        <v>-22.1769129209509</v>
+        <v>-29.19590511049253</v>
       </c>
       <c r="O59">
-        <v>-39.531227317822</v>
+        <v>-52.04285942711606</v>
       </c>
       <c r="P59">
-        <v>-70.40289816174888</v>
+        <v>-92.68541304918264</v>
       </c>
       <c r="Q59">
-        <v>0.3231158179190732</v>
+        <v>1.983050847457627</v>
       </c>
       <c r="R59">
-        <v>5.186440677966102</v>
+        <v>-1.780978968333333</v>
       </c>
       <c r="S59">
-        <v>-1.473423258333334</v>
+        <v>-243.9831776131483</v>
       </c>
       <c r="T59">
-        <v>-205.3805137819482</v>
+        <v>-87.58370478420707</v>
       </c>
       <c r="U59">
-        <v>-73.72633828069937</v>
+        <v>-336.1212350461341</v>
       </c>
       <c r="V59">
-        <v>-282.940621653244</v>
-      </c>
-      <c r="W59">
-        <v>-81.98999209977021</v>
+        <v>-342.6861893479567</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B3A21</t>
+          <t>B3A22</t>
         </is>
       </c>
       <c r="B60">
-        <v>239.5789583333333</v>
+        <v>364.2266794871795</v>
       </c>
       <c r="C60">
-        <v>5.746882124999997</v>
+        <v>68.57861250000001</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E60">
-        <v>21.39791666666667</v>
+        <v>22.76</v>
       </c>
       <c r="F60">
-        <v>15.08041666666667</v>
+        <v>14.44666666666667</v>
       </c>
       <c r="G60">
-        <v>36.47833333333333</v>
+        <v>37.20666666666666</v>
       </c>
       <c r="H60">
-        <v>20.00068769833333</v>
+        <v>22.56712392</v>
       </c>
       <c r="I60">
-        <v>15.62423430166667</v>
+        <v>15.705884195</v>
       </c>
       <c r="J60">
-        <v>1.2796586495</v>
+        <v>1.212829627166667</v>
       </c>
       <c r="K60">
-        <v>35.624922</v>
+        <v>38.273008115</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -4863,74 +4684,71 @@
         </is>
       </c>
       <c r="M60">
-        <v>7.967395770673756</v>
+        <v>0.8158122852628428</v>
       </c>
       <c r="N60">
-        <v>-50.19459335524466</v>
+        <v>-5.139617397155909</v>
       </c>
       <c r="O60">
-        <v>-89.47385450466628</v>
+        <v>-9.161571963501725</v>
       </c>
       <c r="P60">
-        <v>-159.3479154134751</v>
+        <v>-16.31624570525685</v>
       </c>
       <c r="Q60">
-        <v>0.7313311435593506</v>
+        <v>12.3</v>
       </c>
       <c r="R60">
-        <v>1.983050847457627</v>
+        <v>-0.1928760799999978</v>
       </c>
       <c r="S60">
-        <v>-1.397228968333334</v>
+        <v>-25.04292910927768</v>
       </c>
       <c r="T60">
-        <v>-191.4117850959955</v>
+        <v>-8.989769423843269</v>
       </c>
       <c r="U60">
-        <v>-68.71192285497274</v>
+        <v>-34.5001665431608</v>
       </c>
       <c r="V60">
-        <v>-263.6967279394268</v>
-      </c>
-      <c r="W60">
-        <v>-275.1387574756617</v>
+        <v>34.3741114272206</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B3A22</t>
+          <t>B3A23</t>
         </is>
       </c>
       <c r="B61">
-        <v>560.2451333333333</v>
+        <v>301.3658974358974</v>
       </c>
       <c r="C61">
-        <v>208.12820525</v>
+        <v>28.47471153846155</v>
       </c>
       <c r="D61">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E61">
-        <v>21.87833333333333</v>
+        <v>23.685</v>
       </c>
       <c r="F61">
-        <v>14.63</v>
+        <v>13.57833333333333</v>
       </c>
       <c r="G61">
-        <v>36.50833333333333</v>
+        <v>37.26333333333334</v>
       </c>
       <c r="H61">
-        <v>22.56712392</v>
+        <v>22.54396694333333</v>
       </c>
       <c r="I61">
-        <v>15.705884195</v>
+        <v>14.29265470833333</v>
       </c>
       <c r="J61">
-        <v>1.212829627166667</v>
+        <v>1.219427313833333</v>
       </c>
       <c r="K61">
-        <v>38.273008115</v>
+        <v>36.83662165166667</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -4938,74 +4756,71 @@
         </is>
       </c>
       <c r="M61">
-        <v>1.70503530389312</v>
+        <v>1.222969348145958</v>
       </c>
       <c r="N61">
-        <v>-10.74172241452666</v>
+        <v>-7.704706893319538</v>
       </c>
       <c r="O61">
-        <v>-19.14754646271974</v>
+        <v>-13.73394577967911</v>
       </c>
       <c r="P61">
-        <v>-34.1007060778624</v>
+        <v>-24.45938696291917</v>
       </c>
       <c r="Q61">
-        <v>0.1565060221051092</v>
+        <v>3.416666666666667</v>
       </c>
       <c r="R61">
-        <v>12.3</v>
+        <v>-1.141033056666664</v>
       </c>
       <c r="S61">
-        <v>0.6887905866666664</v>
+        <v>-148.95706303375</v>
       </c>
       <c r="T61">
-        <v>89.43220866491743</v>
+        <v>-53.4717662172436</v>
       </c>
       <c r="U61">
-        <v>32.10386977714985</v>
+        <v>-205.2093610942903</v>
       </c>
       <c r="V61">
-        <v>123.2054796704791</v>
-      </c>
-      <c r="W61">
-        <v>278.4128674521977</v>
+        <v>-134.2162972749676</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B3A23</t>
+          <t>B3A24</t>
         </is>
       </c>
       <c r="B62">
-        <v>355.4359583333333</v>
+        <v>512.3392307692308</v>
       </c>
       <c r="C62">
-        <v>78.94472812500001</v>
+        <v>161.7195269230769</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E62">
-        <v>22.65791666666667</v>
+        <v>27.32166666666667</v>
       </c>
       <c r="F62">
-        <v>13.62291666666667</v>
+        <v>16.22333333333333</v>
       </c>
       <c r="G62">
-        <v>36.28083333333333</v>
+        <v>43.545</v>
       </c>
       <c r="H62">
-        <v>22.54396694333333</v>
+        <v>26.54552809833334</v>
       </c>
       <c r="I62">
-        <v>14.29265470833333</v>
+        <v>16.41767707333333</v>
       </c>
       <c r="J62">
-        <v>1.219427313833333</v>
+        <v>1.198807591833333</v>
       </c>
       <c r="K62">
-        <v>36.83662165166667</v>
+        <v>42.96320517166667</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -5013,149 +4828,143 @@
         </is>
       </c>
       <c r="M62">
-        <v>1.189745895568634</v>
+        <v>0.8783340032070126</v>
       </c>
       <c r="N62">
-        <v>-7.495399142082394</v>
+        <v>-5.533504220204179</v>
       </c>
       <c r="O62">
-        <v>-13.36084640723576</v>
+        <v>-9.863690856014752</v>
       </c>
       <c r="P62">
-        <v>-23.79491791137268</v>
+        <v>-17.56668006414025</v>
       </c>
       <c r="Q62">
-        <v>0.1092073560038142</v>
+        <v>11.28813559322034</v>
       </c>
       <c r="R62">
-        <v>3.416666666666667</v>
+        <v>-0.7761385683333302</v>
       </c>
       <c r="S62">
-        <v>-0.1139497233333309</v>
+        <v>-99.6083407039354</v>
       </c>
       <c r="T62">
-        <v>-14.87565677617343</v>
+        <v>-35.75684025269476</v>
       </c>
       <c r="U62">
-        <v>-5.339979355549435</v>
+        <v>-137.2245366497703</v>
       </c>
       <c r="V62">
-        <v>-20.49331505821143</v>
-      </c>
-      <c r="W62">
-        <v>50.70822494159083</v>
+        <v>52.24749536312677</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B3A24</t>
+          <t>B4A01</t>
         </is>
       </c>
       <c r="B63">
-        <v>568.57375</v>
+        <v>615.7452564102564</v>
       </c>
       <c r="C63">
-        <v>212.94360675</v>
+        <v>224.0909588461539</v>
       </c>
       <c r="D63">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E63">
-        <v>26.11791666666667</v>
+        <v>19.25833333333333</v>
       </c>
       <c r="F63">
-        <v>15.86166666666667</v>
+        <v>33.035</v>
       </c>
       <c r="G63">
-        <v>41.97958333333333</v>
+        <v>52.29333333333333</v>
       </c>
       <c r="H63">
-        <v>26.54552809833334</v>
+        <v>21.01716598833333</v>
       </c>
       <c r="I63">
-        <v>16.41767707333333</v>
+        <v>33.50714061833333</v>
       </c>
       <c r="J63">
-        <v>1.198807591833333</v>
+        <v>1.283039363</v>
       </c>
       <c r="K63">
-        <v>42.96320517166667</v>
+        <v>54.52430660666666</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="M63">
-        <v>1.938789752776512</v>
+        <v>1.533643868174295</v>
       </c>
       <c r="N63">
-        <v>-12.21437544249203</v>
+        <v>-9.661956369498061</v>
       </c>
       <c r="O63">
-        <v>-21.77260892368023</v>
+        <v>-17.22282063959734</v>
       </c>
       <c r="P63">
-        <v>-38.77579505553024</v>
+        <v>-30.67287736348591</v>
       </c>
       <c r="Q63">
-        <v>0.1779624569722227</v>
+        <v>34.94915254237288</v>
       </c>
       <c r="R63">
-        <v>11.28813559322034</v>
+        <v>1.758832654999999</v>
       </c>
       <c r="S63">
-        <v>0.4276114316666693</v>
+        <v>241.5858294686546</v>
       </c>
       <c r="T63">
-        <v>54.87894418881447</v>
+        <v>86.72311827079908</v>
       </c>
       <c r="U63">
-        <v>19.70013381136929</v>
+        <v>332.8185498895352</v>
       </c>
       <c r="V63">
-        <v>75.60348495837495</v>
-      </c>
-      <c r="W63">
-        <v>246.0499420151342</v>
+        <v>448.4539676752112</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B4A01</t>
+          <t>B4A02</t>
         </is>
       </c>
       <c r="B64">
-        <v>691.7772916666667</v>
+        <v>306.6930933333333</v>
       </c>
       <c r="C64">
-        <v>283.69190175</v>
+        <v>31.12535130307694</v>
       </c>
       <c r="D64">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E64">
-        <v>19.63625</v>
+        <v>19.835</v>
       </c>
       <c r="F64">
-        <v>32.46708333333333</v>
+        <v>31.02333333333333</v>
       </c>
       <c r="G64">
-        <v>52.10333333333334</v>
+        <v>50.85833333333333</v>
       </c>
       <c r="H64">
-        <v>21.01716598833333</v>
+        <v>22.511840975</v>
       </c>
       <c r="I64">
-        <v>33.50714061833333</v>
+        <v>31.46513772166666</v>
       </c>
       <c r="J64">
-        <v>1.283039363</v>
+        <v>1.214772208</v>
       </c>
       <c r="K64">
-        <v>54.52430660666666</v>
+        <v>53.97697869666666</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -5163,74 +4972,71 @@
         </is>
       </c>
       <c r="M64">
-        <v>1.488076964966721</v>
+        <v>0.6617605719075088</v>
       </c>
       <c r="N64">
-        <v>-9.374884879290342</v>
+        <v>-4.169091603017305</v>
       </c>
       <c r="O64">
-        <v>-16.71110431657628</v>
+        <v>-7.431571222521324</v>
       </c>
       <c r="P64">
-        <v>-29.76153929933442</v>
+        <v>-13.23521143815018</v>
       </c>
       <c r="Q64">
-        <v>0.1365913103625591</v>
+        <v>13</v>
       </c>
       <c r="R64">
-        <v>34.94915254237288</v>
+        <v>2.676840974999998</v>
       </c>
       <c r="S64">
-        <v>1.380915988333332</v>
+        <v>348.116312679413</v>
       </c>
       <c r="T64">
-        <v>189.6767913193169</v>
+        <v>124.9648301926098</v>
       </c>
       <c r="U64">
-        <v>68.08910457616503</v>
+        <v>479.5793140420384</v>
       </c>
       <c r="V64">
-        <v>261.3065293334424</v>
-      </c>
-      <c r="W64">
-        <v>456.6575887527406</v>
+        <v>371.8100927599686</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B4A02</t>
+          <t>B4A04</t>
         </is>
       </c>
       <c r="B65">
-        <v>313.8654273333333</v>
+        <v>284.9810256410257</v>
       </c>
       <c r="C65">
-        <v>51.87944034700001</v>
+        <v>16.29308269230771</v>
       </c>
       <c r="D65">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E65">
-        <v>19.760625</v>
+        <v>15.49333333333333</v>
       </c>
       <c r="F65">
-        <v>31.003125</v>
+        <v>34.9</v>
       </c>
       <c r="G65">
-        <v>50.76375</v>
+        <v>50.39333333333333</v>
       </c>
       <c r="H65">
-        <v>22.511840975</v>
+        <v>14.43724686483333</v>
       </c>
       <c r="I65">
-        <v>31.46513772166666</v>
+        <v>31.33856732333333</v>
       </c>
       <c r="J65">
-        <v>1.214772208</v>
+        <v>1.2871362685</v>
       </c>
       <c r="K65">
-        <v>53.97697869666666</v>
+        <v>45.77581418816666</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -5238,74 +5044,71 @@
         </is>
       </c>
       <c r="M65">
-        <v>0.7219950451524363</v>
+        <v>5.37547026623286</v>
       </c>
       <c r="N65">
-        <v>-4.548568784460349</v>
+        <v>-33.86546267726702</v>
       </c>
       <c r="O65">
-        <v>-8.10800435706186</v>
+        <v>-60.36653108979502</v>
       </c>
       <c r="P65">
-        <v>-14.43990090304873</v>
+        <v>-107.5094053246572</v>
       </c>
       <c r="Q65">
-        <v>0.06627227731789516</v>
+        <v>2.95</v>
       </c>
       <c r="R65">
-        <v>13</v>
+        <v>-1.056086468499998</v>
       </c>
       <c r="S65">
-        <v>2.751215974999997</v>
+        <v>-145.5227729975874</v>
       </c>
       <c r="T65">
-        <v>357.7885909347663</v>
+        <v>-52.23894415298008</v>
       </c>
       <c r="U65">
-        <v>128.4369300791469</v>
+        <v>-200.4781422465224</v>
       </c>
       <c r="V65">
-        <v>492.9042413780288</v>
-      </c>
-      <c r="W65">
-        <v>401.5600269247045</v>
+        <v>-189.5962213950747</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B4A03</t>
+          <t>B4A06</t>
         </is>
       </c>
       <c r="B66">
-        <v>4.230416666666667</v>
+        <v>148.8394871794872</v>
       </c>
       <c r="C66">
-        <v>-109.7816945833333</v>
+        <v>-68.81190769230768</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E66">
-        <v>18.14708333333333</v>
+        <v>18.8</v>
       </c>
       <c r="F66">
-        <v>31.89083333333333</v>
+        <v>34.15166666666666</v>
       </c>
       <c r="G66">
-        <v>50.03791666666667</v>
+        <v>52.95166666666667</v>
       </c>
       <c r="H66">
-        <v>18.58497426683333</v>
+        <v>19.296109655</v>
       </c>
       <c r="I66">
-        <v>32.96422325833333</v>
+        <v>34.73453828666666</v>
       </c>
       <c r="J66">
-        <v>1.297272432333333</v>
+        <v>1.330423571833333</v>
       </c>
       <c r="K66">
-        <v>51.54919752516667</v>
+        <v>54.03064794166666</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -5313,74 +5116,71 @@
         </is>
       </c>
       <c r="M66">
-        <v>1.292398706065661</v>
+        <v>1.782545232434082</v>
       </c>
       <c r="N66">
-        <v>-8.142111848213665</v>
+        <v>-11.23003496433472</v>
       </c>
       <c r="O66">
-        <v>-14.51363746911737</v>
+        <v>-20.01798296023475</v>
       </c>
       <c r="P66">
-        <v>-25.84797412131322</v>
+        <v>-35.65090464868165</v>
       </c>
       <c r="Q66">
-        <v>0.1186299075440176</v>
+        <v>7.689655172413793</v>
       </c>
       <c r="R66">
-        <v>0.8571428571428571</v>
+        <v>0.4961096549999979</v>
       </c>
       <c r="S66">
-        <v>0.4378909335000003</v>
+        <v>70.66015175605011</v>
       </c>
       <c r="T66">
-        <v>60.81407400561564</v>
+        <v>25.36518268165901</v>
       </c>
       <c r="U66">
-        <v>21.83069323278511</v>
+        <v>97.34432393715539</v>
       </c>
       <c r="V66">
-        <v>83.77996328650558</v>
-      </c>
-      <c r="W66">
-        <v>-63.48125804683507</v>
+        <v>-18.16973889649232</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B4A04</t>
+          <t>B4A07</t>
         </is>
       </c>
       <c r="B67">
-        <v>291.6330833333333</v>
+        <v>70.61499999999999</v>
       </c>
       <c r="C67">
-        <v>38.45892475000001</v>
+        <v>-118.7168665384615</v>
       </c>
       <c r="D67">
         <v>4</v>
       </c>
       <c r="E67">
-        <v>16.41916666666667</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="F67">
-        <v>30.875</v>
+        <v>33.49</v>
       </c>
       <c r="G67">
-        <v>47.29416666666667</v>
+        <v>52.65666666666667</v>
       </c>
       <c r="H67">
-        <v>14.43724686483333</v>
+        <v>16.57419823166667</v>
       </c>
       <c r="I67">
-        <v>31.33856732333333</v>
+        <v>35.08676949833333</v>
       </c>
       <c r="J67">
-        <v>1.2871362685</v>
+        <v>1.348954807166667</v>
       </c>
       <c r="K67">
-        <v>45.77581418816666</v>
+        <v>51.66096773</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -5388,74 +5188,71 @@
         </is>
       </c>
       <c r="M67">
-        <v>4.543539835776487</v>
+        <v>6.470060526093794</v>
       </c>
       <c r="N67">
-        <v>-28.62430096539187</v>
+        <v>-40.7613813143909</v>
       </c>
       <c r="O67">
-        <v>-51.02395235576995</v>
+        <v>-72.65877970803331</v>
       </c>
       <c r="P67">
-        <v>-90.87079671552974</v>
+        <v>-129.4012105218759</v>
       </c>
       <c r="Q67">
-        <v>0.4170537374503852</v>
+        <v>2.694915254237288</v>
       </c>
       <c r="R67">
-        <v>2.95</v>
+        <v>-2.592468435000001</v>
       </c>
       <c r="S67">
-        <v>-1.981919801833332</v>
+        <v>-374.3844768385374</v>
       </c>
       <c r="T67">
-        <v>-273.0973968743884</v>
+        <v>-134.3944275830647</v>
       </c>
       <c r="U67">
-        <v>-98.03496298054968</v>
+        <v>-515.7674146559214</v>
       </c>
       <c r="V67">
-        <v>-376.2301779299266</v>
-      </c>
-      <c r="W67">
-        <v>-285.6624244801583</v>
+        <v>-565.7601230850322</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B4A06</t>
+          <t>B4A08</t>
         </is>
       </c>
       <c r="B68">
-        <v>153.0529166666667</v>
+        <v>156.2683333333333</v>
       </c>
       <c r="C68">
-        <v>-50.0267925</v>
+        <v>-64.15647461538461</v>
       </c>
       <c r="D68">
         <v>8</v>
       </c>
       <c r="E68">
-        <v>17.9275</v>
+        <v>15.65333333333333</v>
       </c>
       <c r="F68">
-        <v>34.89541666666667</v>
+        <v>30.44833333333333</v>
       </c>
       <c r="G68">
-        <v>52.82291666666667</v>
+        <v>46.10166666666667</v>
       </c>
       <c r="H68">
-        <v>19.296109655</v>
+        <v>14.94356254216667</v>
       </c>
       <c r="I68">
-        <v>34.73453828666666</v>
+        <v>31.67317683666667</v>
       </c>
       <c r="J68">
-        <v>1.330423571833333</v>
+        <v>1.300956109</v>
       </c>
       <c r="K68">
-        <v>54.03064794166666</v>
+        <v>46.61673937883333</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -5463,74 +5260,71 @@
         </is>
       </c>
       <c r="M68">
-        <v>1.719547623997414</v>
+        <v>1.667006999653265</v>
       </c>
       <c r="N68">
-        <v>-10.83315003118371</v>
+        <v>-10.50214409781557</v>
       </c>
       <c r="O68">
-        <v>-19.31051981749096</v>
+        <v>-18.72048860610616</v>
       </c>
       <c r="P68">
-        <v>-34.39095247994828</v>
+        <v>-33.34013999306529</v>
       </c>
       <c r="Q68">
-        <v>0.1578381150452689</v>
+        <v>6.677966101694915</v>
       </c>
       <c r="R68">
-        <v>7.689655172413793</v>
+        <v>-0.7097707911666653</v>
       </c>
       <c r="S68">
-        <v>1.368609655</v>
+        <v>-98.85251513868158</v>
       </c>
       <c r="T68">
-        <v>194.9290140646342</v>
+        <v>-35.48551825491133</v>
       </c>
       <c r="U68">
-        <v>69.97451786935588</v>
+        <v>-136.1832803428483</v>
       </c>
       <c r="V68">
-        <v>268.5422068631966</v>
-      </c>
-      <c r="W68">
-        <v>125.5917017471432</v>
+        <v>-181.7294783601724</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B4A07</t>
+          <t>B4A09</t>
         </is>
       </c>
       <c r="B69">
-        <v>184.1729583333333</v>
+        <v>41.35012820512821</v>
       </c>
       <c r="C69">
-        <v>-34.340969125</v>
+        <v>-137.2941396153846</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E69">
-        <v>17.80166666666667</v>
+        <v>15.57166666666667</v>
       </c>
       <c r="F69">
-        <v>34.07583333333334</v>
+        <v>36.22166666666666</v>
       </c>
       <c r="G69">
-        <v>51.8775</v>
+        <v>51.79333333333333</v>
       </c>
       <c r="H69">
-        <v>16.57419823166667</v>
+        <v>13.13788787916667</v>
       </c>
       <c r="I69">
-        <v>35.08676949833333</v>
+        <v>37.97236331166667</v>
       </c>
       <c r="J69">
-        <v>1.348954807166667</v>
+        <v>1.306180608666667</v>
       </c>
       <c r="K69">
-        <v>51.66096773</v>
+        <v>51.11025119083334</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -5538,74 +5332,71 @@
         </is>
       </c>
       <c r="M69">
-        <v>6.244953306955439</v>
+        <v>7.426832498544667</v>
       </c>
       <c r="N69">
-        <v>-39.34320583381926</v>
+        <v>-46.7890447408314</v>
       </c>
       <c r="O69">
-        <v>-70.13082563710958</v>
+        <v>-83.40332895865662</v>
       </c>
       <c r="P69">
-        <v>-124.8990661391088</v>
+        <v>-148.5366499708933</v>
       </c>
       <c r="Q69">
-        <v>0.5732273097642612</v>
+        <v>1</v>
       </c>
       <c r="R69">
-        <v>2.694915254237288</v>
+        <v>-2.4337787875</v>
       </c>
       <c r="S69">
-        <v>-1.227468434999999</v>
+        <v>-340.3229909139855</v>
       </c>
       <c r="T69">
-        <v>-177.2616096956616</v>
+        <v>-122.1672275075845</v>
       </c>
       <c r="U69">
-        <v>-63.63237271126314</v>
+        <v>-468.8429142519643</v>
       </c>
       <c r="V69">
-        <v>-244.2028657879104</v>
-      </c>
-      <c r="W69">
-        <v>-281.7334044577712</v>
+        <v>-561.0204594880267</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B4A08</t>
+          <t>B4A10</t>
         </is>
       </c>
       <c r="B70">
-        <v>166.536875</v>
+        <v>350.2982051282052</v>
       </c>
       <c r="C70">
-        <v>-40.806530875</v>
+        <v>60.63239038461541</v>
       </c>
       <c r="D70">
         <v>8</v>
       </c>
       <c r="E70">
-        <v>15.09916666666667</v>
+        <v>17.41666666666667</v>
       </c>
       <c r="F70">
-        <v>30.76541666666667</v>
+        <v>36.48333333333333</v>
       </c>
       <c r="G70">
-        <v>45.86458333333334</v>
+        <v>53.90000000000001</v>
       </c>
       <c r="H70">
-        <v>14.94356254216667</v>
+        <v>18.117422885</v>
       </c>
       <c r="I70">
-        <v>31.67317683666667</v>
+        <v>37.46903936833333</v>
       </c>
       <c r="J70">
-        <v>1.300956109</v>
+        <v>1.244072557</v>
       </c>
       <c r="K70">
-        <v>46.61673937883333</v>
+        <v>55.58646225333334</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -5613,74 +5404,71 @@
         </is>
       </c>
       <c r="M70">
-        <v>1.565465264178534</v>
+        <v>0.7836703974105198</v>
       </c>
       <c r="N70">
-        <v>-9.862431164324764</v>
+        <v>-4.937123503686275</v>
       </c>
       <c r="O70">
-        <v>-17.58017491672494</v>
+        <v>-8.800618562920137</v>
       </c>
       <c r="P70">
-        <v>-31.30930528357068</v>
+        <v>-15.6734079482104</v>
       </c>
       <c r="Q70">
-        <v>0.1436948200901677</v>
+        <v>6.610169491525424</v>
       </c>
       <c r="R70">
-        <v>6.677966101694915</v>
+        <v>0.700756218333332</v>
       </c>
       <c r="S70">
-        <v>-0.1556041244999999</v>
+        <v>93.32964763710972</v>
       </c>
       <c r="T70">
-        <v>-21.67158646736371</v>
+        <v>33.50295043383426</v>
       </c>
       <c r="U70">
-        <v>-7.779543860079281</v>
+        <v>128.5747514935034</v>
       </c>
       <c r="V70">
-        <v>-29.85566660816712</v>
-      </c>
-      <c r="W70">
-        <v>-80.05829225908866</v>
+        <v>145.161419458805</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B4A09</t>
+          <t>B4A11</t>
         </is>
       </c>
       <c r="B71">
-        <v>113.1500833333333</v>
+        <v>350.0344871794872</v>
       </c>
       <c r="C71">
-        <v>-72.91074575</v>
+        <v>59.12839692307695</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E71">
-        <v>14.93541666666667</v>
+        <v>16.605</v>
       </c>
       <c r="F71">
-        <v>36.75625</v>
+        <v>35.695</v>
       </c>
       <c r="G71">
-        <v>51.69166666666667</v>
+        <v>52.3</v>
       </c>
       <c r="H71">
-        <v>13.13788787916667</v>
+        <v>15.29936591116667</v>
       </c>
       <c r="I71">
-        <v>37.97236331166667</v>
+        <v>37.28644950833333</v>
       </c>
       <c r="J71">
-        <v>1.306180608666667</v>
+        <v>1.253556855166667</v>
       </c>
       <c r="K71">
-        <v>51.11025119083334</v>
+        <v>52.5858154195</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -5688,74 +5476,71 @@
         </is>
       </c>
       <c r="M71">
-        <v>6.692488984265891</v>
+        <v>4.916436510502518</v>
       </c>
       <c r="N71">
-        <v>-42.16268060087511</v>
+        <v>-30.97355001616586</v>
       </c>
       <c r="O71">
-        <v>-75.15665129330596</v>
+        <v>-55.21158201294327</v>
       </c>
       <c r="P71">
-        <v>-133.8497796853178</v>
+        <v>-98.32873021005035</v>
       </c>
       <c r="Q71">
-        <v>0.6143068278516856</v>
+        <v>3.779661016949153</v>
       </c>
       <c r="R71">
-        <v>1</v>
+        <v>-1.305634088833333</v>
       </c>
       <c r="S71">
-        <v>-1.797528787499999</v>
+        <v>-175.2154799373369</v>
       </c>
       <c r="T71">
-        <v>-251.3541396440451</v>
+        <v>-62.89786459289017</v>
       </c>
       <c r="U71">
-        <v>-90.2296911542726</v>
+        <v>-241.3840334890573</v>
       </c>
       <c r="V71">
-        <v>-346.2757747383399</v>
-      </c>
-      <c r="W71">
-        <v>-399.4215366873511</v>
+        <v>-171.2986650272032</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B4A10</t>
+          <t>B4A12</t>
         </is>
       </c>
       <c r="B72">
-        <v>310.4554166666667</v>
+        <v>19.21935897435898</v>
       </c>
       <c r="C72">
-        <v>51.92640025000001</v>
+        <v>-151.0551219230769</v>
       </c>
       <c r="D72">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>16.81333333333333</v>
+        <v>15.13166666666667</v>
       </c>
       <c r="F72">
-        <v>36.655</v>
+        <v>32.21666666666667</v>
       </c>
       <c r="G72">
-        <v>53.46833333333333</v>
+        <v>47.34833333333334</v>
       </c>
       <c r="H72">
-        <v>18.117422885</v>
+        <v>13.49411681</v>
       </c>
       <c r="I72">
-        <v>37.46903936833333</v>
+        <v>33.50838837833333</v>
       </c>
       <c r="J72">
-        <v>1.244072557</v>
+        <v>1.384350912</v>
       </c>
       <c r="K72">
-        <v>55.58646225333334</v>
+        <v>47.00250518833333</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -5763,74 +5548,71 @@
         </is>
       </c>
       <c r="M72">
-        <v>0.9113912774758922</v>
+        <v>1.409321096780074</v>
       </c>
       <c r="N72">
-        <v>-5.741765048098121</v>
+        <v>-8.878722909714469</v>
       </c>
       <c r="O72">
-        <v>-10.23492404605427</v>
+        <v>-15.82667591684024</v>
       </c>
       <c r="P72">
-        <v>-18.22782554951785</v>
+        <v>-28.18642193560149</v>
       </c>
       <c r="Q72">
-        <v>0.08365704985307856</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="R72">
-        <v>6.610169491525424</v>
+        <v>-1.637549856666668</v>
       </c>
       <c r="S72">
-        <v>1.304089551666667</v>
+        <v>-242.6876511149146</v>
       </c>
       <c r="T72">
-        <v>173.6841074828564</v>
+        <v>-87.11864398996934</v>
       </c>
       <c r="U72">
-        <v>62.34814114769206</v>
+        <v>-334.3364645923623</v>
       </c>
       <c r="V72">
-        <v>239.2743519702285</v>
-      </c>
-      <c r="W72">
-        <v>215.3755836868022</v>
+        <v>-409.5694489548317</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B4A11</t>
+          <t>B4A13</t>
         </is>
       </c>
       <c r="B73">
-        <v>410.664875</v>
+        <v>98.38858974358973</v>
       </c>
       <c r="C73">
-        <v>112.024265875</v>
+        <v>-102.6289638461538</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>16.55708333333333</v>
+        <v>14.97166666666667</v>
       </c>
       <c r="F73">
-        <v>35.41041666666666</v>
+        <v>37.80333333333333</v>
       </c>
       <c r="G73">
-        <v>51.9675</v>
+        <v>52.77500000000001</v>
       </c>
       <c r="H73">
-        <v>15.29936591116667</v>
+        <v>13.57363288</v>
       </c>
       <c r="I73">
-        <v>37.28644950833333</v>
+        <v>38.47788508666667</v>
       </c>
       <c r="J73">
-        <v>1.253556855166667</v>
+        <v>1.3118625675</v>
       </c>
       <c r="K73">
-        <v>52.5858154195</v>
+        <v>52.05151796666667</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -5838,74 +5620,71 @@
         </is>
       </c>
       <c r="M73">
-        <v>4.410626045842244</v>
+        <v>4.033602709547567</v>
       </c>
       <c r="N73">
-        <v>-27.78694408880614</v>
+        <v>-25.41169707014967</v>
       </c>
       <c r="O73">
-        <v>-49.53133049480841</v>
+        <v>-45.29735842821918</v>
       </c>
       <c r="P73">
-        <v>-88.21252091684488</v>
+        <v>-80.67205419095133</v>
       </c>
       <c r="Q73">
-        <v>0.4048535158490932</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="R73">
-        <v>3.779661016949153</v>
+        <v>-1.398033786666668</v>
       </c>
       <c r="S73">
-        <v>-1.257717422166667</v>
+        <v>-196.3418881832317</v>
       </c>
       <c r="T73">
-        <v>-168.7850858331975</v>
+        <v>-70.48170345039088</v>
       </c>
       <c r="U73">
-        <v>-60.58951799140425</v>
+        <v>-270.4886402130429</v>
       </c>
       <c r="V73">
-        <v>-232.5252587601548</v>
-      </c>
-      <c r="W73">
-        <v>-106.2921504530059</v>
+        <v>-344.2682104576047</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B4A12</t>
+          <t>B4A14</t>
         </is>
       </c>
       <c r="B74">
-        <v>54.90058333333334</v>
+        <v>67.23102564102564</v>
       </c>
       <c r="C74">
-        <v>-110.1315505</v>
+        <v>-120.9663026923077</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74">
-        <v>15.43958333333333</v>
+        <v>16.955</v>
       </c>
       <c r="F74">
-        <v>32.125</v>
+        <v>37.105</v>
       </c>
       <c r="G74">
-        <v>47.56458333333333</v>
+        <v>54.06</v>
       </c>
       <c r="H74">
-        <v>13.49411681</v>
+        <v>15.34313406833333</v>
       </c>
       <c r="I74">
-        <v>33.50838837833333</v>
+        <v>38.127645695</v>
       </c>
       <c r="J74">
-        <v>1.384350912</v>
+        <v>1.2954976355</v>
       </c>
       <c r="K74">
-        <v>47.00250518833333</v>
+        <v>53.47077976333333</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -5913,74 +5692,71 @@
         </is>
       </c>
       <c r="M74">
-        <v>1.557799648651538</v>
+        <v>1.052414688086237</v>
       </c>
       <c r="N74">
-        <v>-9.814137786504689</v>
+        <v>-6.630212534943291</v>
       </c>
       <c r="O74">
-        <v>-17.49409005435677</v>
+        <v>-11.81861694720844</v>
       </c>
       <c r="P74">
-        <v>-31.15599297303076</v>
+        <v>-21.04829376172473</v>
       </c>
       <c r="Q74">
-        <v>0.1429911895023564</v>
+        <v>2</v>
       </c>
       <c r="R74">
-        <v>0.9833333333333333</v>
+        <v>-1.611865931666669</v>
       </c>
       <c r="S74">
-        <v>-1.945466523333334</v>
+        <v>-223.5488791119146</v>
       </c>
       <c r="T74">
-        <v>-288.321420534662</v>
+        <v>-80.24831557863601</v>
       </c>
       <c r="U74">
-        <v>-103.4999971150069</v>
+        <v>-307.9701071006397</v>
       </c>
       <c r="V74">
-        <v>-397.2034174996493</v>
-      </c>
-      <c r="W74">
-        <v>-415.9470610890188</v>
+        <v>-356.3337987514308</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B4A13</t>
+          <t>B4A15</t>
         </is>
       </c>
       <c r="B75">
-        <v>122.4278333333333</v>
+        <v>51.7598717948718</v>
       </c>
       <c r="C75">
-        <v>-68.36646325</v>
+        <v>-131.1401676923077</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>15.17125</v>
+        <v>20.145</v>
       </c>
       <c r="F75">
-        <v>37.69833333333333</v>
+        <v>33.93</v>
       </c>
       <c r="G75">
-        <v>52.86958333333333</v>
+        <v>54.075</v>
       </c>
       <c r="H75">
-        <v>13.57363288</v>
+        <v>15.49836146416667</v>
       </c>
       <c r="I75">
-        <v>38.47788508666667</v>
+        <v>37.19344516666666</v>
       </c>
       <c r="J75">
-        <v>1.3118625675</v>
+        <v>1.264633069333333</v>
       </c>
       <c r="K75">
-        <v>52.05151796666667</v>
+        <v>52.69180663083333</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -5988,74 +5764,71 @@
         </is>
       </c>
       <c r="M75">
-        <v>4.056336430908098</v>
+        <v>1.321750156016363</v>
       </c>
       <c r="N75">
-        <v>-25.55491951472101</v>
+        <v>-8.327025982903084</v>
       </c>
       <c r="O75">
-        <v>-45.55265811909793</v>
+        <v>-14.84325425206375</v>
       </c>
       <c r="P75">
-        <v>-81.12672861816195</v>
+        <v>-26.43500312032725</v>
       </c>
       <c r="Q75">
-        <v>0.3723330993041171</v>
+        <v>1.9</v>
       </c>
       <c r="R75">
-        <v>0.9833333333333333</v>
+        <v>-4.646638535833333</v>
       </c>
       <c r="S75">
-        <v>-1.597617120000001</v>
+        <v>-629.0865207423706</v>
       </c>
       <c r="T75">
-        <v>-224.3716603463226</v>
+        <v>-225.8259305229022</v>
       </c>
       <c r="U75">
-        <v>-80.54367294483376</v>
+        <v>-866.6553996524635</v>
       </c>
       <c r="V75">
-        <v>-309.1036042842877</v>
-      </c>
-      <c r="W75">
-        <v>-338.2907817154205</v>
+        <v>-775.069942686742</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B4A14</t>
+          <t>B4A16</t>
         </is>
       </c>
       <c r="B76">
-        <v>96.73041666666667</v>
+        <v>268.6414102564103</v>
       </c>
       <c r="C76">
-        <v>-84.45979625</v>
+        <v>8.124968461538476</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E76">
-        <v>17.08291666666667</v>
+        <v>17.515</v>
       </c>
       <c r="F76">
-        <v>37.00375</v>
+        <v>30.57666666666667</v>
       </c>
       <c r="G76">
-        <v>54.08666666666667</v>
+        <v>48.09166666666667</v>
       </c>
       <c r="H76">
-        <v>15.34313406833333</v>
+        <v>17.406181905</v>
       </c>
       <c r="I76">
-        <v>38.127645695</v>
+        <v>31.31645307</v>
       </c>
       <c r="J76">
-        <v>1.2954976355</v>
+        <v>1.2258200815</v>
       </c>
       <c r="K76">
-        <v>53.47077976333333</v>
+        <v>48.72263497500001</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -6063,74 +5836,71 @@
         </is>
       </c>
       <c r="M76">
-        <v>1.035234654258313</v>
+        <v>2.539400797029873</v>
       </c>
       <c r="N76">
-        <v>-6.521978321827373</v>
+        <v>-15.9982250212882</v>
       </c>
       <c r="O76">
-        <v>-11.62568516732086</v>
+        <v>-28.51747095064547</v>
       </c>
       <c r="P76">
-        <v>-20.70469308516626</v>
+        <v>-50.78801594059746</v>
       </c>
       <c r="Q76">
-        <v>0.09502469380744438</v>
+        <v>6.35593220338983</v>
       </c>
       <c r="R76">
-        <v>2</v>
+        <v>-0.1088180950000002</v>
       </c>
       <c r="S76">
-        <v>-1.739782598333333</v>
+        <v>-14.28021697806301</v>
       </c>
       <c r="T76">
-        <v>-241.2895775727955</v>
+        <v>-5.126231735714926</v>
       </c>
       <c r="U76">
-        <v>-86.61677143638812</v>
+        <v>-19.67301276403511</v>
       </c>
       <c r="V76">
-        <v>-332.4104211238758</v>
-      </c>
-      <c r="W76">
-        <v>-337.3750589901164</v>
+        <v>-34.67271946717001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B4A15</t>
+          <t>B4A17</t>
         </is>
       </c>
       <c r="B77">
-        <v>80.89975</v>
+        <v>101.8382051282051</v>
       </c>
       <c r="C77">
-        <v>-93.88153149999999</v>
+        <v>-99.10945769230769</v>
       </c>
       <c r="D77">
         <v>2</v>
       </c>
       <c r="E77">
-        <v>17.94041666666667</v>
+        <v>13.47666666666667</v>
       </c>
       <c r="F77">
-        <v>35.31916666666667</v>
+        <v>38.66333333333333</v>
       </c>
       <c r="G77">
-        <v>53.25958333333334</v>
+        <v>52.14</v>
       </c>
       <c r="H77">
-        <v>15.49836146416667</v>
+        <v>11.93623757083333</v>
       </c>
       <c r="I77">
-        <v>37.19344516666666</v>
+        <v>39.78190652666667</v>
       </c>
       <c r="J77">
-        <v>1.264633069333333</v>
+        <v>1.380730892166667</v>
       </c>
       <c r="K77">
-        <v>52.69180663083333</v>
+        <v>51.7181440975</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -6138,74 +5908,71 @@
         </is>
       </c>
       <c r="M77">
-        <v>1.647421926406839</v>
+        <v>3.095392060730346</v>
       </c>
       <c r="N77">
-        <v>-10.37875813636309</v>
+        <v>-19.50096998260118</v>
       </c>
       <c r="O77">
-        <v>-18.5005482335488</v>
+        <v>-34.76125284200179</v>
       </c>
       <c r="P77">
-        <v>-32.94843852813678</v>
+        <v>-61.90784121460692</v>
       </c>
       <c r="Q77">
-        <v>0.151217662087091</v>
+        <v>2</v>
       </c>
       <c r="R77">
-        <v>1.9</v>
+        <v>-1.540429095833334</v>
       </c>
       <c r="S77">
-        <v>-2.442055202500001</v>
+        <v>-227.6972107518007</v>
       </c>
       <c r="T77">
-        <v>-330.6183596925761</v>
+        <v>-81.73746026987718</v>
       </c>
       <c r="U77">
-        <v>-118.6835137357966</v>
+        <v>-313.6850189557114</v>
       </c>
       <c r="V77">
-        <v>-455.4734161426342</v>
-      </c>
-      <c r="W77">
-        <v>-443.0004394261249</v>
+        <v>-361.5679212861102</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B4A16</t>
+          <t>B4A18</t>
         </is>
       </c>
       <c r="B78">
-        <v>260.4987083333334</v>
+        <v>693.4347435897436</v>
       </c>
       <c r="C78">
-        <v>19.70290012500001</v>
+        <v>285.2588969230769</v>
       </c>
       <c r="D78">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E78">
-        <v>16.51958333333333</v>
+        <v>17.305</v>
       </c>
       <c r="F78">
-        <v>31.21333333333333</v>
+        <v>33.38666666666667</v>
       </c>
       <c r="G78">
-        <v>47.73291666666667</v>
+        <v>50.69166666666667</v>
       </c>
       <c r="H78">
-        <v>17.406181905</v>
+        <v>18.410111665</v>
       </c>
       <c r="I78">
-        <v>31.31645307</v>
+        <v>36.12730495333334</v>
       </c>
       <c r="J78">
-        <v>1.2258200815</v>
+        <v>1.2625153515</v>
       </c>
       <c r="K78">
-        <v>48.72263497500001</v>
+        <v>54.53741661833334</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -6213,74 +5980,71 @@
         </is>
       </c>
       <c r="M78">
-        <v>2.668287177350798</v>
+        <v>3.183276175047217</v>
       </c>
       <c r="N78">
-        <v>-16.81020921731002</v>
+        <v>-20.05463990279747</v>
       </c>
       <c r="O78">
-        <v>-29.96486500164946</v>
+        <v>-35.74819144578025</v>
       </c>
       <c r="P78">
-        <v>-53.36574354701596</v>
+        <v>-63.66552350094434</v>
       </c>
       <c r="Q78">
-        <v>0.244923381356226</v>
+        <v>10.48333333333333</v>
       </c>
       <c r="R78">
-        <v>6.35593220338983</v>
+        <v>1.105111664999999</v>
       </c>
       <c r="S78">
-        <v>0.8865985716666671</v>
+        <v>149.3653244380321</v>
       </c>
       <c r="T78">
-        <v>116.3484802398051</v>
+        <v>53.61832159313974</v>
       </c>
       <c r="U78">
-        <v>41.7661211117249</v>
+        <v>205.7717987540151</v>
       </c>
       <c r="V78">
-        <v>160.2864396493397</v>
-      </c>
-      <c r="W78">
-        <v>106.0865153631556</v>
+        <v>398.8760299153288</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B4A17</t>
+          <t>B4A20</t>
         </is>
       </c>
       <c r="B79">
-        <v>128.8154583333333</v>
+        <v>567.9525256410257</v>
       </c>
       <c r="C79">
-        <v>-65.043571625</v>
+        <v>200.100018923077</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E79">
-        <v>13.35333333333333</v>
+        <v>14.46666666666667</v>
       </c>
       <c r="F79">
-        <v>38.83833333333333</v>
+        <v>31.18</v>
       </c>
       <c r="G79">
-        <v>52.19166666666666</v>
+        <v>45.64666666666667</v>
       </c>
       <c r="H79">
-        <v>11.93623757083333</v>
+        <v>15.80617593833333</v>
       </c>
       <c r="I79">
-        <v>39.78190652666667</v>
+        <v>31.66174778166667</v>
       </c>
       <c r="J79">
-        <v>1.380730892166667</v>
+        <v>1.269657585333333</v>
       </c>
       <c r="K79">
-        <v>51.7181440975</v>
+        <v>47.46792372</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -6288,74 +6052,71 @@
         </is>
       </c>
       <c r="M79">
-        <v>3.095392060730346</v>
+        <v>3.28270051142621</v>
       </c>
       <c r="N79">
-        <v>-19.50096998260118</v>
+        <v>-20.68101322198512</v>
       </c>
       <c r="O79">
-        <v>-34.76125284200179</v>
+        <v>-36.86472674331633</v>
       </c>
       <c r="P79">
-        <v>-61.90784121460692</v>
+        <v>-65.65401022852419</v>
       </c>
       <c r="Q79">
-        <v>0.2841275469044544</v>
+        <v>9.85</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>1.339509271666666</v>
       </c>
       <c r="S79">
-        <v>-1.417095762500001</v>
+        <v>182.0703769872692</v>
       </c>
       <c r="T79">
-        <v>-209.4667994536228</v>
+        <v>65.35859686722485</v>
       </c>
       <c r="U79">
-        <v>-75.19321006027485</v>
+        <v>250.8276208915897</v>
       </c>
       <c r="V79">
-        <v>-288.5700564370319</v>
-      </c>
-      <c r="W79">
-        <v>-309.2716239206246</v>
+        <v>345.3056691670298</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B4A18</t>
+          <t>B4A21</t>
         </is>
       </c>
       <c r="B80">
-        <v>693.9295833333333</v>
+        <v>518.9996153846154</v>
       </c>
       <c r="C80">
-        <v>296.457069</v>
+        <v>167.2466507692308</v>
       </c>
       <c r="D80">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E80">
-        <v>17.05375</v>
+        <v>13.26666666666667</v>
       </c>
       <c r="F80">
-        <v>33.77166666666667</v>
+        <v>38.9</v>
       </c>
       <c r="G80">
-        <v>50.82541666666667</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="H80">
-        <v>18.410111665</v>
+        <v>13.02545374183333</v>
       </c>
       <c r="I80">
-        <v>36.12730495333334</v>
+        <v>39.19134638666667</v>
       </c>
       <c r="J80">
-        <v>1.2625153515</v>
+        <v>1.354319834</v>
       </c>
       <c r="K80">
-        <v>54.53741661833334</v>
+        <v>52.2168001285</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -6363,74 +6124,71 @@
         </is>
       </c>
       <c r="M80">
-        <v>2.93340592717423</v>
+        <v>3.038668028517401</v>
       </c>
       <c r="N80">
-        <v>-18.48045734119765</v>
+        <v>-19.14360857965962</v>
       </c>
       <c r="O80">
-        <v>-32.9421485621666</v>
+        <v>-34.12424196025042</v>
       </c>
       <c r="P80">
-        <v>-58.6681185434846</v>
+        <v>-60.77336057034802</v>
       </c>
       <c r="Q80">
-        <v>0.269258760703272</v>
+        <v>1.9</v>
       </c>
       <c r="R80">
-        <v>10.48333333333333</v>
+        <v>-0.2412129248333326</v>
       </c>
       <c r="S80">
-        <v>1.356361664999998</v>
+        <v>-34.97266833978342</v>
       </c>
       <c r="T80">
-        <v>183.3239179029336</v>
+        <v>-12.55429119889661</v>
       </c>
       <c r="U80">
-        <v>65.8085859138736</v>
+        <v>-48.17978268102264</v>
       </c>
       <c r="V80">
-        <v>252.5545502843287</v>
-      </c>
-      <c r="W80">
-        <v>446.838838340767</v>
+        <v>98.14974046919693</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B4A20</t>
+          <t>B4A22</t>
         </is>
       </c>
       <c r="B81">
-        <v>585.0162666666666</v>
+        <v>382.5914102564103</v>
       </c>
       <c r="C81">
-        <v>220.537530425</v>
+        <v>81.10359384615386</v>
       </c>
       <c r="D81">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E81">
-        <v>14.57916666666667</v>
+        <v>15.63333333333333</v>
       </c>
       <c r="F81">
-        <v>30.71583333333333</v>
+        <v>34.77666666666666</v>
       </c>
       <c r="G81">
-        <v>45.295</v>
+        <v>50.41</v>
       </c>
       <c r="H81">
-        <v>15.80617593833333</v>
+        <v>16.39641685833333</v>
       </c>
       <c r="I81">
-        <v>31.66174778166667</v>
+        <v>34.92457740666666</v>
       </c>
       <c r="J81">
-        <v>1.269657585333333</v>
+        <v>1.324271466333333</v>
       </c>
       <c r="K81">
-        <v>47.46792372</v>
+        <v>51.320994265</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -6438,187 +6196,34 @@
         </is>
       </c>
       <c r="M81">
-        <v>3.144980069906421</v>
+        <v>0.7955205331765982</v>
       </c>
       <c r="N81">
-        <v>-19.81337444041045</v>
+        <v>-5.011779359012569</v>
       </c>
       <c r="O81">
-        <v>-35.31812618504911</v>
+        <v>-8.933695587573197</v>
       </c>
       <c r="P81">
-        <v>-62.89960139812842</v>
+        <v>-15.91041066353196</v>
       </c>
       <c r="Q81">
-        <v>0.2886792544512358</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="R81">
-        <v>9.85</v>
+        <v>0.763083524999999</v>
       </c>
       <c r="S81">
-        <v>1.227009271666665</v>
+        <v>108.1822611643839</v>
       </c>
       <c r="T81">
-        <v>166.7790177975099</v>
+        <v>38.8346578538814</v>
       </c>
       <c r="U81">
-        <v>59.86939100423433</v>
+        <v>149.0363212266671</v>
       </c>
       <c r="V81">
-        <v>229.7616171339644</v>
-      </c>
-      <c r="W81">
-        <v>351.9984220374608</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>B4A21</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>538.9304166666667</v>
-      </c>
-      <c r="C82">
-        <v>197.23783275</v>
-      </c>
-      <c r="D82">
-        <v>2</v>
-      </c>
-      <c r="E82">
-        <v>13.445</v>
-      </c>
-      <c r="F82">
-        <v>37.97916666666666</v>
-      </c>
-      <c r="G82">
-        <v>51.42416666666666</v>
-      </c>
-      <c r="H82">
-        <v>13.02545374183333</v>
-      </c>
-      <c r="I82">
-        <v>39.19134638666667</v>
-      </c>
-      <c r="J82">
-        <v>1.354319834</v>
-      </c>
-      <c r="K82">
-        <v>52.2168001285</v>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="M82">
-        <v>2.98039018954707</v>
-      </c>
-      <c r="N82">
-        <v>-18.77645819414654</v>
-      </c>
-      <c r="O82">
-        <v>-33.4697818286136</v>
-      </c>
-      <c r="P82">
-        <v>-59.6078037909414</v>
-      </c>
-      <c r="Q82">
-        <v>0.2735714690611143</v>
-      </c>
-      <c r="R82">
-        <v>1.9</v>
-      </c>
-      <c r="S82">
-        <v>-0.4195462581666671</v>
-      </c>
-      <c r="T82">
-        <v>-60.82863159259875</v>
-      </c>
-      <c r="U82">
-        <v>-21.83591903324058</v>
-      </c>
-      <c r="V82">
-        <v>-83.80001841556785</v>
-      </c>
-      <c r="W82">
-        <v>102.9394193287876</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>B4A22</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>414.1980833333333</v>
-      </c>
-      <c r="C83">
-        <v>118.029267</v>
-      </c>
-      <c r="D83">
-        <v>4</v>
-      </c>
-      <c r="E83">
-        <v>15.55333333333333</v>
-      </c>
-      <c r="F83">
-        <v>34.33833333333333</v>
-      </c>
-      <c r="G83">
-        <v>49.89166666666667</v>
-      </c>
-      <c r="H83">
-        <v>16.39641685833333</v>
-      </c>
-      <c r="I83">
-        <v>34.92457740666666</v>
-      </c>
-      <c r="J83">
-        <v>1.324271466333333</v>
-      </c>
-      <c r="K83">
-        <v>51.320994265</v>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="M83">
-        <v>0.9985906350334441</v>
-      </c>
-      <c r="N83">
-        <v>-6.291121000710698</v>
-      </c>
-      <c r="O83">
-        <v>-11.21417283142558</v>
-      </c>
-      <c r="P83">
-        <v>-19.97181270066888</v>
-      </c>
-      <c r="Q83">
-        <v>0.09166112141118221</v>
-      </c>
-      <c r="R83">
-        <v>2.833333333333333</v>
-      </c>
-      <c r="S83">
-        <v>0.8430835249999973</v>
-      </c>
-      <c r="T83">
-        <v>119.5238517106489</v>
-      </c>
-      <c r="U83">
-        <v>42.90599804997652</v>
-      </c>
-      <c r="V83">
-        <v>164.6609616592241</v>
-      </c>
-      <c r="W83">
-        <v>226.3389458792233</v>
+        <v>180.3521594229646</v>
       </c>
     </row>
   </sheetData>

--- a/Data Analysis/1_Data/economic_MF.xlsx
+++ b/Data Analysis/1_Data/economic_MF.xlsx
@@ -377,17 +377,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mean_org_02</t>
+          <t>mean_org_11</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mean_inorg_02</t>
+          <t>mean_inorg_11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>mean_C_02</t>
+          <t>mean_C_11</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -482,13 +482,13 @@
         <v>16</v>
       </c>
       <c r="E2">
-        <v>16.6</v>
+        <v>15.693274495</v>
       </c>
       <c r="F2">
-        <v>6.383333333333334</v>
+        <v>6.694930096666667</v>
       </c>
       <c r="G2">
-        <v>22.98333333333333</v>
+        <v>22.38820459166666</v>
       </c>
       <c r="H2">
         <v>18.76454505833333</v>
@@ -520,22 +520,22 @@
         <v>-56.26529458574326</v>
       </c>
       <c r="Q2">
-        <v>11.83333333333333</v>
+        <v>11.08333333333333</v>
       </c>
       <c r="R2">
-        <v>2.164545058333331</v>
+        <v>3.071270563333334</v>
       </c>
       <c r="S2">
-        <v>290.7276213575302</v>
+        <v>687.5218281902502</v>
       </c>
       <c r="T2">
-        <v>104.3637615129596</v>
+        <v>246.8027075554744</v>
       </c>
       <c r="U2">
-        <v>400.5182984691637</v>
+        <v>947.1582765386092</v>
       </c>
       <c r="V2">
-        <v>335.1410927553277</v>
+        <v>731.9352995880477</v>
       </c>
     </row>
     <row r="3">
@@ -554,13 +554,13 @@
         <v>8</v>
       </c>
       <c r="E3">
-        <v>17.03833333333333</v>
+        <v>15.69695607833333</v>
       </c>
       <c r="F3">
-        <v>6.225</v>
+        <v>6.371277073333333</v>
       </c>
       <c r="G3">
-        <v>23.26333333333334</v>
+        <v>22.06823315166667</v>
       </c>
       <c r="H3">
         <v>16.83361475166667</v>
@@ -592,22 +592,22 @@
         <v>-100.0756869173245</v>
       </c>
       <c r="Q3">
-        <v>5.728813559322034</v>
+        <v>5.055555555555555</v>
       </c>
       <c r="R3">
-        <v>-0.2047185816666683</v>
+        <v>1.136658673333333</v>
       </c>
       <c r="S3">
-        <v>-28.21970380582596</v>
+        <v>261.1403650534073</v>
       </c>
       <c r="T3">
-        <v>-10.13015008414265</v>
+        <v>93.74269514737699</v>
       </c>
       <c r="U3">
-        <v>-38.87662169434402</v>
+        <v>359.7576803484479</v>
       </c>
       <c r="V3">
-        <v>-23.00486354836517</v>
+        <v>266.3552053108681</v>
       </c>
     </row>
     <row r="4">
@@ -626,13 +626,13 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>15.42</v>
+        <v>15.64949997</v>
       </c>
       <c r="F4">
-        <v>6.928333333333333</v>
+        <v>6.797016461666667</v>
       </c>
       <c r="G4">
-        <v>22.34833333333333</v>
+        <v>22.44651643166667</v>
       </c>
       <c r="H4">
         <v>13.88983349316667</v>
@@ -664,22 +664,22 @@
         <v>-212.4589130862419</v>
       </c>
       <c r="Q4">
-        <v>6.186440677966102</v>
+        <v>5.805555555555555</v>
       </c>
       <c r="R4">
-        <v>-1.530166506833334</v>
+        <v>-1.759666476833335</v>
       </c>
       <c r="S4">
-        <v>-230.153281394325</v>
+        <v>-441.1208540532325</v>
       </c>
       <c r="T4">
-        <v>-82.61912665437308</v>
+        <v>-158.3510758139809</v>
       </c>
       <c r="U4">
-        <v>-317.0686026347255</v>
+        <v>-607.7061858095404</v>
       </c>
       <c r="V4">
-        <v>-405.3851783999421</v>
+        <v>-616.3527510588497</v>
       </c>
     </row>
     <row r="5">
@@ -698,13 +698,13 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>17.11666666666667</v>
+        <v>16.81531028666667</v>
       </c>
       <c r="F5">
-        <v>6.623333333333333</v>
+        <v>6.73690309</v>
       </c>
       <c r="G5">
-        <v>23.74</v>
+        <v>23.55221337666666</v>
       </c>
       <c r="H5">
         <v>16.13080275</v>
@@ -736,22 +736,22 @@
         <v>-200.6417325652373</v>
       </c>
       <c r="Q5">
-        <v>3.35</v>
+        <v>2.972222222222222</v>
       </c>
       <c r="R5">
-        <v>-0.9858639166666663</v>
+        <v>-0.6845075366666649</v>
       </c>
       <c r="S5">
-        <v>-142.2482160701825</v>
+        <v>-164.6102373281035</v>
       </c>
       <c r="T5">
-        <v>-51.06346217903989</v>
+        <v>-59.09085442547303</v>
       </c>
       <c r="U5">
-        <v>-195.9669782825325</v>
+        <v>-226.7738161837011</v>
       </c>
       <c r="V5">
-        <v>-234.6679685209479</v>
+        <v>-257.0299897788688</v>
       </c>
     </row>
     <row r="6">
@@ -770,13 +770,13 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>18.13666666666667</v>
+        <v>15.09488513333333</v>
       </c>
       <c r="F6">
-        <v>6.268333333333334</v>
+        <v>6.450398961666667</v>
       </c>
       <c r="G6">
-        <v>24.405</v>
+        <v>21.545284095</v>
       </c>
       <c r="H6">
         <v>14.88611025333333</v>
@@ -808,22 +808,22 @@
         <v>-152.1483723899917</v>
       </c>
       <c r="Q6">
-        <v>1.864406779661017</v>
+        <v>1.805555555555556</v>
       </c>
       <c r="R6">
-        <v>-3.250556413333333</v>
+        <v>-0.20877488</v>
       </c>
       <c r="S6">
-        <v>-468.6008132950027</v>
+        <v>-50.16170880892521</v>
       </c>
       <c r="T6">
-        <v>-168.2156765674369</v>
+        <v>-18.00676726474238</v>
       </c>
       <c r="U6">
-        <v>-645.5637050439462</v>
+        <v>-69.10482797143419</v>
       </c>
       <c r="V6">
-        <v>-611.3065266996754</v>
+        <v>-192.8674222135978</v>
       </c>
     </row>
     <row r="7">
@@ -842,13 +842,13 @@
         <v>16</v>
       </c>
       <c r="E7">
-        <v>15.41</v>
+        <v>16.30583443666667</v>
       </c>
       <c r="F7">
-        <v>6.038333333333333</v>
+        <v>6.19431128</v>
       </c>
       <c r="G7">
-        <v>21.44833333333333</v>
+        <v>22.50014571666667</v>
       </c>
       <c r="H7">
         <v>16.76970075833334</v>
@@ -880,22 +880,22 @@
         <v>-23.51561348150935</v>
       </c>
       <c r="Q7">
-        <v>12.89830508474576</v>
+        <v>12.47222222222222</v>
       </c>
       <c r="R7">
-        <v>1.359700758333336</v>
+        <v>0.4638663216666679</v>
       </c>
       <c r="S7">
-        <v>194.7869053707685</v>
+        <v>110.7536403989424</v>
       </c>
       <c r="T7">
-        <v>69.92350449207073</v>
+        <v>39.757717066287</v>
       </c>
       <c r="U7">
-        <v>268.3464320964268</v>
+        <v>152.5787587526763</v>
       </c>
       <c r="V7">
-        <v>171.8478089778241</v>
+        <v>87.81454400599794</v>
       </c>
     </row>
     <row r="8">
@@ -914,13 +914,13 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>16.13166666666667</v>
+        <v>15.27825111666667</v>
       </c>
       <c r="F8">
-        <v>5.843333333333334</v>
+        <v>6.3079831</v>
       </c>
       <c r="G8">
-        <v>21.975</v>
+        <v>21.58623421666667</v>
       </c>
       <c r="H8">
         <v>16.93685348</v>
@@ -955,19 +955,19 @@
         <v>2</v>
       </c>
       <c r="R8">
-        <v>0.8051868133333322</v>
+        <v>1.658602363333333</v>
       </c>
       <c r="S8">
-        <v>111.0688404456992</v>
+        <v>381.3173916193334</v>
       </c>
       <c r="T8">
-        <v>39.87086580102022</v>
+        <v>136.8831662223248</v>
       </c>
       <c r="U8">
-        <v>153.0129912683724</v>
+        <v>525.3184824852191</v>
       </c>
       <c r="V8">
-        <v>-76.08817675441108</v>
+        <v>194.1603744192232</v>
       </c>
     </row>
     <row r="9">
@@ -986,13 +986,13 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>16.26333333333333</v>
+        <v>15.37546887666667</v>
       </c>
       <c r="F9">
-        <v>5.896666666666667</v>
+        <v>6.454285086666667</v>
       </c>
       <c r="G9">
-        <v>22.16</v>
+        <v>21.82975396333333</v>
       </c>
       <c r="H9">
         <v>15.82495804166667</v>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="R9">
-        <v>-0.4383752916666666</v>
+        <v>0.4494891649999992</v>
       </c>
       <c r="S9">
-        <v>-60.51076386339979</v>
+        <v>103.4080966678254</v>
       </c>
       <c r="T9">
-        <v>-21.72181266891274</v>
+        <v>37.12085521409119</v>
       </c>
       <c r="U9">
-        <v>-83.36211079109599</v>
+        <v>142.4592363530494</v>
       </c>
       <c r="V9">
-        <v>-148.7325992871653</v>
+        <v>15.18626124405998</v>
       </c>
     </row>
     <row r="10">
@@ -1058,13 +1058,13 @@
         <v>16</v>
       </c>
       <c r="E10">
-        <v>20.57</v>
+        <v>19.95934968833333</v>
       </c>
       <c r="F10">
-        <v>7.835</v>
+        <v>8.20662727</v>
       </c>
       <c r="G10">
-        <v>28.405</v>
+        <v>28.16597695833333</v>
       </c>
       <c r="H10">
         <v>20.74362609</v>
@@ -1096,22 +1096,22 @@
         <v>-54.21340647634543</v>
       </c>
       <c r="Q10">
-        <v>11.03333333333333</v>
+        <v>10.36111111111111</v>
       </c>
       <c r="R10">
-        <v>0.1736260899999991</v>
+        <v>0.7842764016666663</v>
       </c>
       <c r="S10">
-        <v>24.39343127069136</v>
+        <v>183.6436035360149</v>
       </c>
       <c r="T10">
-        <v>8.756616353581514</v>
+        <v>65.92334485908225</v>
       </c>
       <c r="U10">
-        <v>33.60539167465911</v>
+        <v>252.9949623277693</v>
       </c>
       <c r="V10">
-        <v>6.71297314960802</v>
+        <v>165.9631454149315</v>
       </c>
     </row>
     <row r="11">
@@ -1130,13 +1130,13 @@
         <v>8</v>
       </c>
       <c r="E11">
-        <v>18.10333333333333</v>
+        <v>16.720706945</v>
       </c>
       <c r="F11">
-        <v>7.890000000000001</v>
+        <v>7.984850008333334</v>
       </c>
       <c r="G11">
-        <v>25.99333333333333</v>
+        <v>24.70555695333334</v>
       </c>
       <c r="H11">
         <v>15.448378665</v>
@@ -1168,22 +1168,22 @@
         <v>-156.4877963837442</v>
       </c>
       <c r="Q11">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-2.654954668333332</v>
+        <v>-1.27232828</v>
       </c>
       <c r="S11">
-        <v>-354.1340068957437</v>
+        <v>-282.851478443523</v>
       </c>
       <c r="T11">
-        <v>-127.1250281164208</v>
+        <v>-101.5364281592134</v>
       </c>
       <c r="U11">
-        <v>-487.8695364742183</v>
+        <v>-389.6678008670155</v>
       </c>
       <c r="V11">
-        <v>-343.5420380267544</v>
+        <v>-272.2595095745338</v>
       </c>
     </row>
     <row r="12">
@@ -1202,13 +1202,13 @@
         <v>4</v>
       </c>
       <c r="E12">
-        <v>15.54166666666667</v>
+        <v>14.79970766666667</v>
       </c>
       <c r="F12">
-        <v>6.416666666666667</v>
+        <v>6.588684818333333</v>
       </c>
       <c r="G12">
-        <v>21.95833333333333</v>
+        <v>21.388392485</v>
       </c>
       <c r="H12">
         <v>16.183862175</v>
@@ -1240,22 +1240,22 @@
         <v>-132.0756412844439</v>
       </c>
       <c r="Q12">
-        <v>3.2</v>
+        <v>3.194444444444445</v>
       </c>
       <c r="R12">
-        <v>0.6421955083333355</v>
+        <v>1.384154508333335</v>
       </c>
       <c r="S12">
-        <v>88.68375278906213</v>
+        <v>318.5738471800504</v>
       </c>
       <c r="T12">
-        <v>31.83519330889409</v>
+        <v>114.359842577454</v>
       </c>
       <c r="U12">
-        <v>122.1743761500187</v>
+        <v>438.880401571532</v>
       </c>
       <c r="V12">
-        <v>50.32661213092382</v>
+        <v>280.2167065219122</v>
       </c>
     </row>
     <row r="13">
@@ -1274,13 +1274,13 @@
         <v>8</v>
       </c>
       <c r="E13">
-        <v>14.40166666666667</v>
+        <v>15.62836029166667</v>
       </c>
       <c r="F13">
-        <v>6.755</v>
+        <v>6.864643295</v>
       </c>
       <c r="G13">
-        <v>21.15666666666667</v>
+        <v>22.49300358666667</v>
       </c>
       <c r="H13">
         <v>16.193342365</v>
@@ -1312,22 +1312,22 @@
         <v>-27.84047925160479</v>
       </c>
       <c r="Q13">
-        <v>6.559322033898305</v>
+        <v>6.138888888888889</v>
       </c>
       <c r="R13">
-        <v>1.791675698333332</v>
+        <v>0.5649820733333328</v>
       </c>
       <c r="S13">
-        <v>260.3041565167735</v>
+        <v>136.8059913436875</v>
       </c>
       <c r="T13">
-        <v>93.44251772396997</v>
+        <v>49.10984304645191</v>
       </c>
       <c r="U13">
-        <v>358.6056851623899</v>
+        <v>188.4695462285549</v>
       </c>
       <c r="V13">
-        <v>191.0631897246897</v>
+        <v>67.5650245516037</v>
       </c>
     </row>
     <row r="14">
@@ -1346,13 +1346,13 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>18.25833333333333</v>
+        <v>17.893618645</v>
       </c>
       <c r="F14">
-        <v>7.81</v>
+        <v>7.822386326666667</v>
       </c>
       <c r="G14">
-        <v>26.06833333333333</v>
+        <v>25.71600497166667</v>
       </c>
       <c r="H14">
         <v>16.58950539833333</v>
@@ -1384,22 +1384,22 @@
         <v>-84.69932957972681</v>
       </c>
       <c r="Q14">
-        <v>0.95</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="R14">
-        <v>-1.668827934999999</v>
+        <v>-1.304113246666667</v>
       </c>
       <c r="S14">
-        <v>-238.838056873739</v>
+        <v>-311.0684922880419</v>
       </c>
       <c r="T14">
-        <v>-85.73673836493194</v>
+        <v>-111.6656126162202</v>
       </c>
       <c r="U14">
-        <v>-329.0331056336473</v>
+        <v>-428.5407167603055</v>
       </c>
       <c r="V14">
-        <v>-443.2145842789095</v>
+        <v>-515.4450196932123</v>
       </c>
     </row>
     <row r="15">
@@ -1418,13 +1418,13 @@
         <v>2</v>
       </c>
       <c r="E15">
-        <v>18.37</v>
+        <v>17.72635309333333</v>
       </c>
       <c r="F15">
-        <v>8.023333333333333</v>
+        <v>7.703228096666667</v>
       </c>
       <c r="G15">
-        <v>26.39333333333333</v>
+        <v>25.42958119</v>
       </c>
       <c r="H15">
         <v>16.12405039333333</v>
@@ -1456,22 +1456,22 @@
         <v>-21.43160454563642</v>
       </c>
       <c r="Q15">
-        <v>1.983050847457627</v>
+        <v>1.972222222222222</v>
       </c>
       <c r="R15">
-        <v>-2.245949606666667</v>
+        <v>-1.602302699999999</v>
       </c>
       <c r="S15">
-        <v>-316.7664484257349</v>
+        <v>-376.6452388152318</v>
       </c>
       <c r="T15">
-        <v>-113.7110327682125</v>
+        <v>-135.2059831644422</v>
       </c>
       <c r="U15">
-        <v>-436.3904548978945</v>
+        <v>-518.8819331042249</v>
       </c>
       <c r="V15">
-        <v>-415.3504524550328</v>
+        <v>-475.2292428445297</v>
       </c>
     </row>
     <row r="16">
@@ -1490,13 +1490,13 @@
         <v>2</v>
       </c>
       <c r="E16">
-        <v>18.88</v>
+        <v>18.49871817</v>
       </c>
       <c r="F16">
-        <v>8.141666666666667</v>
+        <v>7.65717139</v>
       </c>
       <c r="G16">
-        <v>27.02166666666667</v>
+        <v>26.15588956</v>
       </c>
       <c r="H16">
         <v>16.225695985</v>
@@ -1531,19 +1531,19 @@
         <v>2</v>
       </c>
       <c r="R16">
-        <v>-2.654304015000001</v>
+        <v>-2.273022185000002</v>
       </c>
       <c r="S16">
-        <v>-361.9964745597835</v>
+        <v>-516.6615007903032</v>
       </c>
       <c r="T16">
-        <v>-129.9474524060761</v>
+        <v>-185.4682310529294</v>
       </c>
       <c r="U16">
-        <v>-498.7011944909756</v>
+        <v>-711.7740798579848</v>
       </c>
       <c r="V16">
-        <v>-490.7288702344709</v>
+        <v>-645.3938964649907</v>
       </c>
     </row>
     <row r="17">
@@ -1562,13 +1562,13 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>18.19666666666667</v>
+        <v>17.38958166833333</v>
       </c>
       <c r="F17">
-        <v>7.733333333333333</v>
+        <v>7.768696846666667</v>
       </c>
       <c r="G17">
-        <v>25.93</v>
+        <v>25.158278515</v>
       </c>
       <c r="H17">
         <v>17.84053773833333</v>
@@ -1603,19 +1603,19 @@
         <v>1</v>
       </c>
       <c r="R17">
-        <v>-0.3561289283333338</v>
+        <v>0.4509560700000002</v>
       </c>
       <c r="S17">
-        <v>-47.84091610353833</v>
+        <v>100.9660163067785</v>
       </c>
       <c r="T17">
-        <v>-17.17366219101376</v>
+        <v>36.2442109819205</v>
       </c>
       <c r="U17">
-        <v>-65.9076087284848</v>
+        <v>139.0949262597589</v>
       </c>
       <c r="V17">
-        <v>-204.4208958833973</v>
+        <v>-55.61396347308049</v>
       </c>
     </row>
     <row r="18">
@@ -1634,13 +1634,13 @@
         <v>4</v>
       </c>
       <c r="E18">
-        <v>18.44</v>
+        <v>17.72735899833333</v>
       </c>
       <c r="F18">
-        <v>7.836666666666667</v>
+        <v>7.651144068333333</v>
       </c>
       <c r="G18">
-        <v>26.27666666666666</v>
+        <v>25.37850306666667</v>
       </c>
       <c r="H18">
         <v>17.29026594833334</v>
@@ -1672,22 +1672,22 @@
         <v>-61.26184669473047</v>
       </c>
       <c r="Q18">
-        <v>3.559322033898305</v>
+        <v>3.5</v>
       </c>
       <c r="R18">
-        <v>-1.149734051666663</v>
+        <v>-0.4370930499999979</v>
       </c>
       <c r="S18">
-        <v>-160.2062670333225</v>
+        <v>-101.5090486726043</v>
       </c>
       <c r="T18">
-        <v>-57.50994201196193</v>
+        <v>-36.43914567734512</v>
       </c>
       <c r="U18">
-        <v>-220.7067260299064</v>
+        <v>-139.8430299251713</v>
       </c>
       <c r="V18">
-        <v>-241.9879381831829</v>
+        <v>-183.2907198224646</v>
       </c>
     </row>
     <row r="19">
@@ -1706,13 +1706,13 @@
         <v>16</v>
       </c>
       <c r="E19">
-        <v>20.27166666666667</v>
+        <v>18.94094098</v>
       </c>
       <c r="F19">
-        <v>7.295</v>
+        <v>7.475234071666667</v>
       </c>
       <c r="G19">
-        <v>27.56666666666667</v>
+        <v>26.41617505166667</v>
       </c>
       <c r="H19">
         <v>19.76502023666666</v>
@@ -1744,22 +1744,22 @@
         <v>-51.97218160452968</v>
       </c>
       <c r="Q19">
-        <v>12.15254237288136</v>
+        <v>11.08333333333333</v>
       </c>
       <c r="R19">
-        <v>-0.5066464300000035</v>
+        <v>0.8240792566666642</v>
       </c>
       <c r="S19">
-        <v>-67.43770810878988</v>
+        <v>182.81656621165</v>
       </c>
       <c r="T19">
-        <v>-24.20840803905278</v>
+        <v>65.6264596657205</v>
       </c>
       <c r="U19">
-        <v>-92.9049533658734</v>
+        <v>251.8556017799879</v>
       </c>
       <c r="V19">
-        <v>60.92674384334363</v>
+        <v>311.1810181637834</v>
       </c>
     </row>
     <row r="20">
@@ -1778,13 +1778,13 @@
         <v>4</v>
       </c>
       <c r="E20">
-        <v>19.17833333333333</v>
+        <v>17.24828480833333</v>
       </c>
       <c r="F20">
-        <v>8.326666666666666</v>
+        <v>9.214412571666667</v>
       </c>
       <c r="G20">
-        <v>27.505</v>
+        <v>26.46269738</v>
       </c>
       <c r="H20">
         <v>17.63945969833333</v>
@@ -1816,22 +1816,22 @@
         <v>-16.94042857950097</v>
       </c>
       <c r="Q20">
-        <v>3.694915254237288</v>
+        <v>3.638888888888889</v>
       </c>
       <c r="R20">
-        <v>-1.538873635000002</v>
+        <v>0.3911748899999985</v>
       </c>
       <c r="S20">
-        <v>-232.3794064855021</v>
+        <v>98.44970016032879</v>
       </c>
       <c r="T20">
-        <v>-83.4182484819751</v>
+        <v>35.34091800627187</v>
       </c>
       <c r="U20">
-        <v>-320.1354038885398</v>
+        <v>135.6283459029268</v>
       </c>
       <c r="V20">
-        <v>-341.8652321328919</v>
+        <v>-11.036125487061</v>
       </c>
     </row>
     <row r="21">
@@ -1850,13 +1850,13 @@
         <v>60</v>
       </c>
       <c r="E21">
-        <v>17.25333333333333</v>
+        <v>19.15098685333333</v>
       </c>
       <c r="F21">
-        <v>17.76666666666667</v>
+        <v>9.301857549999999</v>
       </c>
       <c r="G21">
-        <v>35.02</v>
+        <v>28.45284440333333</v>
       </c>
       <c r="H21">
         <v>21.81097294</v>
@@ -1888,22 +1888,22 @@
         <v>-19.61280330538828</v>
       </c>
       <c r="Q21">
-        <v>33.2280701754386</v>
+        <v>29.55555555555556</v>
       </c>
       <c r="R21">
-        <v>4.557639606666665</v>
+        <v>2.659986086666667</v>
       </c>
       <c r="S21">
-        <v>625.3756399867557</v>
+        <v>608.3157967967197</v>
       </c>
       <c r="T21">
-        <v>224.4938194824251</v>
+        <v>218.3697732090789</v>
       </c>
       <c r="U21">
-        <v>861.5431380822669</v>
+        <v>838.0407982126707</v>
       </c>
       <c r="V21">
-        <v>820.0452138153956</v>
+        <v>802.9853706253597</v>
       </c>
     </row>
     <row r="22">
@@ -1922,13 +1922,13 @@
         <v>4</v>
       </c>
       <c r="E22">
-        <v>19.13833333333333</v>
+        <v>18.25023845333333</v>
       </c>
       <c r="F22">
-        <v>8.976666666666667</v>
+        <v>7.428767183333333</v>
       </c>
       <c r="G22">
-        <v>28.115</v>
+        <v>25.67900563666667</v>
       </c>
       <c r="H22">
         <v>19.59409039666667</v>
@@ -1960,22 +1960,22 @@
         <v>-47.18462416197798</v>
       </c>
       <c r="Q22">
-        <v>3.6</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="R22">
-        <v>0.4557570633333334</v>
+        <v>1.343851943333334</v>
       </c>
       <c r="S22">
-        <v>63.21781832783648</v>
+        <v>310.6749730211045</v>
       </c>
       <c r="T22">
-        <v>22.69357580999258</v>
+        <v>111.5243492896273</v>
       </c>
       <c r="U22">
-        <v>87.09146007994869</v>
+        <v>427.9985884737924</v>
       </c>
       <c r="V22">
-        <v>115.4205218608859</v>
+        <v>362.8776765541539</v>
       </c>
     </row>
     <row r="23">
@@ -1994,13 +1994,13 @@
         <v>2</v>
       </c>
       <c r="E23">
-        <v>16.91833333333333</v>
+        <v>15.62478933666667</v>
       </c>
       <c r="F23">
-        <v>8.901666666666667</v>
+        <v>9.755520225</v>
       </c>
       <c r="G23">
-        <v>25.82</v>
+        <v>25.38030956166666</v>
       </c>
       <c r="H23">
         <v>16.15549779666667</v>
@@ -2032,22 +2032,22 @@
         <v>-13.44891339861088</v>
       </c>
       <c r="Q23">
-        <v>1.983050847457627</v>
+        <v>1.972222222222222</v>
       </c>
       <c r="R23">
-        <v>-0.7628355366666675</v>
+        <v>0.5307084599999996</v>
       </c>
       <c r="S23">
-        <v>-116.147619714007</v>
+        <v>134.6741235566853</v>
       </c>
       <c r="T23">
-        <v>-41.6940173332333</v>
+        <v>48.34455717419473</v>
       </c>
       <c r="U23">
-        <v>-160.0097259485685</v>
+        <v>185.5325977039381</v>
       </c>
       <c r="V23">
-        <v>-217.3604357411732</v>
+        <v>33.46130752951915</v>
       </c>
     </row>
     <row r="24">
@@ -2066,13 +2066,13 @@
         <v>60</v>
       </c>
       <c r="E24">
-        <v>20.02</v>
+        <v>17.90186749166667</v>
       </c>
       <c r="F24">
-        <v>7.49</v>
+        <v>8.436962761666667</v>
       </c>
       <c r="G24">
-        <v>27.51</v>
+        <v>26.33883025333333</v>
       </c>
       <c r="H24">
         <v>18.00963822</v>
@@ -2104,22 +2104,22 @@
         <v>-32.75939927760194</v>
       </c>
       <c r="Q24">
-        <v>33.47457627118644</v>
+        <v>31.72222222222222</v>
       </c>
       <c r="R24">
-        <v>-2.01036178</v>
+        <v>0.1077707283333318</v>
       </c>
       <c r="S24">
-        <v>-296.9179977740847</v>
+        <v>26.52844974946723</v>
       </c>
       <c r="T24">
-        <v>-106.5859479189022</v>
+        <v>9.523033243398492</v>
       </c>
       <c r="U24">
-        <v>-409.0464149847698</v>
+        <v>36.54668072152244</v>
       </c>
       <c r="V24">
-        <v>-87.38301335307352</v>
+        <v>236.0634341704784</v>
       </c>
     </row>
     <row r="25">
@@ -2138,13 +2138,13 @@
         <v>1</v>
       </c>
       <c r="E25">
-        <v>16.915</v>
+        <v>15.747574295</v>
       </c>
       <c r="F25">
-        <v>8.970000000000001</v>
+        <v>9.404695233333333</v>
       </c>
       <c r="G25">
-        <v>25.885</v>
+        <v>25.15226952833333</v>
       </c>
       <c r="H25">
         <v>14.5059828</v>
@@ -2179,19 +2179,19 @@
         <v>1</v>
       </c>
       <c r="R25">
-        <v>-2.409017199999999</v>
+        <v>-1.241591495</v>
       </c>
       <c r="S25">
-        <v>-373.2809210242492</v>
+        <v>-320.6441868973749</v>
       </c>
       <c r="T25">
-        <v>-133.9982793420382</v>
+        <v>-115.1030414503397</v>
       </c>
       <c r="U25">
-        <v>-514.2471108920734</v>
+        <v>-441.7325865031323</v>
       </c>
       <c r="V25">
-        <v>-532.7462564330942</v>
+        <v>-480.10952230622</v>
       </c>
     </row>
     <row r="26">
@@ -2210,13 +2210,13 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>19.155</v>
+        <v>18.33970316666667</v>
       </c>
       <c r="F26">
-        <v>10.21</v>
+        <v>10.95371604</v>
       </c>
       <c r="G26">
-        <v>29.365</v>
+        <v>29.29341920666667</v>
       </c>
       <c r="H26">
         <v>17.06013133166667</v>
@@ -2248,22 +2248,22 @@
         <v>-41.51681634409614</v>
       </c>
       <c r="Q26">
-        <v>0.9833333333333333</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="R26">
-        <v>-2.094868668333334</v>
+        <v>-1.279571834999999</v>
       </c>
       <c r="S26">
-        <v>-324.5480409123278</v>
+        <v>-330.396632601507</v>
       </c>
       <c r="T26">
-        <v>-116.5044249428869</v>
+        <v>-118.6039193954128</v>
       </c>
       <c r="U26">
-        <v>-447.1106959522448</v>
+        <v>-455.1679558054812</v>
       </c>
       <c r="V26">
-        <v>-472.6717655972301</v>
+        <v>-478.5203572864093</v>
       </c>
     </row>
     <row r="27">
@@ -2282,13 +2282,13 @@
         <v>4</v>
       </c>
       <c r="E27">
-        <v>20.59166666666667</v>
+        <v>19.853450675</v>
       </c>
       <c r="F27">
-        <v>12.02833333333333</v>
+        <v>12.68932163666667</v>
       </c>
       <c r="G27">
-        <v>32.62</v>
+        <v>32.54277231166667</v>
       </c>
       <c r="H27">
         <v>19.40672484</v>
@@ -2320,22 +2320,22 @@
         <v>-45.37199558404307</v>
       </c>
       <c r="Q27">
-        <v>3.677966101694915</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="R27">
-        <v>-1.18494182666667</v>
+        <v>-0.4467258350000023</v>
       </c>
       <c r="S27">
-        <v>-173.6510652044595</v>
+        <v>-109.1114283085731</v>
       </c>
       <c r="T27">
-        <v>-62.33627981698547</v>
+        <v>-39.16820503384677</v>
       </c>
       <c r="U27">
-        <v>-239.2288315719282</v>
+        <v>-150.3163800041799</v>
       </c>
       <c r="V27">
-        <v>-216.9653261095151</v>
+        <v>-152.4256892136287</v>
       </c>
     </row>
     <row r="28">
@@ -2354,13 +2354,13 @@
         <v>2</v>
       </c>
       <c r="E28">
-        <v>21.44833333333333</v>
+        <v>20.68569447666667</v>
       </c>
       <c r="F28">
-        <v>10.89</v>
+        <v>12.026124995</v>
       </c>
       <c r="G28">
-        <v>32.33833333333333</v>
+        <v>32.71181947166667</v>
       </c>
       <c r="H28">
         <v>20.44729365833333</v>
@@ -2392,22 +2392,22 @@
         <v>-14.72068404251895</v>
       </c>
       <c r="Q28">
-        <v>1.627118644067797</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="R28">
-        <v>-1.001039674999998</v>
+        <v>-0.2384008183333357</v>
       </c>
       <c r="S28">
-        <v>-133.7344546116859</v>
+        <v>-53.08215084613292</v>
       </c>
       <c r="T28">
-        <v>-48.00724011701544</v>
+        <v>-19.05513107297079</v>
       </c>
       <c r="U28">
-        <v>-184.2380712147861</v>
+        <v>-73.12814873489819</v>
       </c>
       <c r="V28">
-        <v>-224.7123658169449</v>
+        <v>-144.0600620513919</v>
       </c>
     </row>
     <row r="29">
@@ -2426,13 +2426,13 @@
         <v>4</v>
       </c>
       <c r="E29">
-        <v>21.98666666666666</v>
+        <v>22.35290135166667</v>
       </c>
       <c r="F29">
-        <v>11.99</v>
+        <v>12.50052412166667</v>
       </c>
       <c r="G29">
-        <v>33.97666666666667</v>
+        <v>34.85342547333333</v>
       </c>
       <c r="H29">
         <v>20.36209860166667</v>
@@ -2464,22 +2464,22 @@
         <v>-13.87268613283695</v>
       </c>
       <c r="Q29">
-        <v>3.933333333333333</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="R29">
-        <v>-1.624568064999998</v>
+        <v>-1.99080275</v>
       </c>
       <c r="S29">
-        <v>-226.59632815965</v>
+        <v>-462.7984949342356</v>
       </c>
       <c r="T29">
-        <v>-81.34227164705385</v>
+        <v>-166.1327930533154</v>
       </c>
       <c r="U29">
-        <v>-312.1683979323506</v>
+        <v>-637.5701932263233</v>
       </c>
       <c r="V29">
-        <v>-306.2250879616994</v>
+        <v>-542.4272547362851</v>
       </c>
     </row>
     <row r="30">
@@ -2498,13 +2498,13 @@
         <v>16</v>
       </c>
       <c r="E30">
-        <v>22.705</v>
+        <v>22.281533595</v>
       </c>
       <c r="F30">
-        <v>11.96666666666667</v>
+        <v>12.30114996333333</v>
       </c>
       <c r="G30">
-        <v>34.67166666666667</v>
+        <v>34.58268355833333</v>
       </c>
       <c r="H30">
         <v>23.50365367666667</v>
@@ -2536,22 +2536,22 @@
         <v>-14.20280962124995</v>
       </c>
       <c r="Q30">
-        <v>12.86440677966102</v>
+        <v>11.36111111111111</v>
       </c>
       <c r="R30">
-        <v>0.7986536766666674</v>
+        <v>1.222120081666667</v>
       </c>
       <c r="S30">
-        <v>105.279811622898</v>
+        <v>268.5030565343279</v>
       </c>
       <c r="T30">
-        <v>37.79275289027108</v>
+        <v>96.38571260206642</v>
       </c>
       <c r="U30">
-        <v>145.0377876634632</v>
+        <v>369.9008261917018</v>
       </c>
       <c r="V30">
-        <v>149.6869070974893</v>
+        <v>312.9101520089192</v>
       </c>
     </row>
     <row r="31">
@@ -2570,13 +2570,13 @@
         <v>8</v>
       </c>
       <c r="E31">
-        <v>17.7</v>
+        <v>18.41433809833334</v>
       </c>
       <c r="F31">
-        <v>8.788333333333334</v>
+        <v>8.493144115</v>
       </c>
       <c r="G31">
-        <v>26.48833333333333</v>
+        <v>26.90748221333333</v>
       </c>
       <c r="H31">
         <v>18.23542061666667</v>
@@ -2608,22 +2608,22 @@
         <v>-18.15451561016695</v>
       </c>
       <c r="Q31">
-        <v>6.135593220338983</v>
+        <v>5.694444444444445</v>
       </c>
       <c r="R31">
-        <v>0.5354206166666664</v>
+        <v>-0.1789174816666694</v>
       </c>
       <c r="S31">
-        <v>79.29394268193208</v>
+        <v>-44.16176769706797</v>
       </c>
       <c r="T31">
-        <v>28.46449224479613</v>
+        <v>-15.85294225022952</v>
       </c>
       <c r="U31">
-        <v>109.2385885234576</v>
+        <v>-60.83906294430943</v>
       </c>
       <c r="V31">
-        <v>118.2671385129772</v>
+        <v>-5.188571866022855</v>
       </c>
     </row>
     <row r="32">
@@ -2642,13 +2642,13 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>15.83</v>
+        <v>14.78553080333333</v>
       </c>
       <c r="F32">
-        <v>13.04333333333333</v>
+        <v>14.93936280333333</v>
       </c>
       <c r="G32">
-        <v>28.87333333333333</v>
+        <v>29.72489360666667</v>
       </c>
       <c r="H32">
         <v>13.97646859166667</v>
@@ -2683,19 +2683,19 @@
         <v>1</v>
       </c>
       <c r="R32">
-        <v>-1.853531408333334</v>
+        <v>-0.8090622116666673</v>
       </c>
       <c r="S32">
-        <v>-294.1341813919292</v>
+        <v>-213.9814934290758</v>
       </c>
       <c r="T32">
-        <v>-105.5866292176156</v>
+        <v>-76.81386943607849</v>
       </c>
       <c r="U32">
-        <v>-405.2113153288608</v>
+        <v>-294.7896840758303</v>
       </c>
       <c r="V32">
-        <v>-486.5090261872564</v>
+        <v>-406.356338224403</v>
       </c>
     </row>
     <row r="33">
@@ -2714,13 +2714,13 @@
         <v>8</v>
       </c>
       <c r="E33">
-        <v>18.02666666666667</v>
+        <v>18.24266179833333</v>
       </c>
       <c r="F33">
-        <v>10.27333333333333</v>
+        <v>9.758735895000001</v>
       </c>
       <c r="G33">
-        <v>28.3</v>
+        <v>28.00139769333333</v>
       </c>
       <c r="H33">
         <v>18.806023575</v>
@@ -2752,22 +2752,22 @@
         <v>-36.88238572933939</v>
       </c>
       <c r="Q33">
-        <v>6</v>
+        <v>5.861111111111111</v>
       </c>
       <c r="R33">
-        <v>0.7793569083333338</v>
+        <v>0.5633617766666674</v>
       </c>
       <c r="S33">
-        <v>112.0333892840541</v>
+        <v>134.9730967463636</v>
       </c>
       <c r="T33">
-        <v>40.21711410196814</v>
+        <v>48.45188088331</v>
       </c>
       <c r="U33">
-        <v>154.3417933193246</v>
+        <v>185.9444754356057</v>
       </c>
       <c r="V33">
-        <v>97.52157085087619</v>
+        <v>120.4612783131856</v>
       </c>
     </row>
     <row r="34">
@@ -2786,13 +2786,13 @@
         <v>1</v>
       </c>
       <c r="E34">
-        <v>19.39833333333333</v>
+        <v>17.26795337666667</v>
       </c>
       <c r="F34">
-        <v>10.76666666666667</v>
+        <v>10.94251334666667</v>
       </c>
       <c r="G34">
-        <v>30.165</v>
+        <v>28.21046672333333</v>
       </c>
       <c r="H34">
         <v>17.420768235</v>
@@ -2824,22 +2824,22 @@
         <v>-89.1658725433148</v>
       </c>
       <c r="Q34">
-        <v>0.7333333333333333</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="R34">
-        <v>-1.977565098333333</v>
+        <v>0.1528148583333326</v>
       </c>
       <c r="S34">
-        <v>-303.5711138379897</v>
+        <v>39.09704986394755</v>
       </c>
       <c r="T34">
-        <v>-108.9742459931245</v>
+        <v>14.03483841269912</v>
       </c>
       <c r="U34">
-        <v>-418.2120206227567</v>
+        <v>53.86169987410702</v>
       </c>
       <c r="V34">
-        <v>-387.2746651172149</v>
+        <v>-44.60650141527756</v>
       </c>
     </row>
     <row r="35">
@@ -2858,13 +2858,13 @@
         <v>4</v>
       </c>
       <c r="E35">
-        <v>21.27166666666667</v>
+        <v>20.72395750666667</v>
       </c>
       <c r="F35">
-        <v>12.33</v>
+        <v>12.162037295</v>
       </c>
       <c r="G35">
-        <v>33.60166666666667</v>
+        <v>32.88599480166667</v>
       </c>
       <c r="H35">
         <v>20.34924550333333</v>
@@ -2896,22 +2896,22 @@
         <v>-26.63439032743988</v>
       </c>
       <c r="Q35">
-        <v>3.610169491525424</v>
+        <v>3.5</v>
       </c>
       <c r="R35">
-        <v>-0.9224211633333361</v>
+        <v>-0.374712003333336</v>
       </c>
       <c r="S35">
-        <v>-134.6648537645158</v>
+        <v>-91.17407380077907</v>
       </c>
       <c r="T35">
-        <v>-48.34122955649285</v>
+        <v>-32.72915469771556</v>
       </c>
       <c r="U35">
-        <v>-185.5198272579462</v>
+        <v>-125.6051445427758</v>
       </c>
       <c r="V35">
-        <v>13.00337933585752</v>
+        <v>56.49415929959423</v>
       </c>
     </row>
     <row r="36">
@@ -2930,13 +2930,13 @@
         <v>8</v>
       </c>
       <c r="E36">
-        <v>20.25666666666667</v>
+        <v>18.31235483166667</v>
       </c>
       <c r="F36">
-        <v>13.38</v>
+        <v>14.00340576833333</v>
       </c>
       <c r="G36">
-        <v>33.63666666666667</v>
+        <v>32.3157606</v>
       </c>
       <c r="H36">
         <v>19.53381813333333</v>
@@ -2968,22 +2968,22 @@
         <v>-59.83473716765864</v>
       </c>
       <c r="Q36">
-        <v>6.220338983050848</v>
+        <v>5.944444444444445</v>
       </c>
       <c r="R36">
-        <v>-0.7228485333333339</v>
+        <v>1.221463301666667</v>
       </c>
       <c r="S36">
-        <v>-105.1584228883923</v>
+        <v>296.1596805234695</v>
       </c>
       <c r="T36">
-        <v>-37.74917744711517</v>
+        <v>106.3137314699634</v>
       </c>
       <c r="U36">
-        <v>-144.8705575627574</v>
+        <v>408.001726029871</v>
       </c>
       <c r="V36">
-        <v>-139.1109816541864</v>
+        <v>262.2071217576753</v>
       </c>
     </row>
     <row r="37">
@@ -3002,13 +3002,13 @@
         <v>16</v>
       </c>
       <c r="E37">
-        <v>21.50666666666667</v>
+        <v>21.03022653333333</v>
       </c>
       <c r="F37">
-        <v>12.89166666666667</v>
+        <v>13.001140755</v>
       </c>
       <c r="G37">
-        <v>34.39833333333333</v>
+        <v>34.03136728833334</v>
       </c>
       <c r="H37">
         <v>21.70943054333333</v>
@@ -3040,22 +3040,22 @@
         <v>-18.33506730737627</v>
       </c>
       <c r="Q37">
-        <v>11.2</v>
+        <v>10.77777777777778</v>
       </c>
       <c r="R37">
-        <v>0.2027638766666655</v>
+        <v>0.6792040099999994</v>
       </c>
       <c r="S37">
-        <v>28.79298493513431</v>
+        <v>160.7478211381349</v>
       </c>
       <c r="T37">
-        <v>10.33594331004821</v>
+        <v>57.7043460495869</v>
       </c>
       <c r="U37">
-        <v>39.66639729730503</v>
+        <v>221.4527931823003</v>
       </c>
       <c r="V37">
-        <v>60.14408406511946</v>
+        <v>192.0989202681201</v>
       </c>
     </row>
     <row r="38">
@@ -3074,13 +3074,13 @@
         <v>2</v>
       </c>
       <c r="E38">
-        <v>22.74666666666667</v>
+        <v>19.93975524333333</v>
       </c>
       <c r="F38">
-        <v>12.90666666666667</v>
+        <v>13.90334904166667</v>
       </c>
       <c r="G38">
-        <v>35.65333333333334</v>
+        <v>33.843104285</v>
       </c>
       <c r="H38">
         <v>21.53524523833333</v>
@@ -3115,19 +3115,19 @@
         <v>2</v>
       </c>
       <c r="R38">
-        <v>-1.211421428333335</v>
+        <v>1.595489994999998</v>
       </c>
       <c r="S38">
-        <v>-167.1434182175345</v>
+        <v>366.8908348201983</v>
       </c>
       <c r="T38">
-        <v>-60.00020141142262</v>
+        <v>131.7044022431481</v>
       </c>
       <c r="U38">
-        <v>-230.263630102351</v>
+        <v>505.4438659799901</v>
       </c>
       <c r="V38">
-        <v>-247.9540369756616</v>
+        <v>286.0802160620711</v>
       </c>
     </row>
     <row r="39">
@@ -3146,13 +3146,13 @@
         <v>2</v>
       </c>
       <c r="E39">
-        <v>22.77666666666667</v>
+        <v>22.18978647833334</v>
       </c>
       <c r="F39">
-        <v>12.88833333333333</v>
+        <v>12.43652800666667</v>
       </c>
       <c r="G39">
-        <v>35.665</v>
+        <v>34.626314485</v>
       </c>
       <c r="H39">
         <v>20.42762157666667</v>
@@ -3184,22 +3184,22 @@
         <v>-27.91498983744396</v>
       </c>
       <c r="Q39">
-        <v>1.88135593220339</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="R39">
-        <v>-2.349045090000001</v>
+        <v>-1.762164901666669</v>
       </c>
       <c r="S39">
-        <v>-323.4794829118566</v>
+        <v>-404.4368167751635</v>
       </c>
       <c r="T39">
-        <v>-116.1208400196408</v>
+        <v>-145.1824470474946</v>
       </c>
       <c r="U39">
-        <v>-445.6386066125186</v>
+        <v>-557.1687510691279</v>
       </c>
       <c r="V39">
-        <v>-422.8886981671198</v>
+        <v>-503.8460320304268</v>
       </c>
     </row>
     <row r="40">
@@ -3218,13 +3218,13 @@
         <v>8</v>
       </c>
       <c r="E40">
-        <v>22.43166666666667</v>
+        <v>20.38238114833333</v>
       </c>
       <c r="F40">
-        <v>13.03166666666667</v>
+        <v>13.65231196166667</v>
       </c>
       <c r="G40">
-        <v>35.46333333333334</v>
+        <v>34.03469311</v>
       </c>
       <c r="H40">
         <v>20.91067990666667</v>
@@ -3256,22 +3256,22 @@
         <v>-22.87255892779823</v>
       </c>
       <c r="Q40">
-        <v>6.915254237288136</v>
+        <v>6.972222222222222</v>
       </c>
       <c r="R40">
-        <v>-1.520986760000003</v>
+        <v>0.5282987583333316</v>
       </c>
       <c r="S40">
-        <v>-191.6526696659098</v>
+        <v>110.9475660565777</v>
       </c>
       <c r="T40">
-        <v>-68.79839423904454</v>
+        <v>39.82733140492535</v>
       </c>
       <c r="U40">
-        <v>-264.0285804053847</v>
+        <v>152.8459186945592</v>
       </c>
       <c r="V40">
-        <v>-131.9977107346377</v>
+        <v>170.6025249878498</v>
       </c>
     </row>
     <row r="41">
@@ -3290,13 +3290,13 @@
         <v>16</v>
       </c>
       <c r="E41">
-        <v>22.64166666666667</v>
+        <v>20.36408032333333</v>
       </c>
       <c r="F41">
-        <v>12.98166666666667</v>
+        <v>12.75228142833333</v>
       </c>
       <c r="G41">
-        <v>35.62333333333333</v>
+        <v>33.11636175166667</v>
       </c>
       <c r="H41">
         <v>23.87834243333333</v>
@@ -3328,22 +3328,22 @@
         <v>-117.1143203317945</v>
       </c>
       <c r="Q41">
-        <v>11.22033898305085</v>
+        <v>10.22222222222222</v>
       </c>
       <c r="R41">
-        <v>1.236675766666668</v>
+        <v>3.514262110000001</v>
       </c>
       <c r="S41">
-        <v>150.1723832207024</v>
+        <v>711.241553830229</v>
       </c>
       <c r="T41">
-        <v>53.90803500230344</v>
+        <v>255.3174808621335</v>
       </c>
       <c r="U41">
-        <v>206.8836360431256</v>
+        <v>979.8355436971934</v>
       </c>
       <c r="V41">
-        <v>161.9857108159383</v>
+        <v>723.0548814254648</v>
       </c>
     </row>
     <row r="42">
@@ -3362,13 +3362,13 @@
         <v>1</v>
       </c>
       <c r="E42">
-        <v>19.05333333333333</v>
+        <v>17.53820831</v>
       </c>
       <c r="F42">
-        <v>13.72</v>
+        <v>14.17948345166667</v>
       </c>
       <c r="G42">
-        <v>32.77333333333333</v>
+        <v>31.71769176166667</v>
       </c>
       <c r="H42">
         <v>18.11070592666667</v>
@@ -3403,19 +3403,19 @@
         <v>1</v>
       </c>
       <c r="R42">
-        <v>-0.9426274066666664</v>
+        <v>0.5724976166666664</v>
       </c>
       <c r="S42">
-        <v>-125.9396698555875</v>
+        <v>127.4808411860072</v>
       </c>
       <c r="T42">
-        <v>-45.20911225585194</v>
+        <v>45.762353246259</v>
       </c>
       <c r="U42">
-        <v>-173.4996559487438</v>
+        <v>175.6228368010717</v>
       </c>
       <c r="V42">
-        <v>-169.484414241698</v>
+        <v>83.93609679989677</v>
       </c>
     </row>
     <row r="43">
@@ -3434,13 +3434,13 @@
         <v>2</v>
       </c>
       <c r="E43">
-        <v>19.465</v>
+        <v>16.30180951666667</v>
       </c>
       <c r="F43">
-        <v>13.27833333333333</v>
+        <v>14.26811456666667</v>
       </c>
       <c r="G43">
-        <v>32.74333333333333</v>
+        <v>30.56992408333333</v>
       </c>
       <c r="H43">
         <v>15.78657563583333</v>
@@ -3472,22 +3472,22 @@
         <v>-75.73444829476304</v>
       </c>
       <c r="Q43">
-        <v>1.932203389830508</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="R43">
-        <v>-3.678424364166666</v>
+        <v>-0.5152338808333319</v>
       </c>
       <c r="S43">
-        <v>-501.4372609232367</v>
+        <v>-117.0598424589533</v>
       </c>
       <c r="T43">
-        <v>-180.0031193057773</v>
+        <v>-42.02148190834222</v>
       </c>
       <c r="U43">
-        <v>-690.8005424329145</v>
+        <v>-161.2664414265293</v>
       </c>
       <c r="V43">
-        <v>-634.6441805638232</v>
+        <v>-250.2667620995397</v>
       </c>
     </row>
     <row r="44">
@@ -3506,13 +3506,13 @@
         <v>4</v>
       </c>
       <c r="E44">
-        <v>16.74666666666667</v>
+        <v>15.87066645166667</v>
       </c>
       <c r="F44">
-        <v>14.75</v>
+        <v>15.19955595333333</v>
       </c>
       <c r="G44">
-        <v>31.49666666666667</v>
+        <v>31.070222405</v>
       </c>
       <c r="H44">
         <v>16.34161234133333</v>
@@ -3544,22 +3544,22 @@
         <v>-48.41958483703014</v>
       </c>
       <c r="Q44">
-        <v>3.491525423728814</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="R44">
-        <v>-0.4050543253333316</v>
+        <v>0.4709458896666678</v>
       </c>
       <c r="S44">
-        <v>-52.44037150035414</v>
+        <v>101.6183750593671</v>
       </c>
       <c r="T44">
-        <v>-18.82474874371687</v>
+        <v>36.4783910469523</v>
       </c>
       <c r="U44">
-        <v>-72.24400717874428</v>
+        <v>139.993642440761</v>
       </c>
       <c r="V44">
-        <v>-130.5055410786543</v>
+        <v>23.55320548106702</v>
       </c>
     </row>
     <row r="45">
@@ -3578,13 +3578,13 @@
         <v>8</v>
       </c>
       <c r="E45">
-        <v>17.50333333333333</v>
+        <v>15.01120542833333</v>
       </c>
       <c r="F45">
-        <v>17.73166666666667</v>
+        <v>18.91071100833333</v>
       </c>
       <c r="G45">
-        <v>35.235</v>
+        <v>33.92191643666666</v>
       </c>
       <c r="H45">
         <v>17.679803865</v>
@@ -3616,22 +3616,22 @@
         <v>-17.57251536543271</v>
       </c>
       <c r="Q45">
-        <v>6.35593220338983</v>
+        <v>5.916666666666667</v>
       </c>
       <c r="R45">
-        <v>0.1764705316666664</v>
+        <v>2.668598436666667</v>
       </c>
       <c r="S45">
-        <v>22.8871831328695</v>
+        <v>576.8356955619695</v>
       </c>
       <c r="T45">
-        <v>8.215911893850588</v>
+        <v>207.0692240478865</v>
       </c>
       <c r="U45">
-        <v>31.53032244520031</v>
+        <v>794.6725192603461</v>
       </c>
       <c r="V45">
-        <v>44.62816613979442</v>
+        <v>598.5766785688944</v>
       </c>
     </row>
     <row r="46">
@@ -3650,13 +3650,13 @@
         <v>8</v>
       </c>
       <c r="E46">
-        <v>20.60166666666667</v>
+        <v>19.261428105</v>
       </c>
       <c r="F46">
-        <v>14.57333333333333</v>
+        <v>14.94687716333333</v>
       </c>
       <c r="G46">
-        <v>35.175</v>
+        <v>34.20830526833333</v>
       </c>
       <c r="H46">
         <v>20.82464430333333</v>
@@ -3688,22 +3688,22 @@
         <v>-20.05767258519995</v>
       </c>
       <c r="Q46">
-        <v>5.491525423728813</v>
+        <v>4.444444444444445</v>
       </c>
       <c r="R46">
-        <v>0.2229776366666663</v>
+        <v>1.563216198333333</v>
       </c>
       <c r="S46">
-        <v>30.33631996665316</v>
+        <v>354.4617558859168</v>
       </c>
       <c r="T46">
-        <v>10.88996101367036</v>
+        <v>127.2426816000727</v>
       </c>
       <c r="U46">
-        <v>41.79255895303437</v>
+        <v>488.3210569291933</v>
       </c>
       <c r="V46">
-        <v>112.4419345023711</v>
+        <v>436.5673704216348</v>
       </c>
     </row>
     <row r="47">
@@ -3722,13 +3722,13 @@
         <v>1</v>
       </c>
       <c r="E47">
-        <v>21.58333333333333</v>
+        <v>19.57522699166667</v>
       </c>
       <c r="F47">
-        <v>15.355</v>
+        <v>15.47139307</v>
       </c>
       <c r="G47">
-        <v>36.93833333333333</v>
+        <v>35.04662006166667</v>
       </c>
       <c r="H47">
         <v>19.75802325166667</v>
@@ -3763,19 +3763,19 @@
         <v>1</v>
       </c>
       <c r="R47">
-        <v>-1.825310081666665</v>
+        <v>0.1827962599999999</v>
       </c>
       <c r="S47">
-        <v>-248.9099067102928</v>
+        <v>41.54526992480934</v>
       </c>
       <c r="T47">
-        <v>-89.35227420369485</v>
+        <v>14.91368663967515</v>
       </c>
       <c r="U47">
-        <v>-342.9084991725798</v>
+        <v>57.23446826974759</v>
       </c>
       <c r="V47">
-        <v>-323.0931270688039</v>
+        <v>-32.63795043370183</v>
       </c>
     </row>
     <row r="48">
@@ -3794,13 +3794,13 @@
         <v>8</v>
       </c>
       <c r="E48">
-        <v>20.42333333333333</v>
+        <v>19.22971065333333</v>
       </c>
       <c r="F48">
-        <v>15.33</v>
+        <v>14.82748369166667</v>
       </c>
       <c r="G48">
-        <v>35.75333333333333</v>
+        <v>34.057194345</v>
       </c>
       <c r="H48">
         <v>20.94664231166667</v>
@@ -3832,22 +3832,22 @@
         <v>-20.85795344753737</v>
       </c>
       <c r="Q48">
-        <v>6.203389830508475</v>
+        <v>6.194444444444445</v>
       </c>
       <c r="R48">
-        <v>0.5233089783333362</v>
+        <v>1.716931658333333</v>
       </c>
       <c r="S48">
-        <v>71.30657492840973</v>
+        <v>389.917878381722</v>
       </c>
       <c r="T48">
-        <v>25.59723202558298</v>
+        <v>139.9705204447207</v>
       </c>
       <c r="U48">
-        <v>98.23486301932302</v>
+        <v>537.1668658895682</v>
       </c>
       <c r="V48">
-        <v>162.809527529156</v>
+        <v>481.4208309824683</v>
       </c>
     </row>
     <row r="49">
@@ -3866,13 +3866,13 @@
         <v>2</v>
       </c>
       <c r="E49">
-        <v>21.07666666666667</v>
+        <v>18.94378669166667</v>
       </c>
       <c r="F49">
-        <v>13.84</v>
+        <v>14.260492525</v>
       </c>
       <c r="G49">
-        <v>34.91666666666667</v>
+        <v>33.20427921666666</v>
       </c>
       <c r="H49">
         <v>18.28368143833333</v>
@@ -3904,22 +3904,22 @@
         <v>-18.09214410546101</v>
       </c>
       <c r="Q49">
-        <v>1.864406779661017</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="R49">
-        <v>-2.792985228333336</v>
+        <v>-0.6601052533333345</v>
       </c>
       <c r="S49">
-        <v>-389.7445376506309</v>
+        <v>-153.522960636802</v>
       </c>
       <c r="T49">
-        <v>-139.9082955668931</v>
+        <v>-55.11080638244176</v>
       </c>
       <c r="U49">
-        <v>-536.9280645870024</v>
+        <v>-211.4995289511308</v>
       </c>
       <c r="V49">
-        <v>-449.0436900273857</v>
+        <v>-212.8221130135568</v>
       </c>
     </row>
     <row r="50">
@@ -3938,13 +3938,13 @@
         <v>16</v>
       </c>
       <c r="E50">
-        <v>24.175</v>
+        <v>21.528021425</v>
       </c>
       <c r="F50">
-        <v>12.51833333333333</v>
+        <v>12.991011935</v>
       </c>
       <c r="G50">
-        <v>36.69333333333334</v>
+        <v>34.51903335999999</v>
       </c>
       <c r="H50">
         <v>22.554342445</v>
@@ -3976,22 +3976,22 @@
         <v>-17.27527521063897</v>
       </c>
       <c r="Q50">
-        <v>11.5</v>
+        <v>10.13888888888889</v>
       </c>
       <c r="R50">
-        <v>-1.620657555000001</v>
+        <v>1.026321020000001</v>
       </c>
       <c r="S50">
-        <v>-215.1207342787013</v>
+        <v>227.0507740792346</v>
       </c>
       <c r="T50">
-        <v>-77.22282768979022</v>
+        <v>81.50540607972523</v>
       </c>
       <c r="U50">
-        <v>-296.3591490083606</v>
+        <v>312.7944612751055</v>
       </c>
       <c r="V50">
-        <v>-136.4074613094751</v>
+        <v>305.7640470484608</v>
       </c>
     </row>
     <row r="51">
@@ -4010,13 +4010,13 @@
         <v>4</v>
       </c>
       <c r="E51">
-        <v>22.30166666666667</v>
+        <v>21.14341975333333</v>
       </c>
       <c r="F51">
-        <v>13.18333333333333</v>
+        <v>13.43872288833333</v>
       </c>
       <c r="G51">
-        <v>35.485</v>
+        <v>34.58214264166666</v>
       </c>
       <c r="H51">
         <v>21.7940397</v>
@@ -4048,22 +4048,22 @@
         <v>-25.37122508632021</v>
       </c>
       <c r="Q51">
-        <v>3.254237288135593</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="R51">
-        <v>-0.5076269666666668</v>
+        <v>0.6506199466666658</v>
       </c>
       <c r="S51">
-        <v>-67.04981896849986</v>
+        <v>143.2283694716211</v>
       </c>
       <c r="T51">
-        <v>-24.06916578356405</v>
+        <v>51.41531211801782</v>
       </c>
       <c r="U51">
-        <v>-92.37058137280924</v>
+        <v>197.3172778197758</v>
       </c>
       <c r="V51">
-        <v>-47.58440531600711</v>
+        <v>162.6937831241138</v>
       </c>
     </row>
     <row r="52">
@@ -4082,13 +4082,13 @@
         <v>1</v>
       </c>
       <c r="E52">
-        <v>24.76</v>
+        <v>24.5741344</v>
       </c>
       <c r="F52">
-        <v>14.07666666666667</v>
+        <v>14.09356097333333</v>
       </c>
       <c r="G52">
-        <v>38.83666666666667</v>
+        <v>38.66769537333333</v>
       </c>
       <c r="H52">
         <v>21.62069094333333</v>
@@ -4123,19 +4123,19 @@
         <v>1</v>
       </c>
       <c r="R52">
-        <v>-3.139309056666665</v>
+        <v>-2.953443456666665</v>
       </c>
       <c r="S52">
-        <v>-418.3356759532402</v>
+        <v>-655.9462302755971</v>
       </c>
       <c r="T52">
-        <v>-150.1717811114196</v>
+        <v>-235.4678775348297</v>
       </c>
       <c r="U52">
-        <v>-576.3163896824536</v>
+        <v>-903.6584374422379</v>
       </c>
       <c r="V52">
-        <v>-678.8690712138427</v>
+        <v>-916.4796255361997</v>
       </c>
     </row>
     <row r="53">
@@ -4154,13 +4154,13 @@
         <v>4</v>
       </c>
       <c r="E53">
-        <v>20.80333333333333</v>
+        <v>20.38869288666666</v>
       </c>
       <c r="F53">
-        <v>19.93166666666666</v>
+        <v>20.37180383833334</v>
       </c>
       <c r="G53">
-        <v>40.735</v>
+        <v>40.760496725</v>
       </c>
       <c r="H53">
         <v>21.31049074166667</v>
@@ -4192,22 +4192,22 @@
         <v>-13.84974560724965</v>
       </c>
       <c r="Q53">
-        <v>3.033898305084746</v>
+        <v>2.555555555555555</v>
       </c>
       <c r="R53">
-        <v>0.507157408333331</v>
+        <v>0.9217978550000012</v>
       </c>
       <c r="S53">
-        <v>61.33437873671558</v>
+        <v>185.799970016746</v>
       </c>
       <c r="T53">
-        <v>22.01746929010303</v>
+        <v>66.69742513421649</v>
       </c>
       <c r="U53">
-        <v>84.49675642990395</v>
+        <v>255.9656612579417</v>
       </c>
       <c r="V53">
-        <v>96.06621273209106</v>
+        <v>220.5318040121215</v>
       </c>
     </row>
     <row r="54">
@@ -4226,13 +4226,13 @@
         <v>60</v>
       </c>
       <c r="E54">
-        <v>20.26333333333333</v>
+        <v>18.91503501666667</v>
       </c>
       <c r="F54">
-        <v>18.00833333333333</v>
+        <v>18.94353111666667</v>
       </c>
       <c r="G54">
-        <v>38.27166666666666</v>
+        <v>37.85856613333333</v>
       </c>
       <c r="H54">
         <v>20.86098047666666</v>
@@ -4264,22 +4264,22 @@
         <v>-16.63200330823436</v>
       </c>
       <c r="Q54">
-        <v>33.78947368421053</v>
+        <v>29.75</v>
       </c>
       <c r="R54">
-        <v>0.597647143333333</v>
+        <v>1.945945459999997</v>
       </c>
       <c r="S54">
-        <v>73.68687079994217</v>
+        <v>399.8753927359298</v>
       </c>
       <c r="T54">
-        <v>26.45169721023565</v>
+        <v>143.5450127770004</v>
       </c>
       <c r="U54">
-        <v>101.5140562651101</v>
+        <v>550.8847461773343</v>
       </c>
       <c r="V54">
-        <v>312.6326797885224</v>
+        <v>638.8212017245102</v>
       </c>
     </row>
     <row r="55">
@@ -4298,13 +4298,13 @@
         <v>16</v>
       </c>
       <c r="E55">
-        <v>18.29</v>
+        <v>16.31114664333333</v>
       </c>
       <c r="F55">
-        <v>20.22333333333333</v>
+        <v>20.07515013166667</v>
       </c>
       <c r="G55">
-        <v>38.51333333333334</v>
+        <v>36.38629677500001</v>
       </c>
       <c r="H55">
         <v>20.22225977666667</v>
@@ -4336,22 +4336,22 @@
         <v>-35.62441400183615</v>
       </c>
       <c r="Q55">
-        <v>10.33898305084746</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="R55">
-        <v>1.932259776666669</v>
+        <v>3.911113133333334</v>
       </c>
       <c r="S55">
-        <v>233.6765817151533</v>
+        <v>788.3132129669794</v>
       </c>
       <c r="T55">
-        <v>83.88390112851657</v>
+        <v>282.9842302958388</v>
       </c>
       <c r="U55">
-        <v>321.9224457023527</v>
+        <v>1086.012623238202</v>
       </c>
       <c r="V55">
-        <v>343.31591594543</v>
+        <v>897.9525471972561</v>
       </c>
     </row>
     <row r="56">
@@ -4370,13 +4370,13 @@
         <v>1</v>
       </c>
       <c r="E56">
-        <v>20.10833333333333</v>
+        <v>15.5350772</v>
       </c>
       <c r="F56">
-        <v>19.19833333333333</v>
+        <v>21.23301645166667</v>
       </c>
       <c r="G56">
-        <v>39.30666666666667</v>
+        <v>36.76809365166667</v>
       </c>
       <c r="H56">
         <v>17.13503540333333</v>
@@ -4411,19 +4411,19 @@
         <v>1</v>
       </c>
       <c r="R56">
-        <v>-2.973297930000001</v>
+        <v>1.599958203333333</v>
       </c>
       <c r="S56">
-        <v>-434.9449519907423</v>
+        <v>390.0796132327102</v>
       </c>
       <c r="T56">
-        <v>-156.13408533001</v>
+        <v>140.028579109178</v>
       </c>
       <c r="U56">
-        <v>-599.1980097579128</v>
+        <v>537.3896784555656</v>
       </c>
       <c r="V56">
-        <v>-604.3363414977691</v>
+        <v>220.6882237256834</v>
       </c>
     </row>
     <row r="57">
@@ -4442,13 +4442,13 @@
         <v>2</v>
       </c>
       <c r="E57">
-        <v>20.47166666666667</v>
+        <v>19.57160066</v>
       </c>
       <c r="F57">
-        <v>16.93</v>
+        <v>17.35135972666667</v>
       </c>
       <c r="G57">
-        <v>37.40166666666667</v>
+        <v>36.92296038666667</v>
       </c>
       <c r="H57">
         <v>19.28397925833333</v>
@@ -4480,22 +4480,22 @@
         <v>-47.09757075423161</v>
       </c>
       <c r="Q57">
-        <v>1.983050847457627</v>
+        <v>1.972222222222222</v>
       </c>
       <c r="R57">
-        <v>-1.187687408333336</v>
+        <v>-0.2876214016666694</v>
       </c>
       <c r="S57">
-        <v>-161.8305207073712</v>
+        <v>-65.31730048343599</v>
       </c>
       <c r="T57">
-        <v>-58.09300743341532</v>
+        <v>-23.44723607097702</v>
       </c>
       <c r="U57">
-        <v>-222.9443645273242</v>
+        <v>-89.98379283010381</v>
       </c>
       <c r="V57">
-        <v>-291.8501316858723</v>
+        <v>-195.336911461937</v>
       </c>
     </row>
     <row r="58">
@@ -4514,13 +4514,13 @@
         <v>8</v>
       </c>
       <c r="E58">
-        <v>21.13833333333333</v>
+        <v>18.96839964333333</v>
       </c>
       <c r="F58">
-        <v>15.39666666666667</v>
+        <v>15.34068266333333</v>
       </c>
       <c r="G58">
-        <v>36.535</v>
+        <v>34.30908230666667</v>
       </c>
       <c r="H58">
         <v>18.90949340833333</v>
@@ -4552,22 +4552,22 @@
         <v>-115.3658925430513</v>
       </c>
       <c r="Q58">
-        <v>5.186440677966102</v>
+        <v>5.111111111111111</v>
       </c>
       <c r="R58">
-        <v>-2.228839924999999</v>
+        <v>-0.05890623500000203</v>
       </c>
       <c r="S58">
-        <v>-310.6780664315124</v>
+        <v>-13.6849032130178</v>
       </c>
       <c r="T58">
-        <v>-111.5254597446455</v>
+        <v>-4.912529358519212</v>
       </c>
       <c r="U58">
-        <v>-428.0028500828794</v>
+        <v>-18.85288409818001</v>
       </c>
       <c r="V58">
-        <v>-290.1154881713587</v>
+        <v>6.877675047135824</v>
       </c>
     </row>
     <row r="59">
@@ -4586,13 +4586,13 @@
         <v>2</v>
       </c>
       <c r="E59">
-        <v>21.78166666666667</v>
+        <v>19.19157407666667</v>
       </c>
       <c r="F59">
-        <v>15.13833333333333</v>
+        <v>15.447678765</v>
       </c>
       <c r="G59">
-        <v>36.92</v>
+        <v>34.63925284166667</v>
       </c>
       <c r="H59">
         <v>20.00068769833333</v>
@@ -4624,22 +4624,22 @@
         <v>-92.68541304918264</v>
       </c>
       <c r="Q59">
-        <v>1.983050847457627</v>
+        <v>2</v>
       </c>
       <c r="R59">
-        <v>-1.780978968333333</v>
+        <v>0.8091136216666648</v>
       </c>
       <c r="S59">
-        <v>-243.9831776131483</v>
+        <v>184.7393259310027</v>
       </c>
       <c r="T59">
-        <v>-87.58370478420707</v>
+        <v>66.31668110343686</v>
       </c>
       <c r="U59">
-        <v>-336.1212350461341</v>
+        <v>254.5044744518183</v>
       </c>
       <c r="V59">
-        <v>-342.6861893479567</v>
+        <v>86.03631419619435</v>
       </c>
     </row>
     <row r="60">
@@ -4658,13 +4658,13 @@
         <v>16</v>
       </c>
       <c r="E60">
-        <v>22.76</v>
+        <v>21.72608776333333</v>
       </c>
       <c r="F60">
-        <v>14.44666666666667</v>
+        <v>14.51037426833333</v>
       </c>
       <c r="G60">
-        <v>37.20666666666666</v>
+        <v>36.23646203166666</v>
       </c>
       <c r="H60">
         <v>22.56712392</v>
@@ -4696,22 +4696,22 @@
         <v>-16.31624570525685</v>
       </c>
       <c r="Q60">
-        <v>12.3</v>
+        <v>12.05555555555556</v>
       </c>
       <c r="R60">
-        <v>-0.1928760799999978</v>
+        <v>0.841036156666668</v>
       </c>
       <c r="S60">
-        <v>-25.04292910927768</v>
+        <v>181.9994894281599</v>
       </c>
       <c r="T60">
-        <v>-8.989769423843269</v>
+        <v>65.33315005113434</v>
       </c>
       <c r="U60">
-        <v>-34.5001665431608</v>
+        <v>250.7299632819532</v>
       </c>
       <c r="V60">
-        <v>34.3741114272206</v>
+        <v>241.4165299646582</v>
       </c>
     </row>
     <row r="61">
@@ -4730,13 +4730,13 @@
         <v>4</v>
       </c>
       <c r="E61">
-        <v>23.685</v>
+        <v>22.25263283333333</v>
       </c>
       <c r="F61">
-        <v>13.57833333333333</v>
+        <v>14.002622765</v>
       </c>
       <c r="G61">
-        <v>37.26333333333334</v>
+        <v>36.25525559833333</v>
       </c>
       <c r="H61">
         <v>22.54396694333333</v>
@@ -4768,22 +4768,22 @@
         <v>-24.45938696291917</v>
       </c>
       <c r="Q61">
-        <v>3.416666666666667</v>
+        <v>3.555555555555555</v>
       </c>
       <c r="R61">
-        <v>-1.141033056666664</v>
+        <v>0.2913341100000011</v>
       </c>
       <c r="S61">
-        <v>-148.95706303375</v>
+        <v>63.38740309874182</v>
       </c>
       <c r="T61">
-        <v>-53.4717662172436</v>
+        <v>22.75445239442014</v>
       </c>
       <c r="U61">
-        <v>-205.2093610942903</v>
+        <v>87.32508701767181</v>
       </c>
       <c r="V61">
-        <v>-134.2162972749676</v>
+        <v>78.12816885752426</v>
       </c>
     </row>
     <row r="62">
@@ -4802,13 +4802,13 @@
         <v>16</v>
       </c>
       <c r="E62">
-        <v>27.32166666666667</v>
+        <v>24.81847847</v>
       </c>
       <c r="F62">
-        <v>16.22333333333333</v>
+        <v>15.63577910333333</v>
       </c>
       <c r="G62">
-        <v>43.545</v>
+        <v>40.45425757333334</v>
       </c>
       <c r="H62">
         <v>26.54552809833334</v>
@@ -4840,22 +4840,22 @@
         <v>-17.56668006414025</v>
       </c>
       <c r="Q62">
-        <v>11.28813559322034</v>
+        <v>10.44444444444444</v>
       </c>
       <c r="R62">
-        <v>-0.7761385683333302</v>
+        <v>1.727049628333333</v>
       </c>
       <c r="S62">
-        <v>-99.6083407039354</v>
+        <v>369.4111567410862</v>
       </c>
       <c r="T62">
-        <v>-35.75684025269476</v>
+        <v>132.6091331891079</v>
       </c>
       <c r="U62">
-        <v>-137.2245366497703</v>
+        <v>508.9159648560278</v>
       </c>
       <c r="V62">
-        <v>52.24749536312677</v>
+        <v>521.2669928081484</v>
       </c>
     </row>
     <row r="63">
@@ -4874,13 +4874,13 @@
         <v>60</v>
       </c>
       <c r="E63">
-        <v>19.25833333333333</v>
+        <v>18.52182941166667</v>
       </c>
       <c r="F63">
-        <v>33.035</v>
+        <v>33.48027269</v>
       </c>
       <c r="G63">
-        <v>52.29333333333333</v>
+        <v>52.00210210166667</v>
       </c>
       <c r="H63">
         <v>21.01716598833333</v>
@@ -4912,22 +4912,22 @@
         <v>-30.67287736348591</v>
       </c>
       <c r="Q63">
-        <v>34.94915254237288</v>
+        <v>32.05555555555556</v>
       </c>
       <c r="R63">
-        <v>1.758832654999999</v>
+        <v>2.495336576666666</v>
       </c>
       <c r="S63">
-        <v>241.5858294686546</v>
+        <v>571.2481656168799</v>
       </c>
       <c r="T63">
-        <v>86.72311827079908</v>
+        <v>205.0634440675979</v>
       </c>
       <c r="U63">
-        <v>332.8185498895352</v>
+        <v>786.9749087759928</v>
       </c>
       <c r="V63">
-        <v>448.4539676752112</v>
+        <v>778.1163038234364</v>
       </c>
     </row>
     <row r="64">
@@ -4946,13 +4946,13 @@
         <v>16</v>
       </c>
       <c r="E64">
-        <v>19.835</v>
+        <v>20.34286945666667</v>
       </c>
       <c r="F64">
-        <v>31.02333333333333</v>
+        <v>30.85022926333333</v>
       </c>
       <c r="G64">
-        <v>50.85833333333333</v>
+        <v>51.19309871999999</v>
       </c>
       <c r="H64">
         <v>22.511840975</v>
@@ -4984,22 +4984,22 @@
         <v>-13.23521143815018</v>
       </c>
       <c r="Q64">
-        <v>13</v>
+        <v>12.27777777777778</v>
       </c>
       <c r="R64">
-        <v>2.676840974999998</v>
+        <v>2.168971518333333</v>
       </c>
       <c r="S64">
-        <v>348.116312679413</v>
+        <v>470.1153177200277</v>
       </c>
       <c r="T64">
-        <v>124.9648301926098</v>
+        <v>168.7593448225741</v>
       </c>
       <c r="U64">
-        <v>479.5793140420384</v>
+        <v>647.6501484733757</v>
       </c>
       <c r="V64">
-        <v>371.8100927599686</v>
+        <v>493.8090978005833</v>
       </c>
     </row>
     <row r="65">
@@ -5018,13 +5018,13 @@
         <v>4</v>
       </c>
       <c r="E65">
-        <v>15.49333333333333</v>
+        <v>14.71919975333333</v>
       </c>
       <c r="F65">
-        <v>34.9</v>
+        <v>29.839411575</v>
       </c>
       <c r="G65">
-        <v>50.39333333333333</v>
+        <v>44.55861132833333</v>
       </c>
       <c r="H65">
         <v>14.43724686483333</v>
@@ -5056,22 +5056,22 @@
         <v>-107.5094053246572</v>
       </c>
       <c r="Q65">
-        <v>2.95</v>
+        <v>2.361111111111111</v>
       </c>
       <c r="R65">
-        <v>-1.056086468499998</v>
+        <v>-0.2819528884999993</v>
       </c>
       <c r="S65">
-        <v>-145.5227729975874</v>
+        <v>-64.75253591604864</v>
       </c>
       <c r="T65">
-        <v>-52.23894415298008</v>
+        <v>-23.24450007242772</v>
       </c>
       <c r="U65">
-        <v>-200.4781422465224</v>
+        <v>-89.20574999224259</v>
       </c>
       <c r="V65">
-        <v>-189.5962213950747</v>
+        <v>-108.825984313536</v>
       </c>
     </row>
     <row r="66">
@@ -5090,13 +5090,13 @@
         <v>8</v>
       </c>
       <c r="E66">
-        <v>18.8</v>
+        <v>18.14486130333333</v>
       </c>
       <c r="F66">
-        <v>34.15166666666666</v>
+        <v>33.961658875</v>
       </c>
       <c r="G66">
-        <v>52.95166666666667</v>
+        <v>52.10652017833333</v>
       </c>
       <c r="H66">
         <v>19.296109655</v>
@@ -5128,22 +5128,22 @@
         <v>-35.65090464868165</v>
       </c>
       <c r="Q66">
-        <v>7.689655172413793</v>
+        <v>7.542857142857143</v>
       </c>
       <c r="R66">
-        <v>0.4961096549999979</v>
+        <v>1.151248351666666</v>
       </c>
       <c r="S66">
-        <v>70.66015175605011</v>
+        <v>273.2842844245443</v>
       </c>
       <c r="T66">
-        <v>25.36518268165901</v>
+        <v>98.10205081906719</v>
       </c>
       <c r="U66">
-        <v>97.34432393715539</v>
+        <v>376.487641886203</v>
       </c>
       <c r="V66">
-        <v>-18.16973889649232</v>
+        <v>184.4543937720019</v>
       </c>
     </row>
     <row r="67">
@@ -5162,13 +5162,13 @@
         <v>4</v>
       </c>
       <c r="E67">
-        <v>19.16666666666667</v>
+        <v>18.10442685166667</v>
       </c>
       <c r="F67">
-        <v>33.49</v>
+        <v>33.43932509166667</v>
       </c>
       <c r="G67">
-        <v>52.65666666666667</v>
+        <v>51.54375194333333</v>
       </c>
       <c r="H67">
         <v>16.57419823166667</v>
@@ -5200,22 +5200,22 @@
         <v>-129.4012105218759</v>
       </c>
       <c r="Q67">
-        <v>2.694915254237288</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="R67">
-        <v>-2.592468435000001</v>
+        <v>-1.530228619999999</v>
       </c>
       <c r="S67">
-        <v>-374.3844768385374</v>
+        <v>-368.3065359688469</v>
       </c>
       <c r="T67">
-        <v>-134.3944275830647</v>
+        <v>-132.2126026554835</v>
       </c>
       <c r="U67">
-        <v>-515.7674146559214</v>
+        <v>-507.3941939624156</v>
       </c>
       <c r="V67">
-        <v>-565.7601230850322</v>
+        <v>-559.6821822153418</v>
       </c>
     </row>
     <row r="68">
@@ -5234,13 +5234,13 @@
         <v>8</v>
       </c>
       <c r="E68">
-        <v>15.65333333333333</v>
+        <v>14.92791318</v>
       </c>
       <c r="F68">
-        <v>30.44833333333333</v>
+        <v>30.64560135166667</v>
       </c>
       <c r="G68">
-        <v>46.10166666666667</v>
+        <v>45.57351453166667</v>
       </c>
       <c r="H68">
         <v>14.94356254216667</v>
@@ -5272,22 +5272,22 @@
         <v>-33.34013999306529</v>
       </c>
       <c r="Q68">
-        <v>6.677966101694915</v>
+        <v>6.527777777777778</v>
       </c>
       <c r="R68">
-        <v>-0.7097707911666653</v>
+        <v>0.01564936216666624</v>
       </c>
       <c r="S68">
-        <v>-98.85251513868158</v>
+        <v>3.632578361314557</v>
       </c>
       <c r="T68">
-        <v>-35.48551825491133</v>
+        <v>1.304002488677021</v>
       </c>
       <c r="U68">
-        <v>-136.1832803428483</v>
+        <v>5.004388979402782</v>
       </c>
       <c r="V68">
-        <v>-181.7294783601724</v>
+        <v>-79.24438486017621</v>
       </c>
     </row>
     <row r="69">
@@ -5306,13 +5306,13 @@
         <v>1</v>
       </c>
       <c r="E69">
-        <v>15.57166666666667</v>
+        <v>13.18105039666667</v>
       </c>
       <c r="F69">
-        <v>36.22166666666666</v>
+        <v>37.45385885333334</v>
       </c>
       <c r="G69">
-        <v>51.79333333333333</v>
+        <v>50.63490925000001</v>
       </c>
       <c r="H69">
         <v>13.13788787916667</v>
@@ -5347,19 +5347,19 @@
         <v>1</v>
       </c>
       <c r="R69">
-        <v>-2.4337787875</v>
+        <v>-0.043162517499999</v>
       </c>
       <c r="S69">
-        <v>-340.3229909139855</v>
+        <v>-10.0592523900291</v>
       </c>
       <c r="T69">
-        <v>-122.1672275075845</v>
+        <v>-3.611013678471985</v>
       </c>
       <c r="U69">
-        <v>-468.8429142519643</v>
+        <v>-13.85803877978163</v>
       </c>
       <c r="V69">
-        <v>-561.0204594880267</v>
+        <v>-230.7567209640703</v>
       </c>
     </row>
     <row r="70">
@@ -5378,13 +5378,13 @@
         <v>8</v>
       </c>
       <c r="E70">
-        <v>17.41666666666667</v>
+        <v>14.67711508166667</v>
       </c>
       <c r="F70">
-        <v>36.48333333333333</v>
+        <v>38.309613865</v>
       </c>
       <c r="G70">
-        <v>53.90000000000001</v>
+        <v>52.98672894666667</v>
       </c>
       <c r="H70">
         <v>18.117422885</v>
@@ -5416,22 +5416,22 @@
         <v>-15.6734079482104</v>
       </c>
       <c r="Q70">
-        <v>6.610169491525424</v>
+        <v>6.027777777777778</v>
       </c>
       <c r="R70">
-        <v>0.700756218333332</v>
+        <v>3.440307803333333</v>
       </c>
       <c r="S70">
-        <v>93.32964763710972</v>
+        <v>763.6576664087194</v>
       </c>
       <c r="T70">
-        <v>33.50295043383426</v>
+        <v>274.1335212749249</v>
       </c>
       <c r="U70">
-        <v>128.5747514935034</v>
+        <v>1052.04613078994</v>
       </c>
       <c r="V70">
-        <v>145.161419458805</v>
+        <v>815.4894382304146</v>
       </c>
     </row>
     <row r="71">
@@ -5450,13 +5450,13 @@
         <v>4</v>
       </c>
       <c r="E71">
-        <v>16.605</v>
+        <v>15.78257399333333</v>
       </c>
       <c r="F71">
-        <v>35.695</v>
+        <v>35.71433067333334</v>
       </c>
       <c r="G71">
-        <v>52.3</v>
+        <v>51.49690466666667</v>
       </c>
       <c r="H71">
         <v>15.29936591116667</v>
@@ -5488,22 +5488,22 @@
         <v>-98.32873021005035</v>
       </c>
       <c r="Q71">
-        <v>3.779661016949153</v>
+        <v>3.722222222222222</v>
       </c>
       <c r="R71">
-        <v>-1.305634088833333</v>
+        <v>-0.4832080821666658</v>
       </c>
       <c r="S71">
-        <v>-175.2154799373369</v>
+        <v>-108.0771618308548</v>
       </c>
       <c r="T71">
-        <v>-62.89786459289017</v>
+        <v>-38.79692988799916</v>
       </c>
       <c r="U71">
-        <v>-241.3840334890573</v>
+        <v>-148.8915320730299</v>
       </c>
       <c r="V71">
-        <v>-171.2986650272032</v>
+        <v>-104.1603469207211</v>
       </c>
     </row>
     <row r="72">
@@ -5522,13 +5522,13 @@
         <v>1</v>
       </c>
       <c r="E72">
-        <v>15.13166666666667</v>
+        <v>13.647493345</v>
       </c>
       <c r="F72">
-        <v>32.21666666666667</v>
+        <v>32.61511166666666</v>
       </c>
       <c r="G72">
-        <v>47.34833333333334</v>
+        <v>46.26260501166666</v>
       </c>
       <c r="H72">
         <v>13.49411681</v>
@@ -5560,22 +5560,22 @@
         <v>-28.18642193560149</v>
       </c>
       <c r="Q72">
-        <v>0.9833333333333333</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="R72">
-        <v>-1.637549856666668</v>
+        <v>-0.1533765349999996</v>
       </c>
       <c r="S72">
-        <v>-242.6876511149146</v>
+        <v>-37.8844353590789</v>
       </c>
       <c r="T72">
-        <v>-87.11864398996934</v>
+        <v>-13.59954089813089</v>
       </c>
       <c r="U72">
-        <v>-334.3364645923623</v>
+        <v>-52.19115238391259</v>
       </c>
       <c r="V72">
-        <v>-409.5694489548317</v>
+        <v>-204.766233198996</v>
       </c>
     </row>
     <row r="73">
@@ -5594,13 +5594,13 @@
         <v>1</v>
       </c>
       <c r="E73">
-        <v>14.97166666666667</v>
+        <v>12.741091735</v>
       </c>
       <c r="F73">
-        <v>37.80333333333333</v>
+        <v>38.41735998833333</v>
       </c>
       <c r="G73">
-        <v>52.77500000000001</v>
+        <v>51.15845172333333</v>
       </c>
       <c r="H73">
         <v>13.57363288</v>
@@ -5632,22 +5632,22 @@
         <v>-80.67205419095133</v>
       </c>
       <c r="Q73">
-        <v>0.9833333333333333</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="R73">
-        <v>-1.398033786666668</v>
+        <v>0.8325411449999987</v>
       </c>
       <c r="S73">
-        <v>-196.3418881832317</v>
+        <v>194.87213871189</v>
       </c>
       <c r="T73">
-        <v>-70.48170345039088</v>
+        <v>69.95410107606308</v>
       </c>
       <c r="U73">
-        <v>-270.4886402130429</v>
+        <v>268.4638530439084</v>
       </c>
       <c r="V73">
-        <v>-344.2682104576047</v>
+        <v>46.945816437517</v>
       </c>
     </row>
     <row r="74">
@@ -5666,13 +5666,13 @@
         <v>2</v>
       </c>
       <c r="E74">
-        <v>16.955</v>
+        <v>16.08225684666667</v>
       </c>
       <c r="F74">
-        <v>37.105</v>
+        <v>36.86274886166667</v>
       </c>
       <c r="G74">
-        <v>54.06</v>
+        <v>52.94500570833333</v>
       </c>
       <c r="H74">
         <v>15.34313406833333</v>
@@ -5707,19 +5707,19 @@
         <v>2</v>
       </c>
       <c r="R74">
-        <v>-1.611865931666669</v>
+        <v>-0.7391227783333338</v>
       </c>
       <c r="S74">
-        <v>-223.5488791119146</v>
+        <v>-170.8476134981163</v>
       </c>
       <c r="T74">
-        <v>-80.24831557863601</v>
+        <v>-61.32991253778533</v>
       </c>
       <c r="U74">
-        <v>-307.9701071006397</v>
+        <v>-235.3666814878664</v>
       </c>
       <c r="V74">
-        <v>-356.3337987514308</v>
+        <v>-303.6325331376324</v>
       </c>
     </row>
     <row r="75">
@@ -5738,13 +5738,13 @@
         <v>2</v>
       </c>
       <c r="E75">
-        <v>20.145</v>
+        <v>16.89603769</v>
       </c>
       <c r="F75">
-        <v>33.93</v>
+        <v>35.35727024166667</v>
       </c>
       <c r="G75">
-        <v>54.075</v>
+        <v>52.25330793166667</v>
       </c>
       <c r="H75">
         <v>15.49836146416667</v>
@@ -5776,22 +5776,22 @@
         <v>-26.43500312032725</v>
       </c>
       <c r="Q75">
-        <v>1.9</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="R75">
-        <v>-4.646638535833333</v>
+        <v>-1.397676225833333</v>
       </c>
       <c r="S75">
-        <v>-629.0865207423706</v>
+        <v>-315.3746761425003</v>
       </c>
       <c r="T75">
-        <v>-225.8259305229022</v>
+        <v>-113.2114222050001</v>
       </c>
       <c r="U75">
-        <v>-866.6553996524635</v>
+        <v>-434.4730923021603</v>
       </c>
       <c r="V75">
-        <v>-775.069942686742</v>
+        <v>-461.3580980868717</v>
       </c>
     </row>
     <row r="76">
@@ -5810,13 +5810,13 @@
         <v>8</v>
       </c>
       <c r="E76">
-        <v>17.515</v>
+        <v>16.947425565</v>
       </c>
       <c r="F76">
-        <v>30.57666666666667</v>
+        <v>30.629589955</v>
       </c>
       <c r="G76">
-        <v>48.09166666666667</v>
+        <v>47.57701552</v>
       </c>
       <c r="H76">
         <v>17.406181905</v>
@@ -5848,22 +5848,22 @@
         <v>-50.78801594059746</v>
       </c>
       <c r="Q76">
-        <v>6.35593220338983</v>
+        <v>6.027777777777778</v>
       </c>
       <c r="R76">
-        <v>-0.1088180950000002</v>
+        <v>0.4587563400000008</v>
       </c>
       <c r="S76">
-        <v>-14.28021697806301</v>
+        <v>100.337786579552</v>
       </c>
       <c r="T76">
-        <v>-5.126231735714926</v>
+        <v>36.0186926183007</v>
       </c>
       <c r="U76">
-        <v>-19.67301276403511</v>
+        <v>138.2294512140043</v>
       </c>
       <c r="V76">
-        <v>-34.67271946717001</v>
+        <v>79.94528409044496</v>
       </c>
     </row>
     <row r="77">
@@ -5882,13 +5882,13 @@
         <v>2</v>
       </c>
       <c r="E77">
-        <v>13.47666666666667</v>
+        <v>12.63691090166667</v>
       </c>
       <c r="F77">
-        <v>38.66333333333333</v>
+        <v>38.467871745</v>
       </c>
       <c r="G77">
-        <v>52.14</v>
+        <v>51.10478264666666</v>
       </c>
       <c r="H77">
         <v>11.93623757083333</v>
@@ -5923,19 +5923,19 @@
         <v>2</v>
       </c>
       <c r="R77">
-        <v>-1.540429095833334</v>
+        <v>-0.7006733308333342</v>
       </c>
       <c r="S77">
-        <v>-227.6972107518007</v>
+        <v>-172.6157163075136</v>
       </c>
       <c r="T77">
-        <v>-81.73746026987718</v>
+        <v>-61.96461611038952</v>
       </c>
       <c r="U77">
-        <v>-313.6850189557114</v>
+        <v>-237.8024924556434</v>
       </c>
       <c r="V77">
-        <v>-361.5679212861102</v>
+        <v>-306.4864268418231</v>
       </c>
     </row>
     <row r="78">
@@ -5954,13 +5954,13 @@
         <v>16</v>
       </c>
       <c r="E78">
-        <v>17.305</v>
+        <v>18.07836725833333</v>
       </c>
       <c r="F78">
-        <v>33.38666666666667</v>
+        <v>34.69260811833333</v>
       </c>
       <c r="G78">
-        <v>50.69166666666667</v>
+        <v>52.77097537666667</v>
       </c>
       <c r="H78">
         <v>18.410111665</v>
@@ -5992,22 +5992,22 @@
         <v>-63.66552350094434</v>
       </c>
       <c r="Q78">
-        <v>10.48333333333333</v>
+        <v>9.972222222222221</v>
       </c>
       <c r="R78">
-        <v>1.105111664999999</v>
+        <v>0.3317444066666653</v>
       </c>
       <c r="S78">
-        <v>149.3653244380321</v>
+        <v>74.7301720746156</v>
       </c>
       <c r="T78">
-        <v>53.61832159313974</v>
+        <v>26.82621561652867</v>
       </c>
       <c r="U78">
-        <v>205.7717987540151</v>
+        <v>102.9513509032038</v>
       </c>
       <c r="V78">
-        <v>398.8760299153288</v>
+        <v>324.2408775519123</v>
       </c>
     </row>
     <row r="79">
@@ -6026,13 +6026,13 @@
         <v>16</v>
       </c>
       <c r="E79">
-        <v>14.46666666666667</v>
+        <v>14.24282284833333</v>
       </c>
       <c r="F79">
-        <v>31.18</v>
+        <v>30.676206745</v>
       </c>
       <c r="G79">
-        <v>45.64666666666667</v>
+        <v>44.91902959333333</v>
       </c>
       <c r="H79">
         <v>15.80617593833333</v>
@@ -6064,22 +6064,22 @@
         <v>-65.65401022852419</v>
       </c>
       <c r="Q79">
-        <v>9.85</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="R79">
-        <v>1.339509271666666</v>
+        <v>1.56335309</v>
       </c>
       <c r="S79">
-        <v>182.0703769872692</v>
+        <v>354.1599057720002</v>
       </c>
       <c r="T79">
-        <v>65.35859686722485</v>
+        <v>127.1343251489232</v>
       </c>
       <c r="U79">
-        <v>250.8276208915897</v>
+        <v>487.9052158286674</v>
       </c>
       <c r="V79">
-        <v>345.3056691670298</v>
+        <v>517.3951979517608</v>
       </c>
     </row>
     <row r="80">
@@ -6098,13 +6098,13 @@
         <v>2</v>
       </c>
       <c r="E80">
-        <v>13.26666666666667</v>
+        <v>13.65484056</v>
       </c>
       <c r="F80">
-        <v>38.9</v>
+        <v>38.165918985</v>
       </c>
       <c r="G80">
-        <v>52.16666666666666</v>
+        <v>51.820759545</v>
       </c>
       <c r="H80">
         <v>13.02545374183333</v>
@@ -6136,22 +6136,22 @@
         <v>-60.77336057034802</v>
       </c>
       <c r="Q80">
-        <v>1.9</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="R80">
-        <v>-0.2412129248333326</v>
+        <v>-0.6293868181666671</v>
       </c>
       <c r="S80">
-        <v>-34.97266833978342</v>
+        <v>-152.0878732927439</v>
       </c>
       <c r="T80">
-        <v>-12.55429119889661</v>
+        <v>-54.59564682303625</v>
       </c>
       <c r="U80">
-        <v>-48.17978268102264</v>
+        <v>-209.522493750578</v>
       </c>
       <c r="V80">
-        <v>98.14974046919693</v>
+        <v>-18.96546448376353</v>
       </c>
     </row>
     <row r="81">
@@ -6170,13 +6170,13 @@
         <v>4</v>
       </c>
       <c r="E81">
-        <v>15.63333333333333</v>
+        <v>15.32690688</v>
       </c>
       <c r="F81">
-        <v>34.77666666666666</v>
+        <v>33.91789635166667</v>
       </c>
       <c r="G81">
-        <v>50.41</v>
+        <v>49.24480323166667</v>
       </c>
       <c r="H81">
         <v>16.39641685833333</v>
@@ -6208,22 +6208,22 @@
         <v>-15.91041066353196</v>
       </c>
       <c r="Q81">
-        <v>2.833333333333333</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="R81">
-        <v>0.763083524999999</v>
+        <v>1.069509978333333</v>
       </c>
       <c r="S81">
-        <v>108.1822611643839</v>
+        <v>252.7071720708672</v>
       </c>
       <c r="T81">
-        <v>38.8346578538814</v>
+        <v>90.71539510236256</v>
       </c>
       <c r="U81">
-        <v>149.0363212266671</v>
+        <v>348.1397677185525</v>
       </c>
       <c r="V81">
-        <v>180.3521594229646</v>
+        <v>324.8770703294478</v>
       </c>
     </row>
   </sheetData>

--- a/Data Analysis/1_Data/economic_MF.xlsx
+++ b/Data Analysis/1_Data/economic_MF.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V81"/>
+  <dimension ref="A1:X81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,100 +367,110 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>SGM_mean</t>
+          <t>profit_mean</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>insurance</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>sowndiv</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>mean_org_11</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>mean_inorg_11</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>mean_C_11</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>mean_org_20</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>mean_inorg_20</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>mean_bulk</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>mean_C_20</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>block</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>av_leaching</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>leach_costs_lo</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>leach_costs_mid</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>leach_costs_hi</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>meanSR</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>mean_org_diff</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SOC_costs_mid</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>SOC_costs_lo</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>SOC_costs_hi</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>costs_total_mid</t>
         </is>
@@ -476,66 +486,72 @@
         <v>382.2721153846154</v>
       </c>
       <c r="C2">
-        <v>76.00643430769233</v>
+        <v>145.7013651050133</v>
       </c>
       <c r="D2">
+        <v>2.259870857882386</v>
+      </c>
+      <c r="E2">
+        <v>28.42270354919071</v>
+      </c>
+      <c r="F2">
         <v>16</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <v>15.693274495</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>6.694930096666667</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>22.38820459166666</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>18.76454505833333</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <v>6.8238517325</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>1.2546214505</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>25.58839679083333</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>2.813264729287163</v>
       </c>
-      <c r="N2">
+      <c r="P2">
         <v>-17.72356779450913</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>-31.59296290989484</v>
       </c>
-      <c r="P2">
+      <c r="R2">
         <v>-56.26529458574326</v>
       </c>
-      <c r="Q2">
+      <c r="S2">
         <v>11.08333333333333</v>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>3.071270563333334</v>
       </c>
-      <c r="S2">
+      <c r="U2">
         <v>687.5218281902502</v>
       </c>
-      <c r="T2">
-        <v>246.8027075554744</v>
-      </c>
-      <c r="U2">
+      <c r="V2">
+        <v>264.4314723808654</v>
+      </c>
+      <c r="W2">
         <v>947.1582765386092</v>
       </c>
-      <c r="V2">
-        <v>731.9352995880477</v>
+      <c r="X2">
+        <v>801.6302303853686</v>
       </c>
     </row>
     <row r="3">
@@ -548,66 +564,72 @@
         <v>350.5780769230769</v>
       </c>
       <c r="C3">
-        <v>61.40733846153847</v>
+        <v>137.7347669152479</v>
       </c>
       <c r="D3">
+        <v>3.037901513434422</v>
+      </c>
+      <c r="E3">
+        <v>31.72172313239069</v>
+      </c>
+      <c r="F3">
         <v>8</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>15.69695607833333</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>6.371277073333333</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>22.06823315166667</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>16.83361475166667</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>6.491076882833333</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>1.287621534333333</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>23.3246916345</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>5.003784345866223</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>-31.5238413789572</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>-56.19249820407769</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>-100.0756869173245</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>5.055555555555555</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>1.136658673333333</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <v>261.1403650534073</v>
       </c>
-      <c r="T3">
-        <v>93.74269514737699</v>
-      </c>
-      <c r="U3">
+      <c r="V3">
+        <v>100.4386019436182</v>
+      </c>
+      <c r="W3">
         <v>359.7576803484479</v>
       </c>
-      <c r="V3">
-        <v>266.3552053108681</v>
+      <c r="X3">
+        <v>342.6826337645775</v>
       </c>
     </row>
     <row r="4">
@@ -620,66 +642,72 @@
         <v>171.8553846153846</v>
       </c>
       <c r="C4">
-        <v>-55.9362173076923</v>
+        <v>67.96626745108389</v>
       </c>
       <c r="D4">
+        <v>1.541192873274919</v>
+      </c>
+      <c r="E4">
+        <v>10.3275716254785</v>
+      </c>
+      <c r="F4">
         <v>8</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>15.64949997</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>6.797016461666667</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>22.44651643166667</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>13.88983349316667</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>7.411676897333333</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>1.404984469833333</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>21.3015103905</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>10.62294565431209</v>
       </c>
-      <c r="N4">
+      <c r="P4">
         <v>-66.92455762216619</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>-119.2956796979248</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>-212.4589130862419</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>5.805555555555555</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>-1.759666476833335</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>-441.1208540532325</v>
       </c>
-      <c r="T4">
-        <v>-158.3510758139809</v>
-      </c>
-      <c r="U4">
+      <c r="V4">
+        <v>-169.661866943551</v>
+      </c>
+      <c r="W4">
         <v>-607.7061858095404</v>
       </c>
-      <c r="V4">
-        <v>-616.3527510588497</v>
+      <c r="X4">
+        <v>-492.4502663000734</v>
       </c>
     </row>
     <row r="5">
@@ -692,66 +720,72 @@
         <v>281.1561538461539</v>
       </c>
       <c r="C5">
-        <v>20.2405803846154</v>
+        <v>114.5516295509591</v>
       </c>
       <c r="D5">
+        <v>2.155129477973325</v>
+      </c>
+      <c r="E5">
+        <v>21.71358431082056</v>
+      </c>
+      <c r="F5">
         <v>4</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>16.81531028666667</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>6.73690309</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>23.55221337666666</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>16.13080275</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>7.018404786333333</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>1.347792084333333</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>23.14920753633334</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>10.03208662826186</v>
       </c>
-      <c r="N5">
+      <c r="P5">
         <v>-63.20214575804974</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>-112.6603328353807</v>
       </c>
-      <c r="P5">
+      <c r="R5">
         <v>-200.6417325652373</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>2.972222222222222</v>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>-0.6845075366666649</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>-164.6102373281035</v>
       </c>
-      <c r="T5">
-        <v>-59.09085442547303</v>
-      </c>
-      <c r="U5">
+      <c r="V5">
+        <v>-63.31162974157826</v>
+      </c>
+      <c r="W5">
         <v>-226.7738161837011</v>
       </c>
-      <c r="V5">
-        <v>-257.0299897788688</v>
+      <c r="X5">
+        <v>-162.718940612525</v>
       </c>
     </row>
     <row r="6">
@@ -764,66 +798,72 @@
         <v>170.7674358974359</v>
       </c>
       <c r="C6">
-        <v>-57.2744023076923</v>
+        <v>65.42028323790227</v>
       </c>
       <c r="D6">
+        <v>1.036141073848968</v>
+      </c>
+      <c r="E6">
+        <v>7.298740527748213</v>
+      </c>
+      <c r="F6">
         <v>2</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>15.09488513333333</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>6.450398961666667</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>21.545284095</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>14.88611025333333</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>6.5496542775</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>1.346599269666667</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <v>21.43576453083333</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>7.607418619499584</v>
       </c>
-      <c r="N6">
+      <c r="P6">
         <v>-47.92673730284738</v>
       </c>
-      <c r="O6">
+      <c r="Q6">
         <v>-85.43131109698034</v>
       </c>
-      <c r="P6">
+      <c r="R6">
         <v>-152.1483723899917</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <v>1.805555555555556</v>
       </c>
-      <c r="R6">
+      <c r="T6">
         <v>-0.20877488</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <v>-50.16170880892521</v>
       </c>
-      <c r="T6">
-        <v>-18.00676726474238</v>
-      </c>
-      <c r="U6">
+      <c r="V6">
+        <v>-19.29296492650969</v>
+      </c>
+      <c r="W6">
         <v>-69.10482797143419</v>
       </c>
-      <c r="V6">
-        <v>-192.8674222135978</v>
+      <c r="X6">
+        <v>-70.17273666800328</v>
       </c>
     </row>
     <row r="7">
@@ -836,66 +876,72 @@
         <v>242.4952179487179</v>
       </c>
       <c r="C7">
-        <v>-9.735079423076913</v>
+        <v>93.97734618440134</v>
       </c>
       <c r="D7">
+        <v>3.859743076186435</v>
+      </c>
+      <c r="E7">
+        <v>24.38791677157077</v>
+      </c>
+      <c r="F7">
         <v>16</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>16.30583443666667</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>6.19431128</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>22.50014571666667</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>16.76970075833334</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>6.545481602666666</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>1.3381643705</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>23.315182361</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>1.175780674075467</v>
       </c>
-      <c r="N7">
+      <c r="P7">
         <v>-7.407418246675445</v>
       </c>
-      <c r="O7">
+      <c r="Q7">
         <v>-13.2040169698675</v>
       </c>
-      <c r="P7">
+      <c r="R7">
         <v>-23.51561348150935</v>
       </c>
-      <c r="Q7">
+      <c r="S7">
         <v>12.47222222222222</v>
       </c>
-      <c r="R7">
+      <c r="T7">
         <v>0.4638663216666679</v>
       </c>
-      <c r="S7">
+      <c r="U7">
         <v>110.7536403989424</v>
       </c>
-      <c r="T7">
-        <v>39.757717066287</v>
-      </c>
-      <c r="U7">
+      <c r="V7">
+        <v>42.59755399959321</v>
+      </c>
+      <c r="W7">
         <v>152.5787587526763</v>
       </c>
-      <c r="V7">
-        <v>87.81454400599794</v>
+      <c r="X7">
+        <v>191.5269696134762</v>
       </c>
     </row>
     <row r="8">
@@ -908,66 +954,72 @@
         <v>117.4245256410256</v>
       </c>
       <c r="C8">
-        <v>-90.71716211538461</v>
+        <v>47.37458253556064</v>
       </c>
       <c r="D8">
+        <v>1.389560270267715</v>
+      </c>
+      <c r="E8">
+        <v>6.676641436639747</v>
+      </c>
+      <c r="F8">
         <v>2</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>15.27825111666667</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>6.3079831</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>21.58623421666667</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>16.93685348</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>6.111142179166666</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>1.288512477</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>23.04799565916667</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>8.587698582789461</v>
       </c>
-      <c r="N8">
+      <c r="P8">
         <v>-54.1025010715736</v>
       </c>
-      <c r="O8">
+      <c r="Q8">
         <v>-96.43985508472565</v>
       </c>
-      <c r="P8">
+      <c r="R8">
         <v>-171.7539716557892</v>
       </c>
-      <c r="Q8">
+      <c r="S8">
         <v>2</v>
       </c>
-      <c r="R8">
+      <c r="T8">
         <v>1.658602363333333</v>
       </c>
-      <c r="S8">
+      <c r="U8">
         <v>381.3173916193334</v>
       </c>
-      <c r="T8">
-        <v>136.8831662223248</v>
-      </c>
-      <c r="U8">
+      <c r="V8">
+        <v>146.6605352382052</v>
+      </c>
+      <c r="W8">
         <v>525.3184824852191</v>
       </c>
-      <c r="V8">
-        <v>194.1603744192232</v>
+      <c r="X8">
+        <v>332.2521190701684</v>
       </c>
     </row>
     <row r="9">
@@ -980,66 +1032,72 @@
         <v>319.7814102564103</v>
       </c>
       <c r="C9">
-        <v>44.22396923076924</v>
+        <v>130.9596011096417</v>
       </c>
       <c r="D9">
+        <v>2.567495039214939</v>
+      </c>
+      <c r="E9">
+        <v>27.517314050276</v>
+      </c>
+      <c r="F9">
         <v>1</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>15.37546887666667</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>6.454285086666667</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>21.82975396333333</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>15.82495804166667</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>6.2890732475</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>1.289376087666667</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>22.11403128916666</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>11.79392739577335</v>
       </c>
-      <c r="N9">
+      <c r="P9">
         <v>-74.3017425933721</v>
       </c>
-      <c r="O9">
+      <c r="Q9">
         <v>-132.4458046545347</v>
       </c>
-      <c r="P9">
+      <c r="R9">
         <v>-235.878547915467</v>
       </c>
-      <c r="Q9">
+      <c r="S9">
         <v>1</v>
       </c>
-      <c r="R9">
+      <c r="T9">
         <v>0.4494891649999992</v>
       </c>
-      <c r="S9">
+      <c r="U9">
         <v>103.4080966678254</v>
       </c>
-      <c r="T9">
-        <v>37.12085521409119</v>
-      </c>
-      <c r="U9">
+      <c r="V9">
+        <v>39.77234487224056</v>
+      </c>
+      <c r="W9">
         <v>142.4592363530494</v>
       </c>
-      <c r="V9">
-        <v>15.18626124405998</v>
+      <c r="X9">
+        <v>101.9218931229324</v>
       </c>
     </row>
     <row r="10">
@@ -1052,66 +1110,72 @@
         <v>277.5409487179487</v>
       </c>
       <c r="C10">
-        <v>12.76036961538462</v>
+        <v>109.4526898952287</v>
       </c>
       <c r="D10">
+        <v>4.078294161783221</v>
+      </c>
+      <c r="E10">
+        <v>29.14396956977761</v>
+      </c>
+      <c r="F10">
         <v>16</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>19.95934968833333</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>8.20662727</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>28.16597695833333</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>20.74362609</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>8.007693386333333</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>1.312353860333333</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>28.75131947633333</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>2.710670323817271</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>-17.07722304004881</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>-30.44082773646796</v>
       </c>
-      <c r="P10">
+      <c r="R10">
         <v>-54.21340647634543</v>
       </c>
-      <c r="Q10">
+      <c r="S10">
         <v>10.36111111111111</v>
       </c>
-      <c r="R10">
+      <c r="T10">
         <v>0.7842764016666663</v>
       </c>
-      <c r="S10">
+      <c r="U10">
         <v>183.6436035360149</v>
       </c>
-      <c r="T10">
-        <v>65.92334485908225</v>
-      </c>
-      <c r="U10">
+      <c r="V10">
+        <v>70.63215520615955</v>
+      </c>
+      <c r="W10">
         <v>252.9949623277693</v>
       </c>
-      <c r="V10">
-        <v>165.9631454149315</v>
+      <c r="X10">
+        <v>262.6554656947756</v>
       </c>
     </row>
     <row r="11">
@@ -1124,66 +1188,72 @@
         <v>404.5358461538461</v>
       </c>
       <c r="C11">
-        <v>98.45986653846157</v>
+        <v>161.239064826035</v>
       </c>
       <c r="D11">
+        <v>2.417458139643523</v>
+      </c>
+      <c r="E11">
+        <v>32.72970534812986</v>
+      </c>
+      <c r="F11">
         <v>8</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>16.720706945</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>7.984850008333334</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>24.70555695333334</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>15.448378665</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>8.4151640775</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>1.245958471666667</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>23.8635427425</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>7.824389819187211</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <v>-49.29365586087943</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>-87.86789766947238</v>
       </c>
-      <c r="P11">
+      <c r="R11">
         <v>-156.4877963837442</v>
       </c>
-      <c r="Q11">
+      <c r="S11">
         <v>5</v>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>-1.27232828</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>-282.851478443523</v>
       </c>
-      <c r="T11">
-        <v>-101.5364281592134</v>
-      </c>
-      <c r="U11">
+      <c r="V11">
+        <v>-108.7890301705858</v>
+      </c>
+      <c r="W11">
         <v>-389.6678008670155</v>
       </c>
-      <c r="V11">
-        <v>-272.2595095745338</v>
+      <c r="X11">
+        <v>-209.4803112869604</v>
       </c>
     </row>
     <row r="12">
@@ -1196,66 +1266,72 @@
         <v>308.8033333333333</v>
       </c>
       <c r="C12">
-        <v>35.80333192307694</v>
+        <v>126.806840250604</v>
       </c>
       <c r="D12">
+        <v>2.332909442000188</v>
+      </c>
+      <c r="E12">
+        <v>25.20913822370119</v>
+      </c>
+      <c r="F12">
         <v>4</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>14.79970766666667</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>6.588684818333333</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>21.388392485</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>16.183862175</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>6.791461165499999</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>1.289940989333333</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>22.9753233405</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>6.603782064222194</v>
       </c>
-      <c r="N12">
+      <c r="P12">
         <v>-41.60382700459982</v>
       </c>
-      <c r="O12">
+      <c r="Q12">
         <v>-74.16047258121525</v>
       </c>
-      <c r="P12">
+      <c r="R12">
         <v>-132.0756412844439</v>
       </c>
-      <c r="Q12">
+      <c r="S12">
         <v>3.194444444444445</v>
       </c>
-      <c r="R12">
+      <c r="T12">
         <v>1.384154508333335</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>318.5738471800504</v>
       </c>
-      <c r="T12">
-        <v>114.359842577454</v>
-      </c>
-      <c r="U12">
+      <c r="V12">
+        <v>122.5284027615579</v>
+      </c>
+      <c r="W12">
         <v>438.880401571532</v>
       </c>
-      <c r="V12">
-        <v>280.2167065219122</v>
+      <c r="X12">
+        <v>371.2202148494392</v>
       </c>
     </row>
     <row r="13">
@@ -1268,66 +1344,72 @@
         <v>173.5197435897436</v>
       </c>
       <c r="C13">
-        <v>-53.60853769230769</v>
+        <v>69.86402397477804</v>
       </c>
       <c r="D13">
+        <v>2.539175812312433</v>
+      </c>
+      <c r="E13">
+        <v>14.58780248974256</v>
+      </c>
+      <c r="F13">
         <v>8</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>15.62836029166667</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>6.864643295</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>22.49300358666667</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>16.193342365</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>7.529579546166667</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>1.357109041833333</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <v>23.72292191116667</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>1.39202396258024</v>
       </c>
-      <c r="N13">
+      <c r="P13">
         <v>-8.769750964255509</v>
       </c>
-      <c r="O13">
+      <c r="Q13">
         <v>-15.63242909977609</v>
       </c>
-      <c r="P13">
+      <c r="R13">
         <v>-27.84047925160479</v>
       </c>
-      <c r="Q13">
+      <c r="S13">
         <v>6.138888888888889</v>
       </c>
-      <c r="R13">
+      <c r="T13">
         <v>0.5649820733333328</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>136.8059913436875</v>
       </c>
-      <c r="T13">
-        <v>49.10984304645191</v>
-      </c>
-      <c r="U13">
+      <c r="V13">
+        <v>52.61768897834133</v>
+      </c>
+      <c r="W13">
         <v>188.4695462285549</v>
       </c>
-      <c r="V13">
-        <v>67.5650245516037</v>
+      <c r="X13">
+        <v>191.0375862186894</v>
       </c>
     </row>
     <row r="14">
@@ -1340,66 +1422,72 @@
         <v>9.844230769230769</v>
       </c>
       <c r="C14">
-        <v>-156.8178538461538</v>
+        <v>3.833164388004581</v>
       </c>
       <c r="D14">
+        <v>0.6035046795562488</v>
+      </c>
+      <c r="E14">
+        <v>0.2521846310983313</v>
+      </c>
+      <c r="F14">
         <v>1</v>
       </c>
-      <c r="E14">
+      <c r="G14">
         <v>17.893618645</v>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>7.822386326666667</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>25.71600497166667</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>16.58950539833333</v>
       </c>
-      <c r="I14">
+      <c r="K14">
         <v>8.428237891833334</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>1.336857178666667</v>
       </c>
-      <c r="K14">
+      <c r="M14">
         <v>25.01774329016667</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>4.23496647898634</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>-26.68028881761394</v>
       </c>
-      <c r="O14">
+      <c r="Q14">
         <v>-47.5586735590166</v>
       </c>
-      <c r="P14">
+      <c r="R14">
         <v>-84.69932957972681</v>
       </c>
-      <c r="Q14">
+      <c r="S14">
         <v>0.9166666666666666</v>
       </c>
-      <c r="R14">
+      <c r="T14">
         <v>-1.304113246666667</v>
       </c>
-      <c r="S14">
+      <c r="U14">
         <v>-311.0684922880419</v>
       </c>
-      <c r="T14">
-        <v>-111.6656126162202</v>
-      </c>
-      <c r="U14">
+      <c r="V14">
+        <v>-119.641727803093</v>
+      </c>
+      <c r="W14">
         <v>-428.5407167603055</v>
       </c>
-      <c r="V14">
-        <v>-515.4450196932123</v>
+      <c r="X14">
+        <v>-354.7940014590539</v>
       </c>
     </row>
     <row r="15">
@@ -1412,66 +1500,72 @@
         <v>119.2246153846154</v>
       </c>
       <c r="C15">
-        <v>-86.55015807692307</v>
+        <v>50.96257335090633</v>
       </c>
       <c r="D15">
+        <v>1.231438563271949</v>
+      </c>
+      <c r="E15">
+        <v>6.548533327731191</v>
+      </c>
+      <c r="F15">
         <v>2</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>17.72635309333333</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>7.703228096666667</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>25.42958119</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>16.12405039333333</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>8.497587742333334</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>1.317444145666667</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>24.62163813566667</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>1.071580227281821</v>
       </c>
-      <c r="N15">
+      <c r="P15">
         <v>-6.750955431875472</v>
       </c>
-      <c r="O15">
+      <c r="Q15">
         <v>-12.03384595237485</v>
       </c>
-      <c r="P15">
+      <c r="R15">
         <v>-21.43160454563642</v>
       </c>
-      <c r="Q15">
+      <c r="S15">
         <v>1.972222222222222</v>
       </c>
-      <c r="R15">
+      <c r="T15">
         <v>-1.602302699999999</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>-376.6452388152318</v>
       </c>
-      <c r="T15">
-        <v>-135.2059831644422</v>
-      </c>
-      <c r="U15">
+      <c r="V15">
+        <v>-144.8635533904738</v>
+      </c>
+      <c r="W15">
         <v>-518.8819331042249</v>
       </c>
-      <c r="V15">
-        <v>-475.2292428445297</v>
+      <c r="X15">
+        <v>-337.7165114167003</v>
       </c>
     </row>
     <row r="16">
@@ -1484,66 +1578,72 @@
         <v>134.5203846153846</v>
       </c>
       <c r="C16">
-        <v>-78.23088269230769</v>
+        <v>55.37124167829312</v>
       </c>
       <c r="D16">
+        <v>1.902551130038404</v>
+      </c>
+      <c r="E16">
+        <v>9.704581890356366</v>
+      </c>
+      <c r="F16">
         <v>2</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>18.49871817</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>7.65717139</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>26.15588956</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>16.225695985</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>9.332896422999999</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>1.2739333915</v>
       </c>
-      <c r="K16">
+      <c r="M16">
         <v>25.558592408</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>4.497018075011564</v>
       </c>
-      <c r="N16">
+      <c r="P16">
         <v>-28.33121387257285</v>
       </c>
-      <c r="O16">
+      <c r="Q16">
         <v>-50.50151298237986</v>
       </c>
-      <c r="P16">
+      <c r="R16">
         <v>-89.94036150023128</v>
       </c>
-      <c r="Q16">
+      <c r="S16">
         <v>2</v>
       </c>
-      <c r="R16">
+      <c r="T16">
         <v>-2.273022185000002</v>
       </c>
-      <c r="S16">
+      <c r="U16">
         <v>-516.6615007903032</v>
       </c>
-      <c r="T16">
-        <v>-185.4682310529294</v>
-      </c>
-      <c r="U16">
+      <c r="V16">
+        <v>-198.7159618424243</v>
+      </c>
+      <c r="W16">
         <v>-711.7740798579848</v>
       </c>
-      <c r="V16">
-        <v>-645.3938964649907</v>
+      <c r="X16">
+        <v>-511.7917720943899</v>
       </c>
     </row>
     <row r="17">
@@ -1556,66 +1656,72 @@
         <v>53.65576923076923</v>
       </c>
       <c r="C17">
-        <v>-129.6682176923077</v>
+        <v>21.74085737360796</v>
       </c>
       <c r="D17">
+        <v>1.279663954042972</v>
+      </c>
+      <c r="E17">
+        <v>2.878506031818905</v>
+      </c>
+      <c r="F17">
         <v>1</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>17.38958166833333</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>7.768696846666667</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>25.158278515</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>17.84053773833333</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>8.176969806833334</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>1.254831114166667</v>
       </c>
-      <c r="K17">
+      <c r="M17">
         <v>26.01750754516667</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>2.39641692676325</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <v>-15.09742663860848</v>
       </c>
-      <c r="O17">
+      <c r="Q17">
         <v>-26.9117620875513</v>
       </c>
-      <c r="P17">
+      <c r="R17">
         <v>-47.928338535265</v>
       </c>
-      <c r="Q17">
+      <c r="S17">
         <v>1</v>
       </c>
-      <c r="R17">
+      <c r="T17">
         <v>0.4509560700000002</v>
       </c>
-      <c r="S17">
+      <c r="U17">
         <v>100.9660163067785</v>
       </c>
-      <c r="T17">
-        <v>36.2442109819205</v>
-      </c>
-      <c r="U17">
+      <c r="V17">
+        <v>38.83308319491481</v>
+      </c>
+      <c r="W17">
         <v>139.0949262597589</v>
       </c>
-      <c r="V17">
-        <v>-55.61396347308049</v>
+      <c r="X17">
+        <v>95.79511159283518</v>
       </c>
     </row>
     <row r="18">
@@ -1628,66 +1734,72 @@
         <v>183.2476923076923</v>
       </c>
       <c r="C18">
-        <v>-47.38314423076922</v>
+        <v>75.94011848467443</v>
       </c>
       <c r="D18">
+        <v>2.560460464897154</v>
+      </c>
+      <c r="E18">
+        <v>15.93181660329086</v>
+      </c>
+      <c r="F18">
         <v>4</v>
       </c>
-      <c r="E18">
+      <c r="G18">
         <v>17.72735899833333</v>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>7.651144068333333</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>25.37850306666667</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>17.29026594833334</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>8.751537780333333</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>1.301592840833333</v>
       </c>
-      <c r="K18">
+      <c r="M18">
         <v>26.04180372866667</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>3.063092334736524</v>
       </c>
-      <c r="N18">
+      <c r="P18">
         <v>-19.2974817088401</v>
       </c>
-      <c r="O18">
+      <c r="Q18">
         <v>-34.39852691909116</v>
       </c>
-      <c r="P18">
+      <c r="R18">
         <v>-61.26184669473047</v>
       </c>
-      <c r="Q18">
+      <c r="S18">
         <v>3.5</v>
       </c>
-      <c r="R18">
+      <c r="T18">
         <v>-0.4370930499999979</v>
       </c>
-      <c r="S18">
+      <c r="U18">
         <v>-101.5090486726043</v>
       </c>
-      <c r="T18">
-        <v>-36.43914567734512</v>
-      </c>
-      <c r="U18">
+      <c r="V18">
+        <v>-39.04194179715548</v>
+      </c>
+      <c r="W18">
         <v>-139.8430299251713</v>
       </c>
-      <c r="V18">
-        <v>-183.2907198224646</v>
+      <c r="X18">
+        <v>-59.96745710702098</v>
       </c>
     </row>
     <row r="19">
@@ -1700,66 +1812,72 @@
         <v>501.1975641025641</v>
       </c>
       <c r="C19">
-        <v>157.5468319230769</v>
+        <v>196.1880290353269</v>
       </c>
       <c r="D19">
+        <v>3.906252654340075</v>
+      </c>
+      <c r="E19">
+        <v>51.20076139307912</v>
+      </c>
+      <c r="F19">
         <v>16</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <v>18.94094098</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>7.475234071666667</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>26.41617505166667</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>19.76502023666666</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>7.915039723833333</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>1.243342730833333</v>
       </c>
-      <c r="K19">
+      <c r="M19">
         <v>27.6800599605</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>2.598609080226484</v>
       </c>
-      <c r="N19">
+      <c r="P19">
         <v>-16.37123720542685</v>
       </c>
-      <c r="O19">
+      <c r="Q19">
         <v>-29.18237997094342</v>
       </c>
-      <c r="P19">
+      <c r="R19">
         <v>-51.97218160452968</v>
       </c>
-      <c r="Q19">
+      <c r="S19">
         <v>11.08333333333333</v>
       </c>
-      <c r="R19">
+      <c r="T19">
         <v>0.8240792566666642</v>
       </c>
-      <c r="S19">
+      <c r="U19">
         <v>182.81656621165</v>
       </c>
-      <c r="T19">
-        <v>65.6264596657205</v>
-      </c>
-      <c r="U19">
+      <c r="V19">
+        <v>70.31406392755768</v>
+      </c>
+      <c r="W19">
         <v>251.8556017799879</v>
       </c>
-      <c r="V19">
-        <v>311.1810181637834</v>
+      <c r="X19">
+        <v>349.8222152760334</v>
       </c>
     </row>
     <row r="20">
@@ -1772,66 +1890,72 @@
         <v>101.4121794871795</v>
       </c>
       <c r="C20">
-        <v>-99.973775</v>
+        <v>41.11801074612283</v>
       </c>
       <c r="D20">
+        <v>1.577221861175118</v>
+      </c>
+      <c r="E20">
+        <v>6.35076065273292</v>
+      </c>
+      <c r="F20">
         <v>4</v>
       </c>
-      <c r="E20">
+      <c r="G20">
         <v>17.24828480833333</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>9.214412571666667</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>26.46269738</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>17.63945969833333</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>8.806338972999999</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>1.410547525</v>
       </c>
-      <c r="K20">
+      <c r="M20">
         <v>26.44579867133333</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>0.8470214289750483</v>
       </c>
-      <c r="N20">
+      <c r="P20">
         <v>-5.336235002542804</v>
       </c>
-      <c r="O20">
+      <c r="Q20">
         <v>-9.512050647389792</v>
       </c>
-      <c r="P20">
+      <c r="R20">
         <v>-16.94042857950097</v>
       </c>
-      <c r="Q20">
+      <c r="S20">
         <v>3.638888888888889</v>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>0.3911748899999985</v>
       </c>
-      <c r="S20">
+      <c r="U20">
         <v>98.44970016032879</v>
       </c>
-      <c r="T20">
-        <v>35.34091800627187</v>
-      </c>
-      <c r="U20">
+      <c r="V20">
+        <v>37.86526929243415</v>
+      </c>
+      <c r="W20">
         <v>135.6283459029268</v>
       </c>
-      <c r="V20">
-        <v>-11.036125487061</v>
+      <c r="X20">
+        <v>130.0556602590618</v>
       </c>
     </row>
     <row r="21">
@@ -1844,66 +1968,72 @@
         <v>580.2130641025641</v>
       </c>
       <c r="C21">
-        <v>205.6821628846154</v>
+        <v>227.0408212088765</v>
       </c>
       <c r="D21">
+        <v>4.982846028437519</v>
+      </c>
+      <c r="E21">
+        <v>66.04673885975737</v>
+      </c>
+      <c r="F21">
         <v>60</v>
       </c>
-      <c r="E21">
+      <c r="G21">
         <v>19.15098685333333</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>9.301857549999999</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>28.45284440333333</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>21.81097294</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>9.169695069499999</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>1.2817225465</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <v>30.9806680095</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>0.9806401652694139</v>
       </c>
-      <c r="N21">
+      <c r="P21">
         <v>-6.178033041197307</v>
       </c>
-      <c r="O21">
+      <c r="Q21">
         <v>-11.01258905597552</v>
       </c>
-      <c r="P21">
+      <c r="R21">
         <v>-19.61280330538828</v>
       </c>
-      <c r="Q21">
+      <c r="S21">
         <v>29.55555555555556</v>
       </c>
-      <c r="R21">
+      <c r="T21">
         <v>2.659986086666667</v>
       </c>
-      <c r="S21">
+      <c r="U21">
         <v>608.3157967967197</v>
       </c>
-      <c r="T21">
-        <v>218.3697732090789</v>
-      </c>
-      <c r="U21">
+      <c r="V21">
+        <v>233.9676141525845</v>
+      </c>
+      <c r="W21">
         <v>838.0407982126707</v>
       </c>
-      <c r="V21">
-        <v>802.9853706253597</v>
+      <c r="X21">
+        <v>824.3440289496208</v>
       </c>
     </row>
     <row r="22">
@@ -1916,66 +2046,72 @@
         <v>379.4884615384615</v>
       </c>
       <c r="C22">
-        <v>78.69687000000002</v>
+        <v>149.678736219569</v>
       </c>
       <c r="D22">
+        <v>5.028966557127412</v>
+      </c>
+      <c r="E22">
+        <v>43.71142997862479</v>
+      </c>
+      <c r="F22">
         <v>4</v>
       </c>
-      <c r="E22">
+      <c r="G22">
         <v>18.25023845333333</v>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>7.428767183333333</v>
       </c>
-      <c r="G22">
+      <c r="I22">
         <v>25.67900563666667</v>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>19.59409039666667</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>7.509411629000001</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>1.295684132333333</v>
       </c>
-      <c r="K22">
+      <c r="M22">
         <v>27.10350202566666</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>2.359231208098899</v>
       </c>
-      <c r="N22">
+      <c r="P22">
         <v>-14.86315661102306</v>
       </c>
-      <c r="O22">
+      <c r="Q22">
         <v>-26.49416646695063</v>
       </c>
-      <c r="P22">
+      <c r="R22">
         <v>-47.18462416197798</v>
       </c>
-      <c r="Q22">
+      <c r="S22">
         <v>3.333333333333333</v>
       </c>
-      <c r="R22">
+      <c r="T22">
         <v>1.343851943333334</v>
       </c>
-      <c r="S22">
+      <c r="U22">
         <v>310.6749730211045</v>
       </c>
-      <c r="T22">
-        <v>111.5243492896273</v>
-      </c>
-      <c r="U22">
+      <c r="V22">
+        <v>119.4903742388864</v>
+      </c>
+      <c r="W22">
         <v>427.9985884737924</v>
       </c>
-      <c r="V22">
-        <v>362.8776765541539</v>
+      <c r="X22">
+        <v>433.8595427737229</v>
       </c>
     </row>
     <row r="23">
@@ -1988,66 +2124,72 @@
         <v>111.9438461538462</v>
       </c>
       <c r="C23">
-        <v>-93.66125115384615</v>
+        <v>44.73364597723211</v>
       </c>
       <c r="D23">
+        <v>1.436201281210562</v>
+      </c>
+      <c r="E23">
+        <v>6.460024410778119</v>
+      </c>
+      <c r="F23">
         <v>2</v>
       </c>
-      <c r="E23">
+      <c r="G23">
         <v>15.62478933666667</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>9.755520225</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>25.38030956166666</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>16.15549779666667</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>9.634761951333333</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>1.422238535666667</v>
       </c>
-      <c r="K23">
+      <c r="M23">
         <v>25.790259748</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>0.6724456699305441</v>
       </c>
-      <c r="N23">
+      <c r="P23">
         <v>-4.236407720562428</v>
       </c>
-      <c r="O23">
+      <c r="Q23">
         <v>-7.551564873320011</v>
       </c>
-      <c r="P23">
+      <c r="R23">
         <v>-13.44891339861088</v>
       </c>
-      <c r="Q23">
+      <c r="S23">
         <v>1.972222222222222</v>
       </c>
-      <c r="R23">
+      <c r="T23">
         <v>0.5307084599999996</v>
       </c>
-      <c r="S23">
+      <c r="U23">
         <v>134.6741235566853</v>
       </c>
-      <c r="T23">
-        <v>48.34455717419473</v>
-      </c>
-      <c r="U23">
+      <c r="V23">
+        <v>51.79773982949435</v>
+      </c>
+      <c r="W23">
         <v>185.5325977039381</v>
       </c>
-      <c r="V23">
-        <v>33.46130752951915</v>
+      <c r="X23">
+        <v>171.8562046605974</v>
       </c>
     </row>
     <row r="24">
@@ -2060,66 +2202,72 @@
         <v>616.7175512820513</v>
       </c>
       <c r="C24">
-        <v>227.9293871153847</v>
+        <v>242.624219954711</v>
       </c>
       <c r="D24">
+        <v>4.993074059988925</v>
+      </c>
+      <c r="E24">
+        <v>70.64114681055177</v>
+      </c>
+      <c r="F24">
         <v>60</v>
       </c>
-      <c r="E24">
+      <c r="G24">
         <v>17.90186749166667</v>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>8.436962761666667</v>
       </c>
-      <c r="G24">
+      <c r="I24">
         <v>26.33883025333333</v>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>18.00963822</v>
       </c>
-      <c r="I24">
+      <c r="K24">
         <v>8.657248975</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>1.379606870166667</v>
       </c>
-      <c r="K24">
+      <c r="M24">
         <v>26.666887195</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>1.637969963880097</v>
       </c>
-      <c r="N24">
+      <c r="P24">
         <v>-10.31921077244461</v>
       </c>
-      <c r="O24">
+      <c r="Q24">
         <v>-18.39440269437349</v>
       </c>
-      <c r="P24">
+      <c r="R24">
         <v>-32.75939927760194</v>
       </c>
-      <c r="Q24">
+      <c r="S24">
         <v>31.72222222222222</v>
       </c>
-      <c r="R24">
+      <c r="T24">
         <v>0.1077707283333318</v>
       </c>
-      <c r="S24">
+      <c r="U24">
         <v>26.52844974946723</v>
       </c>
-      <c r="T24">
-        <v>9.523033243398492</v>
-      </c>
-      <c r="U24">
+      <c r="V24">
+        <v>10.20324990364124</v>
+      </c>
+      <c r="W24">
         <v>36.54668072152244</v>
       </c>
-      <c r="V24">
-        <v>236.0634341704784</v>
+      <c r="X24">
+        <v>250.7582670098047</v>
       </c>
     </row>
     <row r="25">
@@ -2132,66 +2280,72 @@
         <v>118.075</v>
       </c>
       <c r="C25">
-        <v>-90.13130423076923</v>
+        <v>47.90461010685469</v>
       </c>
       <c r="D25">
+        <v>1.062002979425445</v>
+      </c>
+      <c r="E25">
+        <v>5.457296893052952</v>
+      </c>
+      <c r="F25">
         <v>1</v>
       </c>
-      <c r="E25">
+      <c r="G25">
         <v>15.747574295</v>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>9.404695233333333</v>
       </c>
-      <c r="G25">
+      <c r="I25">
         <v>25.15226952833333</v>
       </c>
-      <c r="H25">
+      <c r="J25">
         <v>14.5059828</v>
       </c>
-      <c r="I25">
+      <c r="K25">
         <v>9.411386414333334</v>
       </c>
-      <c r="J25">
+      <c r="L25">
         <v>1.447401226833333</v>
       </c>
-      <c r="K25">
+      <c r="M25">
         <v>23.91736921433333</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>6.174000995376301</v>
       </c>
-      <c r="N25">
+      <c r="P25">
         <v>-38.89620627087069</v>
       </c>
-      <c r="O25">
+      <c r="Q25">
         <v>-69.33403117807586</v>
       </c>
-      <c r="P25">
+      <c r="R25">
         <v>-123.480019907526</v>
       </c>
-      <c r="Q25">
+      <c r="S25">
         <v>1</v>
       </c>
-      <c r="R25">
+      <c r="T25">
         <v>-1.241591495</v>
       </c>
-      <c r="S25">
+      <c r="U25">
         <v>-320.6441868973749</v>
       </c>
-      <c r="T25">
-        <v>-115.1030414503397</v>
-      </c>
-      <c r="U25">
+      <c r="V25">
+        <v>-123.3246872682211</v>
+      </c>
+      <c r="W25">
         <v>-441.7325865031323</v>
       </c>
-      <c r="V25">
-        <v>-480.10952230622</v>
+      <c r="X25">
+        <v>-342.0736079685961</v>
       </c>
     </row>
     <row r="26">
@@ -2204,66 +2358,72 @@
         <v>62.20987179487179</v>
       </c>
       <c r="C26">
-        <v>-124.8120323076923</v>
+        <v>24.86147684920685</v>
       </c>
       <c r="D26">
+        <v>0.8559792271251631</v>
+      </c>
+      <c r="E26">
+        <v>2.339335300052007</v>
+      </c>
+      <c r="F26">
         <v>1</v>
       </c>
-      <c r="E26">
+      <c r="G26">
         <v>18.33970316666667</v>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>10.95371604</v>
       </c>
-      <c r="G26">
+      <c r="I26">
         <v>29.29341920666667</v>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>17.06013133166667</v>
       </c>
-      <c r="I26">
+      <c r="K26">
         <v>11.02718368683333</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>1.4471556175</v>
       </c>
-      <c r="K26">
+      <c r="M26">
         <v>28.0873150185</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>2.075840817204807</v>
       </c>
-      <c r="N26">
+      <c r="P26">
         <v>-13.07779714839029</v>
       </c>
-      <c r="O26">
+      <c r="Q26">
         <v>-23.31169237720999</v>
       </c>
-      <c r="P26">
+      <c r="R26">
         <v>-41.51681634409614</v>
       </c>
-      <c r="Q26">
+      <c r="S26">
         <v>0.9722222222222222</v>
       </c>
-      <c r="R26">
+      <c r="T26">
         <v>-1.279571834999999</v>
       </c>
-      <c r="S26">
+      <c r="U26">
         <v>-330.396632601507</v>
       </c>
-      <c r="T26">
-        <v>-118.6039193954128</v>
-      </c>
-      <c r="U26">
+      <c r="V26">
+        <v>-127.0756279236565</v>
+      </c>
+      <c r="W26">
         <v>-455.1679558054812</v>
       </c>
-      <c r="V26">
-        <v>-478.5203572864093</v>
+      <c r="X26">
+        <v>-328.8468481295101</v>
       </c>
     </row>
     <row r="27">
@@ -2276,66 +2436,72 @@
         <v>229.5128205128205</v>
       </c>
       <c r="C27">
-        <v>-17.83788538461537</v>
+        <v>93.73994764502967</v>
       </c>
       <c r="D27">
+        <v>2.25085548316566</v>
+      </c>
+      <c r="E27">
+        <v>18.24257241244788</v>
+      </c>
+      <c r="F27">
         <v>4</v>
       </c>
-      <c r="E27">
+      <c r="G27">
         <v>19.853450675</v>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>12.68932163666667</v>
       </c>
-      <c r="G27">
+      <c r="I27">
         <v>32.54277231166667</v>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>19.40672484</v>
       </c>
-      <c r="I27">
+      <c r="K27">
         <v>13.72259501166667</v>
       </c>
-      <c r="J27">
+      <c r="L27">
         <v>1.368905493</v>
       </c>
-      <c r="K27">
+      <c r="M27">
         <v>33.12931985166666</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M27">
+      <c r="O27">
         <v>2.268599779202153</v>
       </c>
-      <c r="N27">
+      <c r="P27">
         <v>-14.29217860897357</v>
       </c>
-      <c r="O27">
+      <c r="Q27">
         <v>-25.47637552044019</v>
       </c>
-      <c r="P27">
+      <c r="R27">
         <v>-45.37199558404307</v>
       </c>
-      <c r="Q27">
+      <c r="S27">
         <v>3.666666666666667</v>
       </c>
-      <c r="R27">
+      <c r="T27">
         <v>-0.4467258350000023</v>
       </c>
-      <c r="S27">
+      <c r="U27">
         <v>-109.1114283085731</v>
       </c>
-      <c r="T27">
-        <v>-39.16820503384677</v>
-      </c>
-      <c r="U27">
+      <c r="V27">
+        <v>-41.96593396483583</v>
+      </c>
+      <c r="W27">
         <v>-150.3163800041799</v>
       </c>
-      <c r="V27">
-        <v>-152.4256892136287</v>
+      <c r="X27">
+        <v>-40.84785618398365</v>
       </c>
     </row>
     <row r="28">
@@ -2348,66 +2514,72 @@
         <v>130.1305</v>
       </c>
       <c r="C28">
-        <v>-82.71224711538461</v>
+        <v>53.26814475341833</v>
       </c>
       <c r="D28">
+        <v>1.090745637070177</v>
+      </c>
+      <c r="E28">
+        <v>6.205393694571206</v>
+      </c>
+      <c r="F28">
         <v>2</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>20.68569447666667</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>12.026124995</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>32.71181947166667</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>20.44729365833333</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>12.14286722666667</v>
       </c>
-      <c r="J28">
+      <c r="L28">
         <v>1.247915171166667</v>
       </c>
-      <c r="K28">
+      <c r="M28">
         <v>32.590160885</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>0.7360342021259476</v>
       </c>
-      <c r="N28">
+      <c r="P28">
         <v>-4.63701547339347</v>
       </c>
-      <c r="O28">
+      <c r="Q28">
         <v>-8.265664089874392</v>
       </c>
-      <c r="P28">
+      <c r="R28">
         <v>-14.72068404251895</v>
       </c>
-      <c r="Q28">
+      <c r="S28">
         <v>1.555555555555556</v>
       </c>
-      <c r="R28">
+      <c r="T28">
         <v>-0.2384008183333357</v>
       </c>
-      <c r="S28">
+      <c r="U28">
         <v>-53.08215084613292</v>
       </c>
-      <c r="T28">
-        <v>-19.05513107297079</v>
-      </c>
-      <c r="U28">
+      <c r="V28">
+        <v>-20.41621186389728</v>
+      </c>
+      <c r="W28">
         <v>-73.12814873489819</v>
       </c>
-      <c r="V28">
-        <v>-144.0600620513919</v>
+      <c r="X28">
+        <v>-8.079670182588984</v>
       </c>
     </row>
     <row r="29">
@@ -2420,66 +2592,72 @@
         <v>146.1408974358974</v>
       </c>
       <c r="C29">
-        <v>-71.83924653846152</v>
+        <v>58.48647982432736</v>
       </c>
       <c r="D29">
+        <v>1.557222072208001</v>
+      </c>
+      <c r="E29">
+        <v>8.952481210018838</v>
+      </c>
+      <c r="F29">
         <v>4</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <v>22.35290135166667</v>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>12.50052412166667</v>
       </c>
-      <c r="G29">
+      <c r="I29">
         <v>34.85342547333333</v>
       </c>
-      <c r="H29">
+      <c r="J29">
         <v>20.36209860166667</v>
       </c>
-      <c r="I29">
+      <c r="K29">
         <v>13.86795943166667</v>
       </c>
-      <c r="J29">
+      <c r="L29">
         <v>1.302890749166667</v>
       </c>
-      <c r="K29">
+      <c r="M29">
         <v>34.23005803333334</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M29">
+      <c r="O29">
         <v>0.6936343066418474</v>
       </c>
-      <c r="N29">
+      <c r="P29">
         <v>-4.369896131843639</v>
       </c>
-      <c r="O29">
+      <c r="Q29">
         <v>-7.789513263587947</v>
       </c>
-      <c r="P29">
+      <c r="R29">
         <v>-13.87268613283695</v>
       </c>
-      <c r="Q29">
+      <c r="S29">
         <v>3.888888888888889</v>
       </c>
-      <c r="R29">
+      <c r="T29">
         <v>-1.99080275</v>
       </c>
-      <c r="S29">
+      <c r="U29">
         <v>-462.7984949342356</v>
       </c>
-      <c r="T29">
-        <v>-166.1327930533154</v>
-      </c>
-      <c r="U29">
+      <c r="V29">
+        <v>-177.9994211285522</v>
+      </c>
+      <c r="W29">
         <v>-637.5701932263233</v>
       </c>
-      <c r="V29">
-        <v>-542.4272547362851</v>
+      <c r="X29">
+        <v>-412.1015283734962</v>
       </c>
     </row>
     <row r="30">
@@ -2492,66 +2670,72 @@
         <v>337.4911538461538</v>
       </c>
       <c r="C30">
-        <v>52.38197307692309</v>
+        <v>128.2161296176161</v>
       </c>
       <c r="D30">
+        <v>2.963281691573025</v>
+      </c>
+      <c r="E30">
+        <v>29.14410918623349</v>
+      </c>
+      <c r="F30">
         <v>16</v>
       </c>
-      <c r="E30">
+      <c r="G30">
         <v>22.281533595</v>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>12.30114996333333</v>
       </c>
-      <c r="G30">
+      <c r="I30">
         <v>34.58268355833333</v>
       </c>
-      <c r="H30">
+      <c r="J30">
         <v>23.50365367666667</v>
       </c>
-      <c r="I30">
+      <c r="K30">
         <v>13.197827925</v>
       </c>
-      <c r="J30">
+      <c r="L30">
         <v>1.2313447075</v>
       </c>
-      <c r="K30">
+      <c r="M30">
         <v>36.70148160166666</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M30">
+      <c r="O30">
         <v>0.7101404810624976</v>
       </c>
-      <c r="N30">
+      <c r="P30">
         <v>-4.473885030693735</v>
       </c>
-      <c r="O30">
+      <c r="Q30">
         <v>-7.974877602331849</v>
       </c>
-      <c r="P30">
+      <c r="R30">
         <v>-14.20280962124995</v>
       </c>
-      <c r="Q30">
+      <c r="S30">
         <v>11.36111111111111</v>
       </c>
-      <c r="R30">
+      <c r="T30">
         <v>1.222120081666667</v>
       </c>
-      <c r="S30">
+      <c r="U30">
         <v>268.5030565343279</v>
       </c>
-      <c r="T30">
-        <v>96.38571260206642</v>
-      </c>
-      <c r="U30">
+      <c r="V30">
+        <v>103.2704063593569</v>
+      </c>
+      <c r="W30">
         <v>369.9008261917018</v>
       </c>
-      <c r="V30">
-        <v>312.9101520089192</v>
+      <c r="X30">
+        <v>388.7443085496121</v>
       </c>
     </row>
     <row r="31">
@@ -2564,66 +2748,72 @@
         <v>334.3515</v>
       </c>
       <c r="C31">
-        <v>49.16695634615385</v>
+        <v>128.1403998222181</v>
       </c>
       <c r="D31">
+        <v>2.951371914817594</v>
+      </c>
+      <c r="E31">
+        <v>29.06460649688565</v>
+      </c>
+      <c r="F31">
         <v>8</v>
       </c>
-      <c r="E31">
+      <c r="G31">
         <v>18.41433809833334</v>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>8.493144115</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>26.90748221333333</v>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>18.23542061666667</v>
       </c>
-      <c r="I31">
+      <c r="K31">
         <v>9.010506192166666</v>
       </c>
-      <c r="J31">
+      <c r="L31">
         <v>1.383368769</v>
       </c>
-      <c r="K31">
+      <c r="M31">
         <v>27.24592680883333</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M31">
+      <c r="O31">
         <v>0.9077257805083475</v>
       </c>
-      <c r="N31">
+      <c r="P31">
         <v>-5.71867241720259</v>
       </c>
-      <c r="O31">
+      <c r="Q31">
         <v>-10.19376051510874</v>
       </c>
-      <c r="P31">
+      <c r="R31">
         <v>-18.15451561016695</v>
       </c>
-      <c r="Q31">
+      <c r="S31">
         <v>5.694444444444445</v>
       </c>
-      <c r="R31">
+      <c r="T31">
         <v>-0.1789174816666694</v>
       </c>
-      <c r="S31">
+      <c r="U31">
         <v>-44.16176769706797</v>
       </c>
-      <c r="T31">
-        <v>-15.85294225022952</v>
-      </c>
-      <c r="U31">
+      <c r="V31">
+        <v>-16.98529526810306</v>
+      </c>
+      <c r="W31">
         <v>-60.83906294430943</v>
       </c>
-      <c r="V31">
-        <v>-5.188571866022855</v>
+      <c r="X31">
+        <v>73.78487161004144</v>
       </c>
     </row>
     <row r="32">
@@ -2636,66 +2826,72 @@
         <v>84.00628205128206</v>
       </c>
       <c r="C32">
-        <v>-109.7441807692308</v>
+        <v>32.23490471586838</v>
       </c>
       <c r="D32">
+        <v>1.728354121261013</v>
+      </c>
+      <c r="E32">
+        <v>5.302511200470931</v>
+      </c>
+      <c r="F32">
         <v>1</v>
       </c>
-      <c r="E32">
+      <c r="G32">
         <v>14.78553080333333</v>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>14.93936280333333</v>
       </c>
-      <c r="G32">
+      <c r="I32">
         <v>29.72489360666667</v>
       </c>
-      <c r="H32">
+      <c r="J32">
         <v>13.97646859166667</v>
       </c>
-      <c r="I32">
+      <c r="K32">
         <v>16.79281487833333</v>
       </c>
-      <c r="J32">
+      <c r="L32">
         <v>1.482308474333333</v>
       </c>
-      <c r="K32">
+      <c r="M32">
         <v>30.76928347</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M32">
+      <c r="O32">
         <v>7.358028853615001</v>
       </c>
-      <c r="N32">
+      <c r="P32">
         <v>-46.3555817777745</v>
       </c>
-      <c r="O32">
+      <c r="Q32">
         <v>-82.63066402609647</v>
       </c>
-      <c r="P32">
+      <c r="R32">
         <v>-147.1605770723</v>
       </c>
-      <c r="Q32">
+      <c r="S32">
         <v>1</v>
       </c>
-      <c r="R32">
+      <c r="T32">
         <v>-0.8090622116666673</v>
       </c>
-      <c r="S32">
+      <c r="U32">
         <v>-213.9814934290758</v>
       </c>
-      <c r="T32">
-        <v>-76.81386943607849</v>
-      </c>
-      <c r="U32">
+      <c r="V32">
+        <v>-82.30057439579838</v>
+      </c>
+      <c r="W32">
         <v>-294.7896840758303</v>
       </c>
-      <c r="V32">
-        <v>-406.356338224403</v>
+      <c r="X32">
+        <v>-264.3772527393039</v>
       </c>
     </row>
     <row r="33">
@@ -2708,66 +2904,72 @@
         <v>266.2105897435898</v>
       </c>
       <c r="C33">
-        <v>6.197641153846162</v>
+        <v>100.6533553700835</v>
       </c>
       <c r="D33">
+        <v>2.403224435205201</v>
+      </c>
+      <c r="E33">
+        <v>20.36140204929067</v>
+      </c>
+      <c r="F33">
         <v>8</v>
       </c>
-      <c r="E33">
+      <c r="G33">
         <v>18.24266179833333</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>9.758735895000001</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>28.00139769333333</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>18.806023575</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>10.669294244</v>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>1.342777728666667</v>
       </c>
-      <c r="K33">
+      <c r="M33">
         <v>29.475317819</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M33">
+      <c r="O33">
         <v>1.844119286466969</v>
       </c>
-      <c r="N33">
+      <c r="P33">
         <v>-11.61795150474191</v>
       </c>
-      <c r="O33">
+      <c r="Q33">
         <v>-20.70945958702407</v>
       </c>
-      <c r="P33">
+      <c r="R33">
         <v>-36.88238572933939</v>
       </c>
-      <c r="Q33">
+      <c r="S33">
         <v>5.861111111111111</v>
       </c>
-      <c r="R33">
+      <c r="T33">
         <v>0.5633617766666674</v>
       </c>
-      <c r="S33">
+      <c r="U33">
         <v>134.9730967463636</v>
       </c>
-      <c r="T33">
-        <v>48.45188088331</v>
-      </c>
-      <c r="U33">
+      <c r="V33">
+        <v>51.91272951783213</v>
+      </c>
+      <c r="W33">
         <v>185.9444754356057</v>
       </c>
-      <c r="V33">
-        <v>120.4612783131856</v>
+      <c r="X33">
+        <v>214.9169925294229</v>
       </c>
     </row>
     <row r="34">
@@ -2780,66 +2982,72 @@
         <v>204.8405128205128</v>
       </c>
       <c r="C34">
-        <v>-33.63691384615384</v>
+        <v>78.8648587752663</v>
       </c>
       <c r="D34">
+        <v>0.7129800354265221</v>
+      </c>
+      <c r="E34">
+        <v>6.205575015009935</v>
+      </c>
+      <c r="F34">
         <v>1</v>
       </c>
-      <c r="E34">
+      <c r="G34">
         <v>17.26795337666667</v>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>10.94251334666667</v>
       </c>
-      <c r="G34">
+      <c r="I34">
         <v>28.21046672333333</v>
       </c>
-      <c r="H34">
+      <c r="J34">
         <v>17.420768235</v>
       </c>
-      <c r="I34">
+      <c r="K34">
         <v>11.58500638166667</v>
       </c>
-      <c r="J34">
+      <c r="L34">
         <v>1.4339126615</v>
       </c>
-      <c r="K34">
+      <c r="M34">
         <v>29.00577461666667</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M34">
+      <c r="O34">
         <v>4.45829362716574</v>
       </c>
-      <c r="N34">
+      <c r="P34">
         <v>-28.08724985114416</v>
       </c>
-      <c r="O34">
+      <c r="Q34">
         <v>-50.06663743307126</v>
       </c>
-      <c r="P34">
+      <c r="R34">
         <v>-89.1658725433148</v>
       </c>
-      <c r="Q34">
+      <c r="S34">
         <v>0.5555555555555556</v>
       </c>
-      <c r="R34">
+      <c r="T34">
         <v>0.1528148583333326</v>
       </c>
-      <c r="S34">
+      <c r="U34">
         <v>39.09704986394755</v>
       </c>
-      <c r="T34">
-        <v>14.03483841269912</v>
-      </c>
-      <c r="U34">
+      <c r="V34">
+        <v>15.03732687074906</v>
+      </c>
+      <c r="W34">
         <v>53.86169987410702</v>
       </c>
-      <c r="V34">
-        <v>-44.60650141527756</v>
+      <c r="X34">
+        <v>67.89527120614258</v>
       </c>
     </row>
     <row r="35">
@@ -2852,66 +3060,72 @@
         <v>509.6371538461539</v>
       </c>
       <c r="C35">
-        <v>162.6234432692308</v>
+        <v>200.3841434845547</v>
       </c>
       <c r="D35">
+        <v>2.965130262270036</v>
+      </c>
+      <c r="E35">
+        <v>45.56331380125014</v>
+      </c>
+      <c r="F35">
         <v>4</v>
       </c>
-      <c r="E35">
+      <c r="G35">
         <v>20.72395750666667</v>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>12.162037295</v>
       </c>
-      <c r="G35">
+      <c r="I35">
         <v>32.88599480166667</v>
       </c>
-      <c r="H35">
+      <c r="J35">
         <v>20.34924550333333</v>
       </c>
-      <c r="I35">
+      <c r="K35">
         <v>13.3018109</v>
       </c>
-      <c r="J35">
+      <c r="L35">
         <v>1.363697516166667</v>
       </c>
-      <c r="K35">
+      <c r="M35">
         <v>33.65105640333333</v>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M35">
+      <c r="O35">
         <v>1.331719516371994</v>
       </c>
-      <c r="N35">
+      <c r="P35">
         <v>-8.389832953143562</v>
       </c>
-      <c r="O35">
+      <c r="Q35">
         <v>-14.95521016885749</v>
       </c>
-      <c r="P35">
+      <c r="R35">
         <v>-26.63439032743988</v>
       </c>
-      <c r="Q35">
+      <c r="S35">
         <v>3.5</v>
       </c>
-      <c r="R35">
+      <c r="T35">
         <v>-0.374712003333336</v>
       </c>
-      <c r="S35">
+      <c r="U35">
         <v>-91.17407380077907</v>
       </c>
-      <c r="T35">
-        <v>-32.72915469771556</v>
-      </c>
-      <c r="U35">
+      <c r="V35">
+        <v>-35.0669514618381</v>
+      </c>
+      <c r="W35">
         <v>-125.6051445427758</v>
       </c>
-      <c r="V35">
-        <v>56.49415929959423</v>
+      <c r="X35">
+        <v>94.25485951491814</v>
       </c>
     </row>
     <row r="36">
@@ -2924,66 +3138,72 @@
         <v>259.0865384615385</v>
       </c>
       <c r="C36">
-        <v>-0.3553538461538302</v>
+        <v>106.0108094880664</v>
       </c>
       <c r="D36">
+        <v>1.689488470807592</v>
+      </c>
+      <c r="E36">
+        <v>17.17151735011587</v>
+      </c>
+      <c r="F36">
         <v>8</v>
       </c>
-      <c r="E36">
+      <c r="G36">
         <v>18.31235483166667</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>14.00340576833333</v>
       </c>
-      <c r="G36">
+      <c r="I36">
         <v>32.3157606</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>19.53381813333333</v>
       </c>
-      <c r="I36">
+      <c r="K36">
         <v>14.71755182666667</v>
       </c>
-      <c r="J36">
+      <c r="L36">
         <v>1.358907214</v>
       </c>
-      <c r="K36">
+      <c r="M36">
         <v>34.25136996</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M36">
+      <c r="O36">
         <v>2.991736858382932</v>
       </c>
-      <c r="N36">
+      <c r="P36">
         <v>-18.84794220781247</v>
       </c>
-      <c r="O36">
+      <c r="Q36">
         <v>-33.59720491964033</v>
       </c>
-      <c r="P36">
+      <c r="R36">
         <v>-59.83473716765864</v>
       </c>
-      <c r="Q36">
+      <c r="S36">
         <v>5.944444444444445</v>
       </c>
-      <c r="R36">
+      <c r="T36">
         <v>1.221463301666667</v>
       </c>
-      <c r="S36">
+      <c r="U36">
         <v>296.1596805234695</v>
       </c>
-      <c r="T36">
-        <v>106.3137314699634</v>
-      </c>
-      <c r="U36">
+      <c r="V36">
+        <v>113.9075694321036</v>
+      </c>
+      <c r="W36">
         <v>408.001726029871</v>
       </c>
-      <c r="V36">
-        <v>262.2071217576753</v>
+      <c r="X36">
+        <v>368.5732850918955</v>
       </c>
     </row>
     <row r="37">
@@ -2996,66 +3216,72 @@
         <v>324.4254487179487</v>
       </c>
       <c r="C37">
-        <v>41.64623942307693</v>
+        <v>126.5987710316066</v>
       </c>
       <c r="D37">
+        <v>2.343764760437876</v>
+      </c>
+      <c r="E37">
+        <v>25.23677737461479</v>
+      </c>
+      <c r="F37">
         <v>16</v>
       </c>
-      <c r="E37">
+      <c r="G37">
         <v>21.03022653333333</v>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>13.001140755</v>
       </c>
-      <c r="G37">
+      <c r="I37">
         <v>34.03136728833334</v>
       </c>
-      <c r="H37">
+      <c r="J37">
         <v>21.70943054333333</v>
       </c>
-      <c r="I37">
+      <c r="K37">
         <v>14.36475716833333</v>
       </c>
-      <c r="J37">
+      <c r="L37">
         <v>1.326444698333333</v>
       </c>
-      <c r="K37">
+      <c r="M37">
         <v>36.07418771166667</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M37">
+      <c r="O37">
         <v>0.9167533653688136</v>
       </c>
-      <c r="N37">
+      <c r="P37">
         <v>-5.775546201823525</v>
       </c>
-      <c r="O37">
+      <c r="Q37">
         <v>-10.29514029309178</v>
       </c>
-      <c r="P37">
+      <c r="R37">
         <v>-18.33506730737627</v>
       </c>
-      <c r="Q37">
+      <c r="S37">
         <v>10.77777777777778</v>
       </c>
-      <c r="R37">
+      <c r="T37">
         <v>0.6792040099999994</v>
       </c>
-      <c r="S37">
+      <c r="U37">
         <v>160.7478211381349</v>
       </c>
-      <c r="T37">
-        <v>57.7043460495869</v>
-      </c>
-      <c r="U37">
+      <c r="V37">
+        <v>61.82608505312882</v>
+      </c>
+      <c r="W37">
         <v>221.4527931823003</v>
       </c>
-      <c r="V37">
-        <v>192.0989202681201</v>
+      <c r="X37">
+        <v>277.0514518766497</v>
       </c>
     </row>
     <row r="38">
@@ -3068,66 +3294,72 @@
         <v>142.2470512820513</v>
       </c>
       <c r="C38">
-        <v>-73.8621246153846</v>
+        <v>57.8715096135934</v>
       </c>
       <c r="D38">
+        <v>1.792634842757805</v>
+      </c>
+      <c r="E38">
+        <v>9.755083068534551</v>
+      </c>
+      <c r="F38">
         <v>2</v>
       </c>
-      <c r="E38">
+      <c r="G38">
         <v>19.93975524333333</v>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>13.90334904166667</v>
       </c>
-      <c r="G38">
+      <c r="I38">
         <v>33.843104285</v>
       </c>
-      <c r="H38">
+      <c r="J38">
         <v>21.53524523833333</v>
       </c>
-      <c r="I38">
+      <c r="K38">
         <v>14.45000332833333</v>
       </c>
-      <c r="J38">
+      <c r="L38">
         <v>1.288804584666667</v>
       </c>
-      <c r="K38">
+      <c r="M38">
         <v>35.98524856666667</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M38">
+      <c r="O38">
         <v>0.6187439129779645</v>
       </c>
-      <c r="N38">
+      <c r="P38">
         <v>-3.898086651761176</v>
       </c>
-      <c r="O38">
+      <c r="Q38">
         <v>-6.948494142742542</v>
       </c>
-      <c r="P38">
+      <c r="R38">
         <v>-12.37487825955929</v>
       </c>
-      <c r="Q38">
+      <c r="S38">
         <v>2</v>
       </c>
-      <c r="R38">
+      <c r="T38">
         <v>1.595489994999998</v>
       </c>
-      <c r="S38">
+      <c r="U38">
         <v>366.8908348201983</v>
       </c>
-      <c r="T38">
-        <v>131.7044022431481</v>
-      </c>
-      <c r="U38">
+      <c r="V38">
+        <v>141.1118595462301</v>
+      </c>
+      <c r="W38">
         <v>505.4438659799901</v>
       </c>
-      <c r="V38">
-        <v>286.0802160620711</v>
+      <c r="X38">
+        <v>417.8138502910492</v>
       </c>
     </row>
     <row r="39">
@@ -3140,66 +3372,72 @@
         <v>126.2232051282051</v>
       </c>
       <c r="C39">
-        <v>-83.73494846153845</v>
+        <v>50.32343597562431</v>
       </c>
       <c r="D39">
+        <v>1.507974293939214</v>
+      </c>
+      <c r="E39">
+        <v>7.528754213737447</v>
+      </c>
+      <c r="F39">
         <v>2</v>
       </c>
-      <c r="E39">
+      <c r="G39">
         <v>22.18978647833334</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>12.43652800666667</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>34.626314485</v>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>20.42762157666667</v>
       </c>
-      <c r="I39">
+      <c r="K39">
         <v>14.15560386</v>
       </c>
-      <c r="J39">
+      <c r="L39">
         <v>1.286318249666667</v>
       </c>
-      <c r="K39">
+      <c r="M39">
         <v>34.58322543666667</v>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M39">
+      <c r="O39">
         <v>1.395749491872198</v>
       </c>
-      <c r="N39">
+      <c r="P39">
         <v>-8.793221798794846</v>
       </c>
-      <c r="O39">
+      <c r="Q39">
         <v>-15.67426679372478</v>
       </c>
-      <c r="P39">
+      <c r="R39">
         <v>-27.91498983744396</v>
       </c>
-      <c r="Q39">
+      <c r="S39">
         <v>1.833333333333333</v>
       </c>
-      <c r="R39">
+      <c r="T39">
         <v>-1.762164901666669</v>
       </c>
-      <c r="S39">
+      <c r="U39">
         <v>-404.4368167751635</v>
       </c>
-      <c r="T39">
-        <v>-145.1824470474946</v>
-      </c>
-      <c r="U39">
+      <c r="V39">
+        <v>-155.5526218366014</v>
+      </c>
+      <c r="W39">
         <v>-557.1687510691279</v>
       </c>
-      <c r="V39">
-        <v>-503.8460320304268</v>
+      <c r="X39">
+        <v>-369.787647593264</v>
       </c>
     </row>
     <row r="40">
@@ -3212,66 +3450,72 @@
         <v>372.6879487179487</v>
       </c>
       <c r="C40">
-        <v>72.4979007692308</v>
+        <v>147.6211274417673</v>
       </c>
       <c r="D40">
+        <v>3.401077723047435</v>
+      </c>
+      <c r="E40">
+        <v>36.02408775721546</v>
+      </c>
+      <c r="F40">
         <v>8</v>
       </c>
-      <c r="E40">
+      <c r="G40">
         <v>20.38238114833333</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>13.65231196166667</v>
       </c>
-      <c r="G40">
+      <c r="I40">
         <v>34.03469311</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>20.91067990666667</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>14.24542969666667</v>
       </c>
-      <c r="J40">
+      <c r="L40">
         <v>1.177016317833333</v>
       </c>
-      <c r="K40">
+      <c r="M40">
         <v>35.15610960333333</v>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M40">
+      <c r="O40">
         <v>1.143627946389912</v>
       </c>
-      <c r="N40">
+      <c r="P40">
         <v>-7.204856062256444</v>
       </c>
-      <c r="O40">
+      <c r="Q40">
         <v>-12.84294183795871</v>
       </c>
-      <c r="P40">
+      <c r="R40">
         <v>-22.87255892779823</v>
       </c>
-      <c r="Q40">
+      <c r="S40">
         <v>6.972222222222222</v>
       </c>
-      <c r="R40">
+      <c r="T40">
         <v>0.5282987583333316</v>
       </c>
-      <c r="S40">
+      <c r="U40">
         <v>110.9475660565777</v>
       </c>
-      <c r="T40">
-        <v>39.82733140492535</v>
-      </c>
-      <c r="U40">
+      <c r="V40">
+        <v>42.67214079099144</v>
+      </c>
+      <c r="W40">
         <v>152.8459186945592</v>
       </c>
-      <c r="V40">
-        <v>170.6025249878498</v>
+      <c r="X40">
+        <v>245.7257516603864</v>
       </c>
     </row>
     <row r="41">
@@ -3284,66 +3528,72 @@
         <v>386.626282051282</v>
       </c>
       <c r="C41">
-        <v>77.57301846153848</v>
+        <v>150.3462897602319</v>
       </c>
       <c r="D41">
+        <v>2.189137107426768</v>
+      </c>
+      <c r="E41">
+        <v>28.7717658624749</v>
+      </c>
+      <c r="F41">
         <v>16</v>
       </c>
-      <c r="E41">
+      <c r="G41">
         <v>20.36408032333333</v>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>12.75228142833333</v>
       </c>
-      <c r="G41">
+      <c r="I41">
         <v>33.11636175166667</v>
       </c>
-      <c r="H41">
+      <c r="J41">
         <v>23.87834243333333</v>
       </c>
-      <c r="I41">
+      <c r="K41">
         <v>12.781894505</v>
       </c>
-      <c r="J41">
+      <c r="L41">
         <v>1.134298261833333</v>
       </c>
-      <c r="K41">
+      <c r="M41">
         <v>36.66023693833333</v>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="M41">
+      <c r="O41">
         <v>5.855716016589727</v>
       </c>
-      <c r="N41">
+      <c r="P41">
         <v>-36.89101090451528</v>
       </c>
-      <c r="O41">
+      <c r="Q41">
         <v>-65.75969086630263</v>
       </c>
-      <c r="P41">
+      <c r="R41">
         <v>-117.1143203317945</v>
       </c>
-      <c r="Q41">
+      <c r="S41">
         <v>10.22222222222222</v>
       </c>
-      <c r="R41">
+      <c r="T41">
         <v>3.514262110000001</v>
       </c>
-      <c r="S41">
+      <c r="U41">
         <v>711.241553830229</v>
       </c>
-      <c r="T41">
-        <v>255.3174808621335</v>
-      </c>
-      <c r="U41">
+      <c r="V41">
+        <v>273.5544437808574</v>
+      </c>
+      <c r="W41">
         <v>979.8355436971934</v>
       </c>
-      <c r="V41">
-        <v>723.0548814254648</v>
+      <c r="X41">
+        <v>795.8281527241583</v>
       </c>
     </row>
     <row r="42">
@@ -3356,66 +3606,72 @@
         <v>221.565641025641</v>
       </c>
       <c r="C42">
-        <v>-23.22944307692307</v>
+        <v>90.05586434145199</v>
       </c>
       <c r="D42">
+        <v>2.748694971202441</v>
+      </c>
+      <c r="E42">
+        <v>19.65576041940932</v>
+      </c>
+      <c r="F42">
         <v>1</v>
       </c>
-      <c r="E42">
+      <c r="G42">
         <v>17.53820831</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>14.17948345166667</v>
       </c>
-      <c r="G42">
+      <c r="I42">
         <v>31.71769176166667</v>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>18.11070592666667</v>
       </c>
-      <c r="I42">
+      <c r="K42">
         <v>13.97844794</v>
       </c>
-      <c r="J42">
+      <c r="L42">
         <v>1.2480027205</v>
       </c>
-      <c r="K42">
+      <c r="M42">
         <v>32.08915386666667</v>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M42">
+      <c r="O42">
         <v>1.809020597434316</v>
       </c>
-      <c r="N42">
+      <c r="P42">
         <v>-11.39682976383619</v>
       </c>
-      <c r="O42">
+      <c r="Q42">
         <v>-20.31530130918737</v>
       </c>
-      <c r="P42">
+      <c r="R42">
         <v>-36.18041194868632</v>
       </c>
-      <c r="Q42">
+      <c r="S42">
         <v>1</v>
       </c>
-      <c r="R42">
+      <c r="T42">
         <v>0.5724976166666664</v>
       </c>
-      <c r="S42">
+      <c r="U42">
         <v>127.4808411860072</v>
       </c>
-      <c r="T42">
-        <v>45.762353246259</v>
-      </c>
-      <c r="U42">
+      <c r="V42">
+        <v>49.03109276384893</v>
+      </c>
+      <c r="W42">
         <v>175.6228368010717</v>
       </c>
-      <c r="V42">
-        <v>83.93609679989677</v>
+      <c r="X42">
+        <v>197.2214042182719</v>
       </c>
     </row>
     <row r="43">
@@ -3428,66 +3684,72 @@
         <v>117.894358974359</v>
       </c>
       <c r="C43">
-        <v>-90.68202692307692</v>
+        <v>47.10781310866284</v>
       </c>
       <c r="D43">
+        <v>0.8820082649149968</v>
+      </c>
+      <c r="E43">
+        <v>4.557394938224608</v>
+      </c>
+      <c r="F43">
         <v>2</v>
       </c>
-      <c r="E43">
+      <c r="G43">
         <v>16.30180951666667</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>14.26811456666667</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>30.56992408333333</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>15.78657563583333</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>14.74983727833333</v>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>1.273350069</v>
       </c>
-      <c r="K43">
+      <c r="M43">
         <v>30.53641291416667</v>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M43">
+      <c r="O43">
         <v>3.786722414738152</v>
       </c>
-      <c r="N43">
+      <c r="P43">
         <v>-23.85635121285036</v>
       </c>
-      <c r="O43">
+      <c r="Q43">
         <v>-42.52489271750945</v>
       </c>
-      <c r="P43">
+      <c r="R43">
         <v>-75.73444829476304</v>
       </c>
-      <c r="Q43">
+      <c r="S43">
         <v>1.888888888888889</v>
       </c>
-      <c r="R43">
+      <c r="T43">
         <v>-0.5152338808333319</v>
       </c>
-      <c r="S43">
+      <c r="U43">
         <v>-117.0598424589533</v>
       </c>
-      <c r="T43">
-        <v>-42.02148190834222</v>
-      </c>
-      <c r="U43">
+      <c r="V43">
+        <v>-45.02301633036666</v>
+      </c>
+      <c r="W43">
         <v>-161.2664414265293</v>
       </c>
-      <c r="V43">
-        <v>-250.2667620995397</v>
+      <c r="X43">
+        <v>-112.4769220677999</v>
       </c>
     </row>
     <row r="44">
@@ -3500,66 +3762,72 @@
         <v>181.2729487179487</v>
       </c>
       <c r="C44">
-        <v>-50.87757269230769</v>
+        <v>72.62556805483219</v>
       </c>
       <c r="D44">
+        <v>0.9754249577126824</v>
+      </c>
+      <c r="E44">
+        <v>7.690786828287878</v>
+      </c>
+      <c r="F44">
         <v>4</v>
       </c>
-      <c r="E44">
+      <c r="G44">
         <v>15.87066645166667</v>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>15.19955595333333</v>
       </c>
-      <c r="G44">
+      <c r="I44">
         <v>31.070222405</v>
       </c>
-      <c r="H44">
+      <c r="J44">
         <v>16.34161234133333</v>
       </c>
-      <c r="I44">
+      <c r="K44">
         <v>15.09101679166667</v>
       </c>
-      <c r="J44">
+      <c r="L44">
         <v>1.209331958</v>
       </c>
-      <c r="K44">
+      <c r="M44">
         <v>31.432629133</v>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M44">
+      <c r="O44">
         <v>2.420979241851507</v>
       </c>
-      <c r="N44">
+      <c r="P44">
         <v>-15.25216922366449</v>
       </c>
-      <c r="O44">
+      <c r="Q44">
         <v>-27.18759688599242</v>
       </c>
-      <c r="P44">
+      <c r="R44">
         <v>-48.41958483703014</v>
       </c>
-      <c r="Q44">
+      <c r="S44">
         <v>3.166666666666667</v>
       </c>
-      <c r="R44">
+      <c r="T44">
         <v>0.4709458896666678</v>
       </c>
-      <c r="S44">
+      <c r="U44">
         <v>101.6183750593671</v>
       </c>
-      <c r="T44">
-        <v>36.4783910469523</v>
-      </c>
-      <c r="U44">
+      <c r="V44">
+        <v>39.0839904074489</v>
+      </c>
+      <c r="W44">
         <v>139.993642440761</v>
       </c>
-      <c r="V44">
-        <v>23.55320548106702</v>
+      <c r="X44">
+        <v>147.0563462282069</v>
       </c>
     </row>
     <row r="45">
@@ -3572,66 +3840,72 @@
         <v>309.4958974358975</v>
       </c>
       <c r="C45">
-        <v>31.6079503846154</v>
+        <v>121.4441448756403</v>
       </c>
       <c r="D45">
+        <v>2.348475068568395</v>
+      </c>
+      <c r="E45">
+        <v>24.23787183047328</v>
+      </c>
+      <c r="F45">
         <v>8</v>
       </c>
-      <c r="E45">
+      <c r="G45">
         <v>15.01120542833333</v>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>18.91071100833333</v>
       </c>
-      <c r="G45">
+      <c r="I45">
         <v>33.92191643666666</v>
       </c>
-      <c r="H45">
+      <c r="J45">
         <v>17.679803865</v>
       </c>
-      <c r="I45">
+      <c r="K45">
         <v>18.16225364</v>
       </c>
-      <c r="J45">
+      <c r="L45">
         <v>1.211471480333333</v>
       </c>
-      <c r="K45">
+      <c r="M45">
         <v>35.842057505</v>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M45">
+      <c r="O45">
         <v>0.8786257682716357</v>
       </c>
-      <c r="N45">
+      <c r="P45">
         <v>-5.535342340111305</v>
       </c>
-      <c r="O45">
+      <c r="Q45">
         <v>-9.86696737769047</v>
       </c>
-      <c r="P45">
+      <c r="R45">
         <v>-17.57251536543271</v>
       </c>
-      <c r="Q45">
+      <c r="S45">
         <v>5.916666666666667</v>
       </c>
-      <c r="R45">
+      <c r="T45">
         <v>2.668598436666667</v>
       </c>
-      <c r="S45">
+      <c r="U45">
         <v>576.8356955619695</v>
       </c>
-      <c r="T45">
-        <v>207.0692240478865</v>
-      </c>
-      <c r="U45">
+      <c r="V45">
+        <v>221.8598829084498</v>
+      </c>
+      <c r="W45">
         <v>794.6725192603461</v>
       </c>
-      <c r="V45">
-        <v>598.5766785688944</v>
+      <c r="X45">
+        <v>688.4128730599193</v>
       </c>
     </row>
     <row r="46">
@@ -3644,66 +3918,72 @@
         <v>400.8861538461538</v>
       </c>
       <c r="C46">
-        <v>93.36799769230771</v>
+        <v>162.527018737534</v>
       </c>
       <c r="D46">
+        <v>2.998279994948021</v>
+      </c>
+      <c r="E46">
+        <v>37.17363056770113</v>
+      </c>
+      <c r="F46">
         <v>8</v>
       </c>
-      <c r="E46">
+      <c r="G46">
         <v>19.261428105</v>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>14.94687716333333</v>
       </c>
-      <c r="G46">
+      <c r="I46">
         <v>34.20830526833333</v>
       </c>
-      <c r="H46">
+      <c r="J46">
         <v>20.82464430333333</v>
       </c>
-      <c r="I46">
+      <c r="K46">
         <v>15.52260234</v>
       </c>
-      <c r="J46">
+      <c r="L46">
         <v>1.2708509925</v>
       </c>
-      <c r="K46">
+      <c r="M46">
         <v>36.34724664333334</v>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M46">
+      <c r="O46">
         <v>1.002883629259998</v>
       </c>
-      <c r="N46">
+      <c r="P46">
         <v>-6.318166864337985</v>
       </c>
-      <c r="O46">
+      <c r="Q46">
         <v>-11.26238315658977</v>
       </c>
-      <c r="P46">
+      <c r="R46">
         <v>-20.05767258519995</v>
       </c>
-      <c r="Q46">
+      <c r="S46">
         <v>4.444444444444445</v>
       </c>
-      <c r="R46">
+      <c r="T46">
         <v>1.563216198333333</v>
       </c>
-      <c r="S46">
+      <c r="U46">
         <v>354.4617558859168</v>
       </c>
-      <c r="T46">
-        <v>127.2426816000727</v>
-      </c>
-      <c r="U46">
+      <c r="V46">
+        <v>136.3314445715065</v>
+      </c>
+      <c r="W46">
         <v>488.3210569291933</v>
       </c>
-      <c r="V46">
-        <v>436.5673704216348</v>
+      <c r="X46">
+        <v>505.7263914668611</v>
       </c>
     </row>
     <row r="47">
@@ -3716,66 +3996,72 @@
         <v>153.6873076923077</v>
       </c>
       <c r="C47">
-        <v>-66.60177923076922</v>
+        <v>60.81325994793166</v>
       </c>
       <c r="D47">
+        <v>2.173968670705522</v>
+      </c>
+      <c r="E47">
+        <v>11.58872070575369</v>
+      </c>
+      <c r="F47">
         <v>1</v>
       </c>
-      <c r="E47">
+      <c r="G47">
         <v>19.57522699166667</v>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>15.47139307</v>
       </c>
-      <c r="G47">
+      <c r="I47">
         <v>35.04662006166667</v>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>19.75802325166667</v>
       </c>
-      <c r="I47">
+      <c r="K47">
         <v>16.70883446166667</v>
       </c>
-      <c r="J47">
+      <c r="L47">
         <v>1.273792166333333</v>
       </c>
-      <c r="K47">
+      <c r="M47">
         <v>36.46685771333334</v>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M47">
+      <c r="O47">
         <v>0.675106066584323</v>
       </c>
-      <c r="N47">
+      <c r="P47">
         <v>-4.253168219481235</v>
       </c>
-      <c r="O47">
+      <c r="Q47">
         <v>-7.581441127741948</v>
       </c>
-      <c r="P47">
+      <c r="R47">
         <v>-13.50212133168646</v>
       </c>
-      <c r="Q47">
+      <c r="S47">
         <v>1</v>
       </c>
-      <c r="R47">
+      <c r="T47">
         <v>0.1827962599999999</v>
       </c>
-      <c r="S47">
+      <c r="U47">
         <v>41.54526992480934</v>
       </c>
-      <c r="T47">
-        <v>14.91368663967515</v>
-      </c>
-      <c r="U47">
+      <c r="V47">
+        <v>15.97894997108052</v>
+      </c>
+      <c r="W47">
         <v>57.23446826974759</v>
       </c>
-      <c r="V47">
-        <v>-32.63795043370183</v>
+      <c r="X47">
+        <v>94.77708874499905</v>
       </c>
     </row>
     <row r="48">
@@ -3788,66 +4074,72 @@
         <v>417.6919230769231</v>
       </c>
       <c r="C48">
-        <v>103.2146934615385</v>
+        <v>161.3551916368001</v>
       </c>
       <c r="D48">
+        <v>2.199230907565111</v>
+      </c>
+      <c r="E48">
+        <v>30.96483387166473</v>
+      </c>
+      <c r="F48">
         <v>8</v>
       </c>
-      <c r="E48">
+      <c r="G48">
         <v>19.22971065333333</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>14.82748369166667</v>
       </c>
-      <c r="G48">
+      <c r="I48">
         <v>34.057194345</v>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>20.94664231166667</v>
       </c>
-      <c r="I48">
+      <c r="K48">
         <v>15.58443038</v>
       </c>
-      <c r="J48">
+      <c r="L48">
         <v>1.272812508666667</v>
       </c>
-      <c r="K48">
+      <c r="M48">
         <v>36.53107269166667</v>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M48">
+      <c r="O48">
         <v>1.042897672376869</v>
       </c>
-      <c r="N48">
+      <c r="P48">
         <v>-6.570255335974272</v>
       </c>
-      <c r="O48">
+      <c r="Q48">
         <v>-11.71174086079223</v>
       </c>
-      <c r="P48">
+      <c r="R48">
         <v>-20.85795344753737</v>
       </c>
-      <c r="Q48">
+      <c r="S48">
         <v>6.194444444444445</v>
       </c>
-      <c r="R48">
+      <c r="T48">
         <v>1.716931658333333</v>
       </c>
-      <c r="S48">
+      <c r="U48">
         <v>389.917878381722</v>
       </c>
-      <c r="T48">
-        <v>139.9705204447207</v>
-      </c>
-      <c r="U48">
+      <c r="V48">
+        <v>149.9684147622008</v>
+      </c>
+      <c r="W48">
         <v>537.1668658895682</v>
       </c>
-      <c r="V48">
-        <v>481.4208309824683</v>
+      <c r="X48">
+        <v>539.5613291577299</v>
       </c>
     </row>
     <row r="49">
@@ -3860,66 +4152,72 @@
         <v>182.8228205128205</v>
       </c>
       <c r="C49">
-        <v>-49.14041346153846</v>
+        <v>73.23798057505209</v>
       </c>
       <c r="D49">
+        <v>1.161661085411861</v>
+      </c>
+      <c r="E49">
+        <v>8.983570164265618</v>
+      </c>
+      <c r="F49">
         <v>2</v>
       </c>
-      <c r="E49">
+      <c r="G49">
         <v>18.94378669166667</v>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>14.260492525</v>
       </c>
-      <c r="G49">
+      <c r="I49">
         <v>33.20427921666666</v>
       </c>
-      <c r="H49">
+      <c r="J49">
         <v>18.28368143833333</v>
       </c>
-      <c r="I49">
+      <c r="K49">
         <v>15.45937701166667</v>
       </c>
-      <c r="J49">
+      <c r="L49">
         <v>1.303480212</v>
       </c>
-      <c r="K49">
+      <c r="M49">
         <v>33.74305845</v>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M49">
+      <c r="O49">
         <v>0.9046072052730504</v>
       </c>
-      <c r="N49">
+      <c r="P49">
         <v>-5.699025393220217</v>
       </c>
-      <c r="O49">
+      <c r="Q49">
         <v>-10.15873891521636</v>
       </c>
-      <c r="P49">
+      <c r="R49">
         <v>-18.09214410546101</v>
       </c>
-      <c r="Q49">
+      <c r="S49">
         <v>1.777777777777778</v>
       </c>
-      <c r="R49">
+      <c r="T49">
         <v>-0.6601052533333345</v>
       </c>
-      <c r="S49">
+      <c r="U49">
         <v>-153.522960636802</v>
       </c>
-      <c r="T49">
-        <v>-55.11080638244176</v>
-      </c>
-      <c r="U49">
+      <c r="V49">
+        <v>-59.04729255261617</v>
+      </c>
+      <c r="W49">
         <v>-211.4995289511308</v>
       </c>
-      <c r="V49">
-        <v>-212.8221130135568</v>
+      <c r="X49">
+        <v>-90.4437189769663</v>
       </c>
     </row>
     <row r="50">
@@ -3932,66 +4230,72 @@
         <v>395.8517948717949</v>
       </c>
       <c r="C50">
-        <v>88.41334000000002</v>
+        <v>155.7970491893329</v>
       </c>
       <c r="D50">
+        <v>4.180372373878496</v>
+      </c>
+      <c r="E50">
+        <v>41.95735830473001</v>
+      </c>
+      <c r="F50">
         <v>16</v>
       </c>
-      <c r="E50">
+      <c r="G50">
         <v>21.528021425</v>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>12.991011935</v>
       </c>
-      <c r="G50">
+      <c r="I50">
         <v>34.51903335999999</v>
       </c>
-      <c r="H50">
+      <c r="J50">
         <v>22.554342445</v>
       </c>
-      <c r="I50">
+      <c r="K50">
         <v>14.18910566833333</v>
       </c>
-      <c r="J50">
+      <c r="L50">
         <v>1.2398925705</v>
       </c>
-      <c r="K50">
+      <c r="M50">
         <v>36.74344811333333</v>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M50">
+      <c r="O50">
         <v>0.8637637605319486</v>
       </c>
-      <c r="N50">
+      <c r="P50">
         <v>-5.441711691351276</v>
       </c>
-      <c r="O50">
+      <c r="Q50">
         <v>-9.700067030773782</v>
       </c>
-      <c r="P50">
+      <c r="R50">
         <v>-17.27527521063897</v>
       </c>
-      <c r="Q50">
+      <c r="S50">
         <v>10.13888888888889</v>
       </c>
-      <c r="R50">
+      <c r="T50">
         <v>1.026321020000001</v>
       </c>
-      <c r="S50">
+      <c r="U50">
         <v>227.0507740792346</v>
       </c>
-      <c r="T50">
-        <v>81.50540607972523</v>
-      </c>
-      <c r="U50">
+      <c r="V50">
+        <v>87.32722079970561</v>
+      </c>
+      <c r="W50">
         <v>312.7944612751055</v>
       </c>
-      <c r="V50">
-        <v>305.7640470484608</v>
+      <c r="X50">
+        <v>373.1477562377937</v>
       </c>
     </row>
     <row r="51">
@@ -4004,66 +4308,72 @@
         <v>308.5635897435898</v>
       </c>
       <c r="C51">
-        <v>33.71135653846155</v>
+        <v>120.4256830558205</v>
       </c>
       <c r="D51">
+        <v>4.312780101525268</v>
+      </c>
+      <c r="E51">
+        <v>32.89322220225676</v>
+      </c>
+      <c r="F51">
         <v>4</v>
       </c>
-      <c r="E51">
+      <c r="G51">
         <v>21.14341975333333</v>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>13.43872288833333</v>
       </c>
-      <c r="G51">
+      <c r="I51">
         <v>34.58214264166666</v>
       </c>
-      <c r="H51">
+      <c r="J51">
         <v>21.7940397</v>
       </c>
-      <c r="I51">
+      <c r="K51">
         <v>13.728815925</v>
       </c>
-      <c r="J51">
+      <c r="L51">
         <v>1.233803417166667</v>
       </c>
-      <c r="K51">
+      <c r="M51">
         <v>35.522855625</v>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M51">
+      <c r="O51">
         <v>1.268561254316011</v>
       </c>
-      <c r="N51">
+      <c r="P51">
         <v>-7.991935902190866</v>
       </c>
-      <c r="O51">
+      <c r="Q51">
         <v>-14.2459428859688</v>
       </c>
-      <c r="P51">
+      <c r="R51">
         <v>-25.37122508632021</v>
       </c>
-      <c r="Q51">
+      <c r="S51">
         <v>2.777777777777778</v>
       </c>
-      <c r="R51">
+      <c r="T51">
         <v>0.6506199466666658</v>
       </c>
-      <c r="S51">
+      <c r="U51">
         <v>143.2283694716211</v>
       </c>
-      <c r="T51">
-        <v>51.41531211801782</v>
-      </c>
-      <c r="U51">
+      <c r="V51">
+        <v>55.08783441216195</v>
+      </c>
+      <c r="W51">
         <v>197.3172778197758</v>
       </c>
-      <c r="V51">
-        <v>162.6937831241138</v>
+      <c r="X51">
+        <v>249.4081096414728</v>
       </c>
     </row>
     <row r="52">
@@ -4076,66 +4386,72 @@
         <v>72.74282051282051</v>
       </c>
       <c r="C52">
-        <v>-117.7863165384615</v>
+        <v>29.15391927412195</v>
       </c>
       <c r="D52">
+        <v>1.420991482783528</v>
+      </c>
+      <c r="E52">
+        <v>4.177339451148918</v>
+      </c>
+      <c r="F52">
         <v>1</v>
       </c>
-      <c r="E52">
+      <c r="G52">
         <v>24.5741344</v>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>14.09356097333333</v>
       </c>
-      <c r="G52">
+      <c r="I52">
         <v>38.66769537333333</v>
       </c>
-      <c r="H52">
+      <c r="J52">
         <v>21.62069094333333</v>
       </c>
-      <c r="I52">
+      <c r="K52">
         <v>14.54494359833333</v>
       </c>
-      <c r="J52">
+      <c r="L52">
         <v>1.244754985333333</v>
       </c>
-      <c r="K52">
+      <c r="M52">
         <v>36.16563454166666</v>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M52">
+      <c r="O52">
         <v>12.71122695655753</v>
       </c>
-      <c r="N52">
+      <c r="P52">
         <v>-80.08072982631244</v>
       </c>
-      <c r="O52">
+      <c r="Q52">
         <v>-142.7470787221411</v>
       </c>
-      <c r="P52">
+      <c r="R52">
         <v>-254.2245391311506</v>
       </c>
-      <c r="Q52">
+      <c r="S52">
         <v>1</v>
       </c>
-      <c r="R52">
+      <c r="T52">
         <v>-2.953443456666665</v>
       </c>
-      <c r="S52">
+      <c r="U52">
         <v>-655.9462302755971</v>
       </c>
-      <c r="T52">
-        <v>-235.4678775348297</v>
-      </c>
-      <c r="U52">
+      <c r="V52">
+        <v>-252.2870116444604</v>
+      </c>
+      <c r="W52">
         <v>-903.6584374422379</v>
       </c>
-      <c r="V52">
-        <v>-916.4796255361997</v>
+      <c r="X52">
+        <v>-769.5393897236163</v>
       </c>
     </row>
     <row r="53">
@@ -4148,66 +4464,72 @@
         <v>323.8462820512821</v>
       </c>
       <c r="C53">
-        <v>42.50846615384616</v>
+        <v>128.636010866598</v>
       </c>
       <c r="D53">
+        <v>4.060652057421678</v>
+      </c>
+      <c r="E53">
+        <v>34.18340728529794</v>
+      </c>
+      <c r="F53">
         <v>4</v>
       </c>
-      <c r="E53">
+      <c r="G53">
         <v>20.38869288666666</v>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>20.37180383833334</v>
       </c>
-      <c r="G53">
+      <c r="I53">
         <v>40.760496725</v>
       </c>
-      <c r="H53">
+      <c r="J53">
         <v>21.31049074166667</v>
       </c>
-      <c r="I53">
+      <c r="K53">
         <v>21.137494145</v>
       </c>
-      <c r="J53">
+      <c r="L53">
         <v>1.129676881</v>
       </c>
-      <c r="K53">
+      <c r="M53">
         <v>42.44798488666666</v>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M53">
+      <c r="O53">
         <v>0.6924872803624826</v>
       </c>
-      <c r="N53">
+      <c r="P53">
         <v>-4.362669866283641</v>
       </c>
-      <c r="O53">
+      <c r="Q53">
         <v>-7.77663215847068</v>
       </c>
-      <c r="P53">
+      <c r="R53">
         <v>-13.84974560724965</v>
       </c>
-      <c r="Q53">
+      <c r="S53">
         <v>2.555555555555555</v>
       </c>
-      <c r="R53">
+      <c r="T53">
         <v>0.9217978550000012</v>
       </c>
-      <c r="S53">
+      <c r="U53">
         <v>185.799970016746</v>
       </c>
-      <c r="T53">
-        <v>66.69742513421649</v>
-      </c>
-      <c r="U53">
+      <c r="V53">
+        <v>71.46152692951767</v>
+      </c>
+      <c r="W53">
         <v>255.9656612579417</v>
       </c>
-      <c r="V53">
-        <v>220.5318040121215</v>
+      <c r="X53">
+        <v>306.6593487248733</v>
       </c>
     </row>
     <row r="54">
@@ -4220,66 +4542,72 @@
         <v>650.37</v>
       </c>
       <c r="C54">
-        <v>248.2846788461539</v>
+        <v>254.81831192044</v>
       </c>
       <c r="D54">
+        <v>3.264209423554901</v>
+      </c>
+      <c r="E54">
+        <v>60.9085993917174</v>
+      </c>
+      <c r="F54">
         <v>60</v>
       </c>
-      <c r="E54">
+      <c r="G54">
         <v>18.91503501666667</v>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>18.94353111666667</v>
       </c>
-      <c r="G54">
+      <c r="I54">
         <v>37.85856613333333</v>
       </c>
-      <c r="H54">
+      <c r="J54">
         <v>20.86098047666666</v>
       </c>
-      <c r="I54">
+      <c r="K54">
         <v>19.11635910666667</v>
       </c>
-      <c r="J54">
+      <c r="L54">
         <v>1.151697198166667</v>
       </c>
-      <c r="K54">
+      <c r="M54">
         <v>39.97733958333333</v>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M54">
+      <c r="O54">
         <v>0.8316001654117181</v>
       </c>
-      <c r="N54">
+      <c r="P54">
         <v>-5.239081042093824</v>
       </c>
-      <c r="O54">
+      <c r="Q54">
         <v>-9.338869857573595</v>
       </c>
-      <c r="P54">
+      <c r="R54">
         <v>-16.63200330823436</v>
       </c>
-      <c r="Q54">
+      <c r="S54">
         <v>29.75</v>
       </c>
-      <c r="R54">
+      <c r="T54">
         <v>1.945945459999997</v>
       </c>
-      <c r="S54">
+      <c r="U54">
         <v>399.8753927359298</v>
       </c>
-      <c r="T54">
-        <v>143.5450127770004</v>
-      </c>
-      <c r="U54">
+      <c r="V54">
+        <v>153.7982279753576</v>
+      </c>
+      <c r="W54">
         <v>550.8847461773343</v>
       </c>
-      <c r="V54">
-        <v>638.8212017245102</v>
+      <c r="X54">
+        <v>645.3548347987962</v>
       </c>
     </row>
     <row r="55">
@@ -4292,66 +4620,72 @@
         <v>455.2126923076923</v>
       </c>
       <c r="C55">
-        <v>129.6424426923077</v>
+        <v>189.8996209918883</v>
       </c>
       <c r="D55">
+        <v>2.173784861817515</v>
+      </c>
+      <c r="E55">
+        <v>36.18586349485449</v>
+      </c>
+      <c r="F55">
         <v>16</v>
       </c>
-      <c r="E55">
+      <c r="G55">
         <v>16.31114664333333</v>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>20.07515013166667</v>
       </c>
-      <c r="G55">
+      <c r="I55">
         <v>36.38629677500001</v>
       </c>
-      <c r="H55">
+      <c r="J55">
         <v>20.22225977666667</v>
       </c>
-      <c r="I55">
+      <c r="K55">
         <v>20.56386172833333</v>
       </c>
-      <c r="J55">
+      <c r="L55">
         <v>1.129646918166667</v>
       </c>
-      <c r="K55">
+      <c r="M55">
         <v>40.786121505</v>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M55">
+      <c r="O55">
         <v>1.781220700091808</v>
       </c>
-      <c r="N55">
+      <c r="P55">
         <v>-11.22169041057839</v>
       </c>
-      <c r="O55">
+      <c r="Q55">
         <v>-20.003108462031</v>
       </c>
-      <c r="P55">
+      <c r="R55">
         <v>-35.62441400183615</v>
       </c>
-      <c r="Q55">
+      <c r="S55">
         <v>9.333333333333334</v>
       </c>
-      <c r="R55">
+      <c r="T55">
         <v>3.911113133333334</v>
       </c>
-      <c r="S55">
+      <c r="U55">
         <v>788.3132129669794</v>
       </c>
-      <c r="T55">
-        <v>282.9842302958388</v>
-      </c>
-      <c r="U55">
+      <c r="V55">
+        <v>303.1973896026844</v>
+      </c>
+      <c r="W55">
         <v>1086.012623238202</v>
       </c>
-      <c r="V55">
-        <v>897.9525471972561</v>
+      <c r="X55">
+        <v>958.2097254968367</v>
       </c>
     </row>
     <row r="56">
@@ -4364,66 +4698,72 @@
         <v>29.9974358974359</v>
       </c>
       <c r="C56">
-        <v>-144.1901461538461</v>
+        <v>12.43333966065505</v>
       </c>
       <c r="D56">
+        <v>1.114954172112448</v>
+      </c>
+      <c r="E56">
+        <v>1.474939708608838</v>
+      </c>
+      <c r="F56">
         <v>1</v>
       </c>
-      <c r="E56">
+      <c r="G56">
         <v>15.5350772</v>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>21.23301645166667</v>
       </c>
-      <c r="G56">
+      <c r="I56">
         <v>36.76809365166667</v>
       </c>
-      <c r="H56">
+      <c r="J56">
         <v>17.13503540333333</v>
       </c>
-      <c r="I56">
+      <c r="K56">
         <v>20.508566085</v>
       </c>
-      <c r="J56">
+      <c r="L56">
         <v>1.366434788833333</v>
       </c>
-      <c r="K56">
+      <c r="M56">
         <v>37.64360148833333</v>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M56">
+      <c r="O56">
         <v>2.244100031449752</v>
       </c>
-      <c r="N56">
+      <c r="P56">
         <v>-14.13783019813344</v>
       </c>
-      <c r="O56">
+      <c r="Q56">
         <v>-25.20124335318072</v>
       </c>
-      <c r="P56">
+      <c r="R56">
         <v>-44.88200062899504</v>
       </c>
-      <c r="Q56">
+      <c r="S56">
         <v>1</v>
       </c>
-      <c r="R56">
+      <c r="T56">
         <v>1.599958203333333</v>
       </c>
-      <c r="S56">
+      <c r="U56">
         <v>390.0796132327102</v>
       </c>
-      <c r="T56">
-        <v>140.028579109178</v>
-      </c>
-      <c r="U56">
+      <c r="V56">
+        <v>150.0306204741193</v>
+      </c>
+      <c r="W56">
         <v>537.3896784555656</v>
       </c>
-      <c r="V56">
-        <v>220.6882237256834</v>
+      <c r="X56">
+        <v>377.3117095401846</v>
       </c>
     </row>
     <row r="57">
@@ -4436,66 +4776,72 @@
         <v>93.61538461538461</v>
       </c>
       <c r="C57">
-        <v>-103.574325</v>
+        <v>38.43954418497408</v>
       </c>
       <c r="D57">
+        <v>2.119867323365915</v>
+      </c>
+      <c r="E57">
+        <v>7.212921435014662</v>
+      </c>
+      <c r="F57">
         <v>2</v>
       </c>
-      <c r="E57">
+      <c r="G57">
         <v>19.57160066</v>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>17.35135972666667</v>
       </c>
-      <c r="G57">
+      <c r="I57">
         <v>36.92296038666667</v>
       </c>
-      <c r="H57">
+      <c r="J57">
         <v>19.28397925833333</v>
       </c>
-      <c r="I57">
+      <c r="K57">
         <v>18.13899774833333</v>
       </c>
-      <c r="J57">
+      <c r="L57">
         <v>1.2727740835</v>
       </c>
-      <c r="K57">
+      <c r="M57">
         <v>37.42297700666667</v>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M57">
+      <c r="O57">
         <v>2.35487853771158</v>
       </c>
-      <c r="N57">
+      <c r="P57">
         <v>-14.83573478758296</v>
       </c>
-      <c r="O57">
+      <c r="Q57">
         <v>-26.44528597850105</v>
       </c>
-      <c r="P57">
+      <c r="R57">
         <v>-47.09757075423161</v>
       </c>
-      <c r="Q57">
+      <c r="S57">
         <v>1.972222222222222</v>
       </c>
-      <c r="R57">
+      <c r="T57">
         <v>-0.2876214016666694</v>
       </c>
-      <c r="S57">
+      <c r="U57">
         <v>-65.31730048343599</v>
       </c>
-      <c r="T57">
-        <v>-23.44723607097702</v>
-      </c>
-      <c r="U57">
+      <c r="V57">
+        <v>-25.12203864747538</v>
+      </c>
+      <c r="W57">
         <v>-89.98379283010381</v>
       </c>
-      <c r="V57">
-        <v>-195.336911461937</v>
+      <c r="X57">
+        <v>-53.32304227696295</v>
       </c>
     </row>
     <row r="58">
@@ -4508,66 +4854,72 @@
         <v>391.1703846153846</v>
       </c>
       <c r="C58">
-        <v>85.34052692307694</v>
+        <v>154.2542601178925</v>
       </c>
       <c r="D58">
+        <v>2.834340600322842</v>
+      </c>
+      <c r="E58">
+        <v>34.23592777114803</v>
+      </c>
+      <c r="F58">
         <v>8</v>
       </c>
-      <c r="E58">
+      <c r="G58">
         <v>18.96839964333333</v>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>15.34068266333333</v>
       </c>
-      <c r="G58">
+      <c r="I58">
         <v>34.30908230666667</v>
       </c>
-      <c r="H58">
+      <c r="J58">
         <v>18.90949340833333</v>
       </c>
-      <c r="I58">
+      <c r="K58">
         <v>16.265840325</v>
       </c>
-      <c r="J58">
+      <c r="L58">
         <v>1.302041297333333</v>
       </c>
-      <c r="K58">
+      <c r="M58">
         <v>35.17533373333333</v>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M58">
+      <c r="O58">
         <v>5.768294627152565</v>
       </c>
-      <c r="N58">
+      <c r="P58">
         <v>-36.34025615106115</v>
       </c>
-      <c r="O58">
+      <c r="Q58">
         <v>-64.77794866292331</v>
       </c>
-      <c r="P58">
+      <c r="R58">
         <v>-115.3658925430513</v>
       </c>
-      <c r="Q58">
+      <c r="S58">
         <v>5.111111111111111</v>
       </c>
-      <c r="R58">
+      <c r="T58">
         <v>-0.05890623500000203</v>
       </c>
-      <c r="S58">
+      <c r="U58">
         <v>-13.6849032130178</v>
       </c>
-      <c r="T58">
-        <v>-4.912529358519212</v>
-      </c>
-      <c r="U58">
+      <c r="V58">
+        <v>-5.263424312699155</v>
+      </c>
+      <c r="W58">
         <v>-18.85288409818001</v>
       </c>
-      <c r="V58">
-        <v>6.877675047135824</v>
+      <c r="X58">
+        <v>75.79140824195142</v>
       </c>
     </row>
     <row r="59">
@@ -4580,66 +4932,72 @@
         <v>186.5998717948718</v>
       </c>
       <c r="C59">
-        <v>-46.6601523076923</v>
+        <v>76.31087715908556</v>
       </c>
       <c r="D59">
+        <v>0.9162660823837383</v>
+      </c>
+      <c r="E59">
+        <v>7.643551855774868</v>
+      </c>
+      <c r="F59">
         <v>2</v>
       </c>
-      <c r="E59">
+      <c r="G59">
         <v>19.19157407666667</v>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>15.447678765</v>
       </c>
-      <c r="G59">
+      <c r="I59">
         <v>34.63925284166667</v>
       </c>
-      <c r="H59">
+      <c r="J59">
         <v>20.00068769833333</v>
       </c>
-      <c r="I59">
+      <c r="K59">
         <v>15.62423430166667</v>
       </c>
-      <c r="J59">
+      <c r="L59">
         <v>1.2796586495</v>
       </c>
-      <c r="K59">
+      <c r="M59">
         <v>35.624922</v>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M59">
+      <c r="O59">
         <v>4.634270652459132</v>
       </c>
-      <c r="N59">
+      <c r="P59">
         <v>-29.19590511049253</v>
       </c>
-      <c r="O59">
+      <c r="Q59">
         <v>-52.04285942711606</v>
       </c>
-      <c r="P59">
+      <c r="R59">
         <v>-92.68541304918264</v>
       </c>
-      <c r="Q59">
+      <c r="S59">
         <v>2</v>
       </c>
-      <c r="R59">
+      <c r="T59">
         <v>0.8091136216666648</v>
       </c>
-      <c r="S59">
+      <c r="U59">
         <v>184.7393259310027</v>
       </c>
-      <c r="T59">
-        <v>66.31668110343686</v>
-      </c>
-      <c r="U59">
+      <c r="V59">
+        <v>71.0535868965395</v>
+      </c>
+      <c r="W59">
         <v>254.5044744518183</v>
       </c>
-      <c r="V59">
-        <v>86.03631419619435</v>
+      <c r="X59">
+        <v>209.0073436629722</v>
       </c>
     </row>
     <row r="60">
@@ -4652,66 +5010,72 @@
         <v>364.2266794871795</v>
       </c>
       <c r="C60">
-        <v>68.57861250000001</v>
+        <v>141.8247363730374</v>
       </c>
       <c r="D60">
+        <v>3.629766775435469</v>
+      </c>
+      <c r="E60">
+        <v>35.73719452358404</v>
+      </c>
+      <c r="F60">
         <v>16</v>
       </c>
-      <c r="E60">
+      <c r="G60">
         <v>21.72608776333333</v>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>14.51037426833333</v>
       </c>
-      <c r="G60">
+      <c r="I60">
         <v>36.23646203166666</v>
       </c>
-      <c r="H60">
+      <c r="J60">
         <v>22.56712392</v>
       </c>
-      <c r="I60">
+      <c r="K60">
         <v>15.705884195</v>
       </c>
-      <c r="J60">
+      <c r="L60">
         <v>1.212829627166667</v>
       </c>
-      <c r="K60">
+      <c r="M60">
         <v>38.273008115</v>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M60">
+      <c r="O60">
         <v>0.8158122852628428</v>
       </c>
-      <c r="N60">
+      <c r="P60">
         <v>-5.139617397155909</v>
       </c>
-      <c r="O60">
+      <c r="Q60">
         <v>-9.161571963501725</v>
       </c>
-      <c r="P60">
+      <c r="R60">
         <v>-16.31624570525685</v>
       </c>
-      <c r="Q60">
+      <c r="S60">
         <v>12.05555555555556</v>
       </c>
-      <c r="R60">
+      <c r="T60">
         <v>0.841036156666668</v>
       </c>
-      <c r="S60">
+      <c r="U60">
         <v>181.9994894281599</v>
       </c>
-      <c r="T60">
-        <v>65.33315005113434</v>
-      </c>
-      <c r="U60">
+      <c r="V60">
+        <v>69.99980362621535</v>
+      </c>
+      <c r="W60">
         <v>250.7299632819532</v>
       </c>
-      <c r="V60">
-        <v>241.4165299646582</v>
+      <c r="X60">
+        <v>314.6626538376956</v>
       </c>
     </row>
     <row r="61">
@@ -4724,66 +5088,72 @@
         <v>301.3658974358974</v>
       </c>
       <c r="C61">
-        <v>28.47471153846155</v>
+        <v>113.377868090979</v>
       </c>
       <c r="D61">
+        <v>1.45201807705575</v>
+      </c>
+      <c r="E61">
+        <v>16.50463164723418</v>
+      </c>
+      <c r="F61">
         <v>4</v>
       </c>
-      <c r="E61">
+      <c r="G61">
         <v>22.25263283333333</v>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>14.002622765</v>
       </c>
-      <c r="G61">
+      <c r="I61">
         <v>36.25525559833333</v>
       </c>
-      <c r="H61">
+      <c r="J61">
         <v>22.54396694333333</v>
       </c>
-      <c r="I61">
+      <c r="K61">
         <v>14.29265470833333</v>
       </c>
-      <c r="J61">
+      <c r="L61">
         <v>1.219427313833333</v>
       </c>
-      <c r="K61">
+      <c r="M61">
         <v>36.83662165166667</v>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M61">
+      <c r="O61">
         <v>1.222969348145958</v>
       </c>
-      <c r="N61">
+      <c r="P61">
         <v>-7.704706893319538</v>
       </c>
-      <c r="O61">
+      <c r="Q61">
         <v>-13.73394577967911</v>
       </c>
-      <c r="P61">
+      <c r="R61">
         <v>-24.45938696291917</v>
       </c>
-      <c r="Q61">
+      <c r="S61">
         <v>3.555555555555555</v>
       </c>
-      <c r="R61">
+      <c r="T61">
         <v>0.2913341100000011</v>
       </c>
-      <c r="S61">
+      <c r="U61">
         <v>63.38740309874182</v>
       </c>
-      <c r="T61">
-        <v>22.75445239442014</v>
-      </c>
-      <c r="U61">
+      <c r="V61">
+        <v>24.37977042259301</v>
+      </c>
+      <c r="W61">
         <v>87.32508701767181</v>
       </c>
-      <c r="V61">
-        <v>78.12816885752426</v>
+      <c r="X61">
+        <v>163.0313254100417</v>
       </c>
     </row>
     <row r="62">
@@ -4796,66 +5166,72 @@
         <v>512.3392307692308</v>
       </c>
       <c r="C62">
-        <v>161.7195269230769</v>
+        <v>197.5241073788731</v>
       </c>
       <c r="D62">
+        <v>3.727290492743089</v>
+      </c>
+      <c r="E62">
+        <v>50.41363126013075</v>
+      </c>
+      <c r="F62">
         <v>16</v>
       </c>
-      <c r="E62">
+      <c r="G62">
         <v>24.81847847</v>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>15.63577910333333</v>
       </c>
-      <c r="G62">
+      <c r="I62">
         <v>40.45425757333334</v>
       </c>
-      <c r="H62">
+      <c r="J62">
         <v>26.54552809833334</v>
       </c>
-      <c r="I62">
+      <c r="K62">
         <v>16.41767707333333</v>
       </c>
-      <c r="J62">
+      <c r="L62">
         <v>1.198807591833333</v>
       </c>
-      <c r="K62">
+      <c r="M62">
         <v>42.96320517166667</v>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="M62">
+      <c r="O62">
         <v>0.8783340032070126</v>
       </c>
-      <c r="N62">
+      <c r="P62">
         <v>-5.533504220204179</v>
       </c>
-      <c r="O62">
+      <c r="Q62">
         <v>-9.863690856014752</v>
       </c>
-      <c r="P62">
+      <c r="R62">
         <v>-17.56668006414025</v>
       </c>
-      <c r="Q62">
+      <c r="S62">
         <v>10.44444444444444</v>
       </c>
-      <c r="R62">
+      <c r="T62">
         <v>1.727049628333333</v>
       </c>
-      <c r="S62">
+      <c r="U62">
         <v>369.4111567410862</v>
       </c>
-      <c r="T62">
-        <v>132.6091331891079</v>
-      </c>
-      <c r="U62">
+      <c r="V62">
+        <v>142.081214131187</v>
+      </c>
+      <c r="W62">
         <v>508.9159648560278</v>
       </c>
-      <c r="V62">
-        <v>521.2669928081484</v>
+      <c r="X62">
+        <v>557.0715732639446</v>
       </c>
     </row>
     <row r="63">
@@ -4868,66 +5244,72 @@
         <v>615.7452564102564</v>
       </c>
       <c r="C63">
-        <v>224.0909588461539</v>
+        <v>239.4219209999682</v>
       </c>
       <c r="D63">
+        <v>3.231067725698165</v>
+      </c>
+      <c r="E63">
+        <v>56.93132958965453</v>
+      </c>
+      <c r="F63">
         <v>60</v>
       </c>
-      <c r="E63">
+      <c r="G63">
         <v>18.52182941166667</v>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>33.48027269</v>
       </c>
-      <c r="G63">
+      <c r="I63">
         <v>52.00210210166667</v>
       </c>
-      <c r="H63">
+      <c r="J63">
         <v>21.01716598833333</v>
       </c>
-      <c r="I63">
+      <c r="K63">
         <v>33.50714061833333</v>
       </c>
-      <c r="J63">
+      <c r="L63">
         <v>1.283039363</v>
       </c>
-      <c r="K63">
+      <c r="M63">
         <v>54.52430660666666</v>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M63">
+      <c r="O63">
         <v>1.533643868174295</v>
       </c>
-      <c r="N63">
+      <c r="P63">
         <v>-9.661956369498061</v>
       </c>
-      <c r="O63">
+      <c r="Q63">
         <v>-17.22282063959734</v>
       </c>
-      <c r="P63">
+      <c r="R63">
         <v>-30.67287736348591</v>
       </c>
-      <c r="Q63">
+      <c r="S63">
         <v>32.05555555555556</v>
       </c>
-      <c r="R63">
+      <c r="T63">
         <v>2.495336576666666</v>
       </c>
-      <c r="S63">
+      <c r="U63">
         <v>571.2481656168799</v>
       </c>
-      <c r="T63">
-        <v>205.0634440675979</v>
-      </c>
-      <c r="U63">
+      <c r="V63">
+        <v>219.7108329295692</v>
+      </c>
+      <c r="W63">
         <v>786.9749087759928</v>
       </c>
-      <c r="V63">
-        <v>778.1163038234364</v>
+      <c r="X63">
+        <v>793.4472659772507</v>
       </c>
     </row>
     <row r="64">
@@ -4940,66 +5322,72 @@
         <v>306.6930933333333</v>
       </c>
       <c r="C64">
-        <v>31.12535130307694</v>
+        <v>120.3141233595146</v>
       </c>
       <c r="D64">
+        <v>4.334073732835398</v>
+      </c>
+      <c r="E64">
+        <v>32.93561625901585</v>
+      </c>
+      <c r="F64">
         <v>16</v>
       </c>
-      <c r="E64">
+      <c r="G64">
         <v>20.34286945666667</v>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>30.85022926333333</v>
       </c>
-      <c r="G64">
+      <c r="I64">
         <v>51.19309871999999</v>
       </c>
-      <c r="H64">
+      <c r="J64">
         <v>22.511840975</v>
       </c>
-      <c r="I64">
+      <c r="K64">
         <v>31.46513772166666</v>
       </c>
-      <c r="J64">
+      <c r="L64">
         <v>1.214772208</v>
       </c>
-      <c r="K64">
+      <c r="M64">
         <v>53.97697869666666</v>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M64">
+      <c r="O64">
         <v>0.6617605719075088</v>
       </c>
-      <c r="N64">
+      <c r="P64">
         <v>-4.169091603017305</v>
       </c>
-      <c r="O64">
+      <c r="Q64">
         <v>-7.431571222521324</v>
       </c>
-      <c r="P64">
+      <c r="R64">
         <v>-13.23521143815018</v>
       </c>
-      <c r="Q64">
+      <c r="S64">
         <v>12.27777777777778</v>
       </c>
-      <c r="R64">
+      <c r="T64">
         <v>2.168971518333333</v>
       </c>
-      <c r="S64">
+      <c r="U64">
         <v>470.1153177200277</v>
       </c>
-      <c r="T64">
-        <v>168.7593448225741</v>
-      </c>
-      <c r="U64">
+      <c r="V64">
+        <v>180.8135837384722</v>
+      </c>
+      <c r="W64">
         <v>647.6501484733757</v>
       </c>
-      <c r="V64">
-        <v>493.8090978005833</v>
+      <c r="X64">
+        <v>582.997869857021</v>
       </c>
     </row>
     <row r="65">
@@ -5012,66 +5400,72 @@
         <v>284.9810256410257</v>
       </c>
       <c r="C65">
-        <v>16.29308269230771</v>
+        <v>115.4025372458659</v>
       </c>
       <c r="D65">
+        <v>3.316011292720439</v>
+      </c>
+      <c r="E65">
+        <v>27.80553227245964</v>
+      </c>
+      <c r="F65">
         <v>4</v>
       </c>
-      <c r="E65">
+      <c r="G65">
         <v>14.71919975333333</v>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>29.839411575</v>
       </c>
-      <c r="G65">
+      <c r="I65">
         <v>44.55861132833333</v>
       </c>
-      <c r="H65">
+      <c r="J65">
         <v>14.43724686483333</v>
       </c>
-      <c r="I65">
+      <c r="K65">
         <v>31.33856732333333</v>
       </c>
-      <c r="J65">
+      <c r="L65">
         <v>1.2871362685</v>
       </c>
-      <c r="K65">
+      <c r="M65">
         <v>45.77581418816666</v>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M65">
+      <c r="O65">
         <v>5.37547026623286</v>
       </c>
-      <c r="N65">
+      <c r="P65">
         <v>-33.86546267726702</v>
       </c>
-      <c r="O65">
+      <c r="Q65">
         <v>-60.36653108979502</v>
       </c>
-      <c r="P65">
+      <c r="R65">
         <v>-107.5094053246572</v>
       </c>
-      <c r="Q65">
+      <c r="S65">
         <v>2.361111111111111</v>
       </c>
-      <c r="R65">
+      <c r="T65">
         <v>-0.2819528884999993</v>
       </c>
-      <c r="S65">
+      <c r="U65">
         <v>-64.75253591604864</v>
       </c>
-      <c r="T65">
-        <v>-23.24450007242772</v>
-      </c>
-      <c r="U65">
+      <c r="V65">
+        <v>-24.90482150617255</v>
+      </c>
+      <c r="W65">
         <v>-89.20574999224259</v>
       </c>
-      <c r="V65">
-        <v>-108.825984313536</v>
+      <c r="X65">
+        <v>-9.716529759977732</v>
       </c>
     </row>
     <row r="66">
@@ -5084,66 +5478,72 @@
         <v>148.8394871794872</v>
       </c>
       <c r="C66">
-        <v>-68.81190769230768</v>
+        <v>60.29064891455001</v>
       </c>
       <c r="D66">
+        <v>2.656304490841908</v>
+      </c>
+      <c r="E66">
+        <v>12.91258089143115</v>
+      </c>
+      <c r="F66">
         <v>8</v>
       </c>
-      <c r="E66">
+      <c r="G66">
         <v>18.14486130333333</v>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>33.961658875</v>
       </c>
-      <c r="G66">
+      <c r="I66">
         <v>52.10652017833333</v>
       </c>
-      <c r="H66">
+      <c r="J66">
         <v>19.296109655</v>
       </c>
-      <c r="I66">
+      <c r="K66">
         <v>34.73453828666666</v>
       </c>
-      <c r="J66">
+      <c r="L66">
         <v>1.330423571833333</v>
       </c>
-      <c r="K66">
+      <c r="M66">
         <v>54.03064794166666</v>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M66">
+      <c r="O66">
         <v>1.782545232434082</v>
       </c>
-      <c r="N66">
+      <c r="P66">
         <v>-11.23003496433472</v>
       </c>
-      <c r="O66">
+      <c r="Q66">
         <v>-20.01798296023475</v>
       </c>
-      <c r="P66">
+      <c r="R66">
         <v>-35.65090464868165</v>
       </c>
-      <c r="Q66">
+      <c r="S66">
         <v>7.542857142857143</v>
       </c>
-      <c r="R66">
+      <c r="T66">
         <v>1.151248351666666</v>
       </c>
-      <c r="S66">
+      <c r="U66">
         <v>273.2842844245443</v>
       </c>
-      <c r="T66">
-        <v>98.10205081906719</v>
-      </c>
-      <c r="U66">
+      <c r="V66">
+        <v>105.1093401632863</v>
+      </c>
+      <c r="W66">
         <v>376.487641886203</v>
       </c>
-      <c r="V66">
-        <v>184.4543937720019</v>
+      <c r="X66">
+        <v>313.5569503788595</v>
       </c>
     </row>
     <row r="67">
@@ -5156,66 +5556,72 @@
         <v>70.61499999999999</v>
       </c>
       <c r="C67">
-        <v>-118.7168665384615</v>
+        <v>29.18815631910355</v>
       </c>
       <c r="D67">
+        <v>1.242859854944097</v>
+      </c>
+      <c r="E67">
+        <v>3.777843282920543</v>
+      </c>
+      <c r="F67">
         <v>4</v>
       </c>
-      <c r="E67">
+      <c r="G67">
         <v>18.10442685166667</v>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>33.43932509166667</v>
       </c>
-      <c r="G67">
+      <c r="I67">
         <v>51.54375194333333</v>
       </c>
-      <c r="H67">
+      <c r="J67">
         <v>16.57419823166667</v>
       </c>
-      <c r="I67">
+      <c r="K67">
         <v>35.08676949833333</v>
       </c>
-      <c r="J67">
+      <c r="L67">
         <v>1.348954807166667</v>
       </c>
-      <c r="K67">
+      <c r="M67">
         <v>51.66096773</v>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M67">
+      <c r="O67">
         <v>6.470060526093794</v>
       </c>
-      <c r="N67">
+      <c r="P67">
         <v>-40.7613813143909</v>
       </c>
-      <c r="O67">
+      <c r="Q67">
         <v>-72.65877970803331</v>
       </c>
-      <c r="P67">
+      <c r="R67">
         <v>-129.4012105218759</v>
       </c>
-      <c r="Q67">
+      <c r="S67">
         <v>2.666666666666667</v>
       </c>
-      <c r="R67">
+      <c r="T67">
         <v>-1.530228619999999</v>
       </c>
-      <c r="S67">
+      <c r="U67">
         <v>-368.3065359688469</v>
       </c>
-      <c r="T67">
-        <v>-132.2126026554835</v>
-      </c>
-      <c r="U67">
+      <c r="V67">
+        <v>-141.656359988018</v>
+      </c>
+      <c r="W67">
         <v>-507.3941939624156</v>
       </c>
-      <c r="V67">
-        <v>-559.6821822153418</v>
+      <c r="X67">
+        <v>-411.7771593577767</v>
       </c>
     </row>
     <row r="68">
@@ -5228,66 +5634,72 @@
         <v>156.2683333333333</v>
       </c>
       <c r="C68">
-        <v>-64.15647461538461</v>
+        <v>61.67439794932785</v>
       </c>
       <c r="D68">
+        <v>2.773600791048716</v>
+      </c>
+      <c r="E68">
+        <v>13.52786852616456</v>
+      </c>
+      <c r="F68">
         <v>8</v>
       </c>
-      <c r="E68">
+      <c r="G68">
         <v>14.92791318</v>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>30.64560135166667</v>
       </c>
-      <c r="G68">
+      <c r="I68">
         <v>45.57351453166667</v>
       </c>
-      <c r="H68">
+      <c r="J68">
         <v>14.94356254216667</v>
       </c>
-      <c r="I68">
+      <c r="K68">
         <v>31.67317683666667</v>
       </c>
-      <c r="J68">
+      <c r="L68">
         <v>1.300956109</v>
       </c>
-      <c r="K68">
+      <c r="M68">
         <v>46.61673937883333</v>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M68">
+      <c r="O68">
         <v>1.667006999653265</v>
       </c>
-      <c r="N68">
+      <c r="P68">
         <v>-10.50214409781557</v>
       </c>
-      <c r="O68">
+      <c r="Q68">
         <v>-18.72048860610616</v>
       </c>
-      <c r="P68">
+      <c r="R68">
         <v>-33.34013999306529</v>
       </c>
-      <c r="Q68">
+      <c r="S68">
         <v>6.527777777777778</v>
       </c>
-      <c r="R68">
+      <c r="T68">
         <v>0.01564936216666624</v>
       </c>
-      <c r="S68">
+      <c r="U68">
         <v>3.632578361314557</v>
       </c>
-      <c r="T68">
-        <v>1.304002488677021</v>
-      </c>
-      <c r="U68">
+      <c r="V68">
+        <v>1.397145523582522</v>
+      </c>
+      <c r="W68">
         <v>5.004388979402782</v>
       </c>
-      <c r="V68">
-        <v>-79.24438486017621</v>
+      <c r="X68">
+        <v>46.58648770453625</v>
       </c>
     </row>
     <row r="69">
@@ -5300,66 +5712,72 @@
         <v>41.35012820512821</v>
       </c>
       <c r="C69">
-        <v>-137.2941396153846</v>
+        <v>16.11474299698805</v>
       </c>
       <c r="D69">
+        <v>0.86060439704418</v>
+      </c>
+      <c r="E69">
+        <v>1.523952100352614</v>
+      </c>
+      <c r="F69">
         <v>1</v>
       </c>
-      <c r="E69">
+      <c r="G69">
         <v>13.18105039666667</v>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>37.45385885333334</v>
       </c>
-      <c r="G69">
+      <c r="I69">
         <v>50.63490925000001</v>
       </c>
-      <c r="H69">
+      <c r="J69">
         <v>13.13788787916667</v>
       </c>
-      <c r="I69">
+      <c r="K69">
         <v>37.97236331166667</v>
       </c>
-      <c r="J69">
+      <c r="L69">
         <v>1.306180608666667</v>
       </c>
-      <c r="K69">
+      <c r="M69">
         <v>51.11025119083334</v>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M69">
+      <c r="O69">
         <v>7.426832498544667</v>
       </c>
-      <c r="N69">
+      <c r="P69">
         <v>-46.7890447408314</v>
       </c>
-      <c r="O69">
+      <c r="Q69">
         <v>-83.40332895865662</v>
       </c>
-      <c r="P69">
+      <c r="R69">
         <v>-148.5366499708933</v>
       </c>
-      <c r="Q69">
+      <c r="S69">
         <v>1</v>
       </c>
-      <c r="R69">
+      <c r="T69">
         <v>-0.043162517499999</v>
       </c>
-      <c r="S69">
+      <c r="U69">
         <v>-10.0592523900291</v>
       </c>
-      <c r="T69">
-        <v>-3.611013678471985</v>
-      </c>
-      <c r="U69">
+      <c r="V69">
+        <v>-3.86894322693427</v>
+      </c>
+      <c r="W69">
         <v>-13.85803877978163</v>
       </c>
-      <c r="V69">
-        <v>-230.7567209640703</v>
+      <c r="X69">
+        <v>-77.34783835169767</v>
       </c>
     </row>
     <row r="70">
@@ -5372,66 +5790,72 @@
         <v>350.2982051282052</v>
       </c>
       <c r="C70">
-        <v>60.63239038461541</v>
+        <v>135.9485161655678</v>
       </c>
       <c r="D70">
+        <v>3.198257316627551</v>
+      </c>
+      <c r="E70">
+        <v>32.15812784430829</v>
+      </c>
+      <c r="F70">
         <v>8</v>
       </c>
-      <c r="E70">
+      <c r="G70">
         <v>14.67711508166667</v>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>38.309613865</v>
       </c>
-      <c r="G70">
+      <c r="I70">
         <v>52.98672894666667</v>
       </c>
-      <c r="H70">
+      <c r="J70">
         <v>18.117422885</v>
       </c>
-      <c r="I70">
+      <c r="K70">
         <v>37.46903936833333</v>
       </c>
-      <c r="J70">
+      <c r="L70">
         <v>1.244072557</v>
       </c>
-      <c r="K70">
+      <c r="M70">
         <v>55.58646225333334</v>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M70">
+      <c r="O70">
         <v>0.7836703974105198</v>
       </c>
-      <c r="N70">
+      <c r="P70">
         <v>-4.937123503686275</v>
       </c>
-      <c r="O70">
+      <c r="Q70">
         <v>-8.800618562920137</v>
       </c>
-      <c r="P70">
+      <c r="R70">
         <v>-15.6734079482104</v>
       </c>
-      <c r="Q70">
+      <c r="S70">
         <v>6.027777777777778</v>
       </c>
-      <c r="R70">
+      <c r="T70">
         <v>3.440307803333333</v>
       </c>
-      <c r="S70">
+      <c r="U70">
         <v>763.6576664087194</v>
       </c>
-      <c r="T70">
-        <v>274.1335212749249</v>
-      </c>
-      <c r="U70">
+      <c r="V70">
+        <v>293.7144870802767</v>
+      </c>
+      <c r="W70">
         <v>1052.04613078994</v>
       </c>
-      <c r="V70">
-        <v>815.4894382304146</v>
+      <c r="X70">
+        <v>890.805564011367</v>
       </c>
     </row>
     <row r="71">
@@ -5444,66 +5868,72 @@
         <v>350.0344871794872</v>
       </c>
       <c r="C71">
-        <v>59.12839692307695</v>
+        <v>143.7889625757102</v>
       </c>
       <c r="D71">
+        <v>2.096077665636558</v>
+      </c>
+      <c r="E71">
+        <v>26.79364441113091</v>
+      </c>
+      <c r="F71">
         <v>4</v>
       </c>
-      <c r="E71">
+      <c r="G71">
         <v>15.78257399333333</v>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>35.71433067333334</v>
       </c>
-      <c r="G71">
+      <c r="I71">
         <v>51.49690466666667</v>
       </c>
-      <c r="H71">
+      <c r="J71">
         <v>15.29936591116667</v>
       </c>
-      <c r="I71">
+      <c r="K71">
         <v>37.28644950833333</v>
       </c>
-      <c r="J71">
+      <c r="L71">
         <v>1.253556855166667</v>
       </c>
-      <c r="K71">
+      <c r="M71">
         <v>52.5858154195</v>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M71">
+      <c r="O71">
         <v>4.916436510502518</v>
       </c>
-      <c r="N71">
+      <c r="P71">
         <v>-30.97355001616586</v>
       </c>
-      <c r="O71">
+      <c r="Q71">
         <v>-55.21158201294327</v>
       </c>
-      <c r="P71">
+      <c r="R71">
         <v>-98.32873021005035</v>
       </c>
-      <c r="Q71">
+      <c r="S71">
         <v>3.722222222222222</v>
       </c>
-      <c r="R71">
+      <c r="T71">
         <v>-0.4832080821666658</v>
       </c>
-      <c r="S71">
+      <c r="U71">
         <v>-108.0771618308548</v>
       </c>
-      <c r="T71">
-        <v>-38.79692988799916</v>
-      </c>
-      <c r="U71">
+      <c r="V71">
+        <v>-41.56813916571338</v>
+      </c>
+      <c r="W71">
         <v>-148.8915320730299</v>
       </c>
-      <c r="V71">
-        <v>-104.1603469207211</v>
+      <c r="X71">
+        <v>-19.4997812680879</v>
       </c>
     </row>
     <row r="72">
@@ -5516,66 +5946,72 @@
         <v>19.21935897435898</v>
       </c>
       <c r="C72">
-        <v>-151.0551219230769</v>
+        <v>7.464533394382678</v>
       </c>
       <c r="D72">
+        <v>0.5899254850199525</v>
+      </c>
+      <c r="E72">
+        <v>0.4785961068347522</v>
+      </c>
+      <c r="F72">
         <v>1</v>
       </c>
-      <c r="E72">
+      <c r="G72">
         <v>13.647493345</v>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>32.61511166666666</v>
       </c>
-      <c r="G72">
+      <c r="I72">
         <v>46.26260501166666</v>
       </c>
-      <c r="H72">
+      <c r="J72">
         <v>13.49411681</v>
       </c>
-      <c r="I72">
+      <c r="K72">
         <v>33.50838837833333</v>
       </c>
-      <c r="J72">
+      <c r="L72">
         <v>1.384350912</v>
       </c>
-      <c r="K72">
+      <c r="M72">
         <v>47.00250518833333</v>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M72">
+      <c r="O72">
         <v>1.409321096780074</v>
       </c>
-      <c r="N72">
+      <c r="P72">
         <v>-8.878722909714469</v>
       </c>
-      <c r="O72">
+      <c r="Q72">
         <v>-15.82667591684024</v>
       </c>
-      <c r="P72">
+      <c r="R72">
         <v>-28.18642193560149</v>
       </c>
-      <c r="Q72">
+      <c r="S72">
         <v>0.9722222222222222</v>
       </c>
-      <c r="R72">
+      <c r="T72">
         <v>-0.1533765349999996</v>
       </c>
-      <c r="S72">
+      <c r="U72">
         <v>-37.8844353590789</v>
       </c>
-      <c r="T72">
-        <v>-13.59954089813089</v>
-      </c>
-      <c r="U72">
+      <c r="V72">
+        <v>-14.57093667656881</v>
+      </c>
+      <c r="W72">
         <v>-52.19115238391259</v>
       </c>
-      <c r="V72">
-        <v>-204.766233198996</v>
+      <c r="X72">
+        <v>-46.24657788153646</v>
       </c>
     </row>
     <row r="73">
@@ -5588,66 +6024,72 @@
         <v>98.38858974358973</v>
       </c>
       <c r="C73">
-        <v>-102.6289638461538</v>
+        <v>39.2833534025906</v>
       </c>
       <c r="D73">
+        <v>0.7802323477516001</v>
+      </c>
+      <c r="E73">
+        <v>3.3831032815554</v>
+      </c>
+      <c r="F73">
         <v>1</v>
       </c>
-      <c r="E73">
+      <c r="G73">
         <v>12.741091735</v>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>38.41735998833333</v>
       </c>
-      <c r="G73">
+      <c r="I73">
         <v>51.15845172333333</v>
       </c>
-      <c r="H73">
+      <c r="J73">
         <v>13.57363288</v>
       </c>
-      <c r="I73">
+      <c r="K73">
         <v>38.47788508666667</v>
       </c>
-      <c r="J73">
+      <c r="L73">
         <v>1.3118625675</v>
       </c>
-      <c r="K73">
+      <c r="M73">
         <v>52.05151796666667</v>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M73">
+      <c r="O73">
         <v>4.033602709547567</v>
       </c>
-      <c r="N73">
+      <c r="P73">
         <v>-25.41169707014967</v>
       </c>
-      <c r="O73">
+      <c r="Q73">
         <v>-45.29735842821918</v>
       </c>
-      <c r="P73">
+      <c r="R73">
         <v>-80.67205419095133</v>
       </c>
-      <c r="Q73">
+      <c r="S73">
         <v>0.9722222222222222</v>
       </c>
-      <c r="R73">
+      <c r="T73">
         <v>0.8325411449999987</v>
       </c>
-      <c r="S73">
+      <c r="U73">
         <v>194.87213871189</v>
       </c>
-      <c r="T73">
-        <v>69.95410107606308</v>
-      </c>
-      <c r="U73">
+      <c r="V73">
+        <v>74.95082258149615</v>
+      </c>
+      <c r="W73">
         <v>268.4638530439084</v>
       </c>
-      <c r="V73">
-        <v>46.945816437517</v>
+      <c r="X73">
+        <v>188.8581336862614</v>
       </c>
     </row>
     <row r="74">
@@ -5660,66 +6102,72 @@
         <v>67.23102564102564</v>
       </c>
       <c r="C74">
-        <v>-120.9663026923077</v>
+        <v>25.78804665914402</v>
       </c>
       <c r="D74">
+        <v>1.160429300600832</v>
+      </c>
+      <c r="E74">
+        <v>3.160523161442919</v>
+      </c>
+      <c r="F74">
         <v>2</v>
       </c>
-      <c r="E74">
+      <c r="G74">
         <v>16.08225684666667</v>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>36.86274886166667</v>
       </c>
-      <c r="G74">
+      <c r="I74">
         <v>52.94500570833333</v>
       </c>
-      <c r="H74">
+      <c r="J74">
         <v>15.34313406833333</v>
       </c>
-      <c r="I74">
+      <c r="K74">
         <v>38.127645695</v>
       </c>
-      <c r="J74">
+      <c r="L74">
         <v>1.2954976355</v>
       </c>
-      <c r="K74">
+      <c r="M74">
         <v>53.47077976333333</v>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M74">
+      <c r="O74">
         <v>1.052414688086237</v>
       </c>
-      <c r="N74">
+      <c r="P74">
         <v>-6.630212534943291</v>
       </c>
-      <c r="O74">
+      <c r="Q74">
         <v>-11.81861694720844</v>
       </c>
-      <c r="P74">
+      <c r="R74">
         <v>-21.04829376172473</v>
       </c>
-      <c r="Q74">
+      <c r="S74">
         <v>2</v>
       </c>
-      <c r="R74">
+      <c r="T74">
         <v>-0.7391227783333338</v>
       </c>
-      <c r="S74">
+      <c r="U74">
         <v>-170.8476134981163</v>
       </c>
-      <c r="T74">
-        <v>-61.32991253778533</v>
-      </c>
-      <c r="U74">
+      <c r="V74">
+        <v>-65.71062057619856</v>
+      </c>
+      <c r="W74">
         <v>-235.3666814878664</v>
       </c>
-      <c r="V74">
-        <v>-303.6325331376324</v>
+      <c r="X74">
+        <v>-156.8781837861807</v>
       </c>
     </row>
     <row r="75">
@@ -5732,66 +6180,72 @@
         <v>51.7598717948718</v>
       </c>
       <c r="C75">
-        <v>-131.1401676923077</v>
+        <v>20.72448671080183</v>
       </c>
       <c r="D75">
+        <v>0.7652975136819987</v>
+      </c>
+      <c r="E75">
+        <v>1.751207855310056</v>
+      </c>
+      <c r="F75">
         <v>2</v>
       </c>
-      <c r="E75">
+      <c r="G75">
         <v>16.89603769</v>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>35.35727024166667</v>
       </c>
-      <c r="G75">
+      <c r="I75">
         <v>52.25330793166667</v>
       </c>
-      <c r="H75">
+      <c r="J75">
         <v>15.49836146416667</v>
       </c>
-      <c r="I75">
+      <c r="K75">
         <v>37.19344516666666</v>
       </c>
-      <c r="J75">
+      <c r="L75">
         <v>1.264633069333333</v>
       </c>
-      <c r="K75">
+      <c r="M75">
         <v>52.69180663083333</v>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M75">
+      <c r="O75">
         <v>1.321750156016363</v>
       </c>
-      <c r="N75">
+      <c r="P75">
         <v>-8.327025982903084</v>
       </c>
-      <c r="O75">
+      <c r="Q75">
         <v>-14.84325425206375</v>
       </c>
-      <c r="P75">
+      <c r="R75">
         <v>-26.43500312032725</v>
       </c>
-      <c r="Q75">
+      <c r="S75">
         <v>1.888888888888889</v>
       </c>
-      <c r="R75">
+      <c r="T75">
         <v>-1.397676225833333</v>
       </c>
-      <c r="S75">
+      <c r="U75">
         <v>-315.3746761425003</v>
       </c>
-      <c r="T75">
-        <v>-113.2114222050001</v>
-      </c>
-      <c r="U75">
+      <c r="V75">
+        <v>-121.2979523625001</v>
+      </c>
+      <c r="W75">
         <v>-434.4730923021603</v>
       </c>
-      <c r="V75">
-        <v>-461.3580980868717</v>
+      <c r="X75">
+        <v>-309.4934436837622</v>
       </c>
     </row>
     <row r="76">
@@ -5804,66 +6258,72 @@
         <v>268.6414102564103</v>
       </c>
       <c r="C76">
-        <v>8.124968461538476</v>
+        <v>105.0180102879905</v>
       </c>
       <c r="D76">
+        <v>2.643810951523112</v>
+      </c>
+      <c r="E76">
+        <v>22.43284672343808</v>
+      </c>
+      <c r="F76">
         <v>8</v>
       </c>
-      <c r="E76">
+      <c r="G76">
         <v>16.947425565</v>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>30.629589955</v>
       </c>
-      <c r="G76">
+      <c r="I76">
         <v>47.57701552</v>
       </c>
-      <c r="H76">
+      <c r="J76">
         <v>17.406181905</v>
       </c>
-      <c r="I76">
+      <c r="K76">
         <v>31.31645307</v>
       </c>
-      <c r="J76">
+      <c r="L76">
         <v>1.2258200815</v>
       </c>
-      <c r="K76">
+      <c r="M76">
         <v>48.72263497500001</v>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M76">
+      <c r="O76">
         <v>2.539400797029873</v>
       </c>
-      <c r="N76">
+      <c r="P76">
         <v>-15.9982250212882</v>
       </c>
-      <c r="O76">
+      <c r="Q76">
         <v>-28.51747095064547</v>
       </c>
-      <c r="P76">
+      <c r="R76">
         <v>-50.78801594059746</v>
       </c>
-      <c r="Q76">
+      <c r="S76">
         <v>6.027777777777778</v>
       </c>
-      <c r="R76">
+      <c r="T76">
         <v>0.4587563400000008</v>
       </c>
-      <c r="S76">
+      <c r="U76">
         <v>100.337786579552</v>
       </c>
-      <c r="T76">
-        <v>36.0186926183007</v>
-      </c>
-      <c r="U76">
+      <c r="V76">
+        <v>38.59145637675076</v>
+      </c>
+      <c r="W76">
         <v>138.2294512140043</v>
       </c>
-      <c r="V76">
-        <v>79.94528409044496</v>
+      <c r="X76">
+        <v>176.838325916897</v>
       </c>
     </row>
     <row r="77">
@@ -5876,66 +6336,72 @@
         <v>101.8382051282051</v>
       </c>
       <c r="C77">
-        <v>-99.10945769230769</v>
+        <v>39.57631847796294</v>
       </c>
       <c r="D77">
+        <v>1.412863028854081</v>
+      </c>
+      <c r="E77">
+        <v>5.646782255347036</v>
+      </c>
+      <c r="F77">
         <v>2</v>
       </c>
-      <c r="E77">
+      <c r="G77">
         <v>12.63691090166667</v>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>38.467871745</v>
       </c>
-      <c r="G77">
+      <c r="I77">
         <v>51.10478264666666</v>
       </c>
-      <c r="H77">
+      <c r="J77">
         <v>11.93623757083333</v>
       </c>
-      <c r="I77">
+      <c r="K77">
         <v>39.78190652666667</v>
       </c>
-      <c r="J77">
+      <c r="L77">
         <v>1.380730892166667</v>
       </c>
-      <c r="K77">
+      <c r="M77">
         <v>51.7181440975</v>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M77">
+      <c r="O77">
         <v>3.095392060730346</v>
       </c>
-      <c r="N77">
+      <c r="P77">
         <v>-19.50096998260118</v>
       </c>
-      <c r="O77">
+      <c r="Q77">
         <v>-34.76125284200179</v>
       </c>
-      <c r="P77">
+      <c r="R77">
         <v>-61.90784121460692</v>
       </c>
-      <c r="Q77">
+      <c r="S77">
         <v>2</v>
       </c>
-      <c r="R77">
+      <c r="T77">
         <v>-0.7006733308333342</v>
       </c>
-      <c r="S77">
+      <c r="U77">
         <v>-172.6157163075136</v>
       </c>
-      <c r="T77">
-        <v>-61.96461611038952</v>
-      </c>
-      <c r="U77">
+      <c r="V77">
+        <v>-66.39066011827448</v>
+      </c>
+      <c r="W77">
         <v>-237.8024924556434</v>
       </c>
-      <c r="V77">
-        <v>-306.4864268418231</v>
+      <c r="X77">
+        <v>-167.8006506715525</v>
       </c>
     </row>
     <row r="78">
@@ -5948,66 +6414,72 @@
         <v>693.4347435897436</v>
       </c>
       <c r="C78">
-        <v>285.2588969230769</v>
+        <v>277.5359939115976</v>
       </c>
       <c r="D78">
+        <v>1.630447529738109</v>
+      </c>
+      <c r="E78">
+        <v>43.86992311066624</v>
+      </c>
+      <c r="F78">
         <v>16</v>
       </c>
-      <c r="E78">
+      <c r="G78">
         <v>18.07836725833333</v>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>34.69260811833333</v>
       </c>
-      <c r="G78">
+      <c r="I78">
         <v>52.77097537666667</v>
       </c>
-      <c r="H78">
+      <c r="J78">
         <v>18.410111665</v>
       </c>
-      <c r="I78">
+      <c r="K78">
         <v>36.12730495333334</v>
       </c>
-      <c r="J78">
+      <c r="L78">
         <v>1.2625153515</v>
       </c>
-      <c r="K78">
+      <c r="M78">
         <v>54.53741661833334</v>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M78">
+      <c r="O78">
         <v>3.183276175047217</v>
       </c>
-      <c r="N78">
+      <c r="P78">
         <v>-20.05463990279747</v>
       </c>
-      <c r="O78">
+      <c r="Q78">
         <v>-35.74819144578025</v>
       </c>
-      <c r="P78">
+      <c r="R78">
         <v>-63.66552350094434</v>
       </c>
-      <c r="Q78">
+      <c r="S78">
         <v>9.972222222222221</v>
       </c>
-      <c r="R78">
+      <c r="T78">
         <v>0.3317444066666653</v>
       </c>
-      <c r="S78">
+      <c r="U78">
         <v>74.7301720746156</v>
       </c>
-      <c r="T78">
-        <v>26.82621561652867</v>
-      </c>
-      <c r="U78">
+      <c r="V78">
+        <v>28.74237387485215</v>
+      </c>
+      <c r="W78">
         <v>102.9513509032038</v>
       </c>
-      <c r="V78">
-        <v>324.2408775519123</v>
+      <c r="X78">
+        <v>316.5179745404329</v>
       </c>
     </row>
     <row r="79">
@@ -6020,66 +6492,72 @@
         <v>567.9525256410257</v>
       </c>
       <c r="C79">
-        <v>200.100018923077</v>
+        <v>229.0186227279208</v>
       </c>
       <c r="D79">
+        <v>4.216377240397463</v>
+      </c>
+      <c r="E79">
+        <v>61.91791305184274</v>
+      </c>
+      <c r="F79">
         <v>16</v>
       </c>
-      <c r="E79">
+      <c r="G79">
         <v>14.24282284833333</v>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>30.676206745</v>
       </c>
-      <c r="G79">
+      <c r="I79">
         <v>44.91902959333333</v>
       </c>
-      <c r="H79">
+      <c r="J79">
         <v>15.80617593833333</v>
       </c>
-      <c r="I79">
+      <c r="K79">
         <v>31.66174778166667</v>
       </c>
-      <c r="J79">
+      <c r="L79">
         <v>1.269657585333333</v>
       </c>
-      <c r="K79">
+      <c r="M79">
         <v>47.46792372</v>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M79">
+      <c r="O79">
         <v>3.28270051142621</v>
       </c>
-      <c r="N79">
+      <c r="P79">
         <v>-20.68101322198512</v>
       </c>
-      <c r="O79">
+      <c r="Q79">
         <v>-36.86472674331633</v>
       </c>
-      <c r="P79">
+      <c r="R79">
         <v>-65.65401022852419</v>
       </c>
-      <c r="Q79">
+      <c r="S79">
         <v>8.833333333333334</v>
       </c>
-      <c r="R79">
+      <c r="T79">
         <v>1.56335309</v>
       </c>
-      <c r="S79">
+      <c r="U79">
         <v>354.1599057720002</v>
       </c>
-      <c r="T79">
-        <v>127.1343251489232</v>
-      </c>
-      <c r="U79">
+      <c r="V79">
+        <v>136.2153483738462</v>
+      </c>
+      <c r="W79">
         <v>487.9052158286674</v>
       </c>
-      <c r="V79">
-        <v>517.3951979517608</v>
+      <c r="X79">
+        <v>546.3138017566048</v>
       </c>
     </row>
     <row r="80">
@@ -6092,66 +6570,72 @@
         <v>518.9996153846154</v>
       </c>
       <c r="C80">
-        <v>167.2466507692308</v>
+        <v>208.3667736590992</v>
       </c>
       <c r="D80">
+        <v>3.868551683434767</v>
+      </c>
+      <c r="E80">
+        <v>54.13120780722426</v>
+      </c>
+      <c r="F80">
         <v>2</v>
       </c>
-      <c r="E80">
+      <c r="G80">
         <v>13.65484056</v>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>38.165918985</v>
       </c>
-      <c r="G80">
+      <c r="I80">
         <v>51.820759545</v>
       </c>
-      <c r="H80">
+      <c r="J80">
         <v>13.02545374183333</v>
       </c>
-      <c r="I80">
+      <c r="K80">
         <v>39.19134638666667</v>
       </c>
-      <c r="J80">
+      <c r="L80">
         <v>1.354319834</v>
       </c>
-      <c r="K80">
+      <c r="M80">
         <v>52.2168001285</v>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M80">
+      <c r="O80">
         <v>3.038668028517401</v>
       </c>
-      <c r="N80">
+      <c r="P80">
         <v>-19.14360857965962</v>
       </c>
-      <c r="O80">
+      <c r="Q80">
         <v>-34.12424196025042</v>
       </c>
-      <c r="P80">
+      <c r="R80">
         <v>-60.77336057034802</v>
       </c>
-      <c r="Q80">
+      <c r="S80">
         <v>1.916666666666667</v>
       </c>
-      <c r="R80">
+      <c r="T80">
         <v>-0.6293868181666671</v>
       </c>
-      <c r="S80">
+      <c r="U80">
         <v>-152.0878732927439</v>
       </c>
-      <c r="T80">
-        <v>-54.59564682303625</v>
-      </c>
-      <c r="U80">
+      <c r="V80">
+        <v>-58.49533588182456</v>
+      </c>
+      <c r="W80">
         <v>-209.522493750578</v>
       </c>
-      <c r="V80">
-        <v>-18.96546448376353</v>
+      <c r="X80">
+        <v>22.15465840610494</v>
       </c>
     </row>
     <row r="81">
@@ -6164,66 +6648,72 @@
         <v>382.5914102564103</v>
       </c>
       <c r="C81">
-        <v>81.10359384615386</v>
+        <v>153.3205697003208</v>
       </c>
       <c r="D81">
+        <v>5.984089296781033</v>
+      </c>
+      <c r="E81">
+        <v>48.04470861163389</v>
+      </c>
+      <c r="F81">
         <v>4</v>
       </c>
-      <c r="E81">
+      <c r="G81">
         <v>15.32690688</v>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>33.91789635166667</v>
       </c>
-      <c r="G81">
+      <c r="I81">
         <v>49.24480323166667</v>
       </c>
-      <c r="H81">
+      <c r="J81">
         <v>16.39641685833333</v>
       </c>
-      <c r="I81">
+      <c r="K81">
         <v>34.92457740666666</v>
       </c>
-      <c r="J81">
+      <c r="L81">
         <v>1.324271466333333</v>
       </c>
-      <c r="K81">
+      <c r="M81">
         <v>51.320994265</v>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="M81">
+      <c r="O81">
         <v>0.7955205331765982</v>
       </c>
-      <c r="N81">
+      <c r="P81">
         <v>-5.011779359012569</v>
       </c>
-      <c r="O81">
+      <c r="Q81">
         <v>-8.933695587573197</v>
       </c>
-      <c r="P81">
+      <c r="R81">
         <v>-15.91041066353196</v>
       </c>
-      <c r="Q81">
+      <c r="S81">
         <v>2.666666666666667</v>
       </c>
-      <c r="R81">
+      <c r="T81">
         <v>1.069509978333333</v>
       </c>
-      <c r="S81">
+      <c r="U81">
         <v>252.7071720708672</v>
       </c>
-      <c r="T81">
-        <v>90.71539510236256</v>
-      </c>
-      <c r="U81">
+      <c r="V81">
+        <v>97.19506618110275</v>
+      </c>
+      <c r="W81">
         <v>348.1397677185525</v>
       </c>
-      <c r="V81">
-        <v>324.8770703294478</v>
+      <c r="X81">
+        <v>397.0940461836148</v>
       </c>
     </row>
   </sheetData>

--- a/Data Analysis/1_Data/economic_MF.xlsx
+++ b/Data Analysis/1_Data/economic_MF.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X81"/>
+  <dimension ref="A1:AC77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,7 +362,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>mean_biomass</t>
+          <t>biomass_mean</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -377,102 +377,127 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sowndiv</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>mean_org_11</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>mean_inorg_11</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>mean_C_11</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>mean_org_20</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>mean_inorg_20</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mean_bulk</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_C_20</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>leaching_mean</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>leach_costs_lo</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>leach_costs_mid</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>leach_costs_hi</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>meanSR</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dCVdSR</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>insurance</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sowndiv</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>mean_org_11</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>mean_inorg_11</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>mean_C_11</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>mean_org_20</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>mean_inorg_20</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mean_bulk</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>mean_C_20</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>block</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>av_leaching</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>leach_costs_lo</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>leach_costs_mid</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>leach_costs_hi</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>meanSR</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>mean_org_diff</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>SOC_costs_mid</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>SOC_costs_lo</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>SOC_costs_hi</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>costs_total_mid</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>costs_total_lo</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>costs_total_hi</t>
         </is>
       </c>
     </row>
@@ -483,75 +508,90 @@
         </is>
       </c>
       <c r="B2">
-        <v>382.2721153846154</v>
+        <v>3.822721153846154</v>
       </c>
       <c r="C2">
-        <v>145.7013651050133</v>
+        <v>682.1376342928661</v>
       </c>
       <c r="D2">
-        <v>2.259870857882386</v>
+        <v>0.4425031618563597</v>
       </c>
       <c r="E2">
-        <v>28.42270354919071</v>
+        <v>612.7381338495312</v>
       </c>
       <c r="F2">
+        <v>69.39950044333489</v>
+      </c>
+      <c r="G2">
         <v>16</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>15.693274495</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>6.694930096666667</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>22.38820459166666</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>18.76454505833333</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>6.8238517325</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>1.2546214505</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>25.58839679083333</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>2.813264729287163</v>
       </c>
-      <c r="P2">
-        <v>-17.72356779450913</v>
-      </c>
       <c r="Q2">
+        <v>-14.06632364643581</v>
+      </c>
+      <c r="R2">
         <v>-31.59296290989484</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>-56.26529458574326</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>11.08333333333333</v>
       </c>
-      <c r="T2">
+      <c r="U2">
+        <v>0.04910843718761077</v>
+      </c>
+      <c r="V2">
+        <v>-0.7857349950017722</v>
+      </c>
+      <c r="W2">
         <v>3.071270563333334</v>
       </c>
-      <c r="U2">
-        <v>687.5218281902502</v>
-      </c>
-      <c r="V2">
+      <c r="X2">
+        <v>1057.725889523462</v>
+      </c>
+      <c r="Y2">
         <v>264.4314723808654</v>
       </c>
-      <c r="W2">
-        <v>947.1582765386092</v>
-      </c>
-      <c r="X2">
-        <v>801.6302303853686</v>
+      <c r="Z2">
+        <v>2820.602372062565</v>
+      </c>
+      <c r="AA2">
+        <v>1708.270560906433</v>
+      </c>
+      <c r="AB2">
+        <v>932.5027830272957</v>
+      </c>
+      <c r="AC2">
+        <v>3446.474711769688</v>
       </c>
     </row>
     <row r="3">
@@ -561,75 +601,90 @@
         </is>
       </c>
       <c r="B3">
-        <v>350.5780769230769</v>
+        <v>3.505780769230769</v>
       </c>
       <c r="C3">
-        <v>137.7347669152479</v>
+        <v>622.8314695290859</v>
       </c>
       <c r="D3">
-        <v>3.037901513434422</v>
+        <v>0.3291745948898375</v>
       </c>
       <c r="E3">
-        <v>31.72172313239069</v>
+        <v>585.5486743674595</v>
       </c>
       <c r="F3">
+        <v>37.28279516162638</v>
+      </c>
+      <c r="G3">
         <v>8</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>15.69695607833333</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>6.371277073333333</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>22.06823315166667</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>16.83361475166667</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>6.491076882833333</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>1.287621534333333</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>23.3246916345</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>5.003784345866223</v>
       </c>
-      <c r="P3">
-        <v>-31.5238413789572</v>
-      </c>
       <c r="Q3">
+        <v>-25.01892172933112</v>
+      </c>
+      <c r="R3">
         <v>-56.19249820407769</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>-100.0756869173245</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>5.055555555555555</v>
       </c>
-      <c r="T3">
+      <c r="U3">
+        <v>-0.04227194227847345</v>
+      </c>
+      <c r="V3">
+        <v>0.3381755382277876</v>
+      </c>
+      <c r="W3">
         <v>1.136658673333333</v>
       </c>
-      <c r="U3">
-        <v>261.1403650534073</v>
-      </c>
-      <c r="V3">
+      <c r="X3">
+        <v>401.7544077744728</v>
+      </c>
+      <c r="Y3">
         <v>100.4386019436182</v>
       </c>
-      <c r="W3">
-        <v>359.7576803484479</v>
-      </c>
-      <c r="X3">
-        <v>342.6826337645775</v>
+      <c r="Z3">
+        <v>1071.345087398594</v>
+      </c>
+      <c r="AA3">
+        <v>968.393379099481</v>
+      </c>
+      <c r="AB3">
+        <v>698.2511497433729</v>
+      </c>
+      <c r="AC3">
+        <v>1594.100870010356</v>
       </c>
     </row>
     <row r="4">
@@ -639,75 +694,90 @@
         </is>
       </c>
       <c r="B4">
-        <v>171.8553846153846</v>
+        <v>1.718553846153846</v>
       </c>
       <c r="C4">
-        <v>67.96626745108389</v>
+        <v>284.4622099499374</v>
       </c>
       <c r="D4">
-        <v>1.541192873274919</v>
+        <v>0.6488480561651411</v>
       </c>
       <c r="E4">
-        <v>10.3275716254785</v>
+        <v>230.3920219055406</v>
       </c>
       <c r="F4">
+        <v>54.07018804439684</v>
+      </c>
+      <c r="G4">
         <v>8</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>15.64949997</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>6.797016461666667</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>22.44651643166667</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>13.88983349316667</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>7.411676897333333</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>1.404984469833333</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>21.3015103905</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>10.62294565431209</v>
       </c>
-      <c r="P4">
-        <v>-66.92455762216619</v>
-      </c>
       <c r="Q4">
+        <v>-53.11472827156047</v>
+      </c>
+      <c r="R4">
         <v>-119.2956796979248</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>-212.4589130862419</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>5.805555555555555</v>
       </c>
-      <c r="T4">
+      <c r="U4">
+        <v>-0.04227194227847345</v>
+      </c>
+      <c r="V4">
+        <v>0.3381755382277876</v>
+      </c>
+      <c r="W4">
         <v>-1.759666476833335</v>
       </c>
-      <c r="U4">
-        <v>-441.1208540532325</v>
-      </c>
-      <c r="V4">
+      <c r="X4">
+        <v>-678.6474677742038</v>
+      </c>
+      <c r="Y4">
         <v>-169.661866943551</v>
       </c>
-      <c r="W4">
-        <v>-607.7061858095404</v>
-      </c>
-      <c r="X4">
-        <v>-492.4502663000734</v>
+      <c r="Z4">
+        <v>-1809.72658073121</v>
+      </c>
+      <c r="AA4">
+        <v>-513.4809375221912</v>
+      </c>
+      <c r="AB4">
+        <v>61.68561473482598</v>
+      </c>
+      <c r="AC4">
+        <v>-1737.723283867515</v>
       </c>
     </row>
     <row r="5">
@@ -717,75 +787,90 @@
         </is>
       </c>
       <c r="B5">
-        <v>281.1561538461539</v>
+        <v>2.811561538461539</v>
       </c>
       <c r="C5">
-        <v>114.5516295509591</v>
+        <v>398.2022197538589</v>
       </c>
       <c r="D5">
-        <v>2.155129477973325</v>
+        <v>0.464009244094418</v>
       </c>
       <c r="E5">
-        <v>21.71358431082056</v>
+        <v>354.2359192318893</v>
       </c>
       <c r="F5">
+        <v>43.96630052196957</v>
+      </c>
+      <c r="G5">
         <v>4</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>16.81531028666667</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>6.73690309</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>23.55221337666666</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>16.13080275</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>7.018404786333333</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>1.347792084333333</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>23.14920753633334</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>10.03208662826186</v>
       </c>
-      <c r="P5">
-        <v>-63.20214575804974</v>
-      </c>
       <c r="Q5">
+        <v>-50.16043314130932</v>
+      </c>
+      <c r="R5">
         <v>-112.6603328353807</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>-200.6417325652373</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>2.972222222222222</v>
       </c>
-      <c r="T5">
+      <c r="U5">
+        <v>-0.08796213201151555</v>
+      </c>
+      <c r="V5">
+        <v>0.3518485280460622</v>
+      </c>
+      <c r="W5">
         <v>-0.6845075366666649</v>
       </c>
-      <c r="U5">
-        <v>-164.6102373281035</v>
-      </c>
-      <c r="V5">
+      <c r="X5">
+        <v>-253.246518966313</v>
+      </c>
+      <c r="Y5">
         <v>-63.31162974157826</v>
       </c>
-      <c r="W5">
-        <v>-226.7738161837011</v>
-      </c>
-      <c r="X5">
-        <v>-162.718940612525</v>
+      <c r="Z5">
+        <v>-675.3240505768348</v>
+      </c>
+      <c r="AA5">
+        <v>32.29536795216518</v>
+      </c>
+      <c r="AB5">
+        <v>284.7301568709713</v>
+      </c>
+      <c r="AC5">
+        <v>-477.7635633882131</v>
       </c>
     </row>
     <row r="6">
@@ -795,75 +880,90 @@
         </is>
       </c>
       <c r="B6">
-        <v>170.7674358974359</v>
+        <v>1.707674358974359</v>
       </c>
       <c r="C6">
-        <v>65.42028323790227</v>
+        <v>253.2261512482663</v>
       </c>
       <c r="D6">
-        <v>1.036141073848968</v>
+        <v>0.9651195433120758</v>
       </c>
       <c r="E6">
-        <v>7.298740527748213</v>
+        <v>170.5994783476048</v>
       </c>
       <c r="F6">
+        <v>82.62667290066153</v>
+      </c>
+      <c r="G6">
         <v>2</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>15.09488513333333</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>6.450398961666667</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>21.545284095</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>14.88611025333333</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>6.5496542775</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>1.346599269666667</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>21.43576453083333</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>7.607418619499584</v>
       </c>
-      <c r="P6">
-        <v>-47.92673730284738</v>
-      </c>
       <c r="Q6">
+        <v>-38.03709309749792</v>
+      </c>
+      <c r="R6">
         <v>-85.43131109698034</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>-152.1483723899917</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>1.805555555555556</v>
       </c>
-      <c r="T6">
+      <c r="U6">
+        <v>-0.1108072268780366</v>
+      </c>
+      <c r="V6">
+        <v>0.2216144537560732</v>
+      </c>
+      <c r="W6">
         <v>-0.20877488</v>
       </c>
-      <c r="U6">
-        <v>-50.16170880892521</v>
-      </c>
-      <c r="V6">
+      <c r="X6">
+        <v>-77.17185970603877</v>
+      </c>
+      <c r="Y6">
         <v>-19.29296492650969</v>
       </c>
-      <c r="W6">
-        <v>-69.10482797143419</v>
-      </c>
-      <c r="X6">
-        <v>-70.17273666800328</v>
+      <c r="Z6">
+        <v>-205.7916258827701</v>
+      </c>
+      <c r="AA6">
+        <v>90.62298044524718</v>
+      </c>
+      <c r="AB6">
+        <v>195.8960932242587</v>
+      </c>
+      <c r="AC6">
+        <v>-104.7138470244955</v>
       </c>
     </row>
     <row r="7">
@@ -873,75 +973,90 @@
         </is>
       </c>
       <c r="B7">
-        <v>242.4952179487179</v>
+        <v>2.42495217948718</v>
       </c>
       <c r="C7">
-        <v>93.97734618440134</v>
+        <v>391.0179840900196</v>
       </c>
       <c r="D7">
-        <v>3.859743076186435</v>
+        <v>0.2590846023326598</v>
       </c>
       <c r="E7">
-        <v>24.38791677157077</v>
+        <v>376.0690533905206</v>
       </c>
       <c r="F7">
+        <v>14.94893069949904</v>
+      </c>
+      <c r="G7">
         <v>16</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>16.30583443666667</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>6.19431128</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>22.50014571666667</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>16.76970075833334</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>6.545481602666666</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>1.3381643705</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>23.315182361</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>1.175780674075467</v>
       </c>
-      <c r="P7">
-        <v>-7.407418246675445</v>
-      </c>
       <c r="Q7">
+        <v>-5.878903370377337</v>
+      </c>
+      <c r="R7">
         <v>-13.2040169698675</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>-23.51561348150935</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>12.47222222222222</v>
       </c>
-      <c r="T7">
+      <c r="U7">
+        <v>0.04910843718761077</v>
+      </c>
+      <c r="V7">
+        <v>-0.7857349950017722</v>
+      </c>
+      <c r="W7">
         <v>0.4638663216666679</v>
       </c>
-      <c r="U7">
-        <v>110.7536403989424</v>
-      </c>
-      <c r="V7">
+      <c r="X7">
+        <v>170.3902159983728</v>
+      </c>
+      <c r="Y7">
         <v>42.59755399959321</v>
       </c>
-      <c r="W7">
-        <v>152.5787587526763</v>
-      </c>
-      <c r="X7">
-        <v>191.5269696134762</v>
+      <c r="Z7">
+        <v>454.3739093289942</v>
+      </c>
+      <c r="AA7">
+        <v>548.204183118525</v>
+      </c>
+      <c r="AB7">
+        <v>427.7366347192355</v>
+      </c>
+      <c r="AC7">
+        <v>821.8762799375045</v>
       </c>
     </row>
     <row r="8">
@@ -951,75 +1066,90 @@
         </is>
       </c>
       <c r="B8">
-        <v>117.4245256410256</v>
+        <v>1.174245256410256</v>
       </c>
       <c r="C8">
-        <v>47.37458253556064</v>
+        <v>251.587211126311</v>
       </c>
       <c r="D8">
-        <v>1.389560270267715</v>
+        <v>0.7196521240545678</v>
       </c>
       <c r="E8">
-        <v>6.676641436639747</v>
+        <v>195.8586718656469</v>
       </c>
       <c r="F8">
+        <v>55.72853926066409</v>
+      </c>
+      <c r="G8">
         <v>2</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>15.27825111666667</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>6.3079831</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>21.58623421666667</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>16.93685348</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>6.111142179166666</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>1.288512477</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>23.04799565916667</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>8.587698582789461</v>
       </c>
-      <c r="P8">
-        <v>-54.1025010715736</v>
-      </c>
       <c r="Q8">
+        <v>-42.9384929139473</v>
+      </c>
+      <c r="R8">
         <v>-96.43985508472565</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>-171.7539716557892</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>2</v>
       </c>
-      <c r="T8">
+      <c r="U8">
+        <v>-0.1108072268780366</v>
+      </c>
+      <c r="V8">
+        <v>0.2216144537560732</v>
+      </c>
+      <c r="W8">
         <v>1.658602363333333</v>
       </c>
-      <c r="U8">
-        <v>381.3173916193334</v>
-      </c>
-      <c r="V8">
+      <c r="X8">
+        <v>586.6421409528207</v>
+      </c>
+      <c r="Y8">
         <v>146.6605352382052</v>
       </c>
-      <c r="W8">
-        <v>525.3184824852191</v>
-      </c>
-      <c r="X8">
-        <v>332.2521190701684</v>
+      <c r="Z8">
+        <v>1564.379042540855</v>
+      </c>
+      <c r="AA8">
+        <v>741.789496994406</v>
+      </c>
+      <c r="AB8">
+        <v>355.3092534505688</v>
+      </c>
+      <c r="AC8">
+        <v>1644.212282011377</v>
       </c>
     </row>
     <row r="9">
@@ -1029,75 +1159,90 @@
         </is>
       </c>
       <c r="B9">
-        <v>319.7814102564103</v>
+        <v>3.197814102564103</v>
       </c>
       <c r="C9">
-        <v>130.9596011096417</v>
+        <v>563.6765277476256</v>
       </c>
       <c r="D9">
-        <v>2.567495039214939</v>
+        <v>0.3894846863290412</v>
       </c>
       <c r="E9">
-        <v>27.517314050276</v>
+        <v>517.8771035905054</v>
       </c>
       <c r="F9">
+        <v>45.79942415712026</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>15.37546887666667</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>6.454285086666667</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>21.82975396333333</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>15.82495804166667</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>6.2890732475</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>1.289376087666667</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>22.11403128916666</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>11.79392739577335</v>
       </c>
-      <c r="P9">
-        <v>-74.3017425933721</v>
-      </c>
       <c r="Q9">
+        <v>-58.96963697886675</v>
+      </c>
+      <c r="R9">
         <v>-132.4458046545347</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>-235.878547915467</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>1</v>
       </c>
-      <c r="T9">
+      <c r="U9">
+        <v>-0.1222297743112971</v>
+      </c>
+      <c r="V9">
+        <v>0.1222297743112971</v>
+      </c>
+      <c r="W9">
         <v>0.4494891649999992</v>
       </c>
-      <c r="U9">
-        <v>103.4080966678254</v>
-      </c>
-      <c r="V9">
+      <c r="X9">
+        <v>159.0893794889622</v>
+      </c>
+      <c r="Y9">
         <v>39.77234487224056</v>
       </c>
-      <c r="W9">
-        <v>142.4592363530494</v>
-      </c>
-      <c r="X9">
-        <v>101.9218931229324</v>
+      <c r="Z9">
+        <v>424.2383453038993</v>
+      </c>
+      <c r="AA9">
+        <v>590.3201025820532</v>
+      </c>
+      <c r="AB9">
+        <v>544.4792356409995</v>
+      </c>
+      <c r="AC9">
+        <v>752.0363251360579</v>
       </c>
     </row>
     <row r="10">
@@ -1107,75 +1252,90 @@
         </is>
       </c>
       <c r="B10">
-        <v>277.5409487179487</v>
+        <v>2.775409487179487</v>
       </c>
       <c r="C10">
-        <v>109.4526898952287</v>
+        <v>439.9361936203522</v>
       </c>
       <c r="D10">
-        <v>4.078294161783221</v>
+        <v>0.2452005569806061</v>
       </c>
       <c r="E10">
-        <v>29.14396956977761</v>
+        <v>424.7915428524858</v>
       </c>
       <c r="F10">
+        <v>15.14465076786644</v>
+      </c>
+      <c r="G10">
         <v>16</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>19.95934968833333</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>8.20662727</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>28.16597695833333</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>20.74362609</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>8.007693386333333</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>1.312353860333333</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>28.75131947633333</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>2.710670323817271</v>
       </c>
-      <c r="P10">
-        <v>-17.07722304004881</v>
-      </c>
       <c r="Q10">
+        <v>-13.55335161908636</v>
+      </c>
+      <c r="R10">
         <v>-30.44082773646796</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>-54.21340647634543</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>10.36111111111111</v>
       </c>
-      <c r="T10">
+      <c r="U10">
+        <v>0.04910843718761077</v>
+      </c>
+      <c r="V10">
+        <v>-0.7857349950017722</v>
+      </c>
+      <c r="W10">
         <v>0.7842764016666663</v>
       </c>
-      <c r="U10">
-        <v>183.6436035360149</v>
-      </c>
-      <c r="V10">
+      <c r="X10">
+        <v>282.5286208246382</v>
+      </c>
+      <c r="Y10">
         <v>70.63215520615955</v>
       </c>
-      <c r="W10">
-        <v>252.9949623277693</v>
-      </c>
-      <c r="X10">
-        <v>262.6554656947756</v>
+      <c r="Z10">
+        <v>753.4096555323686</v>
+      </c>
+      <c r="AA10">
+        <v>692.0239867085224</v>
+      </c>
+      <c r="AB10">
+        <v>497.0149972074254</v>
+      </c>
+      <c r="AC10">
+        <v>1139.132442676375</v>
       </c>
     </row>
     <row r="11">
@@ -1185,75 +1345,90 @@
         </is>
       </c>
       <c r="B11">
-        <v>404.5358461538461</v>
+        <v>4.045358461538462</v>
       </c>
       <c r="C11">
-        <v>161.239064826035</v>
+        <v>713.737353282478</v>
       </c>
       <c r="D11">
-        <v>2.417458139643523</v>
+        <v>0.4136576280685709</v>
       </c>
       <c r="E11">
-        <v>32.72970534812986</v>
+        <v>649.2010693406176</v>
       </c>
       <c r="F11">
+        <v>64.53628394186046</v>
+      </c>
+      <c r="G11">
         <v>8</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>16.720706945</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>7.984850008333334</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>24.70555695333334</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>15.448378665</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>8.4151640775</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>1.245958471666667</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>23.8635427425</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>7.824389819187211</v>
       </c>
-      <c r="P11">
-        <v>-49.29365586087943</v>
-      </c>
       <c r="Q11">
+        <v>-39.12194909593605</v>
+      </c>
+      <c r="R11">
         <v>-87.86789766947238</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>-156.4877963837442</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>5</v>
       </c>
-      <c r="T11">
+      <c r="U11">
+        <v>-0.04227194227847345</v>
+      </c>
+      <c r="V11">
+        <v>0.3381755382277876</v>
+      </c>
+      <c r="W11">
         <v>-1.27232828</v>
       </c>
-      <c r="U11">
-        <v>-282.851478443523</v>
-      </c>
-      <c r="V11">
+      <c r="X11">
+        <v>-435.156120682343</v>
+      </c>
+      <c r="Y11">
         <v>-108.7890301705858</v>
       </c>
-      <c r="W11">
-        <v>-389.6678008670155</v>
-      </c>
-      <c r="X11">
-        <v>-209.4803112869604</v>
+      <c r="Z11">
+        <v>-1160.416321819582</v>
+      </c>
+      <c r="AA11">
+        <v>190.7133349306625</v>
+      </c>
+      <c r="AB11">
+        <v>565.8263740159562</v>
+      </c>
+      <c r="AC11">
+        <v>-603.1667649208476</v>
       </c>
     </row>
     <row r="12">
@@ -1263,75 +1438,90 @@
         </is>
       </c>
       <c r="B12">
-        <v>308.8033333333333</v>
+        <v>3.088033333333334</v>
       </c>
       <c r="C12">
-        <v>126.806840250604</v>
+        <v>477.5890622116689</v>
       </c>
       <c r="D12">
-        <v>2.332909442000188</v>
+        <v>0.4286493003100115</v>
       </c>
       <c r="E12">
-        <v>25.20913822370119</v>
+        <v>431.6189750016763</v>
       </c>
       <c r="F12">
+        <v>45.97008720999258</v>
+      </c>
+      <c r="G12">
         <v>4</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>14.79970766666667</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>6.588684818333333</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>21.388392485</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>16.183862175</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>6.791461165499999</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>1.289940989333333</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>22.9753233405</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>6.603782064222194</v>
       </c>
-      <c r="P12">
-        <v>-41.60382700459982</v>
-      </c>
       <c r="Q12">
+        <v>-33.01891032111097</v>
+      </c>
+      <c r="R12">
         <v>-74.16047258121525</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>-132.0756412844439</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>3.194444444444445</v>
       </c>
-      <c r="T12">
+      <c r="U12">
+        <v>-0.08796213201151555</v>
+      </c>
+      <c r="V12">
+        <v>0.3518485280460622</v>
+      </c>
+      <c r="W12">
         <v>1.384154508333335</v>
       </c>
-      <c r="U12">
-        <v>318.5738471800504</v>
-      </c>
-      <c r="V12">
+      <c r="X12">
+        <v>490.1136110462314</v>
+      </c>
+      <c r="Y12">
         <v>122.5284027615579</v>
       </c>
-      <c r="W12">
-        <v>438.880401571532</v>
-      </c>
-      <c r="X12">
-        <v>371.2202148494392</v>
+      <c r="Z12">
+        <v>1306.969629456617</v>
+      </c>
+      <c r="AA12">
+        <v>893.5422006766851</v>
+      </c>
+      <c r="AB12">
+        <v>567.0985546521158</v>
+      </c>
+      <c r="AC12">
+        <v>1652.483050383842</v>
       </c>
     </row>
     <row r="13">
@@ -1341,75 +1531,90 @@
         </is>
       </c>
       <c r="B13">
-        <v>173.5197435897436</v>
+        <v>1.735197435897436</v>
       </c>
       <c r="C13">
-        <v>69.86402397477804</v>
+        <v>323.5588358364622</v>
       </c>
       <c r="D13">
-        <v>2.539175812312433</v>
+        <v>0.3938285782146363</v>
       </c>
       <c r="E13">
-        <v>14.58780248974256</v>
+        <v>296.7435580810762</v>
       </c>
       <c r="F13">
+        <v>26.81527775538598</v>
+      </c>
+      <c r="G13">
         <v>8</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>15.62836029166667</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>6.864643295</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>22.49300358666667</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>16.193342365</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>7.529579546166667</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>1.357109041833333</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>23.72292191116667</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>1.39202396258024</v>
       </c>
-      <c r="P13">
-        <v>-8.769750964255509</v>
-      </c>
       <c r="Q13">
+        <v>-6.960119812901198</v>
+      </c>
+      <c r="R13">
         <v>-15.63242909977609</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>-27.84047925160479</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>6.138888888888889</v>
       </c>
-      <c r="T13">
+      <c r="U13">
+        <v>-0.04227194227847345</v>
+      </c>
+      <c r="V13">
+        <v>0.3381755382277876</v>
+      </c>
+      <c r="W13">
         <v>0.5649820733333328</v>
       </c>
-      <c r="U13">
-        <v>136.8059913436875</v>
-      </c>
-      <c r="V13">
+      <c r="X13">
+        <v>210.4707559133653</v>
+      </c>
+      <c r="Y13">
         <v>52.61768897834133</v>
       </c>
-      <c r="W13">
-        <v>188.4695462285549</v>
-      </c>
-      <c r="X13">
-        <v>191.0375862186894</v>
+      <c r="Z13">
+        <v>561.2553491023076</v>
+      </c>
+      <c r="AA13">
+        <v>518.3971626500514</v>
+      </c>
+      <c r="AB13">
+        <v>369.2164050019023</v>
+      </c>
+      <c r="AC13">
+        <v>856.9737056871651</v>
       </c>
     </row>
     <row r="14">
@@ -1419,75 +1624,90 @@
         </is>
       </c>
       <c r="B14">
-        <v>9.844230769230769</v>
+        <v>0.0984423076923077</v>
       </c>
       <c r="C14">
-        <v>3.833164388004581</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>0.6035046795562488</v>
+        <v>1.656987980168257</v>
       </c>
       <c r="E14">
-        <v>0.2521846310983313</v>
+        <v>0</v>
       </c>
       <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>17.893618645</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>7.822386326666667</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>25.71600497166667</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>16.58950539833333</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>8.428237891833334</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>1.336857178666667</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>25.01774329016667</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>4.23496647898634</v>
       </c>
-      <c r="P14">
-        <v>-26.68028881761394</v>
-      </c>
       <c r="Q14">
+        <v>-21.1748323949317</v>
+      </c>
+      <c r="R14">
         <v>-47.5586735590166</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>-84.69932957972681</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>0.9166666666666666</v>
       </c>
-      <c r="T14">
+      <c r="U14">
+        <v>-0.1222297743112971</v>
+      </c>
+      <c r="V14">
+        <v>0.1222297743112971</v>
+      </c>
+      <c r="W14">
         <v>-1.304113246666667</v>
       </c>
-      <c r="U14">
-        <v>-311.0684922880419</v>
-      </c>
-      <c r="V14">
+      <c r="X14">
+        <v>-478.5669112123721</v>
+      </c>
+      <c r="Y14">
         <v>-119.641727803093</v>
       </c>
-      <c r="W14">
-        <v>-428.5407167603055</v>
-      </c>
-      <c r="X14">
-        <v>-354.7940014590539</v>
+      <c r="Z14">
+        <v>-1276.178429899659</v>
+      </c>
+      <c r="AA14">
+        <v>-526.1255847713887</v>
+      </c>
+      <c r="AB14">
+        <v>-140.8165601980247</v>
+      </c>
+      <c r="AC14">
+        <v>-1360.877759479386</v>
       </c>
     </row>
     <row r="15">
@@ -1497,75 +1717,90 @@
         </is>
       </c>
       <c r="B15">
-        <v>119.2246153846154</v>
+        <v>1.192246153846154</v>
       </c>
       <c r="C15">
-        <v>50.96257335090633</v>
+        <v>158.3891344197874</v>
       </c>
       <c r="D15">
-        <v>1.231438563271949</v>
+        <v>0.8120583761344828</v>
       </c>
       <c r="E15">
-        <v>6.548533327731191</v>
+        <v>116.8822707361399</v>
       </c>
       <c r="F15">
+        <v>41.50686368364742</v>
+      </c>
+      <c r="G15">
         <v>2</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>17.72635309333333</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>7.703228096666667</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>25.42958119</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>16.12405039333333</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>8.497587742333334</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>1.317444145666667</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>24.62163813566667</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>1.071580227281821</v>
       </c>
-      <c r="P15">
-        <v>-6.750955431875472</v>
-      </c>
       <c r="Q15">
+        <v>-5.357901136409104</v>
+      </c>
+      <c r="R15">
         <v>-12.03384595237485</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>-21.43160454563642</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>1.972222222222222</v>
       </c>
-      <c r="T15">
+      <c r="U15">
+        <v>-0.1108072268780366</v>
+      </c>
+      <c r="V15">
+        <v>0.2216144537560732</v>
+      </c>
+      <c r="W15">
         <v>-1.602302699999999</v>
       </c>
-      <c r="U15">
-        <v>-376.6452388152318</v>
-      </c>
-      <c r="V15">
+      <c r="X15">
+        <v>-579.454213561895</v>
+      </c>
+      <c r="Y15">
         <v>-144.8635533904738</v>
       </c>
-      <c r="W15">
-        <v>-518.8819331042249</v>
-      </c>
-      <c r="X15">
-        <v>-337.7165114167003</v>
+      <c r="Z15">
+        <v>-1545.211236165053</v>
+      </c>
+      <c r="AA15">
+        <v>-433.0989250944825</v>
+      </c>
+      <c r="AB15">
+        <v>8.167679892904488</v>
+      </c>
+      <c r="AC15">
+        <v>-1408.253706290903</v>
       </c>
     </row>
     <row r="16">
@@ -1575,75 +1810,90 @@
         </is>
       </c>
       <c r="B16">
-        <v>134.5203846153846</v>
+        <v>1.345203846153846</v>
       </c>
       <c r="C16">
-        <v>55.37124167829312</v>
+        <v>212.9603836477988</v>
       </c>
       <c r="D16">
-        <v>1.902551130038404</v>
+        <v>0.5256100528451051</v>
       </c>
       <c r="E16">
-        <v>9.704581890356366</v>
+        <v>183.9645385698373</v>
       </c>
       <c r="F16">
+        <v>28.99584507796149</v>
+      </c>
+      <c r="G16">
         <v>2</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>18.49871817</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>7.65717139</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>26.15588956</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>16.225695985</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>9.332896422999999</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>1.2739333915</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>25.558592408</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>4.497018075011564</v>
       </c>
-      <c r="P16">
-        <v>-28.33121387257285</v>
-      </c>
       <c r="Q16">
+        <v>-22.48509037505782</v>
+      </c>
+      <c r="R16">
         <v>-50.50151298237986</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>-89.94036150023128</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>2</v>
       </c>
-      <c r="T16">
+      <c r="U16">
+        <v>-0.1108072268780366</v>
+      </c>
+      <c r="V16">
+        <v>0.2216144537560732</v>
+      </c>
+      <c r="W16">
         <v>-2.273022185000002</v>
       </c>
-      <c r="U16">
-        <v>-516.6615007903032</v>
-      </c>
-      <c r="V16">
+      <c r="X16">
+        <v>-794.8638473696973</v>
+      </c>
+      <c r="Y16">
         <v>-198.7159618424243</v>
       </c>
-      <c r="W16">
-        <v>-711.7740798579848</v>
-      </c>
-      <c r="X16">
-        <v>-511.7917720943899</v>
+      <c r="Z16">
+        <v>-2119.636926319192</v>
+      </c>
+      <c r="AA16">
+        <v>-632.4049767042784</v>
+      </c>
+      <c r="AB16">
+        <v>-8.240668569683351</v>
+      </c>
+      <c r="AC16">
+        <v>-1996.616904171625</v>
       </c>
     </row>
     <row r="17">
@@ -1653,75 +1903,90 @@
         </is>
       </c>
       <c r="B17">
-        <v>53.65576923076923</v>
+        <v>0.5365576923076923</v>
       </c>
       <c r="C17">
-        <v>21.74085737360796</v>
+        <v>102.5069644937587</v>
       </c>
       <c r="D17">
-        <v>1.279663954042972</v>
+        <v>0.7814551600368198</v>
       </c>
       <c r="E17">
-        <v>2.878506031818905</v>
+        <v>77.01034706976279</v>
       </c>
       <c r="F17">
+        <v>25.49661742399587</v>
+      </c>
+      <c r="G17">
         <v>1</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>17.38958166833333</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>7.768696846666667</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>25.158278515</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>17.84053773833333</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>8.176969806833334</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>1.254831114166667</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>26.01750754516667</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>2.39641692676325</v>
       </c>
-      <c r="P17">
-        <v>-15.09742663860848</v>
-      </c>
       <c r="Q17">
+        <v>-11.98208463381625</v>
+      </c>
+      <c r="R17">
         <v>-26.9117620875513</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>-47.928338535265</v>
       </c>
-      <c r="S17">
+      <c r="T17">
         <v>1</v>
       </c>
-      <c r="T17">
+      <c r="U17">
+        <v>-0.1222297743112971</v>
+      </c>
+      <c r="V17">
+        <v>0.1222297743112971</v>
+      </c>
+      <c r="W17">
         <v>0.4509560700000002</v>
       </c>
-      <c r="U17">
-        <v>100.9660163067785</v>
-      </c>
-      <c r="V17">
+      <c r="X17">
+        <v>155.3323327796593</v>
+      </c>
+      <c r="Y17">
         <v>38.83308319491481</v>
       </c>
-      <c r="W17">
-        <v>139.0949262597589</v>
-      </c>
-      <c r="X17">
-        <v>95.79511159283518</v>
+      <c r="Z17">
+        <v>414.2195540790913</v>
+      </c>
+      <c r="AA17">
+        <v>230.9275351858666</v>
+      </c>
+      <c r="AB17">
+        <v>129.3579630548572</v>
+      </c>
+      <c r="AC17">
+        <v>468.798180037585</v>
       </c>
     </row>
     <row r="18">
@@ -1731,75 +1996,90 @@
         </is>
       </c>
       <c r="B18">
-        <v>183.2476923076923</v>
+        <v>1.832476923076923</v>
       </c>
       <c r="C18">
-        <v>75.94011848467443</v>
+        <v>342.3109149335644</v>
       </c>
       <c r="D18">
-        <v>2.560460464897154</v>
+        <v>0.3905547512682127</v>
       </c>
       <c r="E18">
-        <v>15.93181660329086</v>
+        <v>314.361044175667</v>
       </c>
       <c r="F18">
+        <v>27.94987075789743</v>
+      </c>
+      <c r="G18">
         <v>4</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>17.72735899833333</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>7.651144068333333</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>25.37850306666667</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>17.29026594833334</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>8.751537780333333</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>1.301592840833333</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>26.04180372866667</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>3.063092334736524</v>
       </c>
-      <c r="P18">
-        <v>-19.2974817088401</v>
-      </c>
       <c r="Q18">
+        <v>-15.31546167368262</v>
+      </c>
+      <c r="R18">
         <v>-34.39852691909116</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>-61.26184669473047</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>3.5</v>
       </c>
-      <c r="T18">
+      <c r="U18">
+        <v>-0.08796213201151555</v>
+      </c>
+      <c r="V18">
+        <v>0.3518485280460622</v>
+      </c>
+      <c r="W18">
         <v>-0.4370930499999979</v>
       </c>
-      <c r="U18">
-        <v>-101.5090486726043</v>
-      </c>
-      <c r="V18">
+      <c r="X18">
+        <v>-156.1677671886219</v>
+      </c>
+      <c r="Y18">
         <v>-39.04194179715548</v>
       </c>
-      <c r="W18">
-        <v>-139.8430299251713</v>
-      </c>
-      <c r="X18">
-        <v>-59.96745710702098</v>
+      <c r="Z18">
+        <v>-416.4473791696585</v>
+      </c>
+      <c r="AA18">
+        <v>151.7446208258513</v>
+      </c>
+      <c r="AB18">
+        <v>287.9535114627263</v>
+      </c>
+      <c r="AC18">
+        <v>-135.3983109308246</v>
       </c>
     </row>
     <row r="19">
@@ -1809,75 +2089,90 @@
         </is>
       </c>
       <c r="B19">
-        <v>501.1975641025641</v>
+        <v>5.011975641025641</v>
       </c>
       <c r="C19">
-        <v>196.1880290353269</v>
+        <v>788.2401427617856</v>
       </c>
       <c r="D19">
-        <v>3.906252654340075</v>
+        <v>0.255999826045287</v>
       </c>
       <c r="E19">
-        <v>51.20076139307912</v>
+        <v>758.7831774811472</v>
       </c>
       <c r="F19">
+        <v>29.45696528063843</v>
+      </c>
+      <c r="G19">
         <v>16</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>18.94094098</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>7.475234071666667</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>26.41617505166667</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>19.76502023666666</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>7.915039723833333</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>1.243342730833333</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>27.6800599605</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>2.598609080226484</v>
       </c>
-      <c r="P19">
-        <v>-16.37123720542685</v>
-      </c>
       <c r="Q19">
+        <v>-12.99304540113242</v>
+      </c>
+      <c r="R19">
         <v>-29.18237997094342</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <v>-51.97218160452968</v>
       </c>
-      <c r="S19">
+      <c r="T19">
         <v>11.08333333333333</v>
       </c>
-      <c r="T19">
+      <c r="U19">
+        <v>0.04910843718761077</v>
+      </c>
+      <c r="V19">
+        <v>-0.7857349950017722</v>
+      </c>
+      <c r="W19">
         <v>0.8240792566666642</v>
       </c>
-      <c r="U19">
-        <v>182.81656621165</v>
-      </c>
-      <c r="V19">
+      <c r="X19">
+        <v>281.2562557102307</v>
+      </c>
+      <c r="Y19">
         <v>70.31406392755768</v>
       </c>
-      <c r="W19">
-        <v>251.8556017799879</v>
-      </c>
-      <c r="X19">
-        <v>349.8222152760334</v>
+      <c r="Z19">
+        <v>750.0166818939487</v>
+      </c>
+      <c r="AA19">
+        <v>1040.314018501073</v>
+      </c>
+      <c r="AB19">
+        <v>845.5611612882109</v>
+      </c>
+      <c r="AC19">
+        <v>1486.284643051205</v>
       </c>
     </row>
     <row r="20">
@@ -1887,4833 +2182,5391 @@
         </is>
       </c>
       <c r="B20">
-        <v>101.4121794871795</v>
+        <v>1.014121794871795</v>
       </c>
       <c r="C20">
-        <v>41.11801074612283</v>
+        <v>200.3435797129811</v>
       </c>
       <c r="D20">
-        <v>1.577221861175118</v>
+        <v>0.6340262106530431</v>
       </c>
       <c r="E20">
-        <v>6.35076065273292</v>
+        <v>163.5794041455828</v>
       </c>
       <c r="F20">
+        <v>36.7641755673983</v>
+      </c>
+      <c r="G20">
         <v>4</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>17.24828480833333</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>9.214412571666667</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>26.46269738</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>17.63945969833333</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>8.806338972999999</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>1.410547525</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>26.44579867133333</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>0.8470214289750483</v>
       </c>
-      <c r="P20">
-        <v>-5.336235002542804</v>
-      </c>
       <c r="Q20">
+        <v>-4.235107144875242</v>
+      </c>
+      <c r="R20">
         <v>-9.512050647389792</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>-16.94042857950097</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <v>3.638888888888889</v>
       </c>
-      <c r="T20">
+      <c r="U20">
+        <v>-0.08796213201151555</v>
+      </c>
+      <c r="V20">
+        <v>0.3518485280460622</v>
+      </c>
+      <c r="W20">
         <v>0.3911748899999985</v>
       </c>
-      <c r="U20">
-        <v>98.44970016032879</v>
-      </c>
-      <c r="V20">
+      <c r="X20">
+        <v>151.4610771697366</v>
+      </c>
+      <c r="Y20">
         <v>37.86526929243415</v>
       </c>
-      <c r="W20">
-        <v>135.6283459029268</v>
-      </c>
-      <c r="X20">
-        <v>130.0556602590618</v>
+      <c r="Z20">
+        <v>403.8962057859642</v>
+      </c>
+      <c r="AA20">
+        <v>342.2926062353279</v>
+      </c>
+      <c r="AB20">
+        <v>233.97374186054</v>
+      </c>
+      <c r="AC20">
+        <v>587.2993569194443</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B1A22</t>
+          <t>B2A01</t>
         </is>
       </c>
       <c r="B21">
-        <v>580.2130641025641</v>
+        <v>3.794884615384615</v>
       </c>
       <c r="C21">
-        <v>227.0408212088765</v>
+        <v>649.2977893081762</v>
       </c>
       <c r="D21">
-        <v>4.982846028437519</v>
+        <v>0.1988480115427947</v>
       </c>
       <c r="E21">
-        <v>66.04673885975737</v>
+        <v>634.3647873403449</v>
       </c>
       <c r="F21">
-        <v>60</v>
+        <v>14.93300196783127</v>
       </c>
       <c r="G21">
-        <v>19.15098685333333</v>
+        <v>4</v>
       </c>
       <c r="H21">
-        <v>9.301857549999999</v>
+        <v>18.25023845333333</v>
       </c>
       <c r="I21">
-        <v>28.45284440333333</v>
+        <v>7.428767183333333</v>
       </c>
       <c r="J21">
-        <v>21.81097294</v>
+        <v>25.67900563666667</v>
       </c>
       <c r="K21">
-        <v>9.169695069499999</v>
+        <v>19.59409039666667</v>
       </c>
       <c r="L21">
-        <v>1.2817225465</v>
+        <v>7.509411629000001</v>
       </c>
       <c r="M21">
-        <v>30.9806680095</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="O21">
-        <v>0.9806401652694139</v>
+        <v>1.295684132333333</v>
+      </c>
+      <c r="N21">
+        <v>27.10350202566666</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
       </c>
       <c r="P21">
-        <v>-6.178033041197307</v>
+        <v>2.359231208098899</v>
       </c>
       <c r="Q21">
-        <v>-11.01258905597552</v>
+        <v>-11.79615604049449</v>
       </c>
       <c r="R21">
-        <v>-19.61280330538828</v>
+        <v>-26.49416646695063</v>
       </c>
       <c r="S21">
-        <v>29.55555555555556</v>
+        <v>-47.18462416197798</v>
       </c>
       <c r="T21">
-        <v>2.659986086666667</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="U21">
-        <v>608.3157967967197</v>
+        <v>-0.08796213201151555</v>
       </c>
       <c r="V21">
-        <v>233.9676141525845</v>
+        <v>0.3518485280460622</v>
       </c>
       <c r="W21">
-        <v>838.0407982126707</v>
+        <v>1.343851943333334</v>
       </c>
       <c r="X21">
-        <v>824.3440289496208</v>
+        <v>477.9614969555454</v>
+      </c>
+      <c r="Y21">
+        <v>119.4903742388864</v>
+      </c>
+      <c r="Z21">
+        <v>1274.563991881455</v>
+      </c>
+      <c r="AA21">
+        <v>1100.765119796771</v>
+      </c>
+      <c r="AB21">
+        <v>756.9920075065681</v>
+      </c>
+      <c r="AC21">
+        <v>1876.677157027653</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B2A01</t>
+          <t>B2A02</t>
         </is>
       </c>
       <c r="B22">
-        <v>379.4884615384615</v>
+        <v>1.119438461538462</v>
       </c>
       <c r="C22">
-        <v>149.678736219569</v>
+        <v>188.0508670360111</v>
       </c>
       <c r="D22">
-        <v>5.028966557127412</v>
+        <v>0.6962812337537454</v>
       </c>
       <c r="E22">
-        <v>43.71142997862479</v>
+        <v>148.3451112776125</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>39.70575575839862</v>
       </c>
       <c r="G22">
-        <v>18.25023845333333</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>7.428767183333333</v>
+        <v>15.62478933666667</v>
       </c>
       <c r="I22">
-        <v>25.67900563666667</v>
+        <v>9.755520225</v>
       </c>
       <c r="J22">
-        <v>19.59409039666667</v>
+        <v>25.38030956166666</v>
       </c>
       <c r="K22">
-        <v>7.509411629000001</v>
+        <v>16.15549779666667</v>
       </c>
       <c r="L22">
-        <v>1.295684132333333</v>
+        <v>9.634761951333333</v>
       </c>
       <c r="M22">
-        <v>27.10350202566666</v>
-      </c>
-      <c r="N22" t="inlineStr">
+        <v>1.422238535666667</v>
+      </c>
+      <c r="N22">
+        <v>25.790259748</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O22">
-        <v>2.359231208098899</v>
-      </c>
       <c r="P22">
-        <v>-14.86315661102306</v>
+        <v>0.6724456699305441</v>
       </c>
       <c r="Q22">
-        <v>-26.49416646695063</v>
+        <v>-3.362228349652721</v>
       </c>
       <c r="R22">
-        <v>-47.18462416197798</v>
+        <v>-7.551564873320011</v>
       </c>
       <c r="S22">
-        <v>3.333333333333333</v>
+        <v>-13.44891339861088</v>
       </c>
       <c r="T22">
-        <v>1.343851943333334</v>
+        <v>1.972222222222222</v>
       </c>
       <c r="U22">
-        <v>310.6749730211045</v>
+        <v>-0.1108072268780366</v>
       </c>
       <c r="V22">
-        <v>119.4903742388864</v>
+        <v>0.2216144537560732</v>
       </c>
       <c r="W22">
-        <v>427.9985884737924</v>
+        <v>0.5307084599999996</v>
       </c>
       <c r="X22">
-        <v>433.8595427737229</v>
+        <v>207.1909593179774</v>
+      </c>
+      <c r="Y22">
+        <v>51.79773982949435</v>
+      </c>
+      <c r="Z22">
+        <v>552.5092248479397</v>
+      </c>
+      <c r="AA22">
+        <v>387.6902614806685</v>
+      </c>
+      <c r="AB22">
+        <v>236.4863785158527</v>
+      </c>
+      <c r="AC22">
+        <v>727.1111784853399</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B2A02</t>
+          <t>B2A04</t>
         </is>
       </c>
       <c r="B23">
-        <v>111.9438461538462</v>
+        <v>1.18075</v>
       </c>
       <c r="C23">
-        <v>44.73364597723211</v>
+        <v>181.9574524469067</v>
       </c>
       <c r="D23">
-        <v>1.436201281210562</v>
+        <v>0.9416169439948382</v>
       </c>
       <c r="E23">
-        <v>6.460024410778119</v>
+        <v>124.324317532748</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>57.63313491415866</v>
       </c>
       <c r="G23">
-        <v>15.62478933666667</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>9.755520225</v>
+        <v>15.747574295</v>
       </c>
       <c r="I23">
-        <v>25.38030956166666</v>
+        <v>9.404695233333333</v>
       </c>
       <c r="J23">
-        <v>16.15549779666667</v>
+        <v>25.15226952833333</v>
       </c>
       <c r="K23">
-        <v>9.634761951333333</v>
+        <v>14.5059828</v>
       </c>
       <c r="L23">
-        <v>1.422238535666667</v>
+        <v>9.411386414333334</v>
       </c>
       <c r="M23">
-        <v>25.790259748</v>
-      </c>
-      <c r="N23" t="inlineStr">
+        <v>1.447401226833333</v>
+      </c>
+      <c r="N23">
+        <v>23.91736921433333</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O23">
-        <v>0.6724456699305441</v>
-      </c>
       <c r="P23">
-        <v>-4.236407720562428</v>
+        <v>6.174000995376301</v>
       </c>
       <c r="Q23">
-        <v>-7.551564873320011</v>
+        <v>-30.8700049768815</v>
       </c>
       <c r="R23">
-        <v>-13.44891339861088</v>
+        <v>-69.33403117807586</v>
       </c>
       <c r="S23">
-        <v>1.972222222222222</v>
+        <v>-123.480019907526</v>
       </c>
       <c r="T23">
-        <v>0.5307084599999996</v>
+        <v>1</v>
       </c>
       <c r="U23">
-        <v>134.6741235566853</v>
+        <v>-0.1222297743112971</v>
       </c>
       <c r="V23">
-        <v>51.79773982949435</v>
+        <v>0.1222297743112971</v>
       </c>
       <c r="W23">
-        <v>185.5325977039381</v>
+        <v>-1.241591495</v>
       </c>
       <c r="X23">
-        <v>171.8562046605974</v>
+        <v>-493.2987490728845</v>
+      </c>
+      <c r="Y23">
+        <v>-123.3246872682211</v>
+      </c>
+      <c r="Z23">
+        <v>-1315.463330861025</v>
+      </c>
+      <c r="AA23">
+        <v>-380.6753278040537</v>
+      </c>
+      <c r="AB23">
+        <v>27.76276020180407</v>
+      </c>
+      <c r="AC23">
+        <v>-1256.985898321645</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B2A03</t>
+          <t>B2A05</t>
         </is>
       </c>
       <c r="B24">
-        <v>616.7175512820513</v>
+        <v>0.622098717948718</v>
       </c>
       <c r="C24">
-        <v>242.624219954711</v>
+        <v>70.78984484512252</v>
       </c>
       <c r="D24">
-        <v>4.993074059988925</v>
+        <v>1.168252649493067</v>
       </c>
       <c r="E24">
-        <v>70.64114681055177</v>
+        <v>42.2369685131489</v>
       </c>
       <c r="F24">
-        <v>60</v>
+        <v>28.55287633197361</v>
       </c>
       <c r="G24">
-        <v>17.90186749166667</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>8.436962761666667</v>
+        <v>18.33970316666667</v>
       </c>
       <c r="I24">
-        <v>26.33883025333333</v>
+        <v>10.95371604</v>
       </c>
       <c r="J24">
-        <v>18.00963822</v>
+        <v>29.29341920666667</v>
       </c>
       <c r="K24">
-        <v>8.657248975</v>
+        <v>17.06013133166667</v>
       </c>
       <c r="L24">
-        <v>1.379606870166667</v>
+        <v>11.02718368683333</v>
       </c>
       <c r="M24">
-        <v>26.666887195</v>
-      </c>
-      <c r="N24" t="inlineStr">
+        <v>1.4471556175</v>
+      </c>
+      <c r="N24">
+        <v>28.0873150185</v>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O24">
-        <v>1.637969963880097</v>
-      </c>
       <c r="P24">
-        <v>-10.31921077244461</v>
+        <v>2.075840817204807</v>
       </c>
       <c r="Q24">
-        <v>-18.39440269437349</v>
+        <v>-10.37920408602404</v>
       </c>
       <c r="R24">
-        <v>-32.75939927760194</v>
+        <v>-23.31169237720999</v>
       </c>
       <c r="S24">
-        <v>31.72222222222222</v>
+        <v>-41.51681634409614</v>
       </c>
       <c r="T24">
-        <v>0.1077707283333318</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="U24">
-        <v>26.52844974946723</v>
+        <v>-0.1222297743112971</v>
       </c>
       <c r="V24">
-        <v>10.20324990364124</v>
+        <v>0.1222297743112971</v>
       </c>
       <c r="W24">
-        <v>36.54668072152244</v>
+        <v>-1.279571834999999</v>
       </c>
       <c r="X24">
-        <v>250.7582670098047</v>
+        <v>-508.3025116946262</v>
+      </c>
+      <c r="Y24">
+        <v>-127.0756279236565</v>
+      </c>
+      <c r="Z24">
+        <v>-1355.473364519003</v>
+      </c>
+      <c r="AA24">
+        <v>-460.8243592267137</v>
+      </c>
+      <c r="AB24">
+        <v>-66.66498716455807</v>
+      </c>
+      <c r="AC24">
+        <v>-1326.200336017977</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B2A04</t>
+          <t>B2A06</t>
         </is>
       </c>
       <c r="B25">
-        <v>118.075</v>
+        <v>2.295128205128205</v>
       </c>
       <c r="C25">
-        <v>47.90461010685469</v>
+        <v>332.1838569199457</v>
       </c>
       <c r="D25">
-        <v>1.062002979425445</v>
+        <v>0.4442755243413384</v>
       </c>
       <c r="E25">
-        <v>5.457296893052952</v>
+        <v>298.1529852371674</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>34.0308716827783</v>
       </c>
       <c r="G25">
-        <v>15.747574295</v>
+        <v>4</v>
       </c>
       <c r="H25">
-        <v>9.404695233333333</v>
+        <v>19.853450675</v>
       </c>
       <c r="I25">
-        <v>25.15226952833333</v>
+        <v>12.68932163666667</v>
       </c>
       <c r="J25">
-        <v>14.5059828</v>
+        <v>32.54277231166667</v>
       </c>
       <c r="K25">
-        <v>9.411386414333334</v>
+        <v>19.40672484</v>
       </c>
       <c r="L25">
-        <v>1.447401226833333</v>
+        <v>13.72259501166667</v>
       </c>
       <c r="M25">
-        <v>23.91736921433333</v>
-      </c>
-      <c r="N25" t="inlineStr">
+        <v>1.368905493</v>
+      </c>
+      <c r="N25">
+        <v>33.12931985166666</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O25">
-        <v>6.174000995376301</v>
-      </c>
       <c r="P25">
-        <v>-38.89620627087069</v>
+        <v>2.268599779202153</v>
       </c>
       <c r="Q25">
-        <v>-69.33403117807586</v>
+        <v>-11.34299889601077</v>
       </c>
       <c r="R25">
-        <v>-123.480019907526</v>
+        <v>-25.47637552044019</v>
       </c>
       <c r="S25">
-        <v>1</v>
+        <v>-45.37199558404307</v>
       </c>
       <c r="T25">
-        <v>-1.241591495</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="U25">
-        <v>-320.6441868973749</v>
+        <v>-0.08796213201151555</v>
       </c>
       <c r="V25">
-        <v>-123.3246872682211</v>
+        <v>0.3518485280460622</v>
       </c>
       <c r="W25">
-        <v>-441.7325865031323</v>
+        <v>-0.4467258350000023</v>
       </c>
       <c r="X25">
-        <v>-342.0736079685961</v>
+        <v>-167.8637358593433</v>
+      </c>
+      <c r="Y25">
+        <v>-41.96593396483583</v>
+      </c>
+      <c r="Z25">
+        <v>-447.6366289582488</v>
+      </c>
+      <c r="AA25">
+        <v>138.8437455401622</v>
+      </c>
+      <c r="AB25">
+        <v>278.8749240590991</v>
+      </c>
+      <c r="AC25">
+        <v>-160.8247676223462</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B2A05</t>
+          <t>B2A08</t>
         </is>
       </c>
       <c r="B26">
-        <v>62.20987179487179</v>
+        <v>1.301305</v>
       </c>
       <c r="C26">
-        <v>24.86147684920685</v>
+        <v>169.4000146015853</v>
       </c>
       <c r="D26">
-        <v>0.8559792271251631</v>
+        <v>0.9168040338772964</v>
       </c>
       <c r="E26">
-        <v>2.339335300052007</v>
+        <v>117.4756223535281</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>51.92439224805725</v>
       </c>
       <c r="G26">
-        <v>18.33970316666667</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>10.95371604</v>
+        <v>20.68569447666667</v>
       </c>
       <c r="I26">
-        <v>29.29341920666667</v>
+        <v>12.026124995</v>
       </c>
       <c r="J26">
-        <v>17.06013133166667</v>
+        <v>32.71181947166667</v>
       </c>
       <c r="K26">
-        <v>11.02718368683333</v>
+        <v>20.44729365833333</v>
       </c>
       <c r="L26">
-        <v>1.4471556175</v>
+        <v>12.14286722666667</v>
       </c>
       <c r="M26">
-        <v>28.0873150185</v>
-      </c>
-      <c r="N26" t="inlineStr">
+        <v>1.247915171166667</v>
+      </c>
+      <c r="N26">
+        <v>32.590160885</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O26">
-        <v>2.075840817204807</v>
-      </c>
       <c r="P26">
-        <v>-13.07779714839029</v>
+        <v>0.7360342021259476</v>
       </c>
       <c r="Q26">
-        <v>-23.31169237720999</v>
+        <v>-3.680171010629738</v>
       </c>
       <c r="R26">
-        <v>-41.51681634409614</v>
+        <v>-8.265664089874392</v>
       </c>
       <c r="S26">
-        <v>0.9722222222222222</v>
+        <v>-14.72068404251895</v>
       </c>
       <c r="T26">
-        <v>-1.279571834999999</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="U26">
-        <v>-330.396632601507</v>
+        <v>-0.1108072268780366</v>
       </c>
       <c r="V26">
-        <v>-127.0756279236565</v>
+        <v>0.2216144537560732</v>
       </c>
       <c r="W26">
-        <v>-455.1679558054812</v>
+        <v>-0.2384008183333357</v>
       </c>
       <c r="X26">
-        <v>-328.8468481295101</v>
+        <v>-81.66484745558911</v>
+      </c>
+      <c r="Y26">
+        <v>-20.41621186389728</v>
+      </c>
+      <c r="Z26">
+        <v>-217.7729265482376</v>
+      </c>
+      <c r="AA26">
+        <v>79.46950305612179</v>
+      </c>
+      <c r="AB26">
+        <v>145.3036317270583</v>
+      </c>
+      <c r="AC26">
+        <v>-63.09359598917126</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B2A06</t>
+          <t>B2A09</t>
         </is>
       </c>
       <c r="B27">
-        <v>229.5128205128205</v>
+        <v>1.461408974358974</v>
       </c>
       <c r="C27">
-        <v>93.73994764502967</v>
+        <v>184.8255126199415</v>
       </c>
       <c r="D27">
-        <v>2.25085548316566</v>
+        <v>0.6421691663939039</v>
       </c>
       <c r="E27">
-        <v>18.24257241244788</v>
+        <v>150.2417921757539</v>
       </c>
       <c r="F27">
+        <v>34.58372044418763</v>
+      </c>
+      <c r="G27">
         <v>4</v>
       </c>
-      <c r="G27">
-        <v>19.853450675</v>
-      </c>
       <c r="H27">
-        <v>12.68932163666667</v>
+        <v>22.35290135166667</v>
       </c>
       <c r="I27">
-        <v>32.54277231166667</v>
+        <v>12.50052412166667</v>
       </c>
       <c r="J27">
-        <v>19.40672484</v>
+        <v>34.85342547333333</v>
       </c>
       <c r="K27">
-        <v>13.72259501166667</v>
+        <v>20.36209860166667</v>
       </c>
       <c r="L27">
-        <v>1.368905493</v>
+        <v>13.86795943166667</v>
       </c>
       <c r="M27">
-        <v>33.12931985166666</v>
-      </c>
-      <c r="N27" t="inlineStr">
+        <v>1.302890749166667</v>
+      </c>
+      <c r="N27">
+        <v>34.23005803333334</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O27">
-        <v>2.268599779202153</v>
-      </c>
       <c r="P27">
-        <v>-14.29217860897357</v>
+        <v>0.6936343066418474</v>
       </c>
       <c r="Q27">
-        <v>-25.47637552044019</v>
+        <v>-3.468171533209237</v>
       </c>
       <c r="R27">
-        <v>-45.37199558404307</v>
+        <v>-7.789513263587947</v>
       </c>
       <c r="S27">
-        <v>3.666666666666667</v>
+        <v>-13.87268613283695</v>
       </c>
       <c r="T27">
-        <v>-0.4467258350000023</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="U27">
-        <v>-109.1114283085731</v>
+        <v>-0.08796213201151555</v>
       </c>
       <c r="V27">
-        <v>-41.96593396483583</v>
+        <v>0.3518485280460622</v>
       </c>
       <c r="W27">
-        <v>-150.3163800041799</v>
+        <v>-1.99080275</v>
       </c>
       <c r="X27">
-        <v>-40.84785618398365</v>
+        <v>-711.9976845142087</v>
+      </c>
+      <c r="Y27">
+        <v>-177.9994211285522</v>
+      </c>
+      <c r="Z27">
+        <v>-1898.66049203789</v>
+      </c>
+      <c r="AA27">
+        <v>-534.9616851578551</v>
+      </c>
+      <c r="AB27">
+        <v>3.357919958180133</v>
+      </c>
+      <c r="AC27">
+        <v>-1727.707665550785</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B2A08</t>
+          <t>B2A10</t>
         </is>
       </c>
       <c r="B28">
-        <v>130.1305</v>
+        <v>3.374911538461538</v>
       </c>
       <c r="C28">
-        <v>53.26814475341833</v>
+        <v>520.0959335836462</v>
       </c>
       <c r="D28">
-        <v>1.090745637070177</v>
+        <v>0.3374636987242213</v>
       </c>
       <c r="E28">
-        <v>6.205393694571206</v>
+        <v>487.5060454120572</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>32.589888171589</v>
       </c>
       <c r="G28">
-        <v>20.68569447666667</v>
+        <v>16</v>
       </c>
       <c r="H28">
-        <v>12.026124995</v>
+        <v>22.281533595</v>
       </c>
       <c r="I28">
-        <v>32.71181947166667</v>
+        <v>12.30114996333333</v>
       </c>
       <c r="J28">
-        <v>20.44729365833333</v>
+        <v>34.58268355833333</v>
       </c>
       <c r="K28">
-        <v>12.14286722666667</v>
+        <v>23.50365367666667</v>
       </c>
       <c r="L28">
-        <v>1.247915171166667</v>
+        <v>13.197827925</v>
       </c>
       <c r="M28">
-        <v>32.590160885</v>
-      </c>
-      <c r="N28" t="inlineStr">
+        <v>1.2313447075</v>
+      </c>
+      <c r="N28">
+        <v>36.70148160166666</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O28">
-        <v>0.7360342021259476</v>
-      </c>
       <c r="P28">
-        <v>-4.63701547339347</v>
+        <v>0.7101404810624976</v>
       </c>
       <c r="Q28">
-        <v>-8.265664089874392</v>
+        <v>-3.550702405312488</v>
       </c>
       <c r="R28">
-        <v>-14.72068404251895</v>
+        <v>-7.974877602331849</v>
       </c>
       <c r="S28">
-        <v>1.555555555555556</v>
+        <v>-14.20280962124995</v>
       </c>
       <c r="T28">
-        <v>-0.2384008183333357</v>
+        <v>11.36111111111111</v>
       </c>
       <c r="U28">
-        <v>-53.08215084613292</v>
+        <v>0.04910843718761077</v>
       </c>
       <c r="V28">
-        <v>-20.41621186389728</v>
+        <v>-0.7857349950017722</v>
       </c>
       <c r="W28">
-        <v>-73.12814873489819</v>
+        <v>1.222120081666667</v>
       </c>
       <c r="X28">
-        <v>-8.079670182588984</v>
+        <v>413.0816254374276</v>
+      </c>
+      <c r="Y28">
+        <v>103.2704063593569</v>
+      </c>
+      <c r="Z28">
+        <v>1101.551001166473</v>
+      </c>
+      <c r="AA28">
+        <v>925.202681418742</v>
+      </c>
+      <c r="AB28">
+        <v>619.8156375376907</v>
+      </c>
+      <c r="AC28">
+        <v>1607.44412512887</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B2A09</t>
+          <t>B2A12</t>
         </is>
       </c>
       <c r="B29">
-        <v>146.1408974358974</v>
+        <v>3.343515</v>
       </c>
       <c r="C29">
-        <v>58.48647982432736</v>
+        <v>573.3902843137255</v>
       </c>
       <c r="D29">
-        <v>1.557222072208001</v>
+        <v>0.33882547806985</v>
       </c>
       <c r="E29">
-        <v>8.952481210018838</v>
+        <v>537.1944556106987</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>36.19582870302679</v>
       </c>
       <c r="G29">
-        <v>22.35290135166667</v>
+        <v>8</v>
       </c>
       <c r="H29">
-        <v>12.50052412166667</v>
+        <v>18.41433809833334</v>
       </c>
       <c r="I29">
-        <v>34.85342547333333</v>
+        <v>8.493144115</v>
       </c>
       <c r="J29">
-        <v>20.36209860166667</v>
+        <v>26.90748221333333</v>
       </c>
       <c r="K29">
-        <v>13.86795943166667</v>
+        <v>18.23542061666667</v>
       </c>
       <c r="L29">
-        <v>1.302890749166667</v>
+        <v>9.010506192166666</v>
       </c>
       <c r="M29">
-        <v>34.23005803333334</v>
-      </c>
-      <c r="N29" t="inlineStr">
+        <v>1.383368769</v>
+      </c>
+      <c r="N29">
+        <v>27.24592680883333</v>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O29">
-        <v>0.6936343066418474</v>
-      </c>
       <c r="P29">
-        <v>-4.369896131843639</v>
+        <v>0.9077257805083475</v>
       </c>
       <c r="Q29">
-        <v>-7.789513263587947</v>
+        <v>-4.538628902541737</v>
       </c>
       <c r="R29">
-        <v>-13.87268613283695</v>
+        <v>-10.19376051510874</v>
       </c>
       <c r="S29">
-        <v>3.888888888888889</v>
+        <v>-18.15451561016695</v>
       </c>
       <c r="T29">
-        <v>-1.99080275</v>
+        <v>5.694444444444445</v>
       </c>
       <c r="U29">
-        <v>-462.7984949342356</v>
+        <v>-0.04227194227847345</v>
       </c>
       <c r="V29">
-        <v>-177.9994211285522</v>
+        <v>0.3381755382277876</v>
       </c>
       <c r="W29">
-        <v>-637.5701932263233</v>
+        <v>-0.1789174816666694</v>
       </c>
       <c r="X29">
-        <v>-412.1015283734962</v>
+        <v>-67.94118107241225</v>
+      </c>
+      <c r="Y29">
+        <v>-16.98529526810306</v>
+      </c>
+      <c r="Z29">
+        <v>-181.176482859766</v>
+      </c>
+      <c r="AA29">
+        <v>495.2553427262045</v>
+      </c>
+      <c r="AB29">
+        <v>551.8663601430807</v>
+      </c>
+      <c r="AC29">
+        <v>374.0592858437925</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B2A10</t>
+          <t>B2A13</t>
         </is>
       </c>
       <c r="B30">
-        <v>337.4911538461538</v>
+        <v>0.8400628205128206</v>
       </c>
       <c r="C30">
-        <v>128.2161296176161</v>
+        <v>136.0551269764216</v>
       </c>
       <c r="D30">
-        <v>2.963281691573025</v>
+        <v>0.5785851335086335</v>
       </c>
       <c r="E30">
-        <v>29.14410918623349</v>
+        <v>114.4123363793962</v>
       </c>
       <c r="F30">
-        <v>16</v>
+        <v>21.64279059702548</v>
       </c>
       <c r="G30">
-        <v>22.281533595</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>12.30114996333333</v>
+        <v>14.78553080333333</v>
       </c>
       <c r="I30">
-        <v>34.58268355833333</v>
+        <v>14.93936280333333</v>
       </c>
       <c r="J30">
-        <v>23.50365367666667</v>
+        <v>29.72489360666667</v>
       </c>
       <c r="K30">
-        <v>13.197827925</v>
+        <v>13.97646859166667</v>
       </c>
       <c r="L30">
-        <v>1.2313447075</v>
+        <v>16.79281487833333</v>
       </c>
       <c r="M30">
-        <v>36.70148160166666</v>
-      </c>
-      <c r="N30" t="inlineStr">
+        <v>1.482308474333333</v>
+      </c>
+      <c r="N30">
+        <v>30.76928347</v>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O30">
-        <v>0.7101404810624976</v>
-      </c>
       <c r="P30">
-        <v>-4.473885030693735</v>
+        <v>7.358028853615001</v>
       </c>
       <c r="Q30">
-        <v>-7.974877602331849</v>
+        <v>-36.790144268075</v>
       </c>
       <c r="R30">
-        <v>-14.20280962124995</v>
+        <v>-82.63066402609647</v>
       </c>
       <c r="S30">
-        <v>11.36111111111111</v>
+        <v>-147.1605770723</v>
       </c>
       <c r="T30">
-        <v>1.222120081666667</v>
+        <v>1</v>
       </c>
       <c r="U30">
-        <v>268.5030565343279</v>
+        <v>-0.1222297743112971</v>
       </c>
       <c r="V30">
-        <v>103.2704063593569</v>
+        <v>0.1222297743112971</v>
       </c>
       <c r="W30">
-        <v>369.9008261917018</v>
+        <v>-0.8090622116666673</v>
       </c>
       <c r="X30">
-        <v>388.7443085496121</v>
+        <v>-329.2022975831935</v>
+      </c>
+      <c r="Y30">
+        <v>-82.30057439579838</v>
+      </c>
+      <c r="Z30">
+        <v>-877.8727935551827</v>
+      </c>
+      <c r="AA30">
+        <v>-275.7778346328683</v>
+      </c>
+      <c r="AB30">
+        <v>16.96440831254824</v>
+      </c>
+      <c r="AC30">
+        <v>-888.9782436510611</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B2A12</t>
+          <t>B2A14</t>
         </is>
       </c>
       <c r="B31">
-        <v>334.3515</v>
+        <v>2.662105897435898</v>
       </c>
       <c r="C31">
-        <v>128.1403998222181</v>
+        <v>452.5040944540729</v>
       </c>
       <c r="D31">
-        <v>2.951371914817594</v>
+        <v>0.4161076199754164</v>
       </c>
       <c r="E31">
-        <v>29.06460649688565</v>
+        <v>411.1604894627204</v>
       </c>
       <c r="F31">
+        <v>41.34360499135244</v>
+      </c>
+      <c r="G31">
         <v>8</v>
       </c>
-      <c r="G31">
-        <v>18.41433809833334</v>
-      </c>
       <c r="H31">
-        <v>8.493144115</v>
+        <v>18.24266179833333</v>
       </c>
       <c r="I31">
-        <v>26.90748221333333</v>
+        <v>9.758735895000001</v>
       </c>
       <c r="J31">
-        <v>18.23542061666667</v>
+        <v>28.00139769333333</v>
       </c>
       <c r="K31">
-        <v>9.010506192166666</v>
+        <v>18.806023575</v>
       </c>
       <c r="L31">
-        <v>1.383368769</v>
+        <v>10.669294244</v>
       </c>
       <c r="M31">
-        <v>27.24592680883333</v>
-      </c>
-      <c r="N31" t="inlineStr">
+        <v>1.342777728666667</v>
+      </c>
+      <c r="N31">
+        <v>29.475317819</v>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O31">
-        <v>0.9077257805083475</v>
-      </c>
       <c r="P31">
-        <v>-5.71867241720259</v>
+        <v>1.844119286466969</v>
       </c>
       <c r="Q31">
-        <v>-10.19376051510874</v>
+        <v>-9.220596432334847</v>
       </c>
       <c r="R31">
-        <v>-18.15451561016695</v>
+        <v>-20.70945958702407</v>
       </c>
       <c r="S31">
-        <v>5.694444444444445</v>
+        <v>-36.88238572933939</v>
       </c>
       <c r="T31">
-        <v>-0.1789174816666694</v>
+        <v>5.861111111111111</v>
       </c>
       <c r="U31">
-        <v>-44.16176769706797</v>
+        <v>-0.04227194227847345</v>
       </c>
       <c r="V31">
-        <v>-16.98529526810306</v>
+        <v>0.3381755382277876</v>
       </c>
       <c r="W31">
-        <v>-60.83906294430943</v>
+        <v>0.5633617766666674</v>
       </c>
       <c r="X31">
-        <v>73.78487161004144</v>
+        <v>207.6509180713285</v>
+      </c>
+      <c r="Y31">
+        <v>51.91272951783213</v>
+      </c>
+      <c r="Z31">
+        <v>553.7357815235428</v>
+      </c>
+      <c r="AA31">
+        <v>639.4455529383773</v>
+      </c>
+      <c r="AB31">
+        <v>495.1962275395701</v>
+      </c>
+      <c r="AC31">
+        <v>969.3574902482762</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B2A13</t>
+          <t>B2A15</t>
         </is>
       </c>
       <c r="B32">
-        <v>84.00628205128206</v>
+        <v>2.048405128205128</v>
       </c>
       <c r="C32">
-        <v>32.23490471586838</v>
+        <v>191.0864384748701</v>
       </c>
       <c r="D32">
-        <v>1.728354121261013</v>
+        <v>1.402563817094508</v>
       </c>
       <c r="E32">
-        <v>5.302511200470931</v>
+        <v>99.49999711860985</v>
       </c>
       <c r="F32">
+        <v>91.5864413562602</v>
+      </c>
+      <c r="G32">
         <v>1</v>
       </c>
-      <c r="G32">
-        <v>14.78553080333333</v>
-      </c>
       <c r="H32">
-        <v>14.93936280333333</v>
+        <v>17.26795337666667</v>
       </c>
       <c r="I32">
-        <v>29.72489360666667</v>
+        <v>10.94251334666667</v>
       </c>
       <c r="J32">
-        <v>13.97646859166667</v>
+        <v>28.21046672333333</v>
       </c>
       <c r="K32">
-        <v>16.79281487833333</v>
+        <v>17.420768235</v>
       </c>
       <c r="L32">
-        <v>1.482308474333333</v>
+        <v>11.58500638166667</v>
       </c>
       <c r="M32">
-        <v>30.76928347</v>
-      </c>
-      <c r="N32" t="inlineStr">
+        <v>1.4339126615</v>
+      </c>
+      <c r="N32">
+        <v>29.00577461666667</v>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O32">
-        <v>7.358028853615001</v>
-      </c>
       <c r="P32">
-        <v>-46.3555817777745</v>
+        <v>4.45829362716574</v>
       </c>
       <c r="Q32">
-        <v>-82.63066402609647</v>
+        <v>-22.2914681358287</v>
       </c>
       <c r="R32">
-        <v>-147.1605770723</v>
+        <v>-50.06663743307126</v>
       </c>
       <c r="S32">
-        <v>1</v>
+        <v>-89.1658725433148</v>
       </c>
       <c r="T32">
-        <v>-0.8090622116666673</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="U32">
-        <v>-213.9814934290758</v>
+        <v>-0.1222297743112971</v>
       </c>
       <c r="V32">
-        <v>-82.30057439579838</v>
+        <v>0.1222297743112971</v>
       </c>
       <c r="W32">
-        <v>-294.7896840758303</v>
+        <v>0.1528148583333326</v>
       </c>
       <c r="X32">
-        <v>-264.3772527393039</v>
+        <v>60.14930748299623</v>
+      </c>
+      <c r="Y32">
+        <v>15.03732687074906</v>
+      </c>
+      <c r="Z32">
+        <v>160.3981532879899</v>
+      </c>
+      <c r="AA32">
+        <v>201.169108524795</v>
+      </c>
+      <c r="AB32">
+        <v>183.8322972097904</v>
+      </c>
+      <c r="AC32">
+        <v>262.3187192195452</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B2A14</t>
+          <t>B2A16</t>
         </is>
       </c>
       <c r="B33">
-        <v>266.2105897435898</v>
+        <v>5.096371538461539</v>
       </c>
       <c r="C33">
-        <v>100.6533553700835</v>
+        <v>953.4614335302806</v>
       </c>
       <c r="D33">
-        <v>2.403224435205201</v>
+        <v>0.3372533115069363</v>
       </c>
       <c r="E33">
-        <v>20.36140204929067</v>
+        <v>893.7846425361907</v>
       </c>
       <c r="F33">
-        <v>8</v>
+        <v>59.67679099408986</v>
       </c>
       <c r="G33">
-        <v>18.24266179833333</v>
+        <v>4</v>
       </c>
       <c r="H33">
-        <v>9.758735895000001</v>
+        <v>20.72395750666667</v>
       </c>
       <c r="I33">
-        <v>28.00139769333333</v>
+        <v>12.162037295</v>
       </c>
       <c r="J33">
-        <v>18.806023575</v>
+        <v>32.88599480166667</v>
       </c>
       <c r="K33">
-        <v>10.669294244</v>
+        <v>20.34924550333333</v>
       </c>
       <c r="L33">
-        <v>1.342777728666667</v>
+        <v>13.3018109</v>
       </c>
       <c r="M33">
-        <v>29.475317819</v>
-      </c>
-      <c r="N33" t="inlineStr">
+        <v>1.363697516166667</v>
+      </c>
+      <c r="N33">
+        <v>33.65105640333333</v>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O33">
-        <v>1.844119286466969</v>
-      </c>
       <c r="P33">
-        <v>-11.61795150474191</v>
+        <v>1.331719516371994</v>
       </c>
       <c r="Q33">
-        <v>-20.70945958702407</v>
+        <v>-6.65859758185997</v>
       </c>
       <c r="R33">
-        <v>-36.88238572933939</v>
+        <v>-14.95521016885749</v>
       </c>
       <c r="S33">
-        <v>5.861111111111111</v>
+        <v>-26.63439032743988</v>
       </c>
       <c r="T33">
-        <v>0.5633617766666674</v>
+        <v>3.5</v>
       </c>
       <c r="U33">
-        <v>134.9730967463636</v>
+        <v>-0.08796213201151555</v>
       </c>
       <c r="V33">
-        <v>51.91272951783213</v>
+        <v>0.3518485280460622</v>
       </c>
       <c r="W33">
-        <v>185.9444754356057</v>
+        <v>-0.374712003333336</v>
       </c>
       <c r="X33">
-        <v>214.9169925294229</v>
+        <v>-140.2678058473524</v>
+      </c>
+      <c r="Y33">
+        <v>-35.0669514618381</v>
+      </c>
+      <c r="Z33">
+        <v>-374.0474822596064</v>
+      </c>
+      <c r="AA33">
+        <v>798.2384175140708</v>
+      </c>
+      <c r="AB33">
+        <v>911.7358844865826</v>
+      </c>
+      <c r="AC33">
+        <v>552.7795609432344</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B2A15</t>
+          <t>B2A17</t>
         </is>
       </c>
       <c r="B34">
-        <v>204.8405128205128</v>
+        <v>2.590865384615385</v>
       </c>
       <c r="C34">
-        <v>78.8648587752663</v>
+        <v>367.3943589041096</v>
       </c>
       <c r="D34">
-        <v>0.7129800354265221</v>
+        <v>0.5918951311469975</v>
       </c>
       <c r="E34">
-        <v>6.205575015009935</v>
+        <v>306.8079676443459</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>60.58639125976367</v>
       </c>
       <c r="G34">
-        <v>17.26795337666667</v>
+        <v>8</v>
       </c>
       <c r="H34">
-        <v>10.94251334666667</v>
+        <v>18.31235483166667</v>
       </c>
       <c r="I34">
-        <v>28.21046672333333</v>
+        <v>14.00340576833333</v>
       </c>
       <c r="J34">
-        <v>17.420768235</v>
+        <v>32.3157606</v>
       </c>
       <c r="K34">
-        <v>11.58500638166667</v>
+        <v>19.53381813333333</v>
       </c>
       <c r="L34">
-        <v>1.4339126615</v>
+        <v>14.71755182666667</v>
       </c>
       <c r="M34">
-        <v>29.00577461666667</v>
-      </c>
-      <c r="N34" t="inlineStr">
+        <v>1.358907214</v>
+      </c>
+      <c r="N34">
+        <v>34.25136996</v>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O34">
-        <v>4.45829362716574</v>
-      </c>
       <c r="P34">
-        <v>-28.08724985114416</v>
+        <v>2.991736858382932</v>
       </c>
       <c r="Q34">
-        <v>-50.06663743307126</v>
+        <v>-14.95868429191466</v>
       </c>
       <c r="R34">
-        <v>-89.1658725433148</v>
+        <v>-33.59720491964033</v>
       </c>
       <c r="S34">
-        <v>0.5555555555555556</v>
+        <v>-59.83473716765864</v>
       </c>
       <c r="T34">
-        <v>0.1528148583333326</v>
+        <v>5.944444444444445</v>
       </c>
       <c r="U34">
-        <v>39.09704986394755</v>
+        <v>-0.04227194227847345</v>
       </c>
       <c r="V34">
-        <v>15.03732687074906</v>
+        <v>0.3381755382277876</v>
       </c>
       <c r="W34">
-        <v>53.86169987410702</v>
+        <v>1.221463301666667</v>
       </c>
       <c r="X34">
-        <v>67.89527120614258</v>
+        <v>455.6302777284146</v>
+      </c>
+      <c r="Y34">
+        <v>113.9075694321036</v>
+      </c>
+      <c r="Z34">
+        <v>1215.014073942439</v>
+      </c>
+      <c r="AA34">
+        <v>789.4274317128838</v>
+      </c>
+      <c r="AB34">
+        <v>466.3432440442986</v>
+      </c>
+      <c r="AC34">
+        <v>1522.57369567889</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B2A16</t>
+          <t>B2A18</t>
         </is>
       </c>
       <c r="B35">
-        <v>509.6371538461539</v>
+        <v>3.244254487179487</v>
       </c>
       <c r="C35">
-        <v>200.3841434845547</v>
+        <v>471.2144161726706</v>
       </c>
       <c r="D35">
-        <v>2.965130262270036</v>
+        <v>0.4266639796278763</v>
       </c>
       <c r="E35">
-        <v>45.56331380125014</v>
+        <v>426.2248733671419</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>44.98954280552874</v>
       </c>
       <c r="G35">
-        <v>20.72395750666667</v>
+        <v>16</v>
       </c>
       <c r="H35">
-        <v>12.162037295</v>
+        <v>21.03022653333333</v>
       </c>
       <c r="I35">
-        <v>32.88599480166667</v>
+        <v>13.001140755</v>
       </c>
       <c r="J35">
-        <v>20.34924550333333</v>
+        <v>34.03136728833334</v>
       </c>
       <c r="K35">
-        <v>13.3018109</v>
+        <v>21.70943054333333</v>
       </c>
       <c r="L35">
-        <v>1.363697516166667</v>
+        <v>14.36475716833333</v>
       </c>
       <c r="M35">
-        <v>33.65105640333333</v>
-      </c>
-      <c r="N35" t="inlineStr">
+        <v>1.326444698333333</v>
+      </c>
+      <c r="N35">
+        <v>36.07418771166667</v>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O35">
-        <v>1.331719516371994</v>
-      </c>
       <c r="P35">
-        <v>-8.389832953143562</v>
+        <v>0.9167533653688136</v>
       </c>
       <c r="Q35">
-        <v>-14.95521016885749</v>
+        <v>-4.583766826844068</v>
       </c>
       <c r="R35">
-        <v>-26.63439032743988</v>
+        <v>-10.29514029309178</v>
       </c>
       <c r="S35">
-        <v>3.5</v>
+        <v>-18.33506730737627</v>
       </c>
       <c r="T35">
-        <v>-0.374712003333336</v>
+        <v>10.77777777777778</v>
       </c>
       <c r="U35">
-        <v>-91.17407380077907</v>
+        <v>0.04910843718761077</v>
       </c>
       <c r="V35">
-        <v>-35.0669514618381</v>
+        <v>-0.7857349950017722</v>
       </c>
       <c r="W35">
-        <v>-125.6051445427758</v>
+        <v>0.6792040099999994</v>
       </c>
       <c r="X35">
-        <v>94.25485951491814</v>
+        <v>247.3043402125153</v>
+      </c>
+      <c r="Y35">
+        <v>61.82608505312882</v>
+      </c>
+      <c r="Z35">
+        <v>659.4782405667074</v>
+      </c>
+      <c r="AA35">
+        <v>708.2236160920941</v>
+      </c>
+      <c r="AB35">
+        <v>528.4567343989554</v>
+      </c>
+      <c r="AC35">
+        <v>1112.357589432002</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B2A17</t>
+          <t>B2A19</t>
         </is>
       </c>
       <c r="B36">
-        <v>259.0865384615385</v>
+        <v>1.422470512820513</v>
       </c>
       <c r="C36">
-        <v>106.0108094880664</v>
+        <v>270.254725281602</v>
       </c>
       <c r="D36">
-        <v>1.689488470807592</v>
+        <v>0.5578380918121569</v>
       </c>
       <c r="E36">
-        <v>17.17151735011587</v>
+        <v>229.7075360239103</v>
       </c>
       <c r="F36">
-        <v>8</v>
+        <v>40.54718925769166</v>
       </c>
       <c r="G36">
-        <v>18.31235483166667</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>14.00340576833333</v>
+        <v>19.93975524333333</v>
       </c>
       <c r="I36">
-        <v>32.3157606</v>
+        <v>13.90334904166667</v>
       </c>
       <c r="J36">
-        <v>19.53381813333333</v>
+        <v>33.843104285</v>
       </c>
       <c r="K36">
-        <v>14.71755182666667</v>
+        <v>21.53524523833333</v>
       </c>
       <c r="L36">
-        <v>1.358907214</v>
+        <v>14.45000332833333</v>
       </c>
       <c r="M36">
-        <v>34.25136996</v>
-      </c>
-      <c r="N36" t="inlineStr">
+        <v>1.288804584666667</v>
+      </c>
+      <c r="N36">
+        <v>35.98524856666667</v>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O36">
-        <v>2.991736858382932</v>
-      </c>
       <c r="P36">
-        <v>-18.84794220781247</v>
+        <v>0.6187439129779645</v>
       </c>
       <c r="Q36">
-        <v>-33.59720491964033</v>
+        <v>-3.093719564889823</v>
       </c>
       <c r="R36">
-        <v>-59.83473716765864</v>
+        <v>-6.948494142742542</v>
       </c>
       <c r="S36">
-        <v>5.944444444444445</v>
+        <v>-12.37487825955929</v>
       </c>
       <c r="T36">
-        <v>1.221463301666667</v>
+        <v>2</v>
       </c>
       <c r="U36">
-        <v>296.1596805234695</v>
+        <v>-0.1108072268780366</v>
       </c>
       <c r="V36">
-        <v>113.9075694321036</v>
+        <v>0.2216144537560732</v>
       </c>
       <c r="W36">
-        <v>408.001726029871</v>
+        <v>1.595489994999998</v>
       </c>
       <c r="X36">
-        <v>368.5732850918955</v>
+        <v>564.4474381849205</v>
+      </c>
+      <c r="Y36">
+        <v>141.1118595462301</v>
+      </c>
+      <c r="Z36">
+        <v>1505.193168493121</v>
+      </c>
+      <c r="AA36">
+        <v>827.7536693237799</v>
+      </c>
+      <c r="AB36">
+        <v>408.2728652629423</v>
+      </c>
+      <c r="AC36">
+        <v>1763.073015515164</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B2A18</t>
+          <t>B2A20</t>
         </is>
       </c>
       <c r="B37">
-        <v>324.4254487179487</v>
+        <v>1.262232051282051</v>
       </c>
       <c r="C37">
-        <v>126.5987710316066</v>
+        <v>168.5447996306556</v>
       </c>
       <c r="D37">
-        <v>2.343764760437876</v>
+        <v>0.6631412776856722</v>
       </c>
       <c r="E37">
-        <v>25.23677737461479</v>
+        <v>135.4384437140516</v>
       </c>
       <c r="F37">
-        <v>16</v>
+        <v>33.106355916604</v>
       </c>
       <c r="G37">
-        <v>21.03022653333333</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>13.001140755</v>
+        <v>22.18978647833334</v>
       </c>
       <c r="I37">
-        <v>34.03136728833334</v>
+        <v>12.43652800666667</v>
       </c>
       <c r="J37">
-        <v>21.70943054333333</v>
+        <v>34.626314485</v>
       </c>
       <c r="K37">
-        <v>14.36475716833333</v>
+        <v>20.42762157666667</v>
       </c>
       <c r="L37">
-        <v>1.326444698333333</v>
+        <v>14.15560386</v>
       </c>
       <c r="M37">
-        <v>36.07418771166667</v>
-      </c>
-      <c r="N37" t="inlineStr">
+        <v>1.286318249666667</v>
+      </c>
+      <c r="N37">
+        <v>34.58322543666667</v>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O37">
-        <v>0.9167533653688136</v>
-      </c>
       <c r="P37">
-        <v>-5.775546201823525</v>
+        <v>1.395749491872198</v>
       </c>
       <c r="Q37">
-        <v>-10.29514029309178</v>
+        <v>-6.97874745936099</v>
       </c>
       <c r="R37">
-        <v>-18.33506730737627</v>
+        <v>-15.67426679372478</v>
       </c>
       <c r="S37">
-        <v>10.77777777777778</v>
+        <v>-27.91498983744396</v>
       </c>
       <c r="T37">
-        <v>0.6792040099999994</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="U37">
-        <v>160.7478211381349</v>
+        <v>-0.1108072268780366</v>
       </c>
       <c r="V37">
-        <v>61.82608505312882</v>
+        <v>0.2216144537560732</v>
       </c>
       <c r="W37">
-        <v>221.4527931823003</v>
+        <v>-1.762164901666669</v>
       </c>
       <c r="X37">
-        <v>277.0514518766497</v>
+        <v>-622.2104873464054</v>
+      </c>
+      <c r="Y37">
+        <v>-155.5526218366014</v>
+      </c>
+      <c r="Z37">
+        <v>-1659.227966257081</v>
+      </c>
+      <c r="AA37">
+        <v>-469.3399545094746</v>
+      </c>
+      <c r="AB37">
+        <v>6.013430334693254</v>
+      </c>
+      <c r="AC37">
+        <v>-1518.598156463869</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B2A19</t>
+          <t>B2A21</t>
         </is>
       </c>
       <c r="B38">
-        <v>142.2470512820513</v>
+        <v>3.726879487179487</v>
       </c>
       <c r="C38">
-        <v>57.8715096135934</v>
+        <v>637.8914167571234</v>
       </c>
       <c r="D38">
-        <v>1.792634842757805</v>
+        <v>0.294024447963506</v>
       </c>
       <c r="E38">
-        <v>9.755083068534551</v>
+        <v>606.9330981955617</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>30.95831856156167</v>
       </c>
       <c r="G38">
-        <v>19.93975524333333</v>
+        <v>8</v>
       </c>
       <c r="H38">
-        <v>13.90334904166667</v>
+        <v>20.38238114833333</v>
       </c>
       <c r="I38">
-        <v>33.843104285</v>
+        <v>13.65231196166667</v>
       </c>
       <c r="J38">
-        <v>21.53524523833333</v>
+        <v>34.03469311</v>
       </c>
       <c r="K38">
-        <v>14.45000332833333</v>
+        <v>20.91067990666667</v>
       </c>
       <c r="L38">
-        <v>1.288804584666667</v>
+        <v>14.24542969666667</v>
       </c>
       <c r="M38">
-        <v>35.98524856666667</v>
-      </c>
-      <c r="N38" t="inlineStr">
+        <v>1.177016317833333</v>
+      </c>
+      <c r="N38">
+        <v>35.15610960333333</v>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O38">
-        <v>0.6187439129779645</v>
-      </c>
       <c r="P38">
-        <v>-3.898086651761176</v>
+        <v>1.143627946389912</v>
       </c>
       <c r="Q38">
-        <v>-6.948494142742542</v>
+        <v>-5.718139731949559</v>
       </c>
       <c r="R38">
-        <v>-12.37487825955929</v>
+        <v>-12.84294183795871</v>
       </c>
       <c r="S38">
-        <v>2</v>
+        <v>-22.87255892779823</v>
       </c>
       <c r="T38">
-        <v>1.595489994999998</v>
+        <v>6.972222222222222</v>
       </c>
       <c r="U38">
-        <v>366.8908348201983</v>
+        <v>-0.04227194227847345</v>
       </c>
       <c r="V38">
-        <v>141.1118595462301</v>
+        <v>0.3381755382277876</v>
       </c>
       <c r="W38">
-        <v>505.4438659799901</v>
+        <v>0.5282987583333316</v>
       </c>
       <c r="X38">
-        <v>417.8138502910492</v>
+        <v>170.6885631639658</v>
+      </c>
+      <c r="Y38">
+        <v>42.67214079099144</v>
+      </c>
+      <c r="Z38">
+        <v>455.1695017705754</v>
+      </c>
+      <c r="AA38">
+        <v>795.7370380831304</v>
+      </c>
+      <c r="AB38">
+        <v>674.8454178161652</v>
+      </c>
+      <c r="AC38">
+        <v>1070.1883595999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B2A20</t>
+          <t>B2A22</t>
         </is>
       </c>
       <c r="B39">
-        <v>126.2232051282051</v>
+        <v>3.866262820512821</v>
       </c>
       <c r="C39">
-        <v>50.32343597562431</v>
+        <v>651.3483015256587</v>
       </c>
       <c r="D39">
-        <v>1.507974293939214</v>
+        <v>0.4568009909509298</v>
       </c>
       <c r="E39">
-        <v>7.528754213737447</v>
+        <v>581.3387263305019</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>70.0095751951568</v>
       </c>
       <c r="G39">
-        <v>22.18978647833334</v>
+        <v>16</v>
       </c>
       <c r="H39">
-        <v>12.43652800666667</v>
+        <v>20.36408032333333</v>
       </c>
       <c r="I39">
-        <v>34.626314485</v>
+        <v>12.75228142833333</v>
       </c>
       <c r="J39">
-        <v>20.42762157666667</v>
+        <v>33.11636175166667</v>
       </c>
       <c r="K39">
-        <v>14.15560386</v>
+        <v>23.87834243333333</v>
       </c>
       <c r="L39">
-        <v>1.286318249666667</v>
+        <v>12.781894505</v>
       </c>
       <c r="M39">
-        <v>34.58322543666667</v>
-      </c>
-      <c r="N39" t="inlineStr">
+        <v>1.134298261833333</v>
+      </c>
+      <c r="N39">
+        <v>36.66023693833333</v>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="O39">
-        <v>1.395749491872198</v>
-      </c>
       <c r="P39">
-        <v>-8.793221798794846</v>
+        <v>5.855716016589727</v>
       </c>
       <c r="Q39">
-        <v>-15.67426679372478</v>
+        <v>-29.27858008294864</v>
       </c>
       <c r="R39">
-        <v>-27.91498983744396</v>
+        <v>-65.75969086630263</v>
       </c>
       <c r="S39">
-        <v>1.833333333333333</v>
+        <v>-117.1143203317945</v>
       </c>
       <c r="T39">
-        <v>-1.762164901666669</v>
+        <v>10.22222222222222</v>
       </c>
       <c r="U39">
-        <v>-404.4368167751635</v>
+        <v>0.04910843718761077</v>
       </c>
       <c r="V39">
-        <v>-155.5526218366014</v>
+        <v>-0.7857349950017722</v>
       </c>
       <c r="W39">
-        <v>-557.1687510691279</v>
+        <v>3.514262110000001</v>
       </c>
       <c r="X39">
-        <v>-369.787647593264</v>
+        <v>1094.217775123429</v>
+      </c>
+      <c r="Y39">
+        <v>273.5544437808574</v>
+      </c>
+      <c r="Z39">
+        <v>2917.914066995812</v>
+      </c>
+      <c r="AA39">
+        <v>1679.806385782786</v>
+      </c>
+      <c r="AB39">
+        <v>895.6241652235674</v>
+      </c>
+      <c r="AC39">
+        <v>3452.148048189676</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B2A21</t>
+          <t>B3A01</t>
         </is>
       </c>
       <c r="B40">
-        <v>372.6879487179487</v>
+        <v>2.21565641025641</v>
       </c>
       <c r="C40">
-        <v>147.6211274417673</v>
+        <v>361.4095828118482</v>
       </c>
       <c r="D40">
-        <v>3.401077723047435</v>
+        <v>0.3638090113587762</v>
       </c>
       <c r="E40">
-        <v>36.02408775721546</v>
+        <v>335.4359787093715</v>
       </c>
       <c r="F40">
-        <v>8</v>
+        <v>25.97360410247666</v>
       </c>
       <c r="G40">
-        <v>20.38238114833333</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>13.65231196166667</v>
+        <v>17.53820831</v>
       </c>
       <c r="I40">
-        <v>34.03469311</v>
+        <v>14.17948345166667</v>
       </c>
       <c r="J40">
-        <v>20.91067990666667</v>
+        <v>31.71769176166667</v>
       </c>
       <c r="K40">
-        <v>14.24542969666667</v>
+        <v>18.11070592666667</v>
       </c>
       <c r="L40">
-        <v>1.177016317833333</v>
+        <v>13.97844794</v>
       </c>
       <c r="M40">
-        <v>35.15610960333333</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="O40">
-        <v>1.143627946389912</v>
+        <v>1.2480027205</v>
+      </c>
+      <c r="N40">
+        <v>32.08915386666667</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
       </c>
       <c r="P40">
-        <v>-7.204856062256444</v>
+        <v>1.809020597434316</v>
       </c>
       <c r="Q40">
-        <v>-12.84294183795871</v>
+        <v>-9.04510298717158</v>
       </c>
       <c r="R40">
-        <v>-22.87255892779823</v>
+        <v>-20.31530130918737</v>
       </c>
       <c r="S40">
-        <v>6.972222222222222</v>
+        <v>-36.18041194868632</v>
       </c>
       <c r="T40">
-        <v>0.5282987583333316</v>
+        <v>1</v>
       </c>
       <c r="U40">
-        <v>110.9475660565777</v>
+        <v>-0.1222297743112971</v>
       </c>
       <c r="V40">
-        <v>42.67214079099144</v>
+        <v>0.1222297743112971</v>
       </c>
       <c r="W40">
-        <v>152.8459186945592</v>
+        <v>0.5724976166666664</v>
       </c>
       <c r="X40">
-        <v>245.7257516603864</v>
+        <v>196.1243710553957</v>
+      </c>
+      <c r="Y40">
+        <v>49.03109276384893</v>
+      </c>
+      <c r="Z40">
+        <v>522.9983228143886</v>
+      </c>
+      <c r="AA40">
+        <v>537.2186525580565</v>
+      </c>
+      <c r="AB40">
+        <v>401.3955725885255</v>
+      </c>
+      <c r="AC40">
+        <v>848.2274936775505</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B2A22</t>
+          <t>B3A02</t>
         </is>
       </c>
       <c r="B41">
-        <v>386.626282051282</v>
+        <v>1.17894358974359</v>
       </c>
       <c r="C41">
-        <v>150.3462897602319</v>
+        <v>122.136068790397</v>
       </c>
       <c r="D41">
-        <v>2.189137107426768</v>
+        <v>1.133776223850209</v>
       </c>
       <c r="E41">
-        <v>28.7717658624749</v>
+        <v>74.38083862558241</v>
       </c>
       <c r="F41">
-        <v>16</v>
+        <v>47.75523016481463</v>
       </c>
       <c r="G41">
-        <v>20.36408032333333</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>12.75228142833333</v>
+        <v>16.30180951666667</v>
       </c>
       <c r="I41">
-        <v>33.11636175166667</v>
+        <v>14.26811456666667</v>
       </c>
       <c r="J41">
-        <v>23.87834243333333</v>
+        <v>30.56992408333333</v>
       </c>
       <c r="K41">
-        <v>12.781894505</v>
+        <v>15.78657563583333</v>
       </c>
       <c r="L41">
-        <v>1.134298261833333</v>
+        <v>14.74983727833333</v>
       </c>
       <c r="M41">
-        <v>36.66023693833333</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="O41">
-        <v>5.855716016589727</v>
+        <v>1.273350069</v>
+      </c>
+      <c r="N41">
+        <v>30.53641291416667</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
       </c>
       <c r="P41">
-        <v>-36.89101090451528</v>
+        <v>3.786722414738152</v>
       </c>
       <c r="Q41">
-        <v>-65.75969086630263</v>
+        <v>-18.93361207369076</v>
       </c>
       <c r="R41">
-        <v>-117.1143203317945</v>
+        <v>-42.52489271750945</v>
       </c>
       <c r="S41">
-        <v>10.22222222222222</v>
+        <v>-75.73444829476304</v>
       </c>
       <c r="T41">
-        <v>3.514262110000001</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="U41">
-        <v>711.241553830229</v>
+        <v>-0.1108072268780366</v>
       </c>
       <c r="V41">
-        <v>273.5544437808574</v>
+        <v>0.2216144537560732</v>
       </c>
       <c r="W41">
-        <v>979.8355436971934</v>
+        <v>-0.5152338808333319</v>
       </c>
       <c r="X41">
-        <v>795.8281527241583</v>
+        <v>-180.0920653214666</v>
+      </c>
+      <c r="Y41">
+        <v>-45.02301633036666</v>
+      </c>
+      <c r="Z41">
+        <v>-480.245507523911</v>
+      </c>
+      <c r="AA41">
+        <v>-100.480889248579</v>
+      </c>
+      <c r="AB41">
+        <v>58.17944038633963</v>
+      </c>
+      <c r="AC41">
+        <v>-433.843887028277</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B3A01</t>
+          <t>B3A03</t>
         </is>
       </c>
       <c r="B42">
-        <v>221.565641025641</v>
+        <v>1.812729487179487</v>
       </c>
       <c r="C42">
-        <v>90.05586434145199</v>
+        <v>213.1443365296804</v>
       </c>
       <c r="D42">
-        <v>2.748694971202441</v>
+        <v>1.025194190586372</v>
       </c>
       <c r="E42">
-        <v>19.65576041940932</v>
+        <v>138.5132957341472</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>74.63104079553315</v>
       </c>
       <c r="G42">
-        <v>17.53820831</v>
+        <v>4</v>
       </c>
       <c r="H42">
-        <v>14.17948345166667</v>
+        <v>15.87066645166667</v>
       </c>
       <c r="I42">
-        <v>31.71769176166667</v>
+        <v>15.19955595333333</v>
       </c>
       <c r="J42">
-        <v>18.11070592666667</v>
+        <v>31.070222405</v>
       </c>
       <c r="K42">
-        <v>13.97844794</v>
+        <v>16.34161234133333</v>
       </c>
       <c r="L42">
-        <v>1.2480027205</v>
+        <v>15.09101679166667</v>
       </c>
       <c r="M42">
-        <v>32.08915386666667</v>
-      </c>
-      <c r="N42" t="inlineStr">
+        <v>1.209331958</v>
+      </c>
+      <c r="N42">
+        <v>31.432629133</v>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O42">
-        <v>1.809020597434316</v>
-      </c>
       <c r="P42">
-        <v>-11.39682976383619</v>
+        <v>2.420979241851507</v>
       </c>
       <c r="Q42">
-        <v>-20.31530130918737</v>
+        <v>-12.10489620925753</v>
       </c>
       <c r="R42">
-        <v>-36.18041194868632</v>
+        <v>-27.18759688599242</v>
       </c>
       <c r="S42">
-        <v>1</v>
+        <v>-48.41958483703014</v>
       </c>
       <c r="T42">
-        <v>0.5724976166666664</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="U42">
-        <v>127.4808411860072</v>
+        <v>-0.08796213201151555</v>
       </c>
       <c r="V42">
-        <v>49.03109276384893</v>
+        <v>0.3518485280460622</v>
       </c>
       <c r="W42">
-        <v>175.6228368010717</v>
+        <v>0.4709458896666678</v>
       </c>
       <c r="X42">
-        <v>197.2214042182719</v>
+        <v>156.3359616297956</v>
+      </c>
+      <c r="Y42">
+        <v>39.0839904074489</v>
+      </c>
+      <c r="Z42">
+        <v>416.8958976794549</v>
+      </c>
+      <c r="AA42">
+        <v>342.2927012734835</v>
+      </c>
+      <c r="AB42">
+        <v>240.1234307278717</v>
+      </c>
+      <c r="AC42">
+        <v>581.6206493721052</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B3A02</t>
+          <t>B3A04</t>
         </is>
       </c>
       <c r="B43">
-        <v>117.894358974359</v>
+        <v>3.094958974358974</v>
       </c>
       <c r="C43">
-        <v>47.10781310866284</v>
+        <v>460.9539548802946</v>
       </c>
       <c r="D43">
-        <v>0.8820082649149968</v>
+        <v>0.4258082248280325</v>
       </c>
       <c r="E43">
-        <v>4.557394938224608</v>
+        <v>417.0985057239417</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>43.85544915635285</v>
       </c>
       <c r="G43">
-        <v>16.30180951666667</v>
+        <v>8</v>
       </c>
       <c r="H43">
-        <v>14.26811456666667</v>
+        <v>15.01120542833333</v>
       </c>
       <c r="I43">
-        <v>30.56992408333333</v>
+        <v>18.91071100833333</v>
       </c>
       <c r="J43">
-        <v>15.78657563583333</v>
+        <v>33.92191643666666</v>
       </c>
       <c r="K43">
-        <v>14.74983727833333</v>
+        <v>17.679803865</v>
       </c>
       <c r="L43">
-        <v>1.273350069</v>
+        <v>18.16225364</v>
       </c>
       <c r="M43">
-        <v>30.53641291416667</v>
-      </c>
-      <c r="N43" t="inlineStr">
+        <v>1.211471480333333</v>
+      </c>
+      <c r="N43">
+        <v>35.842057505</v>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O43">
-        <v>3.786722414738152</v>
-      </c>
       <c r="P43">
-        <v>-23.85635121285036</v>
+        <v>0.8786257682716357</v>
       </c>
       <c r="Q43">
-        <v>-42.52489271750945</v>
+        <v>-4.393128841358179</v>
       </c>
       <c r="R43">
-        <v>-75.73444829476304</v>
+        <v>-9.86696737769047</v>
       </c>
       <c r="S43">
-        <v>1.888888888888889</v>
+        <v>-17.57251536543271</v>
       </c>
       <c r="T43">
-        <v>-0.5152338808333319</v>
+        <v>5.916666666666667</v>
       </c>
       <c r="U43">
-        <v>-117.0598424589533</v>
+        <v>-0.04227194227847345</v>
       </c>
       <c r="V43">
-        <v>-45.02301633036666</v>
+        <v>0.3381755382277876</v>
       </c>
       <c r="W43">
-        <v>-161.2664414265293</v>
+        <v>2.668598436666667</v>
       </c>
       <c r="X43">
-        <v>-112.4769220677999</v>
+        <v>887.4395316337992</v>
+      </c>
+      <c r="Y43">
+        <v>221.8598829084498</v>
+      </c>
+      <c r="Z43">
+        <v>2366.505417690131</v>
+      </c>
+      <c r="AA43">
+        <v>1338.526519136403</v>
+      </c>
+      <c r="AB43">
+        <v>678.4207089473862</v>
+      </c>
+      <c r="AC43">
+        <v>2809.886857204993</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B3A03</t>
+          <t>B3A05</t>
         </is>
       </c>
       <c r="B44">
-        <v>181.2729487179487</v>
+        <v>4.008861538461539</v>
       </c>
       <c r="C44">
-        <v>72.62556805483219</v>
+        <v>601.2093326330532</v>
       </c>
       <c r="D44">
-        <v>0.9754249577126824</v>
+        <v>0.3335245546396465</v>
       </c>
       <c r="E44">
-        <v>7.690786828287878</v>
+        <v>564.3406261335457</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>36.86870649950754</v>
       </c>
       <c r="G44">
-        <v>15.87066645166667</v>
+        <v>8</v>
       </c>
       <c r="H44">
-        <v>15.19955595333333</v>
+        <v>19.261428105</v>
       </c>
       <c r="I44">
-        <v>31.070222405</v>
+        <v>14.94687716333333</v>
       </c>
       <c r="J44">
-        <v>16.34161234133333</v>
+        <v>34.20830526833333</v>
       </c>
       <c r="K44">
-        <v>15.09101679166667</v>
+        <v>20.82464430333333</v>
       </c>
       <c r="L44">
-        <v>1.209331958</v>
+        <v>15.52260234</v>
       </c>
       <c r="M44">
-        <v>31.432629133</v>
-      </c>
-      <c r="N44" t="inlineStr">
+        <v>1.2708509925</v>
+      </c>
+      <c r="N44">
+        <v>36.34724664333334</v>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O44">
-        <v>2.420979241851507</v>
-      </c>
       <c r="P44">
-        <v>-15.25216922366449</v>
+        <v>1.002883629259998</v>
       </c>
       <c r="Q44">
-        <v>-27.18759688599242</v>
+        <v>-5.014418146299988</v>
       </c>
       <c r="R44">
-        <v>-48.41958483703014</v>
+        <v>-11.26238315658977</v>
       </c>
       <c r="S44">
-        <v>3.166666666666667</v>
+        <v>-20.05767258519995</v>
       </c>
       <c r="T44">
-        <v>0.4709458896666678</v>
+        <v>4.444444444444445</v>
       </c>
       <c r="U44">
-        <v>101.6183750593671</v>
+        <v>-0.04227194227847345</v>
       </c>
       <c r="V44">
-        <v>39.0839904074489</v>
+        <v>0.3381755382277876</v>
       </c>
       <c r="W44">
-        <v>139.993642440761</v>
+        <v>1.563216198333333</v>
       </c>
       <c r="X44">
-        <v>147.0563462282069</v>
+        <v>545.3257782860259</v>
+      </c>
+      <c r="Y44">
+        <v>136.3314445715065</v>
+      </c>
+      <c r="Z44">
+        <v>1454.202075429402</v>
+      </c>
+      <c r="AA44">
+        <v>1135.272727762489</v>
+      </c>
+      <c r="AB44">
+        <v>732.5263590582597</v>
+      </c>
+      <c r="AC44">
+        <v>2035.353735477256</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B3A04</t>
+          <t>B3A06</t>
         </is>
       </c>
       <c r="B45">
-        <v>309.4958974358975</v>
+        <v>1.536873076923077</v>
       </c>
       <c r="C45">
-        <v>121.4441448756403</v>
+        <v>297.5514159292035</v>
       </c>
       <c r="D45">
-        <v>2.348475068568395</v>
+        <v>0.4599882295798992</v>
       </c>
       <c r="E45">
-        <v>24.23787183047328</v>
+        <v>265.1849001545697</v>
       </c>
       <c r="F45">
-        <v>8</v>
+        <v>32.3665157746338</v>
       </c>
       <c r="G45">
-        <v>15.01120542833333</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>18.91071100833333</v>
+        <v>19.57522699166667</v>
       </c>
       <c r="I45">
-        <v>33.92191643666666</v>
+        <v>15.47139307</v>
       </c>
       <c r="J45">
-        <v>17.679803865</v>
+        <v>35.04662006166667</v>
       </c>
       <c r="K45">
-        <v>18.16225364</v>
+        <v>19.75802325166667</v>
       </c>
       <c r="L45">
-        <v>1.211471480333333</v>
+        <v>16.70883446166667</v>
       </c>
       <c r="M45">
-        <v>35.842057505</v>
-      </c>
-      <c r="N45" t="inlineStr">
+        <v>1.273792166333333</v>
+      </c>
+      <c r="N45">
+        <v>36.46685771333334</v>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O45">
-        <v>0.8786257682716357</v>
-      </c>
       <c r="P45">
-        <v>-5.535342340111305</v>
+        <v>0.675106066584323</v>
       </c>
       <c r="Q45">
-        <v>-9.86696737769047</v>
+        <v>-3.375530332921615</v>
       </c>
       <c r="R45">
-        <v>-17.57251536543271</v>
+        <v>-7.581441127741948</v>
       </c>
       <c r="S45">
-        <v>5.916666666666667</v>
+        <v>-13.50212133168646</v>
       </c>
       <c r="T45">
-        <v>2.668598436666667</v>
+        <v>1</v>
       </c>
       <c r="U45">
-        <v>576.8356955619695</v>
+        <v>-0.1222297743112971</v>
       </c>
       <c r="V45">
-        <v>221.8598829084498</v>
+        <v>0.1222297743112971</v>
       </c>
       <c r="W45">
-        <v>794.6725192603461</v>
+        <v>0.1827962599999999</v>
       </c>
       <c r="X45">
-        <v>688.4128730599193</v>
+        <v>63.91579988432206</v>
+      </c>
+      <c r="Y45">
+        <v>15.97894997108052</v>
+      </c>
+      <c r="Z45">
+        <v>170.4421330248588</v>
+      </c>
+      <c r="AA45">
+        <v>353.8857746857836</v>
+      </c>
+      <c r="AB45">
+        <v>310.1548355673625</v>
+      </c>
+      <c r="AC45">
+        <v>454.4914276223759</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B3A05</t>
+          <t>B3A07</t>
         </is>
       </c>
       <c r="B46">
-        <v>400.8861538461538</v>
+        <v>4.176919230769231</v>
       </c>
       <c r="C46">
-        <v>162.527018737534</v>
+        <v>720.1289025110783</v>
       </c>
       <c r="D46">
-        <v>2.998279994948021</v>
+        <v>0.4547044135111556</v>
       </c>
       <c r="E46">
-        <v>37.17363056770113</v>
+        <v>643.3370144523936</v>
       </c>
       <c r="F46">
+        <v>76.79188805868466</v>
+      </c>
+      <c r="G46">
         <v>8</v>
       </c>
-      <c r="G46">
-        <v>19.261428105</v>
-      </c>
       <c r="H46">
-        <v>14.94687716333333</v>
+        <v>19.22971065333333</v>
       </c>
       <c r="I46">
-        <v>34.20830526833333</v>
+        <v>14.82748369166667</v>
       </c>
       <c r="J46">
-        <v>20.82464430333333</v>
+        <v>34.057194345</v>
       </c>
       <c r="K46">
-        <v>15.52260234</v>
+        <v>20.94664231166667</v>
       </c>
       <c r="L46">
-        <v>1.2708509925</v>
+        <v>15.58443038</v>
       </c>
       <c r="M46">
-        <v>36.34724664333334</v>
-      </c>
-      <c r="N46" t="inlineStr">
+        <v>1.272812508666667</v>
+      </c>
+      <c r="N46">
+        <v>36.53107269166667</v>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O46">
-        <v>1.002883629259998</v>
-      </c>
       <c r="P46">
-        <v>-6.318166864337985</v>
+        <v>1.042897672376869</v>
       </c>
       <c r="Q46">
-        <v>-11.26238315658977</v>
+        <v>-5.214488361884343</v>
       </c>
       <c r="R46">
-        <v>-20.05767258519995</v>
+        <v>-11.71174086079223</v>
       </c>
       <c r="S46">
-        <v>4.444444444444445</v>
+        <v>-20.85795344753737</v>
       </c>
       <c r="T46">
-        <v>1.563216198333333</v>
+        <v>6.194444444444445</v>
       </c>
       <c r="U46">
-        <v>354.4617558859168</v>
+        <v>-0.04227194227847345</v>
       </c>
       <c r="V46">
-        <v>136.3314445715065</v>
+        <v>0.3381755382277876</v>
       </c>
       <c r="W46">
-        <v>488.3210569291933</v>
+        <v>1.716931658333333</v>
       </c>
       <c r="X46">
-        <v>505.7263914668611</v>
+        <v>599.8736590488031</v>
+      </c>
+      <c r="Y46">
+        <v>149.9684147622008</v>
+      </c>
+      <c r="Z46">
+        <v>1599.663090796808</v>
+      </c>
+      <c r="AA46">
+        <v>1308.290820699089</v>
+      </c>
+      <c r="AB46">
+        <v>864.8828289113948</v>
+      </c>
+      <c r="AC46">
+        <v>2298.934039860349</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B3A06</t>
+          <t>B3A08</t>
         </is>
       </c>
       <c r="B47">
-        <v>153.6873076923077</v>
+        <v>1.828228205128205</v>
       </c>
       <c r="C47">
-        <v>60.81325994793166</v>
+        <v>221.36697053407</v>
       </c>
       <c r="D47">
-        <v>2.173968670705522</v>
+        <v>0.8608362736412534</v>
       </c>
       <c r="E47">
-        <v>11.58872070575369</v>
+        <v>158.7185577393479</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>62.64841279472211</v>
       </c>
       <c r="G47">
-        <v>19.57522699166667</v>
+        <v>2</v>
       </c>
       <c r="H47">
-        <v>15.47139307</v>
+        <v>18.94378669166667</v>
       </c>
       <c r="I47">
-        <v>35.04662006166667</v>
+        <v>14.260492525</v>
       </c>
       <c r="J47">
-        <v>19.75802325166667</v>
+        <v>33.20427921666666</v>
       </c>
       <c r="K47">
-        <v>16.70883446166667</v>
+        <v>18.28368143833333</v>
       </c>
       <c r="L47">
-        <v>1.273792166333333</v>
+        <v>15.45937701166667</v>
       </c>
       <c r="M47">
-        <v>36.46685771333334</v>
-      </c>
-      <c r="N47" t="inlineStr">
+        <v>1.303480212</v>
+      </c>
+      <c r="N47">
+        <v>33.74305845</v>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O47">
-        <v>0.675106066584323</v>
-      </c>
       <c r="P47">
-        <v>-4.253168219481235</v>
+        <v>0.9046072052730504</v>
       </c>
       <c r="Q47">
-        <v>-7.581441127741948</v>
+        <v>-4.523036026365252</v>
       </c>
       <c r="R47">
-        <v>-13.50212133168646</v>
+        <v>-10.15873891521636</v>
       </c>
       <c r="S47">
-        <v>1</v>
+        <v>-18.09214410546101</v>
       </c>
       <c r="T47">
-        <v>0.1827962599999999</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="U47">
-        <v>41.54526992480934</v>
+        <v>-0.1108072268780366</v>
       </c>
       <c r="V47">
-        <v>15.97894997108052</v>
+        <v>0.2216144537560732</v>
       </c>
       <c r="W47">
-        <v>57.23446826974759</v>
+        <v>-0.6601052533333345</v>
       </c>
       <c r="X47">
-        <v>94.77708874499905</v>
+        <v>-236.1891702104647</v>
+      </c>
+      <c r="Y47">
+        <v>-59.04729255261617</v>
+      </c>
+      <c r="Z47">
+        <v>-629.8377872279058</v>
+      </c>
+      <c r="AA47">
+        <v>-24.98093859161108</v>
+      </c>
+      <c r="AB47">
+        <v>157.7966419550885</v>
+      </c>
+      <c r="AC47">
+        <v>-426.5629607992968</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B3A07</t>
+          <t>B3A09</t>
         </is>
       </c>
       <c r="B48">
-        <v>417.6919230769231</v>
+        <v>3.958517948717949</v>
       </c>
       <c r="C48">
-        <v>161.3551916368001</v>
+        <v>627.7532214622282</v>
       </c>
       <c r="D48">
-        <v>2.199230907565111</v>
+        <v>0.2392131395395795</v>
       </c>
       <c r="E48">
-        <v>30.96483387166473</v>
+        <v>607.1402242067081</v>
       </c>
       <c r="F48">
-        <v>8</v>
+        <v>20.6129972555201</v>
       </c>
       <c r="G48">
-        <v>19.22971065333333</v>
+        <v>16</v>
       </c>
       <c r="H48">
-        <v>14.82748369166667</v>
+        <v>21.528021425</v>
       </c>
       <c r="I48">
-        <v>34.057194345</v>
+        <v>12.991011935</v>
       </c>
       <c r="J48">
-        <v>20.94664231166667</v>
+        <v>34.51903335999999</v>
       </c>
       <c r="K48">
-        <v>15.58443038</v>
+        <v>22.554342445</v>
       </c>
       <c r="L48">
-        <v>1.272812508666667</v>
+        <v>14.18910566833333</v>
       </c>
       <c r="M48">
-        <v>36.53107269166667</v>
-      </c>
-      <c r="N48" t="inlineStr">
+        <v>1.2398925705</v>
+      </c>
+      <c r="N48">
+        <v>36.74344811333333</v>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O48">
-        <v>1.042897672376869</v>
-      </c>
       <c r="P48">
-        <v>-6.570255335974272</v>
+        <v>0.8637637605319486</v>
       </c>
       <c r="Q48">
-        <v>-11.71174086079223</v>
+        <v>-4.318818802659743</v>
       </c>
       <c r="R48">
-        <v>-20.85795344753737</v>
+        <v>-9.700067030773782</v>
       </c>
       <c r="S48">
-        <v>6.194444444444445</v>
+        <v>-17.27527521063897</v>
       </c>
       <c r="T48">
-        <v>1.716931658333333</v>
+        <v>10.13888888888889</v>
       </c>
       <c r="U48">
-        <v>389.917878381722</v>
+        <v>0.04910843718761077</v>
       </c>
       <c r="V48">
-        <v>149.9684147622008</v>
+        <v>-0.7857349950017722</v>
       </c>
       <c r="W48">
-        <v>537.1668658895682</v>
+        <v>1.026321020000001</v>
       </c>
       <c r="X48">
-        <v>539.5613291577299</v>
+        <v>349.3088831988225</v>
+      </c>
+      <c r="Y48">
+        <v>87.32722079970561</v>
+      </c>
+      <c r="Z48">
+        <v>931.4903551968597</v>
+      </c>
+      <c r="AA48">
+        <v>967.362037630277</v>
+      </c>
+      <c r="AB48">
+        <v>710.7616234592741</v>
+      </c>
+      <c r="AC48">
+        <v>1541.968301448449</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B3A08</t>
+          <t>B3A11</t>
         </is>
       </c>
       <c r="B49">
-        <v>182.8228205128205</v>
+        <v>3.085635897435898</v>
       </c>
       <c r="C49">
-        <v>73.23798057505209</v>
+        <v>517.1243126614987</v>
       </c>
       <c r="D49">
-        <v>1.161661085411861</v>
+        <v>0.2318689978295758</v>
       </c>
       <c r="E49">
-        <v>8.983570164265618</v>
+        <v>501.1285340404892</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>15.99577862100955</v>
       </c>
       <c r="G49">
-        <v>18.94378669166667</v>
+        <v>4</v>
       </c>
       <c r="H49">
-        <v>14.260492525</v>
+        <v>21.14341975333333</v>
       </c>
       <c r="I49">
-        <v>33.20427921666666</v>
+        <v>13.43872288833333</v>
       </c>
       <c r="J49">
-        <v>18.28368143833333</v>
+        <v>34.58214264166666</v>
       </c>
       <c r="K49">
-        <v>15.45937701166667</v>
+        <v>21.7940397</v>
       </c>
       <c r="L49">
-        <v>1.303480212</v>
+        <v>13.728815925</v>
       </c>
       <c r="M49">
-        <v>33.74305845</v>
-      </c>
-      <c r="N49" t="inlineStr">
+        <v>1.233803417166667</v>
+      </c>
+      <c r="N49">
+        <v>35.522855625</v>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O49">
-        <v>0.9046072052730504</v>
-      </c>
       <c r="P49">
-        <v>-5.699025393220217</v>
+        <v>1.268561254316011</v>
       </c>
       <c r="Q49">
-        <v>-10.15873891521636</v>
+        <v>-6.342806271580052</v>
       </c>
       <c r="R49">
-        <v>-18.09214410546101</v>
+        <v>-14.2459428859688</v>
       </c>
       <c r="S49">
-        <v>1.777777777777778</v>
+        <v>-25.37122508632021</v>
       </c>
       <c r="T49">
-        <v>-0.6601052533333345</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="U49">
-        <v>-153.522960636802</v>
+        <v>-0.08796213201151555</v>
       </c>
       <c r="V49">
-        <v>-59.04729255261617</v>
+        <v>0.3518485280460622</v>
       </c>
       <c r="W49">
-        <v>-211.4995289511308</v>
+        <v>0.6506199466666658</v>
       </c>
       <c r="X49">
-        <v>-90.4437189769663</v>
+        <v>220.3513376486478</v>
+      </c>
+      <c r="Y49">
+        <v>55.08783441216195</v>
+      </c>
+      <c r="Z49">
+        <v>587.6035670630607</v>
+      </c>
+      <c r="AA49">
+        <v>723.2297074241777</v>
+      </c>
+      <c r="AB49">
+        <v>565.8693408020806</v>
+      </c>
+      <c r="AC49">
+        <v>1079.356654638239</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B3A09</t>
+          <t>B3A12</t>
         </is>
       </c>
       <c r="B50">
-        <v>395.8517948717949</v>
+        <v>0.7274282051282052</v>
       </c>
       <c r="C50">
-        <v>155.7970491893329</v>
+        <v>123.4623451327434</v>
       </c>
       <c r="D50">
-        <v>4.180372373878496</v>
+        <v>0.7037339858231498</v>
       </c>
       <c r="E50">
-        <v>41.95735830473001</v>
+        <v>96.98570178516927</v>
       </c>
       <c r="F50">
-        <v>16</v>
+        <v>26.47664334757408</v>
       </c>
       <c r="G50">
-        <v>21.528021425</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>12.991011935</v>
+        <v>24.5741344</v>
       </c>
       <c r="I50">
-        <v>34.51903335999999</v>
+        <v>14.09356097333333</v>
       </c>
       <c r="J50">
-        <v>22.554342445</v>
+        <v>38.66769537333333</v>
       </c>
       <c r="K50">
-        <v>14.18910566833333</v>
+        <v>21.62069094333333</v>
       </c>
       <c r="L50">
-        <v>1.2398925705</v>
+        <v>14.54494359833333</v>
       </c>
       <c r="M50">
-        <v>36.74344811333333</v>
-      </c>
-      <c r="N50" t="inlineStr">
+        <v>1.244754985333333</v>
+      </c>
+      <c r="N50">
+        <v>36.16563454166666</v>
+      </c>
+      <c r="O50" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O50">
-        <v>0.8637637605319486</v>
-      </c>
       <c r="P50">
-        <v>-5.441711691351276</v>
+        <v>12.71122695655753</v>
       </c>
       <c r="Q50">
-        <v>-9.700067030773782</v>
+        <v>-63.55613478278765</v>
       </c>
       <c r="R50">
-        <v>-17.27527521063897</v>
+        <v>-142.7470787221411</v>
       </c>
       <c r="S50">
-        <v>10.13888888888889</v>
+        <v>-254.2245391311506</v>
       </c>
       <c r="T50">
-        <v>1.026321020000001</v>
+        <v>1</v>
       </c>
       <c r="U50">
-        <v>227.0507740792346</v>
+        <v>-0.1222297743112971</v>
       </c>
       <c r="V50">
-        <v>87.32722079970561</v>
+        <v>0.1222297743112971</v>
       </c>
       <c r="W50">
-        <v>312.7944612751055</v>
+        <v>-2.953443456666665</v>
       </c>
       <c r="X50">
-        <v>373.1477562377937</v>
+        <v>-1009.148046577842</v>
+      </c>
+      <c r="Y50">
+        <v>-252.2870116444604</v>
+      </c>
+      <c r="Z50">
+        <v>-2691.061457540911</v>
+      </c>
+      <c r="AA50">
+        <v>-1028.432780167239</v>
+      </c>
+      <c r="AB50">
+        <v>-192.3808012945047</v>
+      </c>
+      <c r="AC50">
+        <v>-2821.823651539319</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B3A11</t>
+          <t>B3A13</t>
         </is>
       </c>
       <c r="B51">
-        <v>308.5635897435898</v>
+        <v>3.238462820512821</v>
       </c>
       <c r="C51">
-        <v>120.4256830558205</v>
+        <v>541.3946961325967</v>
       </c>
       <c r="D51">
-        <v>4.312780101525268</v>
+        <v>0.2462658671215855</v>
       </c>
       <c r="E51">
-        <v>32.89322220225676</v>
+        <v>522.6025279822691</v>
       </c>
       <c r="F51">
+        <v>18.7921681503276</v>
+      </c>
+      <c r="G51">
         <v>4</v>
       </c>
-      <c r="G51">
-        <v>21.14341975333333</v>
-      </c>
       <c r="H51">
-        <v>13.43872288833333</v>
+        <v>20.38869288666666</v>
       </c>
       <c r="I51">
-        <v>34.58214264166666</v>
+        <v>20.37180383833334</v>
       </c>
       <c r="J51">
-        <v>21.7940397</v>
+        <v>40.760496725</v>
       </c>
       <c r="K51">
-        <v>13.728815925</v>
+        <v>21.31049074166667</v>
       </c>
       <c r="L51">
-        <v>1.233803417166667</v>
+        <v>21.137494145</v>
       </c>
       <c r="M51">
-        <v>35.522855625</v>
-      </c>
-      <c r="N51" t="inlineStr">
+        <v>1.129676881</v>
+      </c>
+      <c r="N51">
+        <v>42.44798488666666</v>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O51">
-        <v>1.268561254316011</v>
-      </c>
       <c r="P51">
-        <v>-7.991935902190866</v>
+        <v>0.6924872803624826</v>
       </c>
       <c r="Q51">
-        <v>-14.2459428859688</v>
+        <v>-3.462436401812413</v>
       </c>
       <c r="R51">
-        <v>-25.37122508632021</v>
+        <v>-7.77663215847068</v>
       </c>
       <c r="S51">
-        <v>2.777777777777778</v>
+        <v>-13.84974560724965</v>
       </c>
       <c r="T51">
-        <v>0.6506199466666658</v>
+        <v>2.555555555555555</v>
       </c>
       <c r="U51">
-        <v>143.2283694716211</v>
+        <v>-0.08796213201151555</v>
       </c>
       <c r="V51">
-        <v>55.08783441216195</v>
+        <v>0.3518485280460622</v>
       </c>
       <c r="W51">
-        <v>197.3172778197758</v>
+        <v>0.9217978550000012</v>
       </c>
       <c r="X51">
-        <v>249.4081096414728</v>
+        <v>285.8461077180707</v>
+      </c>
+      <c r="Y51">
+        <v>71.46152692951767</v>
+      </c>
+      <c r="Z51">
+        <v>762.2562872481885</v>
+      </c>
+      <c r="AA51">
+        <v>819.4641716921967</v>
+      </c>
+      <c r="AB51">
+        <v>609.3937866603019</v>
+      </c>
+      <c r="AC51">
+        <v>1289.801237773535</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B3A12</t>
+          <t>B3A16</t>
         </is>
       </c>
       <c r="B52">
-        <v>72.74282051282051</v>
+        <v>4.552126923076923</v>
       </c>
       <c r="C52">
-        <v>29.15391927412195</v>
+        <v>667.3996842139595</v>
       </c>
       <c r="D52">
-        <v>1.420991482783528</v>
+        <v>0.460027124838791</v>
       </c>
       <c r="E52">
-        <v>4.177339451148918</v>
+        <v>594.7919347257389</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>72.60774948822063</v>
       </c>
       <c r="G52">
-        <v>24.5741344</v>
+        <v>16</v>
       </c>
       <c r="H52">
-        <v>14.09356097333333</v>
+        <v>16.31114664333333</v>
       </c>
       <c r="I52">
-        <v>38.66769537333333</v>
+        <v>20.07515013166667</v>
       </c>
       <c r="J52">
-        <v>21.62069094333333</v>
+        <v>36.38629677500001</v>
       </c>
       <c r="K52">
-        <v>14.54494359833333</v>
+        <v>20.22225977666667</v>
       </c>
       <c r="L52">
-        <v>1.244754985333333</v>
+        <v>20.56386172833333</v>
       </c>
       <c r="M52">
-        <v>36.16563454166666</v>
-      </c>
-      <c r="N52" t="inlineStr">
+        <v>1.129646918166667</v>
+      </c>
+      <c r="N52">
+        <v>40.786121505</v>
+      </c>
+      <c r="O52" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O52">
-        <v>12.71122695655753</v>
-      </c>
       <c r="P52">
-        <v>-80.08072982631244</v>
+        <v>1.781220700091808</v>
       </c>
       <c r="Q52">
-        <v>-142.7470787221411</v>
+        <v>-8.906103500459038</v>
       </c>
       <c r="R52">
-        <v>-254.2245391311506</v>
+        <v>-20.003108462031</v>
       </c>
       <c r="S52">
-        <v>1</v>
+        <v>-35.62441400183615</v>
       </c>
       <c r="T52">
-        <v>-2.953443456666665</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="U52">
-        <v>-655.9462302755971</v>
+        <v>0.04910843718761077</v>
       </c>
       <c r="V52">
-        <v>-252.2870116444604</v>
+        <v>-0.7857349950017722</v>
       </c>
       <c r="W52">
-        <v>-903.6584374422379</v>
+        <v>3.911113133333334</v>
       </c>
       <c r="X52">
-        <v>-769.5393897236163</v>
+        <v>1212.789558410738</v>
+      </c>
+      <c r="Y52">
+        <v>303.1973896026844</v>
+      </c>
+      <c r="Z52">
+        <v>3234.1054890953</v>
+      </c>
+      <c r="AA52">
+        <v>1860.186134162666</v>
+      </c>
+      <c r="AB52">
+        <v>961.6909703161848</v>
+      </c>
+      <c r="AC52">
+        <v>3865.880759307423</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B3A13</t>
+          <t>B3A17</t>
         </is>
       </c>
       <c r="B53">
-        <v>323.8462820512821</v>
+        <v>0.299974358974359</v>
       </c>
       <c r="C53">
-        <v>128.636010866598</v>
+        <v>46.47245782033744</v>
       </c>
       <c r="D53">
-        <v>4.060652057421678</v>
+        <v>0.8968978501648638</v>
       </c>
       <c r="E53">
-        <v>34.18340728529794</v>
+        <v>32.61311123668053</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>13.85934658365691</v>
       </c>
       <c r="G53">
-        <v>20.38869288666666</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>20.37180383833334</v>
+        <v>15.5350772</v>
       </c>
       <c r="I53">
-        <v>40.760496725</v>
+        <v>21.23301645166667</v>
       </c>
       <c r="J53">
-        <v>21.31049074166667</v>
+        <v>36.76809365166667</v>
       </c>
       <c r="K53">
-        <v>21.137494145</v>
+        <v>17.13503540333333</v>
       </c>
       <c r="L53">
-        <v>1.129676881</v>
+        <v>20.508566085</v>
       </c>
       <c r="M53">
-        <v>42.44798488666666</v>
-      </c>
-      <c r="N53" t="inlineStr">
+        <v>1.366434788833333</v>
+      </c>
+      <c r="N53">
+        <v>37.64360148833333</v>
+      </c>
+      <c r="O53" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O53">
-        <v>0.6924872803624826</v>
-      </c>
       <c r="P53">
-        <v>-4.362669866283641</v>
+        <v>2.244100031449752</v>
       </c>
       <c r="Q53">
-        <v>-7.77663215847068</v>
+        <v>-11.22050015724876</v>
       </c>
       <c r="R53">
-        <v>-13.84974560724965</v>
+        <v>-25.20124335318072</v>
       </c>
       <c r="S53">
-        <v>2.555555555555555</v>
+        <v>-44.88200062899504</v>
       </c>
       <c r="T53">
-        <v>0.9217978550000012</v>
+        <v>1</v>
       </c>
       <c r="U53">
-        <v>185.799970016746</v>
+        <v>-0.1222297743112971</v>
       </c>
       <c r="V53">
-        <v>71.46152692951767</v>
+        <v>0.1222297743112971</v>
       </c>
       <c r="W53">
-        <v>255.9656612579417</v>
+        <v>1.599958203333333</v>
       </c>
       <c r="X53">
-        <v>306.6593487248733</v>
+        <v>600.1224818964773</v>
+      </c>
+      <c r="Y53">
+        <v>150.0306204741193</v>
+      </c>
+      <c r="Z53">
+        <v>1600.326618390606</v>
+      </c>
+      <c r="AA53">
+        <v>621.393696363634</v>
+      </c>
+      <c r="AB53">
+        <v>185.282578137208</v>
+      </c>
+      <c r="AC53">
+        <v>1601.917075581949</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B3A14</t>
+          <t>B3A19</t>
         </is>
       </c>
       <c r="B54">
-        <v>650.37</v>
+        <v>0.9361538461538461</v>
       </c>
       <c r="C54">
-        <v>254.81831192044</v>
+        <v>175.1352348066298</v>
       </c>
       <c r="D54">
-        <v>3.264209423554901</v>
+        <v>0.4717276354881516</v>
       </c>
       <c r="E54">
-        <v>60.9085993917174</v>
+        <v>155.2453001571154</v>
       </c>
       <c r="F54">
-        <v>60</v>
+        <v>19.88993464951446</v>
       </c>
       <c r="G54">
-        <v>18.91503501666667</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>18.94353111666667</v>
+        <v>19.57160066</v>
       </c>
       <c r="I54">
-        <v>37.85856613333333</v>
+        <v>17.35135972666667</v>
       </c>
       <c r="J54">
-        <v>20.86098047666666</v>
+        <v>36.92296038666667</v>
       </c>
       <c r="K54">
-        <v>19.11635910666667</v>
+        <v>19.28397925833333</v>
       </c>
       <c r="L54">
-        <v>1.151697198166667</v>
+        <v>18.13899774833333</v>
       </c>
       <c r="M54">
-        <v>39.97733958333333</v>
-      </c>
-      <c r="N54" t="inlineStr">
+        <v>1.2727740835</v>
+      </c>
+      <c r="N54">
+        <v>37.42297700666667</v>
+      </c>
+      <c r="O54" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O54">
-        <v>0.8316001654117181</v>
-      </c>
       <c r="P54">
-        <v>-5.239081042093824</v>
+        <v>2.35487853771158</v>
       </c>
       <c r="Q54">
-        <v>-9.338869857573595</v>
+        <v>-11.7743926885579</v>
       </c>
       <c r="R54">
-        <v>-16.63200330823436</v>
+        <v>-26.44528597850105</v>
       </c>
       <c r="S54">
-        <v>29.75</v>
+        <v>-47.09757075423161</v>
       </c>
       <c r="T54">
-        <v>1.945945459999997</v>
+        <v>1.972222222222222</v>
       </c>
       <c r="U54">
-        <v>399.8753927359298</v>
+        <v>-0.1108072268780366</v>
       </c>
       <c r="V54">
-        <v>153.7982279753576</v>
+        <v>0.2216144537560732</v>
       </c>
       <c r="W54">
-        <v>550.8847461773343</v>
+        <v>-0.2876214016666694</v>
       </c>
       <c r="X54">
-        <v>645.3548347987962</v>
+        <v>-100.4881545899015</v>
+      </c>
+      <c r="Y54">
+        <v>-25.12203864747538</v>
+      </c>
+      <c r="Z54">
+        <v>-267.9684122397374</v>
+      </c>
+      <c r="AA54">
+        <v>48.20179423822725</v>
+      </c>
+      <c r="AB54">
+        <v>138.2388034705965</v>
+      </c>
+      <c r="AC54">
+        <v>-139.9307481873392</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B3A16</t>
+          <t>B3A20</t>
         </is>
       </c>
       <c r="B55">
-        <v>455.2126923076923</v>
+        <v>3.911703846153846</v>
       </c>
       <c r="C55">
-        <v>189.8996209918883</v>
+        <v>678.0123716366159</v>
       </c>
       <c r="D55">
-        <v>2.173784861817515</v>
+        <v>0.3528157483564595</v>
       </c>
       <c r="E55">
-        <v>36.18586349485449</v>
+        <v>631.9268666453961</v>
       </c>
       <c r="F55">
-        <v>16</v>
+        <v>46.08550499121975</v>
       </c>
       <c r="G55">
-        <v>16.31114664333333</v>
+        <v>8</v>
       </c>
       <c r="H55">
-        <v>20.07515013166667</v>
+        <v>18.96839964333333</v>
       </c>
       <c r="I55">
-        <v>36.38629677500001</v>
+        <v>15.34068266333333</v>
       </c>
       <c r="J55">
-        <v>20.22225977666667</v>
+        <v>34.30908230666667</v>
       </c>
       <c r="K55">
-        <v>20.56386172833333</v>
+        <v>18.90949340833333</v>
       </c>
       <c r="L55">
-        <v>1.129646918166667</v>
+        <v>16.265840325</v>
       </c>
       <c r="M55">
-        <v>40.786121505</v>
-      </c>
-      <c r="N55" t="inlineStr">
+        <v>1.302041297333333</v>
+      </c>
+      <c r="N55">
+        <v>35.17533373333333</v>
+      </c>
+      <c r="O55" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O55">
-        <v>1.781220700091808</v>
-      </c>
       <c r="P55">
-        <v>-11.22169041057839</v>
+        <v>5.768294627152565</v>
       </c>
       <c r="Q55">
-        <v>-20.003108462031</v>
+        <v>-28.84147313576282</v>
       </c>
       <c r="R55">
-        <v>-35.62441400183615</v>
+        <v>-64.77794866292331</v>
       </c>
       <c r="S55">
-        <v>9.333333333333334</v>
+        <v>-115.3658925430513</v>
       </c>
       <c r="T55">
-        <v>3.911113133333334</v>
+        <v>5.111111111111111</v>
       </c>
       <c r="U55">
-        <v>788.3132129669794</v>
+        <v>-0.04227194227847345</v>
       </c>
       <c r="V55">
-        <v>303.1973896026844</v>
+        <v>0.3381755382277876</v>
       </c>
       <c r="W55">
-        <v>1086.012623238202</v>
+        <v>-0.05890623500000203</v>
       </c>
       <c r="X55">
-        <v>958.2097254968367</v>
+        <v>-21.05369725079662</v>
+      </c>
+      <c r="Y55">
+        <v>-5.263424312699155</v>
+      </c>
+      <c r="Z55">
+        <v>-56.14319266879099</v>
+      </c>
+      <c r="AA55">
+        <v>592.1807257228959</v>
+      </c>
+      <c r="AB55">
+        <v>643.9074741881539</v>
+      </c>
+      <c r="AC55">
+        <v>506.5032864247736</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B3A17</t>
+          <t>B3A21</t>
         </is>
       </c>
       <c r="B56">
-        <v>29.9974358974359</v>
+        <v>1.865998717948718</v>
       </c>
       <c r="C56">
-        <v>12.43333966065505</v>
+        <v>278.7978825011558</v>
       </c>
       <c r="D56">
-        <v>1.114954172112448</v>
+        <v>1.091386027733801</v>
       </c>
       <c r="E56">
-        <v>1.474939708608838</v>
+        <v>174.1363196520388</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>104.661562849117</v>
       </c>
       <c r="G56">
-        <v>15.5350772</v>
+        <v>2</v>
       </c>
       <c r="H56">
-        <v>21.23301645166667</v>
+        <v>19.19157407666667</v>
       </c>
       <c r="I56">
-        <v>36.76809365166667</v>
+        <v>15.447678765</v>
       </c>
       <c r="J56">
-        <v>17.13503540333333</v>
+        <v>34.63925284166667</v>
       </c>
       <c r="K56">
-        <v>20.508566085</v>
+        <v>20.00068769833333</v>
       </c>
       <c r="L56">
-        <v>1.366434788833333</v>
+        <v>15.62423430166667</v>
       </c>
       <c r="M56">
-        <v>37.64360148833333</v>
-      </c>
-      <c r="N56" t="inlineStr">
+        <v>1.2796586495</v>
+      </c>
+      <c r="N56">
+        <v>35.624922</v>
+      </c>
+      <c r="O56" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O56">
-        <v>2.244100031449752</v>
-      </c>
       <c r="P56">
-        <v>-14.13783019813344</v>
+        <v>4.634270652459132</v>
       </c>
       <c r="Q56">
-        <v>-25.20124335318072</v>
+        <v>-23.17135326229566</v>
       </c>
       <c r="R56">
-        <v>-44.88200062899504</v>
+        <v>-52.04285942711606</v>
       </c>
       <c r="S56">
-        <v>1</v>
+        <v>-92.68541304918264</v>
       </c>
       <c r="T56">
-        <v>1.599958203333333</v>
+        <v>2</v>
       </c>
       <c r="U56">
-        <v>390.0796132327102</v>
+        <v>-0.1108072268780366</v>
       </c>
       <c r="V56">
-        <v>150.0306204741193</v>
+        <v>0.2216144537560732</v>
       </c>
       <c r="W56">
-        <v>537.3896784555656</v>
+        <v>0.8091136216666648</v>
       </c>
       <c r="X56">
-        <v>377.3117095401846</v>
+        <v>284.214347586158</v>
+      </c>
+      <c r="Y56">
+        <v>71.0535868965395</v>
+      </c>
+      <c r="Z56">
+        <v>757.9049268964213</v>
+      </c>
+      <c r="AA56">
+        <v>510.9693706601977</v>
+      </c>
+      <c r="AB56">
+        <v>326.6801161353997</v>
+      </c>
+      <c r="AC56">
+        <v>944.0173963483944</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B3A19</t>
+          <t>B3A22</t>
         </is>
       </c>
       <c r="B57">
-        <v>93.61538461538461</v>
+        <v>3.642266794871795</v>
       </c>
       <c r="C57">
-        <v>38.43954418497408</v>
+        <v>641.7850238552437</v>
       </c>
       <c r="D57">
-        <v>2.119867323365915</v>
+        <v>0.2754997943029076</v>
       </c>
       <c r="E57">
-        <v>7.212921435014662</v>
+        <v>614.2234611784173</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>27.56156267682638</v>
       </c>
       <c r="G57">
-        <v>19.57160066</v>
+        <v>16</v>
       </c>
       <c r="H57">
-        <v>17.35135972666667</v>
+        <v>21.72608776333333</v>
       </c>
       <c r="I57">
-        <v>36.92296038666667</v>
+        <v>14.51037426833333</v>
       </c>
       <c r="J57">
-        <v>19.28397925833333</v>
+        <v>36.23646203166666</v>
       </c>
       <c r="K57">
-        <v>18.13899774833333</v>
+        <v>22.56712392</v>
       </c>
       <c r="L57">
-        <v>1.2727740835</v>
+        <v>15.705884195</v>
       </c>
       <c r="M57">
-        <v>37.42297700666667</v>
-      </c>
-      <c r="N57" t="inlineStr">
+        <v>1.212829627166667</v>
+      </c>
+      <c r="N57">
+        <v>38.273008115</v>
+      </c>
+      <c r="O57" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O57">
-        <v>2.35487853771158</v>
-      </c>
       <c r="P57">
-        <v>-14.83573478758296</v>
+        <v>0.8158122852628428</v>
       </c>
       <c r="Q57">
-        <v>-26.44528597850105</v>
+        <v>-4.079061426314214</v>
       </c>
       <c r="R57">
-        <v>-47.09757075423161</v>
+        <v>-9.161571963501725</v>
       </c>
       <c r="S57">
-        <v>1.972222222222222</v>
+        <v>-16.31624570525685</v>
       </c>
       <c r="T57">
-        <v>-0.2876214016666694</v>
+        <v>12.05555555555556</v>
       </c>
       <c r="U57">
-        <v>-65.31730048343599</v>
+        <v>0.04910843718761077</v>
       </c>
       <c r="V57">
-        <v>-25.12203864747538</v>
+        <v>-0.7857349950017722</v>
       </c>
       <c r="W57">
-        <v>-89.98379283010381</v>
+        <v>0.841036156666668</v>
       </c>
       <c r="X57">
-        <v>-53.32304227696295</v>
+        <v>279.9992145048614</v>
+      </c>
+      <c r="Y57">
+        <v>69.99980362621535</v>
+      </c>
+      <c r="Z57">
+        <v>746.664572012964</v>
+      </c>
+      <c r="AA57">
+        <v>912.6226663966033</v>
+      </c>
+      <c r="AB57">
+        <v>707.7057660551449</v>
+      </c>
+      <c r="AC57">
+        <v>1372.133350162951</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B3A20</t>
+          <t>B3A23</t>
         </is>
       </c>
       <c r="B58">
-        <v>391.1703846153846</v>
+        <v>3.013658974358974</v>
       </c>
       <c r="C58">
-        <v>154.2542601178925</v>
+        <v>494.1837895948434</v>
       </c>
       <c r="D58">
-        <v>2.834340600322842</v>
+        <v>0.6886966600496428</v>
       </c>
       <c r="E58">
-        <v>34.23592777114803</v>
+        <v>391.5042041018787</v>
       </c>
       <c r="F58">
-        <v>8</v>
+        <v>102.6795854929647</v>
       </c>
       <c r="G58">
-        <v>18.96839964333333</v>
+        <v>4</v>
       </c>
       <c r="H58">
-        <v>15.34068266333333</v>
+        <v>22.25263283333333</v>
       </c>
       <c r="I58">
-        <v>34.30908230666667</v>
+        <v>14.002622765</v>
       </c>
       <c r="J58">
-        <v>18.90949340833333</v>
+        <v>36.25525559833333</v>
       </c>
       <c r="K58">
-        <v>16.265840325</v>
+        <v>22.54396694333333</v>
       </c>
       <c r="L58">
-        <v>1.302041297333333</v>
+        <v>14.29265470833333</v>
       </c>
       <c r="M58">
-        <v>35.17533373333333</v>
-      </c>
-      <c r="N58" t="inlineStr">
+        <v>1.219427313833333</v>
+      </c>
+      <c r="N58">
+        <v>36.83662165166667</v>
+      </c>
+      <c r="O58" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O58">
-        <v>5.768294627152565</v>
-      </c>
       <c r="P58">
-        <v>-36.34025615106115</v>
+        <v>1.222969348145958</v>
       </c>
       <c r="Q58">
-        <v>-64.77794866292331</v>
+        <v>-6.114846740729792</v>
       </c>
       <c r="R58">
-        <v>-115.3658925430513</v>
+        <v>-13.73394577967911</v>
       </c>
       <c r="S58">
-        <v>5.111111111111111</v>
+        <v>-24.45938696291917</v>
       </c>
       <c r="T58">
-        <v>-0.05890623500000203</v>
+        <v>3.555555555555555</v>
       </c>
       <c r="U58">
-        <v>-13.6849032130178</v>
+        <v>-0.08796213201151555</v>
       </c>
       <c r="V58">
-        <v>-5.263424312699155</v>
+        <v>0.3518485280460622</v>
       </c>
       <c r="W58">
-        <v>-18.85288409818001</v>
+        <v>0.2913341100000011</v>
       </c>
       <c r="X58">
-        <v>75.79140824195142</v>
+        <v>97.51908169037203</v>
+      </c>
+      <c r="Y58">
+        <v>24.37977042259301</v>
+      </c>
+      <c r="Z58">
+        <v>260.0508845076587</v>
+      </c>
+      <c r="AA58">
+        <v>577.9689255055363</v>
+      </c>
+      <c r="AB58">
+        <v>512.4487132767066</v>
+      </c>
+      <c r="AC58">
+        <v>729.775287139583</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B3A21</t>
+          <t>B3A24</t>
         </is>
       </c>
       <c r="B59">
-        <v>186.5998717948718</v>
+        <v>5.123392307692308</v>
       </c>
       <c r="C59">
-        <v>76.31087715908556</v>
+        <v>796.5191902654866</v>
       </c>
       <c r="D59">
-        <v>0.9162660823837383</v>
+        <v>0.2682914041572469</v>
       </c>
       <c r="E59">
-        <v>7.643551855774868</v>
+        <v>763.9838296016885</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>32.53536066379809</v>
       </c>
       <c r="G59">
-        <v>19.19157407666667</v>
+        <v>16</v>
       </c>
       <c r="H59">
-        <v>15.447678765</v>
+        <v>24.81847847</v>
       </c>
       <c r="I59">
-        <v>34.63925284166667</v>
+        <v>15.63577910333333</v>
       </c>
       <c r="J59">
-        <v>20.00068769833333</v>
+        <v>40.45425757333334</v>
       </c>
       <c r="K59">
-        <v>15.62423430166667</v>
+        <v>26.54552809833334</v>
       </c>
       <c r="L59">
-        <v>1.2796586495</v>
+        <v>16.41767707333333</v>
       </c>
       <c r="M59">
-        <v>35.624922</v>
-      </c>
-      <c r="N59" t="inlineStr">
+        <v>1.198807591833333</v>
+      </c>
+      <c r="N59">
+        <v>42.96320517166667</v>
+      </c>
+      <c r="O59" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="O59">
-        <v>4.634270652459132</v>
-      </c>
       <c r="P59">
-        <v>-29.19590511049253</v>
+        <v>0.8783340032070126</v>
       </c>
       <c r="Q59">
-        <v>-52.04285942711606</v>
+        <v>-4.391670016035063</v>
       </c>
       <c r="R59">
-        <v>-92.68541304918264</v>
+        <v>-9.863690856014752</v>
       </c>
       <c r="S59">
-        <v>2</v>
+        <v>-17.56668006414025</v>
       </c>
       <c r="T59">
-        <v>0.8091136216666648</v>
+        <v>10.44444444444444</v>
       </c>
       <c r="U59">
-        <v>184.7393259310027</v>
+        <v>0.04910843718761077</v>
       </c>
       <c r="V59">
-        <v>71.0535868965395</v>
+        <v>-0.7857349950017722</v>
       </c>
       <c r="W59">
-        <v>254.5044744518183</v>
+        <v>1.727049628333333</v>
       </c>
       <c r="X59">
-        <v>209.0073436629722</v>
+        <v>568.324856524748</v>
+      </c>
+      <c r="Y59">
+        <v>142.081214131187</v>
+      </c>
+      <c r="Z59">
+        <v>1515.532950732661</v>
+      </c>
+      <c r="AA59">
+        <v>1354.98035593422</v>
+      </c>
+      <c r="AB59">
+        <v>934.2087343806386</v>
+      </c>
+      <c r="AC59">
+        <v>2294.485460934008</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B3A22</t>
+          <t>B4A02</t>
         </is>
       </c>
       <c r="B60">
-        <v>364.2266794871795</v>
+        <v>3.066930933333333</v>
       </c>
       <c r="C60">
-        <v>141.8247363730374</v>
+        <v>528.2154040616247</v>
       </c>
       <c r="D60">
-        <v>3.629766775435469</v>
+        <v>0.2307298079457889</v>
       </c>
       <c r="E60">
-        <v>35.73719452358404</v>
+        <v>512.0302092984051</v>
       </c>
       <c r="F60">
+        <v>16.18519476321956</v>
+      </c>
+      <c r="G60">
         <v>16</v>
       </c>
-      <c r="G60">
-        <v>21.72608776333333</v>
-      </c>
       <c r="H60">
-        <v>14.51037426833333</v>
+        <v>20.34286945666667</v>
       </c>
       <c r="I60">
-        <v>36.23646203166666</v>
+        <v>30.85022926333333</v>
       </c>
       <c r="J60">
-        <v>22.56712392</v>
+        <v>51.19309871999999</v>
       </c>
       <c r="K60">
-        <v>15.705884195</v>
+        <v>22.511840975</v>
       </c>
       <c r="L60">
-        <v>1.212829627166667</v>
+        <v>31.46513772166666</v>
       </c>
       <c r="M60">
-        <v>38.273008115</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="O60">
-        <v>0.8158122852628428</v>
+        <v>1.214772208</v>
+      </c>
+      <c r="N60">
+        <v>53.97697869666666</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
       </c>
       <c r="P60">
-        <v>-5.139617397155909</v>
+        <v>0.6617605719075088</v>
       </c>
       <c r="Q60">
-        <v>-9.161571963501725</v>
+        <v>-3.308802859537544</v>
       </c>
       <c r="R60">
-        <v>-16.31624570525685</v>
+        <v>-7.431571222521324</v>
       </c>
       <c r="S60">
-        <v>12.05555555555556</v>
+        <v>-13.23521143815018</v>
       </c>
       <c r="T60">
-        <v>0.841036156666668</v>
+        <v>12.27777777777778</v>
       </c>
       <c r="U60">
-        <v>181.9994894281599</v>
+        <v>0.04910843718761077</v>
       </c>
       <c r="V60">
-        <v>69.99980362621535</v>
+        <v>-0.7857349950017722</v>
       </c>
       <c r="W60">
-        <v>250.7299632819532</v>
+        <v>2.168971518333333</v>
       </c>
       <c r="X60">
-        <v>314.6626538376956</v>
+        <v>723.2543349538888</v>
+      </c>
+      <c r="Y60">
+        <v>180.8135837384722</v>
+      </c>
+      <c r="Z60">
+        <v>1928.678226543703</v>
+      </c>
+      <c r="AA60">
+        <v>1244.038167792992</v>
+      </c>
+      <c r="AB60">
+        <v>705.7201849405593</v>
+      </c>
+      <c r="AC60">
+        <v>2443.658419167178</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B3A23</t>
+          <t>B4A04</t>
         </is>
       </c>
       <c r="B61">
-        <v>301.3658974358974</v>
+        <v>2.849810256410256</v>
       </c>
       <c r="C61">
-        <v>113.377868090979</v>
+        <v>506.400087535014</v>
       </c>
       <c r="D61">
-        <v>1.45201807705575</v>
+        <v>0.3015671274085455</v>
       </c>
       <c r="E61">
-        <v>16.50463164723418</v>
+        <v>480.6319089069607</v>
       </c>
       <c r="F61">
+        <v>25.76817862805325</v>
+      </c>
+      <c r="G61">
         <v>4</v>
       </c>
-      <c r="G61">
-        <v>22.25263283333333</v>
-      </c>
       <c r="H61">
-        <v>14.002622765</v>
+        <v>14.71919975333333</v>
       </c>
       <c r="I61">
-        <v>36.25525559833333</v>
+        <v>29.839411575</v>
       </c>
       <c r="J61">
-        <v>22.54396694333333</v>
+        <v>44.55861132833333</v>
       </c>
       <c r="K61">
-        <v>14.29265470833333</v>
+        <v>14.43724686483333</v>
       </c>
       <c r="L61">
-        <v>1.219427313833333</v>
+        <v>31.33856732333333</v>
       </c>
       <c r="M61">
-        <v>36.83662165166667</v>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="O61">
-        <v>1.222969348145958</v>
+        <v>1.2871362685</v>
+      </c>
+      <c r="N61">
+        <v>45.77581418816666</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
       </c>
       <c r="P61">
-        <v>-7.704706893319538</v>
+        <v>5.37547026623286</v>
       </c>
       <c r="Q61">
-        <v>-13.73394577967911</v>
+        <v>-26.8773513311643</v>
       </c>
       <c r="R61">
-        <v>-24.45938696291917</v>
+        <v>-60.36653108979502</v>
       </c>
       <c r="S61">
-        <v>3.555555555555555</v>
+        <v>-107.5094053246572</v>
       </c>
       <c r="T61">
-        <v>0.2913341100000011</v>
+        <v>2.361111111111111</v>
       </c>
       <c r="U61">
-        <v>63.38740309874182</v>
+        <v>-0.08796213201151555</v>
       </c>
       <c r="V61">
-        <v>24.37977042259301</v>
+        <v>0.3518485280460622</v>
       </c>
       <c r="W61">
-        <v>87.32508701767181</v>
+        <v>-0.2819528884999993</v>
       </c>
       <c r="X61">
-        <v>163.0313254100417</v>
+        <v>-99.61928602469021</v>
+      </c>
+      <c r="Y61">
+        <v>-24.90482150617255</v>
+      </c>
+      <c r="Z61">
+        <v>-265.6514293991739</v>
+      </c>
+      <c r="AA61">
+        <v>346.4142704205287</v>
+      </c>
+      <c r="AB61">
+        <v>454.6179146976771</v>
+      </c>
+      <c r="AC61">
+        <v>133.239252811183</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B3A24</t>
+          <t>B4A06</t>
         </is>
       </c>
       <c r="B62">
-        <v>512.3392307692308</v>
+        <v>1.488394871794872</v>
       </c>
       <c r="C62">
-        <v>197.5241073788731</v>
+        <v>215.5082735849057</v>
       </c>
       <c r="D62">
-        <v>3.727290492743089</v>
+        <v>0.3764628654010418</v>
       </c>
       <c r="E62">
-        <v>50.41363126013075</v>
+        <v>199.0339690627768</v>
       </c>
       <c r="F62">
-        <v>16</v>
+        <v>16.47430452212888</v>
       </c>
       <c r="G62">
-        <v>24.81847847</v>
+        <v>8</v>
       </c>
       <c r="H62">
-        <v>15.63577910333333</v>
+        <v>18.14486130333333</v>
       </c>
       <c r="I62">
-        <v>40.45425757333334</v>
+        <v>33.961658875</v>
       </c>
       <c r="J62">
-        <v>26.54552809833334</v>
+        <v>52.10652017833333</v>
       </c>
       <c r="K62">
-        <v>16.41767707333333</v>
+        <v>19.296109655</v>
       </c>
       <c r="L62">
-        <v>1.198807591833333</v>
+        <v>34.73453828666666</v>
       </c>
       <c r="M62">
-        <v>42.96320517166667</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="O62">
-        <v>0.8783340032070126</v>
+        <v>1.330423571833333</v>
+      </c>
+      <c r="N62">
+        <v>54.03064794166666</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
       </c>
       <c r="P62">
-        <v>-5.533504220204179</v>
+        <v>1.782545232434082</v>
       </c>
       <c r="Q62">
-        <v>-9.863690856014752</v>
+        <v>-8.912726162170411</v>
       </c>
       <c r="R62">
-        <v>-17.56668006414025</v>
+        <v>-20.01798296023475</v>
       </c>
       <c r="S62">
-        <v>10.44444444444444</v>
+        <v>-35.65090464868165</v>
       </c>
       <c r="T62">
-        <v>1.727049628333333</v>
+        <v>7.542857142857143</v>
       </c>
       <c r="U62">
-        <v>369.4111567410862</v>
+        <v>-0.04227194227847345</v>
       </c>
       <c r="V62">
-        <v>142.081214131187</v>
+        <v>0.3381755382277876</v>
       </c>
       <c r="W62">
-        <v>508.9159648560278</v>
+        <v>1.151248351666666</v>
       </c>
       <c r="X62">
-        <v>557.0715732639446</v>
+        <v>420.4373606531451</v>
+      </c>
+      <c r="Y62">
+        <v>105.1093401632863</v>
+      </c>
+      <c r="Z62">
+        <v>1121.166295075054</v>
+      </c>
+      <c r="AA62">
+        <v>615.927651277816</v>
+      </c>
+      <c r="AB62">
+        <v>311.7048875860215</v>
+      </c>
+      <c r="AC62">
+        <v>1301.023664011278</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B4A01</t>
+          <t>B4A07</t>
         </is>
       </c>
       <c r="B63">
-        <v>615.7452564102564</v>
+        <v>0.7061499999999999</v>
       </c>
       <c r="C63">
-        <v>239.4219209999682</v>
+        <v>94.39881102413567</v>
       </c>
       <c r="D63">
-        <v>3.231067725698165</v>
+        <v>0.8045959454092909</v>
       </c>
       <c r="E63">
-        <v>56.93132958965453</v>
+        <v>69.96665305434233</v>
       </c>
       <c r="F63">
-        <v>60</v>
+        <v>24.43215796979334</v>
       </c>
       <c r="G63">
-        <v>18.52182941166667</v>
+        <v>4</v>
       </c>
       <c r="H63">
-        <v>33.48027269</v>
+        <v>18.10442685166667</v>
       </c>
       <c r="I63">
-        <v>52.00210210166667</v>
+        <v>33.43932509166667</v>
       </c>
       <c r="J63">
-        <v>21.01716598833333</v>
+        <v>51.54375194333333</v>
       </c>
       <c r="K63">
-        <v>33.50714061833333</v>
+        <v>16.57419823166667</v>
       </c>
       <c r="L63">
-        <v>1.283039363</v>
+        <v>35.08676949833333</v>
       </c>
       <c r="M63">
-        <v>54.52430660666666</v>
-      </c>
-      <c r="N63" t="inlineStr">
+        <v>1.348954807166667</v>
+      </c>
+      <c r="N63">
+        <v>51.66096773</v>
+      </c>
+      <c r="O63" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O63">
-        <v>1.533643868174295</v>
-      </c>
       <c r="P63">
-        <v>-9.661956369498061</v>
+        <v>6.470060526093794</v>
       </c>
       <c r="Q63">
-        <v>-17.22282063959734</v>
+        <v>-32.35030263046897</v>
       </c>
       <c r="R63">
-        <v>-30.67287736348591</v>
+        <v>-72.65877970803331</v>
       </c>
       <c r="S63">
-        <v>32.05555555555556</v>
+        <v>-129.4012105218759</v>
       </c>
       <c r="T63">
-        <v>2.495336576666666</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="U63">
-        <v>571.2481656168799</v>
+        <v>-0.08796213201151555</v>
       </c>
       <c r="V63">
-        <v>219.7108329295692</v>
+        <v>0.3518485280460622</v>
       </c>
       <c r="W63">
-        <v>786.9749087759928</v>
+        <v>-1.530228619999999</v>
       </c>
       <c r="X63">
-        <v>793.4472659772507</v>
+        <v>-566.6254399520722</v>
+      </c>
+      <c r="Y63">
+        <v>-141.656359988018</v>
+      </c>
+      <c r="Z63">
+        <v>-1511.001173205526</v>
+      </c>
+      <c r="AA63">
+        <v>-544.8854086359698</v>
+      </c>
+      <c r="AB63">
+        <v>-79.60785159435135</v>
+      </c>
+      <c r="AC63">
+        <v>-1546.003572703266</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B4A02</t>
+          <t>B4A08</t>
         </is>
       </c>
       <c r="B64">
-        <v>306.6930933333333</v>
+        <v>1.562683333333333</v>
       </c>
       <c r="C64">
-        <v>120.3141233595146</v>
+        <v>264.8430486725663</v>
       </c>
       <c r="D64">
-        <v>4.334073732835398</v>
+        <v>0.3605421527233894</v>
       </c>
       <c r="E64">
-        <v>32.93561625901585</v>
+        <v>246.1181658529007</v>
       </c>
       <c r="F64">
-        <v>16</v>
+        <v>18.72488281966565</v>
       </c>
       <c r="G64">
-        <v>20.34286945666667</v>
+        <v>8</v>
       </c>
       <c r="H64">
-        <v>30.85022926333333</v>
+        <v>14.92791318</v>
       </c>
       <c r="I64">
-        <v>51.19309871999999</v>
+        <v>30.64560135166667</v>
       </c>
       <c r="J64">
-        <v>22.511840975</v>
+        <v>45.57351453166667</v>
       </c>
       <c r="K64">
-        <v>31.46513772166666</v>
+        <v>14.94356254216667</v>
       </c>
       <c r="L64">
-        <v>1.214772208</v>
+        <v>31.67317683666667</v>
       </c>
       <c r="M64">
-        <v>53.97697869666666</v>
-      </c>
-      <c r="N64" t="inlineStr">
+        <v>1.300956109</v>
+      </c>
+      <c r="N64">
+        <v>46.61673937883333</v>
+      </c>
+      <c r="O64" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O64">
-        <v>0.6617605719075088</v>
-      </c>
       <c r="P64">
-        <v>-4.169091603017305</v>
+        <v>1.667006999653265</v>
       </c>
       <c r="Q64">
-        <v>-7.431571222521324</v>
+        <v>-8.335034998266323</v>
       </c>
       <c r="R64">
-        <v>-13.23521143815018</v>
+        <v>-18.72048860610616</v>
       </c>
       <c r="S64">
-        <v>12.27777777777778</v>
+        <v>-33.34013999306529</v>
       </c>
       <c r="T64">
-        <v>2.168971518333333</v>
+        <v>6.527777777777778</v>
       </c>
       <c r="U64">
-        <v>470.1153177200277</v>
+        <v>-0.04227194227847345</v>
       </c>
       <c r="V64">
-        <v>180.8135837384722</v>
+        <v>0.3381755382277876</v>
       </c>
       <c r="W64">
-        <v>647.6501484733757</v>
+        <v>0.01564936216666624</v>
       </c>
       <c r="X64">
-        <v>582.997869857021</v>
+        <v>5.588582094330088</v>
+      </c>
+      <c r="Y64">
+        <v>1.397145523582522</v>
+      </c>
+      <c r="Z64">
+        <v>14.90288558488024</v>
+      </c>
+      <c r="AA64">
+        <v>251.7111421607903</v>
+      </c>
+      <c r="AB64">
+        <v>257.9051591978825</v>
+      </c>
+      <c r="AC64">
+        <v>246.4057942643813</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B4A04</t>
+          <t>B4A09</t>
         </is>
       </c>
       <c r="B65">
-        <v>284.9810256410257</v>
+        <v>0.4135012820512821</v>
       </c>
       <c r="C65">
-        <v>115.4025372458659</v>
+        <v>39.24764202363368</v>
       </c>
       <c r="D65">
-        <v>3.316011292720439</v>
+        <v>1.161974077095802</v>
       </c>
       <c r="E65">
-        <v>27.80553227245964</v>
+        <v>23.50457904501271</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>15.74306297862097</v>
       </c>
       <c r="G65">
-        <v>14.71919975333333</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>29.839411575</v>
+        <v>13.18105039666667</v>
       </c>
       <c r="I65">
-        <v>44.55861132833333</v>
+        <v>37.45385885333334</v>
       </c>
       <c r="J65">
-        <v>14.43724686483333</v>
+        <v>50.63490925000001</v>
       </c>
       <c r="K65">
-        <v>31.33856732333333</v>
+        <v>13.13788787916667</v>
       </c>
       <c r="L65">
-        <v>1.2871362685</v>
+        <v>37.97236331166667</v>
       </c>
       <c r="M65">
-        <v>45.77581418816666</v>
-      </c>
-      <c r="N65" t="inlineStr">
+        <v>1.306180608666667</v>
+      </c>
+      <c r="N65">
+        <v>51.11025119083334</v>
+      </c>
+      <c r="O65" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O65">
-        <v>5.37547026623286</v>
-      </c>
       <c r="P65">
-        <v>-33.86546267726702</v>
+        <v>7.426832498544667</v>
       </c>
       <c r="Q65">
-        <v>-60.36653108979502</v>
+        <v>-37.13416249272333</v>
       </c>
       <c r="R65">
-        <v>-107.5094053246572</v>
+        <v>-83.40332895865662</v>
       </c>
       <c r="S65">
-        <v>2.361111111111111</v>
+        <v>-148.5366499708933</v>
       </c>
       <c r="T65">
-        <v>-0.2819528884999993</v>
+        <v>1</v>
       </c>
       <c r="U65">
-        <v>-64.75253591604864</v>
+        <v>-0.1222297743112971</v>
       </c>
       <c r="V65">
-        <v>-24.90482150617255</v>
+        <v>0.1222297743112971</v>
       </c>
       <c r="W65">
-        <v>-89.20574999224259</v>
+        <v>-0.043162517499999</v>
       </c>
       <c r="X65">
-        <v>-9.716529759977732</v>
+        <v>-15.47577290773708</v>
+      </c>
+      <c r="Y65">
+        <v>-3.86894322693427</v>
+      </c>
+      <c r="Z65">
+        <v>-41.26872775396554</v>
+      </c>
+      <c r="AA65">
+        <v>-59.63145984276002</v>
+      </c>
+      <c r="AB65">
+        <v>-1.755463696023924</v>
+      </c>
+      <c r="AC65">
+        <v>-150.5577357012252</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B4A06</t>
+          <t>B4A10</t>
         </is>
       </c>
       <c r="B66">
-        <v>148.8394871794872</v>
+        <v>3.502982051282051</v>
       </c>
       <c r="C66">
-        <v>60.29064891455001</v>
+        <v>613.0908983751846</v>
       </c>
       <c r="D66">
-        <v>2.656304490841908</v>
+        <v>0.3126702766538074</v>
       </c>
       <c r="E66">
-        <v>12.91258089143115</v>
+        <v>579.7220060108858</v>
       </c>
       <c r="F66">
+        <v>33.36889236429874</v>
+      </c>
+      <c r="G66">
         <v>8</v>
       </c>
-      <c r="G66">
-        <v>18.14486130333333</v>
-      </c>
       <c r="H66">
-        <v>33.961658875</v>
+        <v>14.67711508166667</v>
       </c>
       <c r="I66">
-        <v>52.10652017833333</v>
+        <v>38.309613865</v>
       </c>
       <c r="J66">
-        <v>19.296109655</v>
+        <v>52.98672894666667</v>
       </c>
       <c r="K66">
-        <v>34.73453828666666</v>
+        <v>18.117422885</v>
       </c>
       <c r="L66">
-        <v>1.330423571833333</v>
+        <v>37.46903936833333</v>
       </c>
       <c r="M66">
-        <v>54.03064794166666</v>
-      </c>
-      <c r="N66" t="inlineStr">
+        <v>1.244072557</v>
+      </c>
+      <c r="N66">
+        <v>55.58646225333334</v>
+      </c>
+      <c r="O66" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O66">
-        <v>1.782545232434082</v>
-      </c>
       <c r="P66">
-        <v>-11.23003496433472</v>
+        <v>0.7836703974105198</v>
       </c>
       <c r="Q66">
-        <v>-20.01798296023475</v>
+        <v>-3.918351987052599</v>
       </c>
       <c r="R66">
-        <v>-35.65090464868165</v>
+        <v>-8.800618562920137</v>
       </c>
       <c r="S66">
-        <v>7.542857142857143</v>
+        <v>-15.6734079482104</v>
       </c>
       <c r="T66">
-        <v>1.151248351666666</v>
+        <v>6.027777777777778</v>
       </c>
       <c r="U66">
-        <v>273.2842844245443</v>
+        <v>-0.04227194227847345</v>
       </c>
       <c r="V66">
-        <v>105.1093401632863</v>
+        <v>0.3381755382277876</v>
       </c>
       <c r="W66">
-        <v>376.487641886203</v>
+        <v>3.440307803333333</v>
       </c>
       <c r="X66">
-        <v>313.5569503788595</v>
+        <v>1174.857948321107</v>
+      </c>
+      <c r="Y66">
+        <v>293.7144870802767</v>
+      </c>
+      <c r="Z66">
+        <v>3132.954528856285</v>
+      </c>
+      <c r="AA66">
+        <v>1779.148228133371</v>
+      </c>
+      <c r="AB66">
+        <v>902.8870334684086</v>
+      </c>
+      <c r="AC66">
+        <v>3730.37201928326</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B4A07</t>
+          <t>B4A11</t>
         </is>
       </c>
       <c r="B67">
-        <v>70.61499999999999</v>
+        <v>3.500344871794872</v>
       </c>
       <c r="C67">
-        <v>29.18815631910355</v>
+        <v>551.3885637119114</v>
       </c>
       <c r="D67">
-        <v>1.242859854944097</v>
+        <v>0.4770815587581342</v>
       </c>
       <c r="E67">
-        <v>3.777843282920543</v>
+        <v>487.5533895226946</v>
       </c>
       <c r="F67">
+        <v>63.83517418921679</v>
+      </c>
+      <c r="G67">
         <v>4</v>
       </c>
-      <c r="G67">
-        <v>18.10442685166667</v>
-      </c>
       <c r="H67">
-        <v>33.43932509166667</v>
+        <v>15.78257399333333</v>
       </c>
       <c r="I67">
-        <v>51.54375194333333</v>
+        <v>35.71433067333334</v>
       </c>
       <c r="J67">
-        <v>16.57419823166667</v>
+        <v>51.49690466666667</v>
       </c>
       <c r="K67">
-        <v>35.08676949833333</v>
+        <v>15.29936591116667</v>
       </c>
       <c r="L67">
-        <v>1.348954807166667</v>
+        <v>37.28644950833333</v>
       </c>
       <c r="M67">
-        <v>51.66096773</v>
-      </c>
-      <c r="N67" t="inlineStr">
+        <v>1.253556855166667</v>
+      </c>
+      <c r="N67">
+        <v>52.5858154195</v>
+      </c>
+      <c r="O67" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O67">
-        <v>6.470060526093794</v>
-      </c>
       <c r="P67">
-        <v>-40.7613813143909</v>
+        <v>4.916436510502518</v>
       </c>
       <c r="Q67">
-        <v>-72.65877970803331</v>
+        <v>-24.58218255251259</v>
       </c>
       <c r="R67">
-        <v>-129.4012105218759</v>
+        <v>-55.21158201294327</v>
       </c>
       <c r="S67">
-        <v>2.666666666666667</v>
+        <v>-98.32873021005035</v>
       </c>
       <c r="T67">
-        <v>-1.530228619999999</v>
+        <v>3.722222222222222</v>
       </c>
       <c r="U67">
-        <v>-368.3065359688469</v>
+        <v>-0.08796213201151555</v>
       </c>
       <c r="V67">
-        <v>-141.656359988018</v>
+        <v>0.3518485280460622</v>
       </c>
       <c r="W67">
-        <v>-507.3941939624156</v>
+        <v>-0.4832080821666658</v>
       </c>
       <c r="X67">
-        <v>-411.7771593577767</v>
+        <v>-166.2725566628535</v>
+      </c>
+      <c r="Y67">
+        <v>-41.56813916571338</v>
+      </c>
+      <c r="Z67">
+        <v>-443.3934844342761</v>
+      </c>
+      <c r="AA67">
+        <v>329.9044250361146</v>
+      </c>
+      <c r="AB67">
+        <v>485.2382419936854</v>
+      </c>
+      <c r="AC67">
+        <v>9.666349067584974</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B4A08</t>
+          <t>B4A12</t>
         </is>
       </c>
       <c r="B68">
-        <v>156.2683333333333</v>
+        <v>0.1921935897435897</v>
       </c>
       <c r="C68">
-        <v>61.67439794932785</v>
+        <v>16.24284908218606</v>
       </c>
       <c r="D68">
-        <v>2.773600791048716</v>
+        <v>1.695129343269817</v>
       </c>
       <c r="E68">
-        <v>13.52786852616456</v>
+        <v>7.207796706954481</v>
       </c>
       <c r="F68">
-        <v>8</v>
+        <v>9.035052375231581</v>
       </c>
       <c r="G68">
-        <v>14.92791318</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>30.64560135166667</v>
+        <v>13.647493345</v>
       </c>
       <c r="I68">
-        <v>45.57351453166667</v>
+        <v>32.61511166666666</v>
       </c>
       <c r="J68">
-        <v>14.94356254216667</v>
+        <v>46.26260501166666</v>
       </c>
       <c r="K68">
-        <v>31.67317683666667</v>
+        <v>13.49411681</v>
       </c>
       <c r="L68">
-        <v>1.300956109</v>
+        <v>33.50838837833333</v>
       </c>
       <c r="M68">
-        <v>46.61673937883333</v>
-      </c>
-      <c r="N68" t="inlineStr">
+        <v>1.384350912</v>
+      </c>
+      <c r="N68">
+        <v>47.00250518833333</v>
+      </c>
+      <c r="O68" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O68">
-        <v>1.667006999653265</v>
-      </c>
       <c r="P68">
-        <v>-10.50214409781557</v>
+        <v>1.409321096780074</v>
       </c>
       <c r="Q68">
-        <v>-18.72048860610616</v>
+        <v>-7.046605483900372</v>
       </c>
       <c r="R68">
-        <v>-33.34013999306529</v>
+        <v>-15.82667591684024</v>
       </c>
       <c r="S68">
-        <v>6.527777777777778</v>
+        <v>-28.18642193560149</v>
       </c>
       <c r="T68">
-        <v>0.01564936216666624</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="U68">
-        <v>3.632578361314557</v>
+        <v>-0.1222297743112971</v>
       </c>
       <c r="V68">
-        <v>1.397145523582522</v>
+        <v>0.1222297743112971</v>
       </c>
       <c r="W68">
-        <v>5.004388979402782</v>
+        <v>-0.1533765349999996</v>
       </c>
       <c r="X68">
-        <v>46.58648770453625</v>
+        <v>-58.28374670627523</v>
+      </c>
+      <c r="Y68">
+        <v>-14.57093667656881</v>
+      </c>
+      <c r="Z68">
+        <v>-155.4233245500673</v>
+      </c>
+      <c r="AA68">
+        <v>-57.86757354092941</v>
+      </c>
+      <c r="AB68">
+        <v>-5.374693078283116</v>
+      </c>
+      <c r="AC68">
+        <v>-167.3668974034827</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B4A09</t>
+          <t>B4A13</t>
         </is>
       </c>
       <c r="B69">
-        <v>41.35012820512821</v>
+        <v>0.9838858974358974</v>
       </c>
       <c r="C69">
-        <v>16.11474299698805</v>
+        <v>99.91652770083101</v>
       </c>
       <c r="D69">
-        <v>0.86060439704418</v>
+        <v>1.281669496120874</v>
       </c>
       <c r="E69">
-        <v>1.523952100352614</v>
+        <v>55.77131850886145</v>
       </c>
       <c r="F69">
+        <v>44.14520919196956</v>
+      </c>
+      <c r="G69">
         <v>1</v>
       </c>
-      <c r="G69">
-        <v>13.18105039666667</v>
-      </c>
       <c r="H69">
-        <v>37.45385885333334</v>
+        <v>12.741091735</v>
       </c>
       <c r="I69">
-        <v>50.63490925000001</v>
+        <v>38.41735998833333</v>
       </c>
       <c r="J69">
-        <v>13.13788787916667</v>
+        <v>51.15845172333333</v>
       </c>
       <c r="K69">
-        <v>37.97236331166667</v>
+        <v>13.57363288</v>
       </c>
       <c r="L69">
-        <v>1.306180608666667</v>
+        <v>38.47788508666667</v>
       </c>
       <c r="M69">
-        <v>51.11025119083334</v>
-      </c>
-      <c r="N69" t="inlineStr">
+        <v>1.3118625675</v>
+      </c>
+      <c r="N69">
+        <v>52.05151796666667</v>
+      </c>
+      <c r="O69" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O69">
-        <v>7.426832498544667</v>
-      </c>
       <c r="P69">
-        <v>-46.7890447408314</v>
+        <v>4.033602709547567</v>
       </c>
       <c r="Q69">
-        <v>-83.40332895865662</v>
+        <v>-20.16801354773783</v>
       </c>
       <c r="R69">
-        <v>-148.5366499708933</v>
+        <v>-45.29735842821918</v>
       </c>
       <c r="S69">
-        <v>1</v>
+        <v>-80.67205419095133</v>
       </c>
       <c r="T69">
-        <v>-0.043162517499999</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="U69">
-        <v>-10.0592523900291</v>
+        <v>-0.1222297743112971</v>
       </c>
       <c r="V69">
-        <v>-3.86894322693427</v>
+        <v>0.1222297743112971</v>
       </c>
       <c r="W69">
-        <v>-13.85803877978163</v>
+        <v>0.8325411449999987</v>
       </c>
       <c r="X69">
-        <v>-77.34783835169767</v>
+        <v>299.8032903259846</v>
+      </c>
+      <c r="Y69">
+        <v>74.95082258149615</v>
+      </c>
+      <c r="Z69">
+        <v>799.4754408692924</v>
+      </c>
+      <c r="AA69">
+        <v>354.4224595985964</v>
+      </c>
+      <c r="AB69">
+        <v>154.6993367345893</v>
+      </c>
+      <c r="AC69">
+        <v>818.719914379172</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B4A10</t>
+          <t>B4A14</t>
         </is>
       </c>
       <c r="B70">
-        <v>350.2982051282052</v>
+        <v>0.6723102564102564</v>
       </c>
       <c r="C70">
-        <v>135.9485161655678</v>
+        <v>100.1815980392157</v>
       </c>
       <c r="D70">
-        <v>3.198257316627551</v>
+        <v>0.8617500432660855</v>
       </c>
       <c r="E70">
-        <v>32.15812784430829</v>
+        <v>71.79056392386993</v>
       </c>
       <c r="F70">
-        <v>8</v>
+        <v>28.39103411534578</v>
       </c>
       <c r="G70">
-        <v>14.67711508166667</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>38.309613865</v>
+        <v>16.08225684666667</v>
       </c>
       <c r="I70">
-        <v>52.98672894666667</v>
+        <v>36.86274886166667</v>
       </c>
       <c r="J70">
-        <v>18.117422885</v>
+        <v>52.94500570833333</v>
       </c>
       <c r="K70">
-        <v>37.46903936833333</v>
+        <v>15.34313406833333</v>
       </c>
       <c r="L70">
-        <v>1.244072557</v>
+        <v>38.127645695</v>
       </c>
       <c r="M70">
-        <v>55.58646225333334</v>
-      </c>
-      <c r="N70" t="inlineStr">
+        <v>1.2954976355</v>
+      </c>
+      <c r="N70">
+        <v>53.47077976333333</v>
+      </c>
+      <c r="O70" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O70">
-        <v>0.7836703974105198</v>
-      </c>
       <c r="P70">
-        <v>-4.937123503686275</v>
+        <v>1.052414688086237</v>
       </c>
       <c r="Q70">
-        <v>-8.800618562920137</v>
+        <v>-5.262073440431183</v>
       </c>
       <c r="R70">
-        <v>-15.6734079482104</v>
+        <v>-11.81861694720844</v>
       </c>
       <c r="S70">
-        <v>6.027777777777778</v>
+        <v>-21.04829376172473</v>
       </c>
       <c r="T70">
-        <v>3.440307803333333</v>
+        <v>2</v>
       </c>
       <c r="U70">
-        <v>763.6576664087194</v>
+        <v>-0.1108072268780366</v>
       </c>
       <c r="V70">
-        <v>293.7144870802767</v>
+        <v>0.2216144537560732</v>
       </c>
       <c r="W70">
-        <v>1052.04613078994</v>
+        <v>-0.7391227783333338</v>
       </c>
       <c r="X70">
-        <v>890.805564011367</v>
+        <v>-262.8424823047943</v>
+      </c>
+      <c r="Y70">
+        <v>-65.71062057619856</v>
+      </c>
+      <c r="Z70">
+        <v>-700.913286146118</v>
+      </c>
+      <c r="AA70">
+        <v>-174.479501212787</v>
+      </c>
+      <c r="AB70">
+        <v>29.20890402258595</v>
+      </c>
+      <c r="AC70">
+        <v>-621.779981868627</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B4A11</t>
+          <t>B4A15</t>
         </is>
       </c>
       <c r="B71">
-        <v>350.0344871794872</v>
+        <v>0.5175987179487179</v>
       </c>
       <c r="C71">
-        <v>143.7889625757102</v>
+        <v>64.48926960784313</v>
       </c>
       <c r="D71">
-        <v>2.096077665636558</v>
+        <v>1.306681365249445</v>
       </c>
       <c r="E71">
-        <v>26.79364441113091</v>
+        <v>35.47761734936251</v>
       </c>
       <c r="F71">
-        <v>4</v>
+        <v>29.01165225848062</v>
       </c>
       <c r="G71">
-        <v>15.78257399333333</v>
+        <v>2</v>
       </c>
       <c r="H71">
-        <v>35.71433067333334</v>
+        <v>16.89603769</v>
       </c>
       <c r="I71">
-        <v>51.49690466666667</v>
+        <v>35.35727024166667</v>
       </c>
       <c r="J71">
-        <v>15.29936591116667</v>
+        <v>52.25330793166667</v>
       </c>
       <c r="K71">
-        <v>37.28644950833333</v>
+        <v>15.49836146416667</v>
       </c>
       <c r="L71">
-        <v>1.253556855166667</v>
+        <v>37.19344516666666</v>
       </c>
       <c r="M71">
-        <v>52.5858154195</v>
-      </c>
-      <c r="N71" t="inlineStr">
+        <v>1.264633069333333</v>
+      </c>
+      <c r="N71">
+        <v>52.69180663083333</v>
+      </c>
+      <c r="O71" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O71">
-        <v>4.916436510502518</v>
-      </c>
       <c r="P71">
-        <v>-30.97355001616586</v>
+        <v>1.321750156016363</v>
       </c>
       <c r="Q71">
-        <v>-55.21158201294327</v>
+        <v>-6.608750780081813</v>
       </c>
       <c r="R71">
-        <v>-98.32873021005035</v>
+        <v>-14.84325425206375</v>
       </c>
       <c r="S71">
-        <v>3.722222222222222</v>
+        <v>-26.43500312032725</v>
       </c>
       <c r="T71">
-        <v>-0.4832080821666658</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="U71">
-        <v>-108.0771618308548</v>
+        <v>-0.1108072268780366</v>
       </c>
       <c r="V71">
-        <v>-41.56813916571338</v>
+        <v>0.2216144537560732</v>
       </c>
       <c r="W71">
-        <v>-148.8915320730299</v>
+        <v>-1.397676225833333</v>
       </c>
       <c r="X71">
-        <v>-19.4997812680879</v>
+        <v>-485.1918094500004</v>
+      </c>
+      <c r="Y71">
+        <v>-121.2979523625001</v>
+      </c>
+      <c r="Z71">
+        <v>-1293.844825200001</v>
+      </c>
+      <c r="AA71">
+        <v>-435.545794094221</v>
+      </c>
+      <c r="AB71">
+        <v>-63.41743353473878</v>
+      </c>
+      <c r="AC71">
+        <v>-1255.790558712485</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B4A12</t>
+          <t>B4A16</t>
         </is>
       </c>
       <c r="B72">
-        <v>19.21935897435898</v>
+        <v>2.686414102564103</v>
       </c>
       <c r="C72">
-        <v>7.464533394382678</v>
+        <v>397.5878710691824</v>
       </c>
       <c r="D72">
-        <v>0.5899254850199525</v>
+        <v>0.3782418706692683</v>
       </c>
       <c r="E72">
-        <v>0.4785961068347522</v>
+        <v>366.9358416233753</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>30.6520294458071</v>
       </c>
       <c r="G72">
-        <v>13.647493345</v>
+        <v>8</v>
       </c>
       <c r="H72">
-        <v>32.61511166666666</v>
+        <v>16.947425565</v>
       </c>
       <c r="I72">
-        <v>46.26260501166666</v>
+        <v>30.629589955</v>
       </c>
       <c r="J72">
-        <v>13.49411681</v>
+        <v>47.57701552</v>
       </c>
       <c r="K72">
-        <v>33.50838837833333</v>
+        <v>17.406181905</v>
       </c>
       <c r="L72">
-        <v>1.384350912</v>
+        <v>31.31645307</v>
       </c>
       <c r="M72">
-        <v>47.00250518833333</v>
-      </c>
-      <c r="N72" t="inlineStr">
+        <v>1.2258200815</v>
+      </c>
+      <c r="N72">
+        <v>48.72263497500001</v>
+      </c>
+      <c r="O72" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O72">
-        <v>1.409321096780074</v>
-      </c>
       <c r="P72">
-        <v>-8.878722909714469</v>
+        <v>2.539400797029873</v>
       </c>
       <c r="Q72">
-        <v>-15.82667591684024</v>
+        <v>-12.69700398514937</v>
       </c>
       <c r="R72">
-        <v>-28.18642193560149</v>
+        <v>-28.51747095064547</v>
       </c>
       <c r="S72">
-        <v>0.9722222222222222</v>
+        <v>-50.78801594059746</v>
       </c>
       <c r="T72">
-        <v>-0.1533765349999996</v>
+        <v>6.027777777777778</v>
       </c>
       <c r="U72">
-        <v>-37.8844353590789</v>
+        <v>-0.04227194227847345</v>
       </c>
       <c r="V72">
-        <v>-14.57093667656881</v>
+        <v>0.3381755382277876</v>
       </c>
       <c r="W72">
-        <v>-52.19115238391259</v>
+        <v>0.4587563400000008</v>
       </c>
       <c r="X72">
-        <v>-46.24657788153646</v>
+        <v>154.365825507003</v>
+      </c>
+      <c r="Y72">
+        <v>38.59145637675076</v>
+      </c>
+      <c r="Z72">
+        <v>411.642201352008</v>
+      </c>
+      <c r="AA72">
+        <v>523.4362256255399</v>
+      </c>
+      <c r="AB72">
+        <v>423.4823234607838</v>
+      </c>
+      <c r="AC72">
+        <v>758.442056480593</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B4A13</t>
+          <t>B4A17</t>
         </is>
       </c>
       <c r="B73">
-        <v>98.38858974358973</v>
+        <v>1.018382051282051</v>
       </c>
       <c r="C73">
-        <v>39.2833534025906</v>
+        <v>122.1217476842792</v>
       </c>
       <c r="D73">
-        <v>0.7802323477516001</v>
+        <v>0.7077826934229156</v>
       </c>
       <c r="E73">
-        <v>3.3831032815554</v>
+        <v>95.71327461532913</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>26.40847306895007</v>
       </c>
       <c r="G73">
-        <v>12.741091735</v>
+        <v>2</v>
       </c>
       <c r="H73">
-        <v>38.41735998833333</v>
+        <v>12.63691090166667</v>
       </c>
       <c r="I73">
-        <v>51.15845172333333</v>
+        <v>38.467871745</v>
       </c>
       <c r="J73">
-        <v>13.57363288</v>
+        <v>51.10478264666666</v>
       </c>
       <c r="K73">
-        <v>38.47788508666667</v>
+        <v>11.93623757083333</v>
       </c>
       <c r="L73">
-        <v>1.3118625675</v>
+        <v>39.78190652666667</v>
       </c>
       <c r="M73">
-        <v>52.05151796666667</v>
-      </c>
-      <c r="N73" t="inlineStr">
+        <v>1.380730892166667</v>
+      </c>
+      <c r="N73">
+        <v>51.7181440975</v>
+      </c>
+      <c r="O73" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O73">
-        <v>4.033602709547567</v>
-      </c>
       <c r="P73">
-        <v>-25.41169707014967</v>
+        <v>3.095392060730346</v>
       </c>
       <c r="Q73">
-        <v>-45.29735842821918</v>
+        <v>-15.47696030365173</v>
       </c>
       <c r="R73">
-        <v>-80.67205419095133</v>
+        <v>-34.76125284200179</v>
       </c>
       <c r="S73">
-        <v>0.9722222222222222</v>
+        <v>-61.90784121460692</v>
       </c>
       <c r="T73">
-        <v>0.8325411449999987</v>
+        <v>2</v>
       </c>
       <c r="U73">
-        <v>194.87213871189</v>
+        <v>-0.1108072268780366</v>
       </c>
       <c r="V73">
-        <v>74.95082258149615</v>
+        <v>0.2216144537560732</v>
       </c>
       <c r="W73">
-        <v>268.4638530439084</v>
+        <v>-0.7006733308333342</v>
       </c>
       <c r="X73">
-        <v>188.8581336862614</v>
+        <v>-265.5626404730979</v>
+      </c>
+      <c r="Y73">
+        <v>-66.39066011827448</v>
+      </c>
+      <c r="Z73">
+        <v>-708.1670412615945</v>
+      </c>
+      <c r="AA73">
+        <v>-178.2021456308205</v>
+      </c>
+      <c r="AB73">
+        <v>40.25412726235299</v>
+      </c>
+      <c r="AC73">
+        <v>-647.9531347919223</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B4A14</t>
+          <t>B4A18</t>
         </is>
       </c>
       <c r="B74">
-        <v>67.23102564102564</v>
+        <v>6.934347435897436</v>
       </c>
       <c r="C74">
-        <v>25.78804665914402</v>
+        <v>951.4958761061948</v>
       </c>
       <c r="D74">
-        <v>1.160429300600832</v>
+        <v>0.6133285381840071</v>
       </c>
       <c r="E74">
-        <v>3.160523161442919</v>
+        <v>785.6033011147916</v>
       </c>
       <c r="F74">
-        <v>2</v>
+        <v>165.8925749914032</v>
       </c>
       <c r="G74">
-        <v>16.08225684666667</v>
+        <v>16</v>
       </c>
       <c r="H74">
-        <v>36.86274886166667</v>
+        <v>18.07836725833333</v>
       </c>
       <c r="I74">
-        <v>52.94500570833333</v>
+        <v>34.69260811833333</v>
       </c>
       <c r="J74">
-        <v>15.34313406833333</v>
+        <v>52.77097537666667</v>
       </c>
       <c r="K74">
-        <v>38.127645695</v>
+        <v>18.410111665</v>
       </c>
       <c r="L74">
-        <v>1.2954976355</v>
+        <v>36.12730495333334</v>
       </c>
       <c r="M74">
-        <v>53.47077976333333</v>
-      </c>
-      <c r="N74" t="inlineStr">
+        <v>1.2625153515</v>
+      </c>
+      <c r="N74">
+        <v>54.53741661833334</v>
+      </c>
+      <c r="O74" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O74">
-        <v>1.052414688086237</v>
-      </c>
       <c r="P74">
-        <v>-6.630212534943291</v>
+        <v>3.183276175047217</v>
       </c>
       <c r="Q74">
-        <v>-11.81861694720844</v>
+        <v>-15.91638087523608</v>
       </c>
       <c r="R74">
-        <v>-21.04829376172473</v>
+        <v>-35.74819144578025</v>
       </c>
       <c r="S74">
-        <v>2</v>
+        <v>-63.66552350094434</v>
       </c>
       <c r="T74">
-        <v>-0.7391227783333338</v>
+        <v>9.972222222222221</v>
       </c>
       <c r="U74">
-        <v>-170.8476134981163</v>
+        <v>0.04910843718761077</v>
       </c>
       <c r="V74">
-        <v>-65.71062057619856</v>
+        <v>-0.7857349950017722</v>
       </c>
       <c r="W74">
-        <v>-235.3666814878664</v>
+        <v>0.3317444066666653</v>
       </c>
       <c r="X74">
-        <v>-156.8781837861807</v>
+        <v>114.9694954994086</v>
+      </c>
+      <c r="Y74">
+        <v>28.74237387485215</v>
+      </c>
+      <c r="Z74">
+        <v>306.5853213317563</v>
+      </c>
+      <c r="AA74">
+        <v>1030.717180159823</v>
+      </c>
+      <c r="AB74">
+        <v>964.3218691058109</v>
+      </c>
+      <c r="AC74">
+        <v>1194.415673937007</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B4A15</t>
+          <t>B4A20</t>
         </is>
       </c>
       <c r="B75">
-        <v>51.7598717948718</v>
+        <v>5.679525256410257</v>
       </c>
       <c r="C75">
-        <v>20.72448671080183</v>
+        <v>906.8422184873949</v>
       </c>
       <c r="D75">
-        <v>0.7652975136819987</v>
+        <v>0.2371704292535583</v>
       </c>
       <c r="E75">
-        <v>1.751207855310056</v>
+        <v>877.5497438657299</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>29.29247462166506</v>
       </c>
       <c r="G75">
-        <v>16.89603769</v>
+        <v>16</v>
       </c>
       <c r="H75">
-        <v>35.35727024166667</v>
+        <v>14.24282284833333</v>
       </c>
       <c r="I75">
-        <v>52.25330793166667</v>
+        <v>30.676206745</v>
       </c>
       <c r="J75">
-        <v>15.49836146416667</v>
+        <v>44.91902959333333</v>
       </c>
       <c r="K75">
-        <v>37.19344516666666</v>
+        <v>15.80617593833333</v>
       </c>
       <c r="L75">
-        <v>1.264633069333333</v>
+        <v>31.66174778166667</v>
       </c>
       <c r="M75">
-        <v>52.69180663083333</v>
-      </c>
-      <c r="N75" t="inlineStr">
+        <v>1.269657585333333</v>
+      </c>
+      <c r="N75">
+        <v>47.46792372</v>
+      </c>
+      <c r="O75" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O75">
-        <v>1.321750156016363</v>
-      </c>
       <c r="P75">
-        <v>-8.327025982903084</v>
+        <v>3.28270051142621</v>
       </c>
       <c r="Q75">
-        <v>-14.84325425206375</v>
+        <v>-16.41350255713105</v>
       </c>
       <c r="R75">
-        <v>-26.43500312032725</v>
+        <v>-36.86472674331633</v>
       </c>
       <c r="S75">
-        <v>1.888888888888889</v>
+        <v>-65.65401022852419</v>
       </c>
       <c r="T75">
-        <v>-1.397676225833333</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="U75">
-        <v>-315.3746761425003</v>
+        <v>0.04910843718761077</v>
       </c>
       <c r="V75">
-        <v>-121.2979523625001</v>
+        <v>-0.7857349950017722</v>
       </c>
       <c r="W75">
-        <v>-434.4730923021603</v>
+        <v>1.56335309</v>
       </c>
       <c r="X75">
-        <v>-309.4934436837622</v>
+        <v>544.861393495385</v>
+      </c>
+      <c r="Y75">
+        <v>136.2153483738462</v>
+      </c>
+      <c r="Z75">
+        <v>1452.963715987693</v>
+      </c>
+      <c r="AA75">
+        <v>1414.838885239463</v>
+      </c>
+      <c r="AB75">
+        <v>1026.64406430411</v>
+      </c>
+      <c r="AC75">
+        <v>2294.151924246564</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B4A16</t>
+          <t>B4A21</t>
         </is>
       </c>
       <c r="B76">
-        <v>268.6414102564103</v>
+        <v>5.189996153846153</v>
       </c>
       <c r="C76">
-        <v>105.0180102879905</v>
+        <v>895.9101928076259</v>
       </c>
       <c r="D76">
-        <v>2.643810951523112</v>
+        <v>0.2584946723814043</v>
       </c>
       <c r="E76">
-        <v>22.43284672343808</v>
+        <v>861.8067898910178</v>
       </c>
       <c r="F76">
-        <v>8</v>
+        <v>34.10340291660805</v>
       </c>
       <c r="G76">
-        <v>16.947425565</v>
+        <v>2</v>
       </c>
       <c r="H76">
-        <v>30.629589955</v>
+        <v>13.65484056</v>
       </c>
       <c r="I76">
-        <v>47.57701552</v>
+        <v>38.165918985</v>
       </c>
       <c r="J76">
-        <v>17.406181905</v>
+        <v>51.820759545</v>
       </c>
       <c r="K76">
-        <v>31.31645307</v>
+        <v>13.02545374183333</v>
       </c>
       <c r="L76">
-        <v>1.2258200815</v>
+        <v>39.19134638666667</v>
       </c>
       <c r="M76">
-        <v>48.72263497500001</v>
-      </c>
-      <c r="N76" t="inlineStr">
+        <v>1.354319834</v>
+      </c>
+      <c r="N76">
+        <v>52.2168001285</v>
+      </c>
+      <c r="O76" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O76">
-        <v>2.539400797029873</v>
-      </c>
       <c r="P76">
-        <v>-15.9982250212882</v>
+        <v>3.038668028517401</v>
       </c>
       <c r="Q76">
-        <v>-28.51747095064547</v>
+        <v>-15.193340142587</v>
       </c>
       <c r="R76">
-        <v>-50.78801594059746</v>
+        <v>-34.12424196025042</v>
       </c>
       <c r="S76">
-        <v>6.027777777777778</v>
+        <v>-60.77336057034802</v>
       </c>
       <c r="T76">
-        <v>0.4587563400000008</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="U76">
-        <v>100.337786579552</v>
+        <v>-0.1108072268780366</v>
       </c>
       <c r="V76">
-        <v>38.59145637675076</v>
+        <v>0.2216144537560732</v>
       </c>
       <c r="W76">
-        <v>138.2294512140043</v>
+        <v>-0.6293868181666671</v>
       </c>
       <c r="X76">
-        <v>176.838325916897</v>
+        <v>-233.9813435272982</v>
+      </c>
+      <c r="Y76">
+        <v>-58.49533588182456</v>
+      </c>
+      <c r="Z76">
+        <v>-623.9502494061286</v>
+      </c>
+      <c r="AA76">
+        <v>627.8046073200773</v>
+      </c>
+      <c r="AB76">
+        <v>822.2215167832144</v>
+      </c>
+      <c r="AC76">
+        <v>211.1865828311493</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B4A17</t>
+          <t>B4A22</t>
         </is>
       </c>
       <c r="B77">
-        <v>101.8382051282051</v>
+        <v>3.825914102564103</v>
       </c>
       <c r="C77">
-        <v>39.57631847796294</v>
+        <v>684.2966150442478</v>
       </c>
       <c r="D77">
-        <v>1.412863028854081</v>
+        <v>0.1671098057540553</v>
       </c>
       <c r="E77">
-        <v>5.646782255347036</v>
+        <v>673.0810450460471</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>11.21556999820075</v>
       </c>
       <c r="G77">
-        <v>12.63691090166667</v>
+        <v>4</v>
       </c>
       <c r="H77">
-        <v>38.467871745</v>
+        <v>15.32690688</v>
       </c>
       <c r="I77">
-        <v>51.10478264666666</v>
+        <v>33.91789635166667</v>
       </c>
       <c r="J77">
-        <v>11.93623757083333</v>
+        <v>49.24480323166667</v>
       </c>
       <c r="K77">
-        <v>39.78190652666667</v>
+        <v>16.39641685833333</v>
       </c>
       <c r="L77">
-        <v>1.380730892166667</v>
+        <v>34.92457740666666</v>
       </c>
       <c r="M77">
-        <v>51.7181440975</v>
-      </c>
-      <c r="N77" t="inlineStr">
+        <v>1.324271466333333</v>
+      </c>
+      <c r="N77">
+        <v>51.320994265</v>
+      </c>
+      <c r="O77" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="O77">
-        <v>3.095392060730346</v>
-      </c>
       <c r="P77">
-        <v>-19.50096998260118</v>
+        <v>0.7955205331765982</v>
       </c>
       <c r="Q77">
-        <v>-34.76125284200179</v>
+        <v>-3.977602665882991</v>
       </c>
       <c r="R77">
-        <v>-61.90784121460692</v>
+        <v>-8.933695587573197</v>
       </c>
       <c r="S77">
-        <v>2</v>
+        <v>-15.91041066353196</v>
       </c>
       <c r="T77">
-        <v>-0.7006733308333342</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="U77">
-        <v>-172.6157163075136</v>
+        <v>-0.08796213201151555</v>
       </c>
       <c r="V77">
-        <v>-66.39066011827448</v>
+        <v>0.3518485280460622</v>
       </c>
       <c r="W77">
-        <v>-237.8024924556434</v>
+        <v>1.069509978333333</v>
       </c>
       <c r="X77">
-        <v>-167.8006506715525</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>B4A18</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>693.4347435897436</v>
-      </c>
-      <c r="C78">
-        <v>277.5359939115976</v>
-      </c>
-      <c r="D78">
-        <v>1.630447529738109</v>
-      </c>
-      <c r="E78">
-        <v>43.86992311066624</v>
-      </c>
-      <c r="F78">
-        <v>16</v>
-      </c>
-      <c r="G78">
-        <v>18.07836725833333</v>
-      </c>
-      <c r="H78">
-        <v>34.69260811833333</v>
-      </c>
-      <c r="I78">
-        <v>52.77097537666667</v>
-      </c>
-      <c r="J78">
-        <v>18.410111665</v>
-      </c>
-      <c r="K78">
-        <v>36.12730495333334</v>
-      </c>
-      <c r="L78">
-        <v>1.2625153515</v>
-      </c>
-      <c r="M78">
-        <v>54.53741661833334</v>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="O78">
-        <v>3.183276175047217</v>
-      </c>
-      <c r="P78">
-        <v>-20.05463990279747</v>
-      </c>
-      <c r="Q78">
-        <v>-35.74819144578025</v>
-      </c>
-      <c r="R78">
-        <v>-63.66552350094434</v>
-      </c>
-      <c r="S78">
-        <v>9.972222222222221</v>
-      </c>
-      <c r="T78">
-        <v>0.3317444066666653</v>
-      </c>
-      <c r="U78">
-        <v>74.7301720746156</v>
-      </c>
-      <c r="V78">
-        <v>28.74237387485215</v>
-      </c>
-      <c r="W78">
-        <v>102.9513509032038</v>
-      </c>
-      <c r="X78">
-        <v>316.5179745404329</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>B4A20</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>567.9525256410257</v>
-      </c>
-      <c r="C79">
-        <v>229.0186227279208</v>
-      </c>
-      <c r="D79">
-        <v>4.216377240397463</v>
-      </c>
-      <c r="E79">
-        <v>61.91791305184274</v>
-      </c>
-      <c r="F79">
-        <v>16</v>
-      </c>
-      <c r="G79">
-        <v>14.24282284833333</v>
-      </c>
-      <c r="H79">
-        <v>30.676206745</v>
-      </c>
-      <c r="I79">
-        <v>44.91902959333333</v>
-      </c>
-      <c r="J79">
-        <v>15.80617593833333</v>
-      </c>
-      <c r="K79">
-        <v>31.66174778166667</v>
-      </c>
-      <c r="L79">
-        <v>1.269657585333333</v>
-      </c>
-      <c r="M79">
-        <v>47.46792372</v>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="O79">
-        <v>3.28270051142621</v>
-      </c>
-      <c r="P79">
-        <v>-20.68101322198512</v>
-      </c>
-      <c r="Q79">
-        <v>-36.86472674331633</v>
-      </c>
-      <c r="R79">
-        <v>-65.65401022852419</v>
-      </c>
-      <c r="S79">
-        <v>8.833333333333334</v>
-      </c>
-      <c r="T79">
-        <v>1.56335309</v>
-      </c>
-      <c r="U79">
-        <v>354.1599057720002</v>
-      </c>
-      <c r="V79">
-        <v>136.2153483738462</v>
-      </c>
-      <c r="W79">
-        <v>487.9052158286674</v>
-      </c>
-      <c r="X79">
-        <v>546.3138017566048</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>B4A21</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>518.9996153846154</v>
-      </c>
-      <c r="C80">
-        <v>208.3667736590992</v>
-      </c>
-      <c r="D80">
-        <v>3.868551683434767</v>
-      </c>
-      <c r="E80">
-        <v>54.13120780722426</v>
-      </c>
-      <c r="F80">
-        <v>2</v>
-      </c>
-      <c r="G80">
-        <v>13.65484056</v>
-      </c>
-      <c r="H80">
-        <v>38.165918985</v>
-      </c>
-      <c r="I80">
-        <v>51.820759545</v>
-      </c>
-      <c r="J80">
-        <v>13.02545374183333</v>
-      </c>
-      <c r="K80">
-        <v>39.19134638666667</v>
-      </c>
-      <c r="L80">
-        <v>1.354319834</v>
-      </c>
-      <c r="M80">
-        <v>52.2168001285</v>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="O80">
-        <v>3.038668028517401</v>
-      </c>
-      <c r="P80">
-        <v>-19.14360857965962</v>
-      </c>
-      <c r="Q80">
-        <v>-34.12424196025042</v>
-      </c>
-      <c r="R80">
-        <v>-60.77336057034802</v>
-      </c>
-      <c r="S80">
-        <v>1.916666666666667</v>
-      </c>
-      <c r="T80">
-        <v>-0.6293868181666671</v>
-      </c>
-      <c r="U80">
-        <v>-152.0878732927439</v>
-      </c>
-      <c r="V80">
-        <v>-58.49533588182456</v>
-      </c>
-      <c r="W80">
-        <v>-209.522493750578</v>
-      </c>
-      <c r="X80">
-        <v>22.15465840610494</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>B4A22</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>382.5914102564103</v>
-      </c>
-      <c r="C81">
-        <v>153.3205697003208</v>
-      </c>
-      <c r="D81">
-        <v>5.984089296781033</v>
-      </c>
-      <c r="E81">
-        <v>48.04470861163389</v>
-      </c>
-      <c r="F81">
-        <v>4</v>
-      </c>
-      <c r="G81">
-        <v>15.32690688</v>
-      </c>
-      <c r="H81">
-        <v>33.91789635166667</v>
-      </c>
-      <c r="I81">
-        <v>49.24480323166667</v>
-      </c>
-      <c r="J81">
-        <v>16.39641685833333</v>
-      </c>
-      <c r="K81">
-        <v>34.92457740666666</v>
-      </c>
-      <c r="L81">
-        <v>1.324271466333333</v>
-      </c>
-      <c r="M81">
-        <v>51.320994265</v>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="O81">
-        <v>0.7955205331765982</v>
-      </c>
-      <c r="P81">
-        <v>-5.011779359012569</v>
-      </c>
-      <c r="Q81">
-        <v>-8.933695587573197</v>
-      </c>
-      <c r="R81">
-        <v>-15.91041066353196</v>
-      </c>
-      <c r="S81">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T81">
-        <v>1.069509978333333</v>
-      </c>
-      <c r="U81">
-        <v>252.7071720708672</v>
-      </c>
-      <c r="V81">
+        <v>388.780264724411</v>
+      </c>
+      <c r="Y77">
         <v>97.19506618110275</v>
       </c>
-      <c r="W81">
-        <v>348.1397677185525</v>
-      </c>
-      <c r="X81">
-        <v>397.0940461836148</v>
+      <c r="Z77">
+        <v>1036.747372598429</v>
+      </c>
+      <c r="AA77">
+        <v>1064.143184181086</v>
+      </c>
+      <c r="AB77">
+        <v>777.5140785594675</v>
+      </c>
+      <c r="AC77">
+        <v>1705.133576979145</v>
       </c>
     </row>
   </sheetData>
